--- a/medicao_energia.xlsx
+++ b/medicao_energia.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="I:\14.Sec Adm - Sgt Marquezzini\13 - Fiscal de Contrato CEMIG\dashboard_energia\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\sgt.marquezzini\Documents\GitHub\Dashboardenergia\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9F99D075-9C4F-486C-9C17-BD4D4F2EC962}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{20C22391-3977-4BAC-BAFD-6185D1EF86D5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="19080" yWindow="-120" windowWidth="19440" windowHeight="15000" firstSheet="5" activeTab="7" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="19080" yWindow="-120" windowWidth="19440" windowHeight="15000" firstSheet="5" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="DEZEMBRO" sheetId="23" r:id="rId1"/>
@@ -262,7 +262,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="35">
+  <cellXfs count="34">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -312,15 +312,6 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -354,6 +345,14 @@
     <xf numFmtId="0" fontId="7" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1111,14 +1110,14 @@
     </row>
     <row r="34" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A34" s="4"/>
-      <c r="B34" s="21"/>
-      <c r="C34" s="20"/>
-      <c r="D34" s="20"/>
-      <c r="E34" s="20"/>
-      <c r="F34" s="20"/>
-      <c r="G34" s="20"/>
-      <c r="H34" s="20"/>
-      <c r="I34" s="20"/>
+      <c r="B34" s="32"/>
+      <c r="C34" s="31"/>
+      <c r="D34" s="31"/>
+      <c r="E34" s="31"/>
+      <c r="F34" s="31"/>
+      <c r="G34" s="31"/>
+      <c r="H34" s="31"/>
+      <c r="I34" s="31"/>
     </row>
     <row r="35" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A35" s="4"/>
@@ -1496,15 +1495,15 @@
       <c r="I68" s="4"/>
     </row>
     <row r="69" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A69" s="21"/>
-      <c r="B69" s="20"/>
-      <c r="C69" s="20"/>
-      <c r="D69" s="20"/>
-      <c r="E69" s="20"/>
-      <c r="F69" s="20"/>
-      <c r="G69" s="20"/>
-      <c r="H69" s="20"/>
-      <c r="I69" s="20"/>
+      <c r="A69" s="32"/>
+      <c r="B69" s="31"/>
+      <c r="C69" s="31"/>
+      <c r="D69" s="31"/>
+      <c r="E69" s="31"/>
+      <c r="F69" s="31"/>
+      <c r="G69" s="31"/>
+      <c r="H69" s="31"/>
+      <c r="I69" s="31"/>
     </row>
     <row r="70" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A70" s="4"/>
@@ -1529,15 +1528,15 @@
       <c r="I71" s="6"/>
     </row>
     <row r="74" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A74" s="19"/>
-      <c r="B74" s="20"/>
-      <c r="C74" s="20"/>
-      <c r="D74" s="20"/>
-      <c r="E74" s="20"/>
-      <c r="F74" s="20"/>
-      <c r="G74" s="20"/>
-      <c r="H74" s="20"/>
-      <c r="I74" s="20"/>
+      <c r="A74" s="30"/>
+      <c r="B74" s="31"/>
+      <c r="C74" s="31"/>
+      <c r="D74" s="31"/>
+      <c r="E74" s="31"/>
+      <c r="F74" s="31"/>
+      <c r="G74" s="31"/>
+      <c r="H74" s="31"/>
+      <c r="I74" s="31"/>
     </row>
     <row r="75" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A75" s="4"/>
@@ -1573,15 +1572,15 @@
       <c r="I77" s="8"/>
     </row>
     <row r="78" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A78" s="22"/>
-      <c r="B78" s="20"/>
-      <c r="C78" s="20"/>
-      <c r="D78" s="20"/>
-      <c r="E78" s="20"/>
-      <c r="F78" s="20"/>
-      <c r="G78" s="20"/>
-      <c r="H78" s="20"/>
-      <c r="I78" s="20"/>
+      <c r="A78" s="33"/>
+      <c r="B78" s="31"/>
+      <c r="C78" s="31"/>
+      <c r="D78" s="31"/>
+      <c r="E78" s="31"/>
+      <c r="F78" s="31"/>
+      <c r="G78" s="31"/>
+      <c r="H78" s="31"/>
+      <c r="I78" s="31"/>
     </row>
     <row r="79" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A79" s="4"/>
@@ -1617,15 +1616,15 @@
       <c r="B84" s="6"/>
     </row>
     <row r="86" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A86" s="19"/>
-      <c r="B86" s="20"/>
-      <c r="C86" s="20"/>
-      <c r="D86" s="20"/>
-      <c r="E86" s="20"/>
-      <c r="F86" s="20"/>
-      <c r="G86" s="20"/>
-      <c r="H86" s="20"/>
-      <c r="I86" s="20"/>
+      <c r="A86" s="30"/>
+      <c r="B86" s="31"/>
+      <c r="C86" s="31"/>
+      <c r="D86" s="31"/>
+      <c r="E86" s="31"/>
+      <c r="F86" s="31"/>
+      <c r="G86" s="31"/>
+      <c r="H86" s="31"/>
+      <c r="I86" s="31"/>
     </row>
     <row r="87" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A87" s="4"/>
@@ -1728,15 +1727,15 @@
       <c r="B97" s="9"/>
     </row>
     <row r="99" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A99" s="21"/>
-      <c r="B99" s="20"/>
-      <c r="C99" s="20"/>
-      <c r="D99" s="20"/>
-      <c r="E99" s="20"/>
-      <c r="F99" s="20"/>
-      <c r="G99" s="20"/>
-      <c r="H99" s="20"/>
-      <c r="I99" s="20"/>
+      <c r="A99" s="32"/>
+      <c r="B99" s="31"/>
+      <c r="C99" s="31"/>
+      <c r="D99" s="31"/>
+      <c r="E99" s="31"/>
+      <c r="F99" s="31"/>
+      <c r="G99" s="31"/>
+      <c r="H99" s="31"/>
+      <c r="I99" s="31"/>
     </row>
     <row r="100" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A100" s="4"/>
@@ -1794,924 +1793,924 @@
       <c r="A1" s="12" t="s">
         <v>8</v>
       </c>
-      <c r="B1" s="26" t="s">
+      <c r="B1" s="21" t="s">
         <v>0</v>
       </c>
-      <c r="C1" s="26" t="s">
+      <c r="C1" s="21" t="s">
         <v>1</v>
       </c>
-      <c r="D1" s="26" t="s">
+      <c r="D1" s="21" t="s">
         <v>2</v>
       </c>
-      <c r="E1" s="26" t="s">
+      <c r="E1" s="21" t="s">
         <v>3</v>
       </c>
-      <c r="F1" s="26" t="s">
+      <c r="F1" s="21" t="s">
         <v>4</v>
       </c>
-      <c r="G1" s="26" t="s">
+      <c r="G1" s="21" t="s">
         <v>5</v>
       </c>
-      <c r="H1" s="26" t="s">
+      <c r="H1" s="21" t="s">
         <v>6</v>
       </c>
-      <c r="I1" s="26" t="s">
+      <c r="I1" s="21" t="s">
         <v>7</v>
       </c>
     </row>
     <row r="2" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A2" s="24">
+      <c r="A2" s="19">
         <v>1</v>
       </c>
-      <c r="B2" s="27">
+      <c r="B2" s="22">
         <v>594</v>
       </c>
-      <c r="C2" s="27">
+      <c r="C2" s="22">
         <v>1193</v>
       </c>
-      <c r="D2" s="27">
+      <c r="D2" s="22">
         <v>8925</v>
       </c>
-      <c r="E2" s="27">
+      <c r="E2" s="22">
         <v>10736</v>
       </c>
-      <c r="F2" s="27">
+      <c r="F2" s="22">
         <v>1256</v>
       </c>
-      <c r="G2" s="27">
+      <c r="G2" s="22">
         <v>3235</v>
       </c>
-      <c r="H2" s="27">
+      <c r="H2" s="22">
         <v>321</v>
       </c>
-      <c r="I2" s="27">
+      <c r="I2" s="22">
         <v>2913</v>
       </c>
     </row>
     <row r="3" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A3" s="24">
+      <c r="A3" s="19">
         <f t="shared" ref="A3:A32" si="0">A2+1</f>
         <v>2</v>
       </c>
-      <c r="B3" s="27">
+      <c r="B3" s="22">
         <v>671</v>
       </c>
-      <c r="C3" s="27">
+      <c r="C3" s="22">
         <v>1289</v>
       </c>
-      <c r="D3" s="27">
+      <c r="D3" s="22">
         <v>8928</v>
       </c>
-      <c r="E3" s="27">
+      <c r="E3" s="22">
         <v>10736</v>
       </c>
-      <c r="F3" s="27">
+      <c r="F3" s="22">
         <v>1256</v>
       </c>
-      <c r="G3" s="27">
+      <c r="G3" s="22">
         <v>3238</v>
       </c>
-      <c r="H3" s="27">
+      <c r="H3" s="22">
         <v>321</v>
       </c>
-      <c r="I3" s="27">
+      <c r="I3" s="22">
         <v>2917</v>
       </c>
     </row>
     <row r="4" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A4" s="24">
+      <c r="A4" s="19">
         <f t="shared" si="0"/>
         <v>3</v>
       </c>
-      <c r="B4" s="27">
+      <c r="B4" s="22">
         <v>692</v>
       </c>
-      <c r="C4" s="27">
+      <c r="C4" s="22">
         <v>1453</v>
       </c>
-      <c r="D4" s="27">
+      <c r="D4" s="22">
         <v>8931</v>
       </c>
-      <c r="E4" s="27">
+      <c r="E4" s="22">
         <v>10736</v>
       </c>
-      <c r="F4" s="27">
+      <c r="F4" s="22">
         <v>1256</v>
       </c>
-      <c r="G4" s="27">
+      <c r="G4" s="22">
         <v>3243</v>
       </c>
-      <c r="H4" s="27">
+      <c r="H4" s="22">
         <v>321</v>
       </c>
-      <c r="I4" s="27">
+      <c r="I4" s="22">
         <v>2922</v>
       </c>
     </row>
     <row r="5" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A5" s="24">
+      <c r="A5" s="19">
         <f t="shared" si="0"/>
         <v>4</v>
       </c>
-      <c r="B5" s="27">
+      <c r="B5" s="22">
         <v>728</v>
       </c>
-      <c r="C5" s="27">
+      <c r="C5" s="22">
         <v>1501</v>
       </c>
-      <c r="D5" s="27">
+      <c r="D5" s="22">
         <v>8935</v>
       </c>
-      <c r="E5" s="27">
+      <c r="E5" s="22">
         <v>10738</v>
       </c>
-      <c r="F5" s="27">
+      <c r="F5" s="22">
         <v>1256</v>
       </c>
-      <c r="G5" s="27">
+      <c r="G5" s="22">
         <v>3251</v>
       </c>
-      <c r="H5" s="27">
+      <c r="H5" s="22">
         <v>322</v>
       </c>
-      <c r="I5" s="27">
+      <c r="I5" s="22">
         <v>2928</v>
       </c>
     </row>
     <row r="6" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A6" s="24">
+      <c r="A6" s="19">
         <f t="shared" si="0"/>
         <v>5</v>
       </c>
-      <c r="B6" s="28"/>
-      <c r="C6" s="28"/>
-      <c r="D6" s="28"/>
-      <c r="E6" s="28"/>
-      <c r="F6" s="28"/>
-      <c r="G6" s="28"/>
-      <c r="H6" s="28"/>
-      <c r="I6" s="28"/>
+      <c r="B6" s="23"/>
+      <c r="C6" s="23"/>
+      <c r="D6" s="23"/>
+      <c r="E6" s="23"/>
+      <c r="F6" s="23"/>
+      <c r="G6" s="23"/>
+      <c r="H6" s="23"/>
+      <c r="I6" s="23"/>
     </row>
     <row r="7" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A7" s="24">
+      <c r="A7" s="19">
         <f t="shared" si="0"/>
         <v>6</v>
       </c>
-      <c r="B7" s="27">
+      <c r="B7" s="22">
         <v>882</v>
       </c>
-      <c r="C7" s="27">
+      <c r="C7" s="22">
         <v>1705</v>
       </c>
-      <c r="D7" s="27">
+      <c r="D7" s="22">
         <v>8946</v>
       </c>
-      <c r="E7" s="27">
+      <c r="E7" s="22">
         <v>10739</v>
       </c>
-      <c r="F7" s="27">
+      <c r="F7" s="22">
         <v>1256</v>
       </c>
-      <c r="G7" s="27">
+      <c r="G7" s="22">
         <v>3263</v>
       </c>
-      <c r="H7" s="27">
+      <c r="H7" s="22">
         <v>322</v>
       </c>
-      <c r="I7" s="27">
+      <c r="I7" s="22">
         <v>2928</v>
       </c>
     </row>
     <row r="8" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A8" s="24">
+      <c r="A8" s="19">
         <f t="shared" si="0"/>
         <v>7</v>
       </c>
-      <c r="B8" s="28"/>
-      <c r="C8" s="28"/>
-      <c r="D8" s="28"/>
-      <c r="E8" s="28"/>
-      <c r="F8" s="28"/>
-      <c r="G8" s="28"/>
-      <c r="H8" s="28"/>
-      <c r="I8" s="28"/>
+      <c r="B8" s="23"/>
+      <c r="C8" s="23"/>
+      <c r="D8" s="23"/>
+      <c r="E8" s="23"/>
+      <c r="F8" s="23"/>
+      <c r="G8" s="23"/>
+      <c r="H8" s="23"/>
+      <c r="I8" s="23"/>
     </row>
     <row r="9" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A9" s="24">
+      <c r="A9" s="19">
         <f t="shared" si="0"/>
         <v>8</v>
       </c>
-      <c r="B9" s="27">
+      <c r="B9" s="22">
         <v>1058</v>
       </c>
-      <c r="C9" s="27">
+      <c r="C9" s="22">
         <v>1995</v>
       </c>
-      <c r="D9" s="27">
+      <c r="D9" s="22">
         <v>8952</v>
       </c>
-      <c r="E9" s="27">
+      <c r="E9" s="22">
         <v>10741</v>
       </c>
-      <c r="F9" s="27">
+      <c r="F9" s="22">
         <v>1257</v>
       </c>
-      <c r="G9" s="27">
+      <c r="G9" s="22">
         <v>3274</v>
       </c>
-      <c r="H9" s="27">
+      <c r="H9" s="22">
         <v>325</v>
       </c>
-      <c r="I9" s="27">
+      <c r="I9" s="22">
         <v>2948</v>
       </c>
     </row>
     <row r="10" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A10" s="24">
+      <c r="A10" s="19">
         <f t="shared" si="0"/>
         <v>9</v>
       </c>
-      <c r="B10" s="27">
+      <c r="B10" s="22">
         <v>1080</v>
       </c>
-      <c r="C10" s="27">
+      <c r="C10" s="22">
         <v>2125</v>
       </c>
-      <c r="D10" s="27">
+      <c r="D10" s="22">
         <v>8952</v>
       </c>
-      <c r="E10" s="27">
+      <c r="E10" s="22">
         <v>10741</v>
       </c>
-      <c r="F10" s="27">
+      <c r="F10" s="22">
         <v>1257</v>
       </c>
-      <c r="G10" s="27">
+      <c r="G10" s="22">
         <v>3280</v>
       </c>
-      <c r="H10" s="27">
+      <c r="H10" s="22">
         <v>325</v>
       </c>
-      <c r="I10" s="27">
+      <c r="I10" s="22">
         <v>2955</v>
       </c>
     </row>
     <row r="11" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A11" s="24">
+      <c r="A11" s="19">
         <f t="shared" si="0"/>
         <v>10</v>
       </c>
-      <c r="B11" s="27">
+      <c r="B11" s="22">
         <v>1135</v>
       </c>
-      <c r="C11" s="27">
+      <c r="C11" s="22">
         <v>2301</v>
       </c>
-      <c r="D11" s="27">
+      <c r="D11" s="22">
         <v>8960</v>
       </c>
-      <c r="E11" s="27">
+      <c r="E11" s="22">
         <v>10742</v>
       </c>
-      <c r="F11" s="27">
+      <c r="F11" s="22">
         <v>1257</v>
       </c>
-      <c r="G11" s="27">
+      <c r="G11" s="22">
         <v>3287</v>
       </c>
-      <c r="H11" s="27">
+      <c r="H11" s="22">
         <v>325</v>
       </c>
-      <c r="I11" s="27">
+      <c r="I11" s="22">
         <v>2962</v>
       </c>
     </row>
     <row r="12" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A12" s="24">
+      <c r="A12" s="19">
         <f t="shared" si="0"/>
         <v>11</v>
       </c>
-      <c r="B12" s="27">
+      <c r="B12" s="22">
         <v>1230</v>
       </c>
-      <c r="C12" s="27">
+      <c r="C12" s="22">
         <v>2418</v>
       </c>
-      <c r="D12" s="27">
+      <c r="D12" s="22">
         <v>8964</v>
       </c>
-      <c r="E12" s="27">
+      <c r="E12" s="22">
         <v>10743</v>
       </c>
-      <c r="F12" s="27">
+      <c r="F12" s="22">
         <v>1257</v>
       </c>
-      <c r="G12" s="27">
+      <c r="G12" s="22">
         <v>3287</v>
       </c>
-      <c r="H12" s="27">
+      <c r="H12" s="22">
         <v>325</v>
       </c>
-      <c r="I12" s="27">
+      <c r="I12" s="22">
         <v>2962</v>
       </c>
     </row>
     <row r="13" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A13" s="24">
+      <c r="A13" s="19">
         <f t="shared" si="0"/>
         <v>12</v>
       </c>
-      <c r="B13" s="27">
+      <c r="B13" s="22">
         <v>1347</v>
       </c>
-      <c r="C13" s="27">
+      <c r="C13" s="22">
         <v>2611</v>
       </c>
-      <c r="D13" s="27">
+      <c r="D13" s="22">
         <v>8967</v>
       </c>
-      <c r="E13" s="27">
+      <c r="E13" s="22">
         <v>10744</v>
       </c>
-      <c r="F13" s="27">
+      <c r="F13" s="22">
         <v>1257</v>
       </c>
-      <c r="G13" s="27">
+      <c r="G13" s="22">
         <v>3300</v>
       </c>
-      <c r="H13" s="27">
+      <c r="H13" s="22">
         <v>327</v>
       </c>
-      <c r="I13" s="27">
+      <c r="I13" s="22">
         <v>2973</v>
       </c>
     </row>
     <row r="14" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A14" s="24">
+      <c r="A14" s="19">
         <f t="shared" si="0"/>
         <v>13</v>
       </c>
-      <c r="B14" s="27">
+      <c r="B14" s="22">
         <v>1470</v>
       </c>
-      <c r="C14" s="27">
+      <c r="C14" s="22">
         <v>2681</v>
       </c>
-      <c r="D14" s="27">
+      <c r="D14" s="22">
         <v>8971</v>
       </c>
-      <c r="E14" s="27">
+      <c r="E14" s="22">
         <v>10744</v>
       </c>
-      <c r="F14" s="27">
+      <c r="F14" s="22">
         <v>1258</v>
       </c>
-      <c r="G14" s="27">
+      <c r="G14" s="22">
         <v>3306</v>
       </c>
-      <c r="H14" s="27">
+      <c r="H14" s="22">
         <v>328</v>
       </c>
-      <c r="I14" s="27">
+      <c r="I14" s="22">
         <v>2977</v>
       </c>
     </row>
     <row r="15" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A15" s="24">
+      <c r="A15" s="19">
         <f t="shared" si="0"/>
         <v>14</v>
       </c>
-      <c r="B15" s="28"/>
-      <c r="C15" s="28"/>
-      <c r="D15" s="28"/>
-      <c r="E15" s="28"/>
-      <c r="F15" s="28"/>
-      <c r="G15" s="28"/>
-      <c r="H15" s="28"/>
-      <c r="I15" s="28"/>
+      <c r="B15" s="23"/>
+      <c r="C15" s="23"/>
+      <c r="D15" s="23"/>
+      <c r="E15" s="23"/>
+      <c r="F15" s="23"/>
+      <c r="G15" s="23"/>
+      <c r="H15" s="23"/>
+      <c r="I15" s="23"/>
     </row>
     <row r="16" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A16" s="24">
+      <c r="A16" s="19">
         <f t="shared" si="0"/>
         <v>15</v>
       </c>
-      <c r="B16" s="27">
+      <c r="B16" s="22">
         <v>1674</v>
       </c>
-      <c r="C16" s="27">
+      <c r="C16" s="22">
         <v>2914</v>
       </c>
-      <c r="D16" s="27">
+      <c r="D16" s="22">
         <v>8979</v>
       </c>
-      <c r="E16" s="27">
+      <c r="E16" s="22">
         <v>10745</v>
       </c>
-      <c r="F16" s="27">
+      <c r="F16" s="22">
         <v>1258</v>
       </c>
-      <c r="G16" s="27">
+      <c r="G16" s="22">
         <v>3317</v>
       </c>
-      <c r="H16" s="27">
+      <c r="H16" s="22">
         <v>329</v>
       </c>
-      <c r="I16" s="27">
+      <c r="I16" s="22">
         <v>2988</v>
       </c>
     </row>
     <row r="17" spans="1:10" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A17" s="24">
+      <c r="A17" s="19">
         <f t="shared" si="0"/>
         <v>16</v>
       </c>
-      <c r="B17" s="27">
+      <c r="B17" s="22">
         <v>1690</v>
       </c>
-      <c r="C17" s="27">
+      <c r="C17" s="22">
         <v>2986</v>
       </c>
-      <c r="D17" s="27">
+      <c r="D17" s="22">
         <v>8979</v>
       </c>
-      <c r="E17" s="27">
+      <c r="E17" s="22">
         <v>10747</v>
       </c>
-      <c r="F17" s="27">
+      <c r="F17" s="22">
         <v>1258</v>
       </c>
-      <c r="G17" s="27">
+      <c r="G17" s="22">
         <v>3324</v>
       </c>
-      <c r="H17" s="27">
+      <c r="H17" s="22">
         <v>329</v>
       </c>
-      <c r="I17" s="27">
+      <c r="I17" s="22">
         <v>2994</v>
       </c>
     </row>
     <row r="18" spans="1:10" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A18" s="24">
+      <c r="A18" s="19">
         <f t="shared" si="0"/>
         <v>17</v>
       </c>
-      <c r="B18" s="27">
+      <c r="B18" s="22">
         <v>1733</v>
       </c>
-      <c r="C18" s="27">
+      <c r="C18" s="22">
         <v>3061</v>
       </c>
-      <c r="D18" s="27">
+      <c r="D18" s="22">
         <v>8985</v>
       </c>
-      <c r="E18" s="27">
+      <c r="E18" s="22">
         <v>10747</v>
       </c>
-      <c r="F18" s="27">
+      <c r="F18" s="22">
         <v>1258</v>
       </c>
-      <c r="G18" s="27">
+      <c r="G18" s="22">
         <v>3330</v>
       </c>
-      <c r="H18" s="27">
+      <c r="H18" s="22">
         <v>329</v>
       </c>
-      <c r="I18" s="27">
+      <c r="I18" s="22">
         <v>3000</v>
       </c>
       <c r="J18" s="3"/>
     </row>
     <row r="19" spans="1:10" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A19" s="24">
+      <c r="A19" s="19">
         <f t="shared" si="0"/>
         <v>18</v>
       </c>
-      <c r="B19" s="27">
+      <c r="B19" s="22">
         <v>1859</v>
       </c>
-      <c r="C19" s="27">
+      <c r="C19" s="22">
         <v>3301</v>
       </c>
-      <c r="D19" s="27">
+      <c r="D19" s="22">
         <v>8988</v>
       </c>
-      <c r="E19" s="27">
+      <c r="E19" s="22">
         <v>10748</v>
       </c>
-      <c r="F19" s="27">
+      <c r="F19" s="22">
         <v>1258</v>
       </c>
-      <c r="G19" s="27">
+      <c r="G19" s="22">
         <v>3336</v>
       </c>
-      <c r="H19" s="27">
+      <c r="H19" s="22">
         <v>330</v>
       </c>
-      <c r="I19" s="27">
+      <c r="I19" s="22">
         <v>3005</v>
       </c>
     </row>
     <row r="20" spans="1:10" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A20" s="24">
+      <c r="A20" s="19">
         <f t="shared" si="0"/>
         <v>19</v>
       </c>
-      <c r="B20" s="27">
+      <c r="B20" s="22">
         <v>1951</v>
       </c>
-      <c r="C20" s="27">
+      <c r="C20" s="22">
         <v>3368</v>
       </c>
-      <c r="D20" s="27">
+      <c r="D20" s="22">
         <v>8992</v>
       </c>
-      <c r="E20" s="27">
+      <c r="E20" s="22">
         <v>10749</v>
       </c>
-      <c r="F20" s="27">
+      <c r="F20" s="22">
         <v>1258</v>
       </c>
-      <c r="G20" s="27">
+      <c r="G20" s="22">
         <v>3342</v>
       </c>
-      <c r="H20" s="27">
+      <c r="H20" s="22">
         <v>331</v>
       </c>
-      <c r="I20" s="27">
+      <c r="I20" s="22">
         <v>3010</v>
       </c>
     </row>
     <row r="21" spans="1:10" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A21" s="24">
+      <c r="A21" s="19">
         <f t="shared" si="0"/>
         <v>20</v>
       </c>
-      <c r="B21" s="27">
+      <c r="B21" s="22">
         <v>2048</v>
       </c>
-      <c r="C21" s="27">
+      <c r="C21" s="22">
         <v>3506</v>
       </c>
-      <c r="D21" s="27">
+      <c r="D21" s="22">
         <v>8995</v>
       </c>
-      <c r="E21" s="27">
+      <c r="E21" s="22">
         <v>10749</v>
       </c>
-      <c r="F21" s="27">
+      <c r="F21" s="22">
         <v>1258</v>
       </c>
-      <c r="G21" s="27">
+      <c r="G21" s="22">
         <v>3347</v>
       </c>
-      <c r="H21" s="27">
+      <c r="H21" s="22">
         <v>332</v>
       </c>
-      <c r="I21" s="27">
+      <c r="I21" s="22">
         <v>3015</v>
       </c>
     </row>
     <row r="22" spans="1:10" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A22" s="24">
+      <c r="A22" s="19">
         <f t="shared" si="0"/>
         <v>21</v>
       </c>
-      <c r="B22" s="27">
+      <c r="B22" s="22">
         <v>2170</v>
       </c>
-      <c r="C22" s="27">
+      <c r="C22" s="22">
         <v>3628</v>
       </c>
-      <c r="D22" s="27">
+      <c r="D22" s="22">
         <v>8985</v>
       </c>
-      <c r="E22" s="27">
+      <c r="E22" s="22">
         <v>10749</v>
       </c>
-      <c r="F22" s="27">
+      <c r="F22" s="22">
         <v>1258</v>
       </c>
-      <c r="G22" s="27">
+      <c r="G22" s="22">
         <v>3350</v>
       </c>
-      <c r="H22" s="27">
+      <c r="H22" s="22">
         <v>333</v>
       </c>
-      <c r="I22" s="27">
+      <c r="I22" s="22">
         <v>3017</v>
       </c>
     </row>
     <row r="23" spans="1:10" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A23" s="24">
+      <c r="A23" s="19">
         <f t="shared" si="0"/>
         <v>22</v>
       </c>
-      <c r="B23" s="27">
+      <c r="B23" s="22">
         <v>2199</v>
       </c>
-      <c r="C23" s="27">
+      <c r="C23" s="22">
         <v>3713</v>
       </c>
-      <c r="D23" s="27">
+      <c r="D23" s="22">
         <v>8999</v>
       </c>
-      <c r="E23" s="27">
+      <c r="E23" s="22">
         <v>10752</v>
       </c>
-      <c r="F23" s="27">
+      <c r="F23" s="22">
         <v>1259</v>
       </c>
-      <c r="G23" s="27">
+      <c r="G23" s="22">
         <v>3356</v>
       </c>
-      <c r="H23" s="27">
+      <c r="H23" s="22">
         <v>334</v>
       </c>
-      <c r="I23" s="27">
+      <c r="I23" s="22">
         <v>3021</v>
       </c>
     </row>
     <row r="24" spans="1:10" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A24" s="24">
+      <c r="A24" s="19">
         <f t="shared" si="0"/>
         <v>23</v>
       </c>
-      <c r="B24" s="27">
+      <c r="B24" s="22">
         <v>2248</v>
       </c>
-      <c r="C24" s="27">
+      <c r="C24" s="22">
         <v>3790</v>
       </c>
-      <c r="D24" s="27">
+      <c r="D24" s="22">
         <v>9004</v>
       </c>
-      <c r="E24" s="27">
+      <c r="E24" s="22">
         <v>10752</v>
       </c>
-      <c r="F24" s="27">
+      <c r="F24" s="22">
         <v>1259</v>
       </c>
-      <c r="G24" s="27">
+      <c r="G24" s="22">
         <v>3364</v>
       </c>
-      <c r="H24" s="27">
+      <c r="H24" s="22">
         <v>334</v>
       </c>
-      <c r="I24" s="27">
+      <c r="I24" s="22">
         <v>3023</v>
       </c>
     </row>
     <row r="25" spans="1:10" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A25" s="24">
+      <c r="A25" s="19">
         <f t="shared" si="0"/>
         <v>24</v>
       </c>
-      <c r="B25" s="27">
+      <c r="B25" s="22">
         <v>2286</v>
       </c>
-      <c r="C25" s="27">
+      <c r="C25" s="22">
         <v>3790</v>
       </c>
-      <c r="D25" s="27">
+      <c r="D25" s="22">
         <v>9009</v>
       </c>
-      <c r="E25" s="27">
+      <c r="E25" s="22">
         <v>10753</v>
       </c>
-      <c r="F25" s="27">
+      <c r="F25" s="22">
         <v>1259</v>
       </c>
-      <c r="G25" s="27">
+      <c r="G25" s="22">
         <v>3369</v>
       </c>
-      <c r="H25" s="27">
+      <c r="H25" s="22">
         <v>334</v>
       </c>
-      <c r="I25" s="27">
+      <c r="I25" s="22">
         <v>3035</v>
       </c>
     </row>
     <row r="26" spans="1:10" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A26" s="24">
+      <c r="A26" s="19">
         <f t="shared" si="0"/>
         <v>25</v>
       </c>
-      <c r="B26" s="27">
+      <c r="B26" s="22">
         <v>2384</v>
       </c>
-      <c r="C26" s="27">
+      <c r="C26" s="22">
         <v>3934</v>
       </c>
-      <c r="D26" s="27">
+      <c r="D26" s="22">
         <v>9011</v>
       </c>
-      <c r="E26" s="27">
+      <c r="E26" s="22">
         <v>10753</v>
       </c>
-      <c r="F26" s="27">
+      <c r="F26" s="22">
         <v>1259</v>
       </c>
-      <c r="G26" s="27">
+      <c r="G26" s="22">
         <v>3371</v>
       </c>
-      <c r="H26" s="27">
+      <c r="H26" s="22">
         <v>334</v>
       </c>
-      <c r="I26" s="27">
+      <c r="I26" s="22">
         <v>3036</v>
       </c>
     </row>
     <row r="27" spans="1:10" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A27" s="24">
+      <c r="A27" s="19">
         <f t="shared" si="0"/>
         <v>26</v>
       </c>
-      <c r="B27" s="27">
+      <c r="B27" s="22">
         <v>2452</v>
       </c>
-      <c r="C27" s="27">
+      <c r="C27" s="22">
         <v>4054</v>
       </c>
-      <c r="D27" s="27">
+      <c r="D27" s="22">
         <v>9015</v>
       </c>
-      <c r="E27" s="27">
+      <c r="E27" s="22">
         <v>10755</v>
       </c>
-      <c r="F27" s="27">
+      <c r="F27" s="22">
         <v>1259</v>
       </c>
-      <c r="G27" s="27">
+      <c r="G27" s="22">
         <v>3379</v>
       </c>
-      <c r="H27" s="27">
+      <c r="H27" s="22">
         <v>336</v>
       </c>
-      <c r="I27" s="27">
+      <c r="I27" s="22">
         <v>3043</v>
       </c>
     </row>
     <row r="28" spans="1:10" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A28" s="24">
+      <c r="A28" s="19">
         <f t="shared" si="0"/>
         <v>27</v>
       </c>
-      <c r="B28" s="27">
+      <c r="B28" s="22">
         <v>2601</v>
       </c>
-      <c r="C28" s="27">
+      <c r="C28" s="22">
         <v>4174</v>
       </c>
-      <c r="D28" s="27">
+      <c r="D28" s="22">
         <v>9017</v>
       </c>
-      <c r="E28" s="27">
+      <c r="E28" s="22">
         <v>10755</v>
       </c>
-      <c r="F28" s="27">
+      <c r="F28" s="22">
         <v>1259</v>
       </c>
-      <c r="G28" s="27">
+      <c r="G28" s="22">
         <v>3384</v>
       </c>
-      <c r="H28" s="27">
+      <c r="H28" s="22">
         <v>336</v>
       </c>
-      <c r="I28" s="27">
+      <c r="I28" s="22">
         <v>3048</v>
       </c>
     </row>
     <row r="29" spans="1:10" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A29" s="24">
+      <c r="A29" s="19">
         <f t="shared" si="0"/>
         <v>28</v>
       </c>
-      <c r="B29" s="27">
+      <c r="B29" s="22">
         <v>2674</v>
       </c>
-      <c r="C29" s="27">
+      <c r="C29" s="22">
         <v>4247</v>
       </c>
-      <c r="D29" s="27">
+      <c r="D29" s="22">
         <v>9020</v>
       </c>
-      <c r="E29" s="27">
+      <c r="E29" s="22">
         <v>10756</v>
       </c>
-      <c r="F29" s="27">
+      <c r="F29" s="22">
         <v>1260</v>
       </c>
-      <c r="G29" s="27">
+      <c r="G29" s="22">
         <v>3390</v>
       </c>
-      <c r="H29" s="27">
+      <c r="H29" s="22">
         <v>337</v>
       </c>
-      <c r="I29" s="27">
+      <c r="I29" s="22">
         <v>3052</v>
       </c>
     </row>
     <row r="30" spans="1:10" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A30" s="24">
+      <c r="A30" s="19">
         <f t="shared" si="0"/>
         <v>29</v>
       </c>
-      <c r="B30" s="27">
+      <c r="B30" s="22">
         <v>2742</v>
       </c>
-      <c r="C30" s="27">
+      <c r="C30" s="22">
         <v>4306</v>
       </c>
-      <c r="D30" s="27">
+      <c r="D30" s="22">
         <v>9020</v>
       </c>
-      <c r="E30" s="27">
+      <c r="E30" s="22">
         <v>10757</v>
       </c>
-      <c r="F30" s="27">
+      <c r="F30" s="22">
         <v>1260</v>
       </c>
-      <c r="G30" s="27">
+      <c r="G30" s="22">
         <v>3395</v>
       </c>
-      <c r="H30" s="27">
+      <c r="H30" s="22">
         <v>338</v>
       </c>
-      <c r="I30" s="27">
+      <c r="I30" s="22">
         <v>3057</v>
       </c>
     </row>
     <row r="31" spans="1:10" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A31" s="24">
+      <c r="A31" s="19">
         <f t="shared" si="0"/>
         <v>30</v>
       </c>
-      <c r="B31" s="27">
+      <c r="B31" s="22">
         <v>2801</v>
       </c>
-      <c r="C31" s="27">
+      <c r="C31" s="22">
         <v>4403</v>
       </c>
-      <c r="D31" s="27">
+      <c r="D31" s="22">
         <v>9034</v>
       </c>
-      <c r="E31" s="27">
+      <c r="E31" s="22">
         <v>10757</v>
       </c>
-      <c r="F31" s="27">
+      <c r="F31" s="22">
         <v>1260</v>
       </c>
-      <c r="G31" s="27">
+      <c r="G31" s="22">
         <v>3402</v>
       </c>
-      <c r="H31" s="27">
+      <c r="H31" s="22">
         <v>338</v>
       </c>
-      <c r="I31" s="27">
+      <c r="I31" s="22">
         <v>3063</v>
       </c>
     </row>
     <row r="32" spans="1:10" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A32" s="25">
+      <c r="A32" s="20">
         <f t="shared" si="0"/>
         <v>31</v>
       </c>
-      <c r="B32" s="27">
+      <c r="B32" s="22">
         <v>2812</v>
       </c>
-      <c r="C32" s="27">
+      <c r="C32" s="22">
         <v>4489</v>
       </c>
-      <c r="D32" s="27">
+      <c r="D32" s="22">
         <v>9036</v>
       </c>
-      <c r="E32" s="27">
+      <c r="E32" s="22">
         <v>10758</v>
       </c>
-      <c r="F32" s="27">
+      <c r="F32" s="22">
         <v>1260</v>
       </c>
-      <c r="G32" s="27">
+      <c r="G32" s="22">
         <v>3408</v>
       </c>
-      <c r="H32" s="27">
+      <c r="H32" s="22">
         <v>338</v>
       </c>
-      <c r="I32" s="27">
+      <c r="I32" s="22">
         <v>3069</v>
       </c>
     </row>
     <row r="33" spans="1:9" ht="12.75" x14ac:dyDescent="0.2"/>
     <row r="35" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A35" s="4"/>
-      <c r="B35" s="21"/>
-      <c r="C35" s="20"/>
-      <c r="D35" s="20"/>
-      <c r="E35" s="20"/>
-      <c r="F35" s="20"/>
-      <c r="G35" s="20"/>
-      <c r="H35" s="20"/>
-      <c r="I35" s="20"/>
+      <c r="B35" s="32"/>
+      <c r="C35" s="31"/>
+      <c r="D35" s="31"/>
+      <c r="E35" s="31"/>
+      <c r="F35" s="31"/>
+      <c r="G35" s="31"/>
+      <c r="H35" s="31"/>
+      <c r="I35" s="31"/>
     </row>
     <row r="36" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A36" s="4"/>
@@ -3088,15 +3087,15 @@
       <c r="I69" s="4"/>
     </row>
     <row r="70" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A70" s="21"/>
-      <c r="B70" s="20"/>
-      <c r="C70" s="20"/>
-      <c r="D70" s="20"/>
-      <c r="E70" s="20"/>
-      <c r="F70" s="20"/>
-      <c r="G70" s="20"/>
-      <c r="H70" s="20"/>
-      <c r="I70" s="20"/>
+      <c r="A70" s="32"/>
+      <c r="B70" s="31"/>
+      <c r="C70" s="31"/>
+      <c r="D70" s="31"/>
+      <c r="E70" s="31"/>
+      <c r="F70" s="31"/>
+      <c r="G70" s="31"/>
+      <c r="H70" s="31"/>
+      <c r="I70" s="31"/>
     </row>
     <row r="71" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A71" s="4"/>
@@ -3121,15 +3120,15 @@
       <c r="I72" s="6"/>
     </row>
     <row r="75" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A75" s="19"/>
-      <c r="B75" s="20"/>
-      <c r="C75" s="20"/>
-      <c r="D75" s="20"/>
-      <c r="E75" s="20"/>
-      <c r="F75" s="20"/>
-      <c r="G75" s="20"/>
-      <c r="H75" s="20"/>
-      <c r="I75" s="20"/>
+      <c r="A75" s="30"/>
+      <c r="B75" s="31"/>
+      <c r="C75" s="31"/>
+      <c r="D75" s="31"/>
+      <c r="E75" s="31"/>
+      <c r="F75" s="31"/>
+      <c r="G75" s="31"/>
+      <c r="H75" s="31"/>
+      <c r="I75" s="31"/>
     </row>
     <row r="76" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A76" s="4"/>
@@ -3165,15 +3164,15 @@
       <c r="I78" s="8"/>
     </row>
     <row r="79" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A79" s="22"/>
-      <c r="B79" s="20"/>
-      <c r="C79" s="20"/>
-      <c r="D79" s="20"/>
-      <c r="E79" s="20"/>
-      <c r="F79" s="20"/>
-      <c r="G79" s="20"/>
-      <c r="H79" s="20"/>
-      <c r="I79" s="20"/>
+      <c r="A79" s="33"/>
+      <c r="B79" s="31"/>
+      <c r="C79" s="31"/>
+      <c r="D79" s="31"/>
+      <c r="E79" s="31"/>
+      <c r="F79" s="31"/>
+      <c r="G79" s="31"/>
+      <c r="H79" s="31"/>
+      <c r="I79" s="31"/>
     </row>
     <row r="80" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A80" s="4"/>
@@ -3209,15 +3208,15 @@
       <c r="B85" s="6"/>
     </row>
     <row r="87" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A87" s="19"/>
-      <c r="B87" s="20"/>
-      <c r="C87" s="20"/>
-      <c r="D87" s="20"/>
-      <c r="E87" s="20"/>
-      <c r="F87" s="20"/>
-      <c r="G87" s="20"/>
-      <c r="H87" s="20"/>
-      <c r="I87" s="20"/>
+      <c r="A87" s="30"/>
+      <c r="B87" s="31"/>
+      <c r="C87" s="31"/>
+      <c r="D87" s="31"/>
+      <c r="E87" s="31"/>
+      <c r="F87" s="31"/>
+      <c r="G87" s="31"/>
+      <c r="H87" s="31"/>
+      <c r="I87" s="31"/>
     </row>
     <row r="88" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A88" s="4"/>
@@ -3320,15 +3319,15 @@
       <c r="B98" s="9"/>
     </row>
     <row r="100" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A100" s="21"/>
-      <c r="B100" s="20"/>
-      <c r="C100" s="20"/>
-      <c r="D100" s="20"/>
-      <c r="E100" s="20"/>
-      <c r="F100" s="20"/>
-      <c r="G100" s="20"/>
-      <c r="H100" s="20"/>
-      <c r="I100" s="20"/>
+      <c r="A100" s="32"/>
+      <c r="B100" s="31"/>
+      <c r="C100" s="31"/>
+      <c r="D100" s="31"/>
+      <c r="E100" s="31"/>
+      <c r="F100" s="31"/>
+      <c r="G100" s="31"/>
+      <c r="H100" s="31"/>
+      <c r="I100" s="31"/>
     </row>
     <row r="101" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A101" s="4"/>
@@ -3848,14 +3847,14 @@
     <row r="33" spans="1:9" ht="12.75" x14ac:dyDescent="0.2"/>
     <row r="35" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A35" s="4"/>
-      <c r="B35" s="21"/>
-      <c r="C35" s="20"/>
-      <c r="D35" s="20"/>
-      <c r="E35" s="20"/>
-      <c r="F35" s="20"/>
-      <c r="G35" s="20"/>
-      <c r="H35" s="20"/>
-      <c r="I35" s="20"/>
+      <c r="B35" s="32"/>
+      <c r="C35" s="31"/>
+      <c r="D35" s="31"/>
+      <c r="E35" s="31"/>
+      <c r="F35" s="31"/>
+      <c r="G35" s="31"/>
+      <c r="H35" s="31"/>
+      <c r="I35" s="31"/>
     </row>
     <row r="36" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A36" s="4"/>
@@ -4232,15 +4231,15 @@
       <c r="I69" s="4"/>
     </row>
     <row r="70" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A70" s="21"/>
-      <c r="B70" s="20"/>
-      <c r="C70" s="20"/>
-      <c r="D70" s="20"/>
-      <c r="E70" s="20"/>
-      <c r="F70" s="20"/>
-      <c r="G70" s="20"/>
-      <c r="H70" s="20"/>
-      <c r="I70" s="20"/>
+      <c r="A70" s="32"/>
+      <c r="B70" s="31"/>
+      <c r="C70" s="31"/>
+      <c r="D70" s="31"/>
+      <c r="E70" s="31"/>
+      <c r="F70" s="31"/>
+      <c r="G70" s="31"/>
+      <c r="H70" s="31"/>
+      <c r="I70" s="31"/>
     </row>
     <row r="71" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A71" s="4"/>
@@ -4265,15 +4264,15 @@
       <c r="I72" s="6"/>
     </row>
     <row r="75" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A75" s="19"/>
-      <c r="B75" s="20"/>
-      <c r="C75" s="20"/>
-      <c r="D75" s="20"/>
-      <c r="E75" s="20"/>
-      <c r="F75" s="20"/>
-      <c r="G75" s="20"/>
-      <c r="H75" s="20"/>
-      <c r="I75" s="20"/>
+      <c r="A75" s="30"/>
+      <c r="B75" s="31"/>
+      <c r="C75" s="31"/>
+      <c r="D75" s="31"/>
+      <c r="E75" s="31"/>
+      <c r="F75" s="31"/>
+      <c r="G75" s="31"/>
+      <c r="H75" s="31"/>
+      <c r="I75" s="31"/>
     </row>
     <row r="76" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A76" s="4"/>
@@ -4309,15 +4308,15 @@
       <c r="I78" s="8"/>
     </row>
     <row r="79" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A79" s="22"/>
-      <c r="B79" s="20"/>
-      <c r="C79" s="20"/>
-      <c r="D79" s="20"/>
-      <c r="E79" s="20"/>
-      <c r="F79" s="20"/>
-      <c r="G79" s="20"/>
-      <c r="H79" s="20"/>
-      <c r="I79" s="20"/>
+      <c r="A79" s="33"/>
+      <c r="B79" s="31"/>
+      <c r="C79" s="31"/>
+      <c r="D79" s="31"/>
+      <c r="E79" s="31"/>
+      <c r="F79" s="31"/>
+      <c r="G79" s="31"/>
+      <c r="H79" s="31"/>
+      <c r="I79" s="31"/>
     </row>
     <row r="80" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A80" s="4"/>
@@ -4353,15 +4352,15 @@
       <c r="B85" s="6"/>
     </row>
     <row r="87" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A87" s="19"/>
-      <c r="B87" s="20"/>
-      <c r="C87" s="20"/>
-      <c r="D87" s="20"/>
-      <c r="E87" s="20"/>
-      <c r="F87" s="20"/>
-      <c r="G87" s="20"/>
-      <c r="H87" s="20"/>
-      <c r="I87" s="20"/>
+      <c r="A87" s="30"/>
+      <c r="B87" s="31"/>
+      <c r="C87" s="31"/>
+      <c r="D87" s="31"/>
+      <c r="E87" s="31"/>
+      <c r="F87" s="31"/>
+      <c r="G87" s="31"/>
+      <c r="H87" s="31"/>
+      <c r="I87" s="31"/>
     </row>
     <row r="88" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A88" s="4"/>
@@ -4464,15 +4463,15 @@
       <c r="B98" s="9"/>
     </row>
     <row r="100" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A100" s="21"/>
-      <c r="B100" s="20"/>
-      <c r="C100" s="20"/>
-      <c r="D100" s="20"/>
-      <c r="E100" s="20"/>
-      <c r="F100" s="20"/>
-      <c r="G100" s="20"/>
-      <c r="H100" s="20"/>
-      <c r="I100" s="20"/>
+      <c r="A100" s="32"/>
+      <c r="B100" s="31"/>
+      <c r="C100" s="31"/>
+      <c r="D100" s="31"/>
+      <c r="E100" s="31"/>
+      <c r="F100" s="31"/>
+      <c r="G100" s="31"/>
+      <c r="H100" s="31"/>
+      <c r="I100" s="31"/>
     </row>
     <row r="101" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A101" s="4"/>
@@ -4991,14 +4990,14 @@
     <row r="33" spans="1:9" ht="12.75" x14ac:dyDescent="0.2"/>
     <row r="35" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A35" s="4"/>
-      <c r="B35" s="21"/>
-      <c r="C35" s="20"/>
-      <c r="D35" s="20"/>
-      <c r="E35" s="20"/>
-      <c r="F35" s="20"/>
-      <c r="G35" s="20"/>
-      <c r="H35" s="20"/>
-      <c r="I35" s="20"/>
+      <c r="B35" s="32"/>
+      <c r="C35" s="31"/>
+      <c r="D35" s="31"/>
+      <c r="E35" s="31"/>
+      <c r="F35" s="31"/>
+      <c r="G35" s="31"/>
+      <c r="H35" s="31"/>
+      <c r="I35" s="31"/>
     </row>
     <row r="36" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A36" s="4"/>
@@ -5375,15 +5374,15 @@
       <c r="I69" s="4"/>
     </row>
     <row r="70" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A70" s="21"/>
-      <c r="B70" s="20"/>
-      <c r="C70" s="20"/>
-      <c r="D70" s="20"/>
-      <c r="E70" s="20"/>
-      <c r="F70" s="20"/>
-      <c r="G70" s="20"/>
-      <c r="H70" s="20"/>
-      <c r="I70" s="20"/>
+      <c r="A70" s="32"/>
+      <c r="B70" s="31"/>
+      <c r="C70" s="31"/>
+      <c r="D70" s="31"/>
+      <c r="E70" s="31"/>
+      <c r="F70" s="31"/>
+      <c r="G70" s="31"/>
+      <c r="H70" s="31"/>
+      <c r="I70" s="31"/>
     </row>
     <row r="71" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A71" s="4"/>
@@ -5408,15 +5407,15 @@
       <c r="I72" s="6"/>
     </row>
     <row r="75" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A75" s="19"/>
-      <c r="B75" s="20"/>
-      <c r="C75" s="20"/>
-      <c r="D75" s="20"/>
-      <c r="E75" s="20"/>
-      <c r="F75" s="20"/>
-      <c r="G75" s="20"/>
-      <c r="H75" s="20"/>
-      <c r="I75" s="20"/>
+      <c r="A75" s="30"/>
+      <c r="B75" s="31"/>
+      <c r="C75" s="31"/>
+      <c r="D75" s="31"/>
+      <c r="E75" s="31"/>
+      <c r="F75" s="31"/>
+      <c r="G75" s="31"/>
+      <c r="H75" s="31"/>
+      <c r="I75" s="31"/>
     </row>
     <row r="76" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A76" s="4"/>
@@ -5452,15 +5451,15 @@
       <c r="I78" s="8"/>
     </row>
     <row r="79" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A79" s="22"/>
-      <c r="B79" s="20"/>
-      <c r="C79" s="20"/>
-      <c r="D79" s="20"/>
-      <c r="E79" s="20"/>
-      <c r="F79" s="20"/>
-      <c r="G79" s="20"/>
-      <c r="H79" s="20"/>
-      <c r="I79" s="20"/>
+      <c r="A79" s="33"/>
+      <c r="B79" s="31"/>
+      <c r="C79" s="31"/>
+      <c r="D79" s="31"/>
+      <c r="E79" s="31"/>
+      <c r="F79" s="31"/>
+      <c r="G79" s="31"/>
+      <c r="H79" s="31"/>
+      <c r="I79" s="31"/>
     </row>
     <row r="80" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A80" s="4"/>
@@ -5496,15 +5495,15 @@
       <c r="B85" s="6"/>
     </row>
     <row r="87" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A87" s="19"/>
-      <c r="B87" s="20"/>
-      <c r="C87" s="20"/>
-      <c r="D87" s="20"/>
-      <c r="E87" s="20"/>
-      <c r="F87" s="20"/>
-      <c r="G87" s="20"/>
-      <c r="H87" s="20"/>
-      <c r="I87" s="20"/>
+      <c r="A87" s="30"/>
+      <c r="B87" s="31"/>
+      <c r="C87" s="31"/>
+      <c r="D87" s="31"/>
+      <c r="E87" s="31"/>
+      <c r="F87" s="31"/>
+      <c r="G87" s="31"/>
+      <c r="H87" s="31"/>
+      <c r="I87" s="31"/>
     </row>
     <row r="88" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A88" s="4"/>
@@ -5607,15 +5606,15 @@
       <c r="B98" s="9"/>
     </row>
     <row r="100" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A100" s="21"/>
-      <c r="B100" s="20"/>
-      <c r="C100" s="20"/>
-      <c r="D100" s="20"/>
-      <c r="E100" s="20"/>
-      <c r="F100" s="20"/>
-      <c r="G100" s="20"/>
-      <c r="H100" s="20"/>
-      <c r="I100" s="20"/>
+      <c r="A100" s="32"/>
+      <c r="B100" s="31"/>
+      <c r="C100" s="31"/>
+      <c r="D100" s="31"/>
+      <c r="E100" s="31"/>
+      <c r="F100" s="31"/>
+      <c r="G100" s="31"/>
+      <c r="H100" s="31"/>
+      <c r="I100" s="31"/>
     </row>
     <row r="101" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A101" s="4"/>
@@ -6142,14 +6141,14 @@
     <row r="33" spans="1:9" ht="12.75" x14ac:dyDescent="0.2"/>
     <row r="35" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A35" s="4"/>
-      <c r="B35" s="21"/>
-      <c r="C35" s="20"/>
-      <c r="D35" s="20"/>
-      <c r="E35" s="20"/>
-      <c r="F35" s="20"/>
-      <c r="G35" s="20"/>
-      <c r="H35" s="20"/>
-      <c r="I35" s="20"/>
+      <c r="B35" s="32"/>
+      <c r="C35" s="31"/>
+      <c r="D35" s="31"/>
+      <c r="E35" s="31"/>
+      <c r="F35" s="31"/>
+      <c r="G35" s="31"/>
+      <c r="H35" s="31"/>
+      <c r="I35" s="31"/>
     </row>
     <row r="36" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A36" s="4"/>
@@ -6527,15 +6526,15 @@
       <c r="I69" s="4"/>
     </row>
     <row r="70" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A70" s="21"/>
-      <c r="B70" s="20"/>
-      <c r="C70" s="20"/>
-      <c r="D70" s="20"/>
-      <c r="E70" s="20"/>
-      <c r="F70" s="20"/>
-      <c r="G70" s="20"/>
-      <c r="H70" s="20"/>
-      <c r="I70" s="20"/>
+      <c r="A70" s="32"/>
+      <c r="B70" s="31"/>
+      <c r="C70" s="31"/>
+      <c r="D70" s="31"/>
+      <c r="E70" s="31"/>
+      <c r="F70" s="31"/>
+      <c r="G70" s="31"/>
+      <c r="H70" s="31"/>
+      <c r="I70" s="31"/>
     </row>
     <row r="71" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A71" s="4"/>
@@ -6560,15 +6559,15 @@
       <c r="I72" s="6"/>
     </row>
     <row r="75" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A75" s="19"/>
-      <c r="B75" s="20"/>
-      <c r="C75" s="20"/>
-      <c r="D75" s="20"/>
-      <c r="E75" s="20"/>
-      <c r="F75" s="20"/>
-      <c r="G75" s="20"/>
-      <c r="H75" s="20"/>
-      <c r="I75" s="20"/>
+      <c r="A75" s="30"/>
+      <c r="B75" s="31"/>
+      <c r="C75" s="31"/>
+      <c r="D75" s="31"/>
+      <c r="E75" s="31"/>
+      <c r="F75" s="31"/>
+      <c r="G75" s="31"/>
+      <c r="H75" s="31"/>
+      <c r="I75" s="31"/>
     </row>
     <row r="76" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A76" s="4"/>
@@ -6604,15 +6603,15 @@
       <c r="I78" s="8"/>
     </row>
     <row r="79" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A79" s="22"/>
-      <c r="B79" s="20"/>
-      <c r="C79" s="20"/>
-      <c r="D79" s="20"/>
-      <c r="E79" s="20"/>
-      <c r="F79" s="20"/>
-      <c r="G79" s="20"/>
-      <c r="H79" s="20"/>
-      <c r="I79" s="20"/>
+      <c r="A79" s="33"/>
+      <c r="B79" s="31"/>
+      <c r="C79" s="31"/>
+      <c r="D79" s="31"/>
+      <c r="E79" s="31"/>
+      <c r="F79" s="31"/>
+      <c r="G79" s="31"/>
+      <c r="H79" s="31"/>
+      <c r="I79" s="31"/>
     </row>
     <row r="80" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A80" s="4"/>
@@ -6648,15 +6647,15 @@
       <c r="B85" s="6"/>
     </row>
     <row r="87" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A87" s="19"/>
-      <c r="B87" s="20"/>
-      <c r="C87" s="20"/>
-      <c r="D87" s="20"/>
-      <c r="E87" s="20"/>
-      <c r="F87" s="20"/>
-      <c r="G87" s="20"/>
-      <c r="H87" s="20"/>
-      <c r="I87" s="20"/>
+      <c r="A87" s="30"/>
+      <c r="B87" s="31"/>
+      <c r="C87" s="31"/>
+      <c r="D87" s="31"/>
+      <c r="E87" s="31"/>
+      <c r="F87" s="31"/>
+      <c r="G87" s="31"/>
+      <c r="H87" s="31"/>
+      <c r="I87" s="31"/>
     </row>
     <row r="88" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A88" s="4"/>
@@ -6759,15 +6758,15 @@
       <c r="B98" s="9"/>
     </row>
     <row r="100" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A100" s="21"/>
-      <c r="B100" s="20"/>
-      <c r="C100" s="20"/>
-      <c r="D100" s="20"/>
-      <c r="E100" s="20"/>
-      <c r="F100" s="20"/>
-      <c r="G100" s="20"/>
-      <c r="H100" s="20"/>
-      <c r="I100" s="20"/>
+      <c r="A100" s="32"/>
+      <c r="B100" s="31"/>
+      <c r="C100" s="31"/>
+      <c r="D100" s="31"/>
+      <c r="E100" s="31"/>
+      <c r="F100" s="31"/>
+      <c r="G100" s="31"/>
+      <c r="H100" s="31"/>
+      <c r="I100" s="31"/>
     </row>
     <row r="101" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A101" s="4"/>
@@ -7294,14 +7293,14 @@
     <row r="33" spans="1:9" ht="12.75" x14ac:dyDescent="0.2"/>
     <row r="35" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A35" s="4"/>
-      <c r="B35" s="21"/>
-      <c r="C35" s="20"/>
-      <c r="D35" s="20"/>
-      <c r="E35" s="20"/>
-      <c r="F35" s="20"/>
-      <c r="G35" s="20"/>
-      <c r="H35" s="20"/>
-      <c r="I35" s="20"/>
+      <c r="B35" s="32"/>
+      <c r="C35" s="31"/>
+      <c r="D35" s="31"/>
+      <c r="E35" s="31"/>
+      <c r="F35" s="31"/>
+      <c r="G35" s="31"/>
+      <c r="H35" s="31"/>
+      <c r="I35" s="31"/>
     </row>
     <row r="36" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A36" s="4"/>
@@ -7679,15 +7678,15 @@
       <c r="I69" s="4"/>
     </row>
     <row r="70" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A70" s="21"/>
-      <c r="B70" s="20"/>
-      <c r="C70" s="20"/>
-      <c r="D70" s="20"/>
-      <c r="E70" s="20"/>
-      <c r="F70" s="20"/>
-      <c r="G70" s="20"/>
-      <c r="H70" s="20"/>
-      <c r="I70" s="20"/>
+      <c r="A70" s="32"/>
+      <c r="B70" s="31"/>
+      <c r="C70" s="31"/>
+      <c r="D70" s="31"/>
+      <c r="E70" s="31"/>
+      <c r="F70" s="31"/>
+      <c r="G70" s="31"/>
+      <c r="H70" s="31"/>
+      <c r="I70" s="31"/>
     </row>
     <row r="71" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A71" s="4"/>
@@ -7712,15 +7711,15 @@
       <c r="I72" s="6"/>
     </row>
     <row r="75" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A75" s="19"/>
-      <c r="B75" s="20"/>
-      <c r="C75" s="20"/>
-      <c r="D75" s="20"/>
-      <c r="E75" s="20"/>
-      <c r="F75" s="20"/>
-      <c r="G75" s="20"/>
-      <c r="H75" s="20"/>
-      <c r="I75" s="20"/>
+      <c r="A75" s="30"/>
+      <c r="B75" s="31"/>
+      <c r="C75" s="31"/>
+      <c r="D75" s="31"/>
+      <c r="E75" s="31"/>
+      <c r="F75" s="31"/>
+      <c r="G75" s="31"/>
+      <c r="H75" s="31"/>
+      <c r="I75" s="31"/>
     </row>
     <row r="76" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A76" s="4"/>
@@ -7756,15 +7755,15 @@
       <c r="I78" s="8"/>
     </row>
     <row r="79" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A79" s="22"/>
-      <c r="B79" s="20"/>
-      <c r="C79" s="20"/>
-      <c r="D79" s="20"/>
-      <c r="E79" s="20"/>
-      <c r="F79" s="20"/>
-      <c r="G79" s="20"/>
-      <c r="H79" s="20"/>
-      <c r="I79" s="20"/>
+      <c r="A79" s="33"/>
+      <c r="B79" s="31"/>
+      <c r="C79" s="31"/>
+      <c r="D79" s="31"/>
+      <c r="E79" s="31"/>
+      <c r="F79" s="31"/>
+      <c r="G79" s="31"/>
+      <c r="H79" s="31"/>
+      <c r="I79" s="31"/>
     </row>
     <row r="80" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A80" s="4"/>
@@ -7800,15 +7799,15 @@
       <c r="B85" s="6"/>
     </row>
     <row r="87" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A87" s="19"/>
-      <c r="B87" s="20"/>
-      <c r="C87" s="20"/>
-      <c r="D87" s="20"/>
-      <c r="E87" s="20"/>
-      <c r="F87" s="20"/>
-      <c r="G87" s="20"/>
-      <c r="H87" s="20"/>
-      <c r="I87" s="20"/>
+      <c r="A87" s="30"/>
+      <c r="B87" s="31"/>
+      <c r="C87" s="31"/>
+      <c r="D87" s="31"/>
+      <c r="E87" s="31"/>
+      <c r="F87" s="31"/>
+      <c r="G87" s="31"/>
+      <c r="H87" s="31"/>
+      <c r="I87" s="31"/>
     </row>
     <row r="88" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A88" s="4"/>
@@ -7911,15 +7910,15 @@
       <c r="B98" s="9"/>
     </row>
     <row r="100" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A100" s="21"/>
-      <c r="B100" s="20"/>
-      <c r="C100" s="20"/>
-      <c r="D100" s="20"/>
-      <c r="E100" s="20"/>
-      <c r="F100" s="20"/>
-      <c r="G100" s="20"/>
-      <c r="H100" s="20"/>
-      <c r="I100" s="20"/>
+      <c r="A100" s="32"/>
+      <c r="B100" s="31"/>
+      <c r="C100" s="31"/>
+      <c r="D100" s="31"/>
+      <c r="E100" s="31"/>
+      <c r="F100" s="31"/>
+      <c r="G100" s="31"/>
+      <c r="H100" s="31"/>
+      <c r="I100" s="31"/>
     </row>
     <row r="101" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A101" s="4"/>
@@ -8443,27 +8442,17 @@
       <c r="H32" s="11"/>
       <c r="I32" s="11"/>
     </row>
-    <row r="33" spans="1:9" s="23" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A33"/>
-      <c r="B33"/>
-      <c r="C33"/>
-      <c r="D33"/>
-      <c r="E33"/>
-      <c r="F33"/>
-      <c r="G33"/>
-      <c r="H33"/>
-      <c r="I33"/>
-    </row>
+    <row r="33" spans="1:9" ht="12.75" x14ac:dyDescent="0.2"/>
     <row r="35" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A35" s="4"/>
-      <c r="B35" s="21"/>
-      <c r="C35" s="20"/>
-      <c r="D35" s="20"/>
-      <c r="E35" s="20"/>
-      <c r="F35" s="20"/>
-      <c r="G35" s="20"/>
-      <c r="H35" s="20"/>
-      <c r="I35" s="20"/>
+      <c r="B35" s="32"/>
+      <c r="C35" s="31"/>
+      <c r="D35" s="31"/>
+      <c r="E35" s="31"/>
+      <c r="F35" s="31"/>
+      <c r="G35" s="31"/>
+      <c r="H35" s="31"/>
+      <c r="I35" s="31"/>
     </row>
     <row r="36" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A36" s="4"/>
@@ -8841,15 +8830,15 @@
       <c r="I69" s="4"/>
     </row>
     <row r="70" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A70" s="21"/>
-      <c r="B70" s="20"/>
-      <c r="C70" s="20"/>
-      <c r="D70" s="20"/>
-      <c r="E70" s="20"/>
-      <c r="F70" s="20"/>
-      <c r="G70" s="20"/>
-      <c r="H70" s="20"/>
-      <c r="I70" s="20"/>
+      <c r="A70" s="32"/>
+      <c r="B70" s="31"/>
+      <c r="C70" s="31"/>
+      <c r="D70" s="31"/>
+      <c r="E70" s="31"/>
+      <c r="F70" s="31"/>
+      <c r="G70" s="31"/>
+      <c r="H70" s="31"/>
+      <c r="I70" s="31"/>
     </row>
     <row r="71" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A71" s="4"/>
@@ -8874,15 +8863,15 @@
       <c r="I72" s="6"/>
     </row>
     <row r="75" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A75" s="19"/>
-      <c r="B75" s="20"/>
-      <c r="C75" s="20"/>
-      <c r="D75" s="20"/>
-      <c r="E75" s="20"/>
-      <c r="F75" s="20"/>
-      <c r="G75" s="20"/>
-      <c r="H75" s="20"/>
-      <c r="I75" s="20"/>
+      <c r="A75" s="30"/>
+      <c r="B75" s="31"/>
+      <c r="C75" s="31"/>
+      <c r="D75" s="31"/>
+      <c r="E75" s="31"/>
+      <c r="F75" s="31"/>
+      <c r="G75" s="31"/>
+      <c r="H75" s="31"/>
+      <c r="I75" s="31"/>
     </row>
     <row r="76" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A76" s="4"/>
@@ -8918,15 +8907,15 @@
       <c r="I78" s="8"/>
     </row>
     <row r="79" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A79" s="22"/>
-      <c r="B79" s="20"/>
-      <c r="C79" s="20"/>
-      <c r="D79" s="20"/>
-      <c r="E79" s="20"/>
-      <c r="F79" s="20"/>
-      <c r="G79" s="20"/>
-      <c r="H79" s="20"/>
-      <c r="I79" s="20"/>
+      <c r="A79" s="33"/>
+      <c r="B79" s="31"/>
+      <c r="C79" s="31"/>
+      <c r="D79" s="31"/>
+      <c r="E79" s="31"/>
+      <c r="F79" s="31"/>
+      <c r="G79" s="31"/>
+      <c r="H79" s="31"/>
+      <c r="I79" s="31"/>
     </row>
     <row r="80" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A80" s="4"/>
@@ -8962,15 +8951,15 @@
       <c r="B85" s="6"/>
     </row>
     <row r="87" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A87" s="19"/>
-      <c r="B87" s="20"/>
-      <c r="C87" s="20"/>
-      <c r="D87" s="20"/>
-      <c r="E87" s="20"/>
-      <c r="F87" s="20"/>
-      <c r="G87" s="20"/>
-      <c r="H87" s="20"/>
-      <c r="I87" s="20"/>
+      <c r="A87" s="30"/>
+      <c r="B87" s="31"/>
+      <c r="C87" s="31"/>
+      <c r="D87" s="31"/>
+      <c r="E87" s="31"/>
+      <c r="F87" s="31"/>
+      <c r="G87" s="31"/>
+      <c r="H87" s="31"/>
+      <c r="I87" s="31"/>
     </row>
     <row r="88" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A88" s="4"/>
@@ -9073,15 +9062,15 @@
       <c r="B98" s="9"/>
     </row>
     <row r="100" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A100" s="21"/>
-      <c r="B100" s="20"/>
-      <c r="C100" s="20"/>
-      <c r="D100" s="20"/>
-      <c r="E100" s="20"/>
-      <c r="F100" s="20"/>
-      <c r="G100" s="20"/>
-      <c r="H100" s="20"/>
-      <c r="I100" s="20"/>
+      <c r="A100" s="32"/>
+      <c r="B100" s="31"/>
+      <c r="C100" s="31"/>
+      <c r="D100" s="31"/>
+      <c r="E100" s="31"/>
+      <c r="F100" s="31"/>
+      <c r="G100" s="31"/>
+      <c r="H100" s="31"/>
+      <c r="I100" s="31"/>
     </row>
     <row r="101" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A101" s="4"/>
@@ -9608,14 +9597,14 @@
     <row r="33" spans="1:9" ht="12.75" x14ac:dyDescent="0.2"/>
     <row r="35" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A35" s="4"/>
-      <c r="B35" s="21"/>
-      <c r="C35" s="20"/>
-      <c r="D35" s="20"/>
-      <c r="E35" s="20"/>
-      <c r="F35" s="20"/>
-      <c r="G35" s="20"/>
-      <c r="H35" s="20"/>
-      <c r="I35" s="20"/>
+      <c r="B35" s="32"/>
+      <c r="C35" s="31"/>
+      <c r="D35" s="31"/>
+      <c r="E35" s="31"/>
+      <c r="F35" s="31"/>
+      <c r="G35" s="31"/>
+      <c r="H35" s="31"/>
+      <c r="I35" s="31"/>
     </row>
     <row r="36" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A36" s="4"/>
@@ -9993,15 +9982,15 @@
       <c r="I69" s="4"/>
     </row>
     <row r="70" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A70" s="21"/>
-      <c r="B70" s="20"/>
-      <c r="C70" s="20"/>
-      <c r="D70" s="20"/>
-      <c r="E70" s="20"/>
-      <c r="F70" s="20"/>
-      <c r="G70" s="20"/>
-      <c r="H70" s="20"/>
-      <c r="I70" s="20"/>
+      <c r="A70" s="32"/>
+      <c r="B70" s="31"/>
+      <c r="C70" s="31"/>
+      <c r="D70" s="31"/>
+      <c r="E70" s="31"/>
+      <c r="F70" s="31"/>
+      <c r="G70" s="31"/>
+      <c r="H70" s="31"/>
+      <c r="I70" s="31"/>
     </row>
     <row r="71" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A71" s="4"/>
@@ -10026,15 +10015,15 @@
       <c r="I72" s="6"/>
     </row>
     <row r="75" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A75" s="19"/>
-      <c r="B75" s="20"/>
-      <c r="C75" s="20"/>
-      <c r="D75" s="20"/>
-      <c r="E75" s="20"/>
-      <c r="F75" s="20"/>
-      <c r="G75" s="20"/>
-      <c r="H75" s="20"/>
-      <c r="I75" s="20"/>
+      <c r="A75" s="30"/>
+      <c r="B75" s="31"/>
+      <c r="C75" s="31"/>
+      <c r="D75" s="31"/>
+      <c r="E75" s="31"/>
+      <c r="F75" s="31"/>
+      <c r="G75" s="31"/>
+      <c r="H75" s="31"/>
+      <c r="I75" s="31"/>
     </row>
     <row r="76" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A76" s="4"/>
@@ -10070,15 +10059,15 @@
       <c r="I78" s="8"/>
     </row>
     <row r="79" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A79" s="22"/>
-      <c r="B79" s="20"/>
-      <c r="C79" s="20"/>
-      <c r="D79" s="20"/>
-      <c r="E79" s="20"/>
-      <c r="F79" s="20"/>
-      <c r="G79" s="20"/>
-      <c r="H79" s="20"/>
-      <c r="I79" s="20"/>
+      <c r="A79" s="33"/>
+      <c r="B79" s="31"/>
+      <c r="C79" s="31"/>
+      <c r="D79" s="31"/>
+      <c r="E79" s="31"/>
+      <c r="F79" s="31"/>
+      <c r="G79" s="31"/>
+      <c r="H79" s="31"/>
+      <c r="I79" s="31"/>
     </row>
     <row r="80" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A80" s="4"/>
@@ -10114,15 +10103,15 @@
       <c r="B85" s="6"/>
     </row>
     <row r="87" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A87" s="19"/>
-      <c r="B87" s="20"/>
-      <c r="C87" s="20"/>
-      <c r="D87" s="20"/>
-      <c r="E87" s="20"/>
-      <c r="F87" s="20"/>
-      <c r="G87" s="20"/>
-      <c r="H87" s="20"/>
-      <c r="I87" s="20"/>
+      <c r="A87" s="30"/>
+      <c r="B87" s="31"/>
+      <c r="C87" s="31"/>
+      <c r="D87" s="31"/>
+      <c r="E87" s="31"/>
+      <c r="F87" s="31"/>
+      <c r="G87" s="31"/>
+      <c r="H87" s="31"/>
+      <c r="I87" s="31"/>
     </row>
     <row r="88" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A88" s="4"/>
@@ -10225,15 +10214,15 @@
       <c r="B98" s="9"/>
     </row>
     <row r="100" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A100" s="21"/>
-      <c r="B100" s="20"/>
-      <c r="C100" s="20"/>
-      <c r="D100" s="20"/>
-      <c r="E100" s="20"/>
-      <c r="F100" s="20"/>
-      <c r="G100" s="20"/>
-      <c r="H100" s="20"/>
-      <c r="I100" s="20"/>
+      <c r="A100" s="32"/>
+      <c r="B100" s="31"/>
+      <c r="C100" s="31"/>
+      <c r="D100" s="31"/>
+      <c r="E100" s="31"/>
+      <c r="F100" s="31"/>
+      <c r="G100" s="31"/>
+      <c r="H100" s="31"/>
+      <c r="I100" s="31"/>
     </row>
     <row r="101" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A101" s="4"/>
@@ -10760,14 +10749,14 @@
     <row r="33" spans="1:9" ht="12.75" x14ac:dyDescent="0.2"/>
     <row r="35" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A35" s="4"/>
-      <c r="B35" s="21"/>
-      <c r="C35" s="20"/>
-      <c r="D35" s="20"/>
-      <c r="E35" s="20"/>
-      <c r="F35" s="20"/>
-      <c r="G35" s="20"/>
-      <c r="H35" s="20"/>
-      <c r="I35" s="20"/>
+      <c r="B35" s="32"/>
+      <c r="C35" s="31"/>
+      <c r="D35" s="31"/>
+      <c r="E35" s="31"/>
+      <c r="F35" s="31"/>
+      <c r="G35" s="31"/>
+      <c r="H35" s="31"/>
+      <c r="I35" s="31"/>
     </row>
     <row r="36" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A36" s="4"/>
@@ -11145,15 +11134,15 @@
       <c r="I69" s="4"/>
     </row>
     <row r="70" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A70" s="21"/>
-      <c r="B70" s="20"/>
-      <c r="C70" s="20"/>
-      <c r="D70" s="20"/>
-      <c r="E70" s="20"/>
-      <c r="F70" s="20"/>
-      <c r="G70" s="20"/>
-      <c r="H70" s="20"/>
-      <c r="I70" s="20"/>
+      <c r="A70" s="32"/>
+      <c r="B70" s="31"/>
+      <c r="C70" s="31"/>
+      <c r="D70" s="31"/>
+      <c r="E70" s="31"/>
+      <c r="F70" s="31"/>
+      <c r="G70" s="31"/>
+      <c r="H70" s="31"/>
+      <c r="I70" s="31"/>
     </row>
     <row r="71" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A71" s="4"/>
@@ -11178,15 +11167,15 @@
       <c r="I72" s="6"/>
     </row>
     <row r="75" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A75" s="19"/>
-      <c r="B75" s="20"/>
-      <c r="C75" s="20"/>
-      <c r="D75" s="20"/>
-      <c r="E75" s="20"/>
-      <c r="F75" s="20"/>
-      <c r="G75" s="20"/>
-      <c r="H75" s="20"/>
-      <c r="I75" s="20"/>
+      <c r="A75" s="30"/>
+      <c r="B75" s="31"/>
+      <c r="C75" s="31"/>
+      <c r="D75" s="31"/>
+      <c r="E75" s="31"/>
+      <c r="F75" s="31"/>
+      <c r="G75" s="31"/>
+      <c r="H75" s="31"/>
+      <c r="I75" s="31"/>
     </row>
     <row r="76" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A76" s="4"/>
@@ -11222,15 +11211,15 @@
       <c r="I78" s="8"/>
     </row>
     <row r="79" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A79" s="22"/>
-      <c r="B79" s="20"/>
-      <c r="C79" s="20"/>
-      <c r="D79" s="20"/>
-      <c r="E79" s="20"/>
-      <c r="F79" s="20"/>
-      <c r="G79" s="20"/>
-      <c r="H79" s="20"/>
-      <c r="I79" s="20"/>
+      <c r="A79" s="33"/>
+      <c r="B79" s="31"/>
+      <c r="C79" s="31"/>
+      <c r="D79" s="31"/>
+      <c r="E79" s="31"/>
+      <c r="F79" s="31"/>
+      <c r="G79" s="31"/>
+      <c r="H79" s="31"/>
+      <c r="I79" s="31"/>
     </row>
     <row r="80" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A80" s="4"/>
@@ -11266,15 +11255,15 @@
       <c r="B85" s="6"/>
     </row>
     <row r="87" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A87" s="19"/>
-      <c r="B87" s="20"/>
-      <c r="C87" s="20"/>
-      <c r="D87" s="20"/>
-      <c r="E87" s="20"/>
-      <c r="F87" s="20"/>
-      <c r="G87" s="20"/>
-      <c r="H87" s="20"/>
-      <c r="I87" s="20"/>
+      <c r="A87" s="30"/>
+      <c r="B87" s="31"/>
+      <c r="C87" s="31"/>
+      <c r="D87" s="31"/>
+      <c r="E87" s="31"/>
+      <c r="F87" s="31"/>
+      <c r="G87" s="31"/>
+      <c r="H87" s="31"/>
+      <c r="I87" s="31"/>
     </row>
     <row r="88" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A88" s="4"/>
@@ -11377,15 +11366,15 @@
       <c r="B98" s="9"/>
     </row>
     <row r="100" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A100" s="21"/>
-      <c r="B100" s="20"/>
-      <c r="C100" s="20"/>
-      <c r="D100" s="20"/>
-      <c r="E100" s="20"/>
-      <c r="F100" s="20"/>
-      <c r="G100" s="20"/>
-      <c r="H100" s="20"/>
-      <c r="I100" s="20"/>
+      <c r="A100" s="32"/>
+      <c r="B100" s="31"/>
+      <c r="C100" s="31"/>
+      <c r="D100" s="31"/>
+      <c r="E100" s="31"/>
+      <c r="F100" s="31"/>
+      <c r="G100" s="31"/>
+      <c r="H100" s="31"/>
+      <c r="I100" s="31"/>
     </row>
     <row r="101" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A101" s="4"/>
@@ -11450,327 +11439,327 @@
       <c r="A1" s="12" t="s">
         <v>8</v>
       </c>
-      <c r="B1" s="26" t="s">
+      <c r="B1" s="21" t="s">
         <v>0</v>
       </c>
-      <c r="C1" s="26" t="s">
+      <c r="C1" s="21" t="s">
         <v>1</v>
       </c>
-      <c r="D1" s="26" t="s">
+      <c r="D1" s="21" t="s">
         <v>2</v>
       </c>
-      <c r="E1" s="26" t="s">
+      <c r="E1" s="21" t="s">
         <v>3</v>
       </c>
-      <c r="F1" s="26" t="s">
+      <c r="F1" s="21" t="s">
         <v>4</v>
       </c>
-      <c r="G1" s="26" t="s">
+      <c r="G1" s="21" t="s">
         <v>5</v>
       </c>
-      <c r="H1" s="26" t="s">
+      <c r="H1" s="21" t="s">
         <v>6</v>
       </c>
-      <c r="I1" s="26" t="s">
+      <c r="I1" s="21" t="s">
         <v>7</v>
       </c>
     </row>
     <row r="2" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A2" s="24">
+      <c r="A2" s="19">
         <v>1</v>
       </c>
-      <c r="B2" s="27">
+      <c r="B2" s="22">
         <v>6429</v>
       </c>
-      <c r="C2" s="27">
+      <c r="C2" s="22">
         <v>8198</v>
       </c>
-      <c r="D2" s="27">
+      <c r="D2" s="22">
         <v>9269</v>
       </c>
-      <c r="E2" s="27">
+      <c r="E2" s="22">
         <v>10803</v>
       </c>
-      <c r="F2" s="27">
+      <c r="F2" s="22">
         <v>1271</v>
       </c>
-      <c r="G2" s="27">
+      <c r="G2" s="22">
         <v>3694</v>
       </c>
-      <c r="H2" s="27">
+      <c r="H2" s="22">
         <v>369</v>
       </c>
-      <c r="I2" s="27">
+      <c r="I2" s="22">
         <v>3325</v>
       </c>
     </row>
     <row r="3" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A3" s="24">
+      <c r="A3" s="19">
         <f t="shared" ref="A3:A32" si="0">A2+1</f>
         <v>2</v>
       </c>
-      <c r="B3" s="27">
+      <c r="B3" s="22">
         <v>6461</v>
       </c>
-      <c r="C3" s="27">
+      <c r="C3" s="22">
         <v>8283</v>
       </c>
-      <c r="D3" s="27">
+      <c r="D3" s="22">
         <v>9272</v>
       </c>
-      <c r="E3" s="27">
+      <c r="E3" s="22">
         <v>10804</v>
       </c>
-      <c r="F3" s="27">
+      <c r="F3" s="22">
         <v>1271</v>
       </c>
-      <c r="G3" s="27">
+      <c r="G3" s="22">
         <v>3697</v>
       </c>
-      <c r="H3" s="27">
+      <c r="H3" s="22">
         <v>369</v>
       </c>
-      <c r="I3" s="27">
+      <c r="I3" s="22">
         <v>3328</v>
       </c>
     </row>
     <row r="4" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A4" s="24">
+      <c r="A4" s="19">
         <f t="shared" si="0"/>
         <v>3</v>
       </c>
-      <c r="B4" s="27">
+      <c r="B4" s="22">
         <v>6524</v>
       </c>
-      <c r="C4" s="27">
+      <c r="C4" s="22">
         <v>8298</v>
       </c>
-      <c r="D4" s="27">
+      <c r="D4" s="22">
         <v>9275</v>
       </c>
-      <c r="E4" s="27">
+      <c r="E4" s="22">
         <v>10804</v>
       </c>
-      <c r="F4" s="27">
+      <c r="F4" s="22">
         <v>1271</v>
       </c>
-      <c r="G4" s="27">
+      <c r="G4" s="22">
         <v>3702</v>
       </c>
-      <c r="H4" s="27">
+      <c r="H4" s="22">
         <v>369</v>
       </c>
-      <c r="I4" s="27">
+      <c r="I4" s="22">
         <v>3333</v>
       </c>
     </row>
     <row r="5" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A5" s="24">
+      <c r="A5" s="19">
         <f t="shared" si="0"/>
         <v>4</v>
       </c>
-      <c r="B5" s="27">
+      <c r="B5" s="22">
         <v>6619</v>
       </c>
-      <c r="C5" s="27">
+      <c r="C5" s="22">
         <v>8371</v>
       </c>
-      <c r="D5" s="27">
+      <c r="D5" s="22">
         <v>9279</v>
       </c>
-      <c r="E5" s="27">
+      <c r="E5" s="22">
         <v>10805</v>
       </c>
-      <c r="F5" s="27">
+      <c r="F5" s="22">
         <v>1271</v>
       </c>
-      <c r="G5" s="27">
+      <c r="G5" s="22">
         <v>3707</v>
       </c>
-      <c r="H5" s="27">
+      <c r="H5" s="22">
         <v>370</v>
       </c>
-      <c r="I5" s="27">
+      <c r="I5" s="22">
         <v>3336</v>
       </c>
     </row>
     <row r="6" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A6" s="24">
+      <c r="A6" s="19">
         <f t="shared" si="0"/>
         <v>5</v>
       </c>
-      <c r="B6" s="27">
+      <c r="B6" s="22">
         <v>6676</v>
       </c>
-      <c r="C6" s="27">
+      <c r="C6" s="22">
         <v>8399</v>
       </c>
-      <c r="D6" s="27">
+      <c r="D6" s="22">
         <v>9281</v>
       </c>
-      <c r="E6" s="27">
+      <c r="E6" s="22">
         <v>10806</v>
       </c>
-      <c r="F6" s="27">
+      <c r="F6" s="22">
         <v>1271</v>
       </c>
-      <c r="G6" s="27">
+      <c r="G6" s="22">
         <v>3711</v>
       </c>
-      <c r="H6" s="27">
+      <c r="H6" s="22">
         <v>371</v>
       </c>
-      <c r="I6" s="27">
+      <c r="I6" s="22">
         <v>3340</v>
       </c>
     </row>
     <row r="7" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A7" s="24">
+      <c r="A7" s="19">
         <f t="shared" si="0"/>
         <v>6</v>
       </c>
-      <c r="B7" s="27">
+      <c r="B7" s="22">
         <v>6759</v>
       </c>
-      <c r="C7" s="27">
+      <c r="C7" s="22">
         <v>8479</v>
       </c>
-      <c r="D7" s="27">
+      <c r="D7" s="22">
         <v>9287</v>
       </c>
-      <c r="E7" s="27">
+      <c r="E7" s="22">
         <v>10807</v>
       </c>
-      <c r="F7" s="27">
+      <c r="F7" s="22">
         <v>1272</v>
       </c>
-      <c r="G7" s="27">
+      <c r="G7" s="22">
         <v>3712</v>
       </c>
-      <c r="H7" s="27">
+      <c r="H7" s="22">
         <v>371</v>
       </c>
-      <c r="I7" s="27">
+      <c r="I7" s="22">
         <v>3343</v>
       </c>
     </row>
     <row r="8" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A8" s="24">
+      <c r="A8" s="19">
         <f t="shared" si="0"/>
         <v>7</v>
       </c>
-      <c r="B8" s="27">
+      <c r="B8" s="22">
         <v>6793</v>
       </c>
-      <c r="C8" s="27">
+      <c r="C8" s="22">
         <v>8509</v>
       </c>
-      <c r="D8" s="27">
+      <c r="D8" s="22">
         <v>9291</v>
       </c>
-      <c r="E8" s="27">
+      <c r="E8" s="22">
         <v>10808</v>
       </c>
-      <c r="F8" s="27">
+      <c r="F8" s="22">
         <v>1273</v>
       </c>
-      <c r="G8" s="27">
+      <c r="G8" s="22">
         <v>3719</v>
       </c>
-      <c r="H8" s="27">
+      <c r="H8" s="22">
         <v>372</v>
       </c>
-      <c r="I8" s="27">
+      <c r="I8" s="22">
         <v>3347</v>
       </c>
     </row>
     <row r="9" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A9" s="24">
+      <c r="A9" s="19">
         <f t="shared" si="0"/>
         <v>8</v>
       </c>
-      <c r="B9" s="27">
+      <c r="B9" s="22">
         <v>6840</v>
       </c>
-      <c r="C9" s="27">
+      <c r="C9" s="22">
         <v>8572</v>
       </c>
-      <c r="D9" s="27">
+      <c r="D9" s="22">
         <v>9291</v>
       </c>
-      <c r="E9" s="27">
+      <c r="E9" s="22">
         <v>10808</v>
       </c>
-      <c r="F9" s="27">
+      <c r="F9" s="22">
         <v>1273</v>
       </c>
-      <c r="G9" s="27">
+      <c r="G9" s="22">
         <v>3723</v>
       </c>
-      <c r="H9" s="27">
+      <c r="H9" s="22">
         <v>372</v>
       </c>
-      <c r="I9" s="27">
+      <c r="I9" s="22">
         <v>3351</v>
       </c>
     </row>
     <row r="10" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A10" s="24">
+      <c r="A10" s="19">
         <f t="shared" si="0"/>
         <v>9</v>
       </c>
-      <c r="B10" s="27">
+      <c r="B10" s="22">
         <v>6845</v>
       </c>
-      <c r="C10" s="27">
+      <c r="C10" s="22">
         <v>8607</v>
       </c>
-      <c r="D10" s="27">
+      <c r="D10" s="22">
         <v>9299</v>
       </c>
-      <c r="E10" s="27">
+      <c r="E10" s="22">
         <v>10809</v>
       </c>
-      <c r="F10" s="27">
+      <c r="F10" s="22">
         <v>1273</v>
       </c>
-      <c r="G10" s="27">
+      <c r="G10" s="22">
         <v>3726</v>
       </c>
-      <c r="H10" s="27">
+      <c r="H10" s="22">
         <v>373</v>
       </c>
-      <c r="I10" s="27">
+      <c r="I10" s="22">
         <v>3349</v>
       </c>
     </row>
     <row r="11" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A11" s="24">
+      <c r="A11" s="19">
         <f t="shared" si="0"/>
         <v>10</v>
       </c>
-      <c r="B11" s="27">
+      <c r="B11" s="22">
         <v>6902</v>
       </c>
-      <c r="C11" s="27">
+      <c r="C11" s="22">
         <v>8690</v>
       </c>
-      <c r="D11" s="27">
+      <c r="D11" s="22">
         <v>9302</v>
       </c>
-      <c r="E11" s="27">
+      <c r="E11" s="22">
         <v>10810</v>
       </c>
-      <c r="F11" s="27">
+      <c r="F11" s="22">
         <v>1273</v>
       </c>
-      <c r="G11" s="27">
+      <c r="G11" s="22">
         <v>3733</v>
       </c>
-      <c r="H11" s="27">
+      <c r="H11" s="22">
         <v>373</v>
       </c>
-      <c r="I11" s="27">
+      <c r="I11" s="22">
         <v>3359</v>
       </c>
     </row>
@@ -11779,14 +11768,30 @@
         <f t="shared" si="0"/>
         <v>11</v>
       </c>
-      <c r="B12" s="29"/>
-      <c r="C12" s="30"/>
-      <c r="D12" s="29"/>
-      <c r="E12" s="29"/>
-      <c r="F12" s="29"/>
-      <c r="G12" s="29"/>
-      <c r="H12" s="29"/>
-      <c r="I12" s="29"/>
+      <c r="B12" s="24">
+        <v>6917</v>
+      </c>
+      <c r="C12" s="25">
+        <v>8710</v>
+      </c>
+      <c r="D12" s="24">
+        <v>9309</v>
+      </c>
+      <c r="E12" s="24">
+        <v>10811</v>
+      </c>
+      <c r="F12" s="24">
+        <v>1274</v>
+      </c>
+      <c r="G12" s="24">
+        <v>3734</v>
+      </c>
+      <c r="H12" s="24">
+        <v>373</v>
+      </c>
+      <c r="I12" s="24">
+        <v>3360</v>
+      </c>
     </row>
     <row r="13" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A13" s="1">
@@ -12072,14 +12077,14 @@
     <row r="33" spans="1:9" ht="12.75" x14ac:dyDescent="0.2"/>
     <row r="35" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A35" s="4"/>
-      <c r="B35" s="21"/>
-      <c r="C35" s="20"/>
-      <c r="D35" s="20"/>
-      <c r="E35" s="20"/>
-      <c r="F35" s="20"/>
-      <c r="G35" s="20"/>
-      <c r="H35" s="20"/>
-      <c r="I35" s="20"/>
+      <c r="B35" s="32"/>
+      <c r="C35" s="31"/>
+      <c r="D35" s="31"/>
+      <c r="E35" s="31"/>
+      <c r="F35" s="31"/>
+      <c r="G35" s="31"/>
+      <c r="H35" s="31"/>
+      <c r="I35" s="31"/>
     </row>
     <row r="36" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A36" s="4"/>
@@ -12457,15 +12462,15 @@
       <c r="I69" s="4"/>
     </row>
     <row r="70" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A70" s="21"/>
-      <c r="B70" s="20"/>
-      <c r="C70" s="20"/>
-      <c r="D70" s="20"/>
-      <c r="E70" s="20"/>
-      <c r="F70" s="20"/>
-      <c r="G70" s="20"/>
-      <c r="H70" s="20"/>
-      <c r="I70" s="20"/>
+      <c r="A70" s="32"/>
+      <c r="B70" s="31"/>
+      <c r="C70" s="31"/>
+      <c r="D70" s="31"/>
+      <c r="E70" s="31"/>
+      <c r="F70" s="31"/>
+      <c r="G70" s="31"/>
+      <c r="H70" s="31"/>
+      <c r="I70" s="31"/>
     </row>
     <row r="71" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A71" s="4"/>
@@ -12490,15 +12495,15 @@
       <c r="I72" s="6"/>
     </row>
     <row r="75" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A75" s="19"/>
-      <c r="B75" s="20"/>
-      <c r="C75" s="20"/>
-      <c r="D75" s="20"/>
-      <c r="E75" s="20"/>
-      <c r="F75" s="20"/>
-      <c r="G75" s="20"/>
-      <c r="H75" s="20"/>
-      <c r="I75" s="20"/>
+      <c r="A75" s="30"/>
+      <c r="B75" s="31"/>
+      <c r="C75" s="31"/>
+      <c r="D75" s="31"/>
+      <c r="E75" s="31"/>
+      <c r="F75" s="31"/>
+      <c r="G75" s="31"/>
+      <c r="H75" s="31"/>
+      <c r="I75" s="31"/>
     </row>
     <row r="76" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A76" s="4"/>
@@ -12534,15 +12539,15 @@
       <c r="I78" s="8"/>
     </row>
     <row r="79" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A79" s="22"/>
-      <c r="B79" s="20"/>
-      <c r="C79" s="20"/>
-      <c r="D79" s="20"/>
-      <c r="E79" s="20"/>
-      <c r="F79" s="20"/>
-      <c r="G79" s="20"/>
-      <c r="H79" s="20"/>
-      <c r="I79" s="20"/>
+      <c r="A79" s="33"/>
+      <c r="B79" s="31"/>
+      <c r="C79" s="31"/>
+      <c r="D79" s="31"/>
+      <c r="E79" s="31"/>
+      <c r="F79" s="31"/>
+      <c r="G79" s="31"/>
+      <c r="H79" s="31"/>
+      <c r="I79" s="31"/>
     </row>
     <row r="80" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A80" s="4"/>
@@ -12578,15 +12583,15 @@
       <c r="B85" s="6"/>
     </row>
     <row r="87" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A87" s="19"/>
-      <c r="B87" s="20"/>
-      <c r="C87" s="20"/>
-      <c r="D87" s="20"/>
-      <c r="E87" s="20"/>
-      <c r="F87" s="20"/>
-      <c r="G87" s="20"/>
-      <c r="H87" s="20"/>
-      <c r="I87" s="20"/>
+      <c r="A87" s="30"/>
+      <c r="B87" s="31"/>
+      <c r="C87" s="31"/>
+      <c r="D87" s="31"/>
+      <c r="E87" s="31"/>
+      <c r="F87" s="31"/>
+      <c r="G87" s="31"/>
+      <c r="H87" s="31"/>
+      <c r="I87" s="31"/>
     </row>
     <row r="88" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A88" s="4"/>
@@ -12689,15 +12694,15 @@
       <c r="B98" s="9"/>
     </row>
     <row r="100" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A100" s="21"/>
-      <c r="B100" s="20"/>
-      <c r="C100" s="20"/>
-      <c r="D100" s="20"/>
-      <c r="E100" s="20"/>
-      <c r="F100" s="20"/>
-      <c r="G100" s="20"/>
-      <c r="H100" s="20"/>
-      <c r="I100" s="20"/>
+      <c r="A100" s="32"/>
+      <c r="B100" s="31"/>
+      <c r="C100" s="31"/>
+      <c r="D100" s="31"/>
+      <c r="E100" s="31"/>
+      <c r="F100" s="31"/>
+      <c r="G100" s="31"/>
+      <c r="H100" s="31"/>
+      <c r="I100" s="31"/>
     </row>
     <row r="101" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A101" s="4"/>
@@ -12759,697 +12764,697 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A1" s="31" t="s">
+      <c r="A1" s="26" t="s">
         <v>8</v>
       </c>
-      <c r="B1" s="32" t="s">
+      <c r="B1" s="27" t="s">
         <v>0</v>
       </c>
-      <c r="C1" s="32" t="s">
+      <c r="C1" s="27" t="s">
         <v>1</v>
       </c>
-      <c r="D1" s="32" t="s">
+      <c r="D1" s="27" t="s">
         <v>2</v>
       </c>
-      <c r="E1" s="32" t="s">
+      <c r="E1" s="27" t="s">
         <v>3</v>
       </c>
-      <c r="F1" s="32" t="s">
+      <c r="F1" s="27" t="s">
         <v>4</v>
       </c>
-      <c r="G1" s="32" t="s">
+      <c r="G1" s="27" t="s">
         <v>5</v>
       </c>
-      <c r="H1" s="32" t="s">
+      <c r="H1" s="27" t="s">
         <v>6</v>
       </c>
-      <c r="I1" s="32" t="s">
+      <c r="I1" s="27" t="s">
         <v>7</v>
       </c>
     </row>
     <row r="2" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A2" s="33">
+      <c r="A2" s="28">
         <v>1</v>
       </c>
-      <c r="B2" s="27">
+      <c r="B2" s="22">
         <v>4909</v>
       </c>
-      <c r="C2" s="27">
+      <c r="C2" s="22">
         <v>6810</v>
       </c>
-      <c r="D2" s="27">
+      <c r="D2" s="22">
         <v>9145</v>
       </c>
-      <c r="E2" s="27">
+      <c r="E2" s="22">
         <v>10783</v>
       </c>
-      <c r="F2" s="27">
+      <c r="F2" s="22">
         <v>1266</v>
       </c>
-      <c r="G2" s="27">
+      <c r="G2" s="22">
         <v>3565</v>
       </c>
-      <c r="H2" s="27">
+      <c r="H2" s="22">
         <v>354</v>
       </c>
-      <c r="I2" s="27">
+      <c r="I2" s="22">
         <v>3210</v>
       </c>
     </row>
     <row r="3" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A3" s="33">
+      <c r="A3" s="28">
         <f t="shared" ref="A3:A32" si="0">A2+1</f>
         <v>2</v>
       </c>
-      <c r="B3" s="28"/>
-      <c r="C3" s="28"/>
-      <c r="D3" s="28"/>
-      <c r="E3" s="28"/>
-      <c r="F3" s="28"/>
-      <c r="G3" s="28"/>
-      <c r="H3" s="28"/>
-      <c r="I3" s="28"/>
+      <c r="B3" s="23"/>
+      <c r="C3" s="23"/>
+      <c r="D3" s="23"/>
+      <c r="E3" s="23"/>
+      <c r="F3" s="23"/>
+      <c r="G3" s="23"/>
+      <c r="H3" s="23"/>
+      <c r="I3" s="23"/>
     </row>
     <row r="4" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A4" s="33">
+      <c r="A4" s="28">
         <f t="shared" si="0"/>
         <v>3</v>
       </c>
-      <c r="B4" s="27">
+      <c r="B4" s="22">
         <v>5009</v>
       </c>
-      <c r="C4" s="27">
+      <c r="C4" s="22">
         <v>6932</v>
       </c>
-      <c r="D4" s="27">
+      <c r="D4" s="22">
         <v>9157</v>
       </c>
-      <c r="E4" s="27">
+      <c r="E4" s="22">
         <v>10784</v>
       </c>
-      <c r="F4" s="27">
+      <c r="F4" s="22">
         <v>1267</v>
       </c>
-      <c r="G4" s="27">
+      <c r="G4" s="22">
         <v>3574</v>
       </c>
-      <c r="H4" s="27">
+      <c r="H4" s="22">
         <v>355</v>
       </c>
-      <c r="I4" s="27">
+      <c r="I4" s="22">
         <v>3218</v>
       </c>
     </row>
     <row r="5" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A5" s="33">
+      <c r="A5" s="28">
         <f t="shared" si="0"/>
         <v>4</v>
       </c>
-      <c r="B5" s="27">
+      <c r="B5" s="22">
         <v>5025</v>
       </c>
-      <c r="C5" s="27">
+      <c r="C5" s="22">
         <v>6932</v>
       </c>
-      <c r="D5" s="27">
+      <c r="D5" s="22">
         <v>9158</v>
       </c>
-      <c r="E5" s="27">
+      <c r="E5" s="22">
         <v>10784</v>
       </c>
-      <c r="F5" s="27">
+      <c r="F5" s="22">
         <v>1267</v>
       </c>
-      <c r="G5" s="27">
+      <c r="G5" s="22">
         <v>3578</v>
       </c>
-      <c r="H5" s="27">
+      <c r="H5" s="22">
         <v>355</v>
       </c>
-      <c r="I5" s="27">
+      <c r="I5" s="22">
         <v>3223</v>
       </c>
     </row>
     <row r="6" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A6" s="33">
+      <c r="A6" s="28">
         <f t="shared" si="0"/>
         <v>5</v>
       </c>
-      <c r="B6" s="27">
+      <c r="B6" s="22">
         <v>5069</v>
       </c>
-      <c r="C6" s="27">
+      <c r="C6" s="22">
         <v>6997</v>
       </c>
-      <c r="D6" s="27">
+      <c r="D6" s="22">
         <v>9168</v>
       </c>
-      <c r="E6" s="27">
+      <c r="E6" s="22">
         <v>10784</v>
       </c>
-      <c r="F6" s="27">
+      <c r="F6" s="22">
         <v>1267</v>
       </c>
-      <c r="G6" s="27">
+      <c r="G6" s="22">
         <v>3583</v>
       </c>
-      <c r="H6" s="27">
+      <c r="H6" s="22">
         <v>355</v>
       </c>
-      <c r="I6" s="27">
+      <c r="I6" s="22">
         <v>3227</v>
       </c>
     </row>
     <row r="7" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A7" s="33">
+      <c r="A7" s="28">
         <f t="shared" si="0"/>
         <v>6</v>
       </c>
-      <c r="B7" s="27">
+      <c r="B7" s="22">
         <v>5127</v>
       </c>
-      <c r="C7" s="27">
+      <c r="C7" s="22">
         <v>7107</v>
       </c>
-      <c r="D7" s="27">
+      <c r="D7" s="22">
         <v>9172</v>
       </c>
-      <c r="E7" s="27">
+      <c r="E7" s="22">
         <v>10785</v>
       </c>
-      <c r="F7" s="27">
+      <c r="F7" s="22">
         <v>1267</v>
       </c>
-      <c r="G7" s="27">
+      <c r="G7" s="22">
         <v>3584</v>
       </c>
-      <c r="H7" s="27">
+      <c r="H7" s="22">
         <v>355</v>
       </c>
-      <c r="I7" s="27">
+      <c r="I7" s="22">
         <v>3228</v>
       </c>
     </row>
     <row r="8" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A8" s="33">
+      <c r="A8" s="28">
         <f t="shared" si="0"/>
         <v>7</v>
       </c>
-      <c r="B8" s="27">
+      <c r="B8" s="22">
         <v>5130</v>
       </c>
-      <c r="C8" s="27">
+      <c r="C8" s="22">
         <v>7110</v>
       </c>
-      <c r="D8" s="27">
+      <c r="D8" s="22">
         <v>9176</v>
       </c>
-      <c r="E8" s="27">
+      <c r="E8" s="22">
         <v>10787</v>
       </c>
-      <c r="F8" s="27">
+      <c r="F8" s="22">
         <v>1268</v>
       </c>
-      <c r="G8" s="27">
+      <c r="G8" s="22">
         <v>3590</v>
       </c>
-      <c r="H8" s="27">
+      <c r="H8" s="22">
         <v>356</v>
       </c>
-      <c r="I8" s="27">
+      <c r="I8" s="22">
         <v>3233</v>
       </c>
     </row>
     <row r="9" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A9" s="33">
+      <c r="A9" s="28">
         <f t="shared" si="0"/>
         <v>8</v>
       </c>
-      <c r="B9" s="28"/>
-      <c r="C9" s="28"/>
-      <c r="D9" s="28"/>
-      <c r="E9" s="28"/>
-      <c r="F9" s="28"/>
-      <c r="G9" s="28"/>
-      <c r="H9" s="28"/>
-      <c r="I9" s="28"/>
+      <c r="B9" s="23"/>
+      <c r="C9" s="23"/>
+      <c r="D9" s="23"/>
+      <c r="E9" s="23"/>
+      <c r="F9" s="23"/>
+      <c r="G9" s="23"/>
+      <c r="H9" s="23"/>
+      <c r="I9" s="23"/>
     </row>
     <row r="10" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A10" s="33">
+      <c r="A10" s="28">
         <f t="shared" si="0"/>
         <v>9</v>
       </c>
-      <c r="B10" s="28"/>
-      <c r="C10" s="28"/>
-      <c r="D10" s="28"/>
-      <c r="E10" s="28"/>
-      <c r="F10" s="28"/>
-      <c r="G10" s="28"/>
-      <c r="H10" s="28"/>
-      <c r="I10" s="28"/>
+      <c r="B10" s="23"/>
+      <c r="C10" s="23"/>
+      <c r="D10" s="23"/>
+      <c r="E10" s="23"/>
+      <c r="F10" s="23"/>
+      <c r="G10" s="23"/>
+      <c r="H10" s="23"/>
+      <c r="I10" s="23"/>
     </row>
     <row r="11" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A11" s="33">
+      <c r="A11" s="28">
         <f t="shared" si="0"/>
         <v>10</v>
       </c>
-      <c r="B11" s="27">
+      <c r="B11" s="22">
         <v>5416</v>
       </c>
-      <c r="C11" s="27">
+      <c r="C11" s="22">
         <v>7409</v>
       </c>
-      <c r="D11" s="27">
+      <c r="D11" s="22">
         <v>9192</v>
       </c>
-      <c r="E11" s="27">
+      <c r="E11" s="22">
         <v>10787</v>
       </c>
-      <c r="F11" s="27">
+      <c r="F11" s="22">
         <v>1269</v>
       </c>
-      <c r="G11" s="27">
+      <c r="G11" s="22">
         <v>3604</v>
       </c>
-      <c r="H11" s="27">
+      <c r="H11" s="22">
         <v>358</v>
       </c>
-      <c r="I11" s="27">
+      <c r="I11" s="22">
         <v>3245</v>
       </c>
     </row>
     <row r="12" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A12" s="33">
+      <c r="A12" s="28">
         <f t="shared" si="0"/>
         <v>11</v>
       </c>
-      <c r="B12" s="27">
+      <c r="B12" s="22">
         <v>5429</v>
       </c>
-      <c r="C12" s="27">
+      <c r="C12" s="22">
         <v>7435</v>
       </c>
-      <c r="D12" s="27">
+      <c r="D12" s="22">
         <v>9195</v>
       </c>
-      <c r="E12" s="27">
+      <c r="E12" s="22">
         <v>10788</v>
       </c>
-      <c r="F12" s="27">
+      <c r="F12" s="22">
         <v>1269</v>
       </c>
-      <c r="G12" s="27">
+      <c r="G12" s="22">
         <v>3609</v>
       </c>
-      <c r="H12" s="27">
+      <c r="H12" s="22">
         <v>358</v>
       </c>
-      <c r="I12" s="27">
+      <c r="I12" s="22">
         <v>3250</v>
       </c>
     </row>
     <row r="13" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A13" s="33">
+      <c r="A13" s="28">
         <f t="shared" si="0"/>
         <v>12</v>
       </c>
-      <c r="B13" s="27">
+      <c r="B13" s="22">
         <v>5458</v>
       </c>
-      <c r="C13" s="27">
+      <c r="C13" s="22">
         <v>7553</v>
       </c>
-      <c r="D13" s="27">
+      <c r="D13" s="22">
         <v>9200</v>
       </c>
-      <c r="E13" s="27">
+      <c r="E13" s="22">
         <v>10789</v>
       </c>
-      <c r="F13" s="27">
+      <c r="F13" s="22">
         <v>1269</v>
       </c>
-      <c r="G13" s="27">
+      <c r="G13" s="22">
         <v>3614</v>
       </c>
-      <c r="H13" s="27">
+      <c r="H13" s="22">
         <v>358</v>
       </c>
-      <c r="I13" s="27">
+      <c r="I13" s="22">
         <v>3255</v>
       </c>
     </row>
     <row r="14" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A14" s="33">
+      <c r="A14" s="28">
         <f t="shared" si="0"/>
         <v>13</v>
       </c>
-      <c r="B14" s="27">
+      <c r="B14" s="22">
         <v>5553</v>
       </c>
-      <c r="C14" s="27">
+      <c r="C14" s="22">
         <v>7571</v>
       </c>
-      <c r="D14" s="27">
+      <c r="D14" s="22">
         <v>9201</v>
       </c>
-      <c r="E14" s="27">
+      <c r="E14" s="22">
         <v>10789</v>
       </c>
-      <c r="F14" s="27">
+      <c r="F14" s="22">
         <v>1269</v>
       </c>
-      <c r="G14" s="28"/>
-      <c r="H14" s="28"/>
-      <c r="I14" s="28"/>
+      <c r="G14" s="23"/>
+      <c r="H14" s="23"/>
+      <c r="I14" s="23"/>
     </row>
     <row r="15" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A15" s="33">
+      <c r="A15" s="28">
         <f t="shared" si="0"/>
         <v>14</v>
       </c>
-      <c r="B15" s="28"/>
-      <c r="C15" s="28"/>
-      <c r="D15" s="28"/>
-      <c r="E15" s="28"/>
-      <c r="F15" s="28"/>
-      <c r="G15" s="28"/>
-      <c r="H15" s="28"/>
-      <c r="I15" s="28"/>
+      <c r="B15" s="23"/>
+      <c r="C15" s="23"/>
+      <c r="D15" s="23"/>
+      <c r="E15" s="23"/>
+      <c r="F15" s="23"/>
+      <c r="G15" s="23"/>
+      <c r="H15" s="23"/>
+      <c r="I15" s="23"/>
     </row>
     <row r="16" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A16" s="33">
+      <c r="A16" s="28">
         <f t="shared" si="0"/>
         <v>15</v>
       </c>
-      <c r="B16" s="27">
+      <c r="B16" s="22">
         <v>5695</v>
       </c>
-      <c r="C16" s="27">
+      <c r="C16" s="22">
         <v>7647</v>
       </c>
-      <c r="D16" s="27">
+      <c r="D16" s="22">
         <v>9209</v>
       </c>
-      <c r="E16" s="27">
+      <c r="E16" s="22">
         <v>10791</v>
       </c>
-      <c r="F16" s="27">
+      <c r="F16" s="22">
         <v>1269</v>
       </c>
-      <c r="G16" s="27">
+      <c r="G16" s="22">
         <v>3627</v>
       </c>
-      <c r="H16" s="27">
+      <c r="H16" s="22">
         <v>360</v>
       </c>
-      <c r="I16" s="27">
+      <c r="I16" s="22">
         <v>3266</v>
       </c>
     </row>
     <row r="17" spans="1:10" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A17" s="33">
+      <c r="A17" s="28">
         <f t="shared" si="0"/>
         <v>16</v>
       </c>
-      <c r="B17" s="28"/>
-      <c r="C17" s="28"/>
-      <c r="D17" s="28"/>
-      <c r="E17" s="28"/>
-      <c r="F17" s="28"/>
-      <c r="G17" s="28"/>
-      <c r="H17" s="28"/>
-      <c r="I17" s="28"/>
+      <c r="B17" s="23"/>
+      <c r="C17" s="23"/>
+      <c r="D17" s="23"/>
+      <c r="E17" s="23"/>
+      <c r="F17" s="23"/>
+      <c r="G17" s="23"/>
+      <c r="H17" s="23"/>
+      <c r="I17" s="23"/>
     </row>
     <row r="18" spans="1:10" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A18" s="33">
+      <c r="A18" s="28">
         <f t="shared" si="0"/>
         <v>17</v>
       </c>
-      <c r="B18" s="28"/>
-      <c r="C18" s="28"/>
-      <c r="D18" s="28"/>
-      <c r="E18" s="28"/>
-      <c r="F18" s="28"/>
-      <c r="G18" s="28"/>
-      <c r="H18" s="28"/>
-      <c r="I18" s="28"/>
+      <c r="B18" s="23"/>
+      <c r="C18" s="23"/>
+      <c r="D18" s="23"/>
+      <c r="E18" s="23"/>
+      <c r="F18" s="23"/>
+      <c r="G18" s="23"/>
+      <c r="H18" s="23"/>
+      <c r="I18" s="23"/>
       <c r="J18" s="3"/>
     </row>
     <row r="19" spans="1:10" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A19" s="33">
+      <c r="A19" s="28">
         <f t="shared" si="0"/>
         <v>18</v>
       </c>
-      <c r="B19" s="28"/>
-      <c r="C19" s="28"/>
-      <c r="D19" s="28"/>
-      <c r="E19" s="28"/>
-      <c r="F19" s="28"/>
-      <c r="G19" s="28"/>
-      <c r="H19" s="28"/>
-      <c r="I19" s="28"/>
+      <c r="B19" s="23"/>
+      <c r="C19" s="23"/>
+      <c r="D19" s="23"/>
+      <c r="E19" s="23"/>
+      <c r="F19" s="23"/>
+      <c r="G19" s="23"/>
+      <c r="H19" s="23"/>
+      <c r="I19" s="23"/>
     </row>
     <row r="20" spans="1:10" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A20" s="33">
+      <c r="A20" s="28">
         <f t="shared" si="0"/>
         <v>19</v>
       </c>
-      <c r="B20" s="28"/>
-      <c r="C20" s="28"/>
-      <c r="D20" s="28"/>
-      <c r="E20" s="28"/>
-      <c r="F20" s="28"/>
-      <c r="G20" s="28"/>
-      <c r="H20" s="28"/>
-      <c r="I20" s="28"/>
+      <c r="B20" s="23"/>
+      <c r="C20" s="23"/>
+      <c r="D20" s="23"/>
+      <c r="E20" s="23"/>
+      <c r="F20" s="23"/>
+      <c r="G20" s="23"/>
+      <c r="H20" s="23"/>
+      <c r="I20" s="23"/>
     </row>
     <row r="21" spans="1:10" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A21" s="33">
+      <c r="A21" s="28">
         <f t="shared" si="0"/>
         <v>20</v>
       </c>
-      <c r="B21" s="28"/>
-      <c r="C21" s="28"/>
-      <c r="D21" s="28"/>
-      <c r="E21" s="28"/>
-      <c r="F21" s="28"/>
-      <c r="G21" s="28"/>
-      <c r="H21" s="28"/>
-      <c r="I21" s="28"/>
+      <c r="B21" s="23"/>
+      <c r="C21" s="23"/>
+      <c r="D21" s="23"/>
+      <c r="E21" s="23"/>
+      <c r="F21" s="23"/>
+      <c r="G21" s="23"/>
+      <c r="H21" s="23"/>
+      <c r="I21" s="23"/>
     </row>
     <row r="22" spans="1:10" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A22" s="33">
+      <c r="A22" s="28">
         <f t="shared" si="0"/>
         <v>21</v>
       </c>
-      <c r="B22" s="28"/>
-      <c r="C22" s="28"/>
-      <c r="D22" s="28"/>
-      <c r="E22" s="28"/>
-      <c r="F22" s="28"/>
-      <c r="G22" s="28"/>
-      <c r="H22" s="28"/>
-      <c r="I22" s="28"/>
+      <c r="B22" s="23"/>
+      <c r="C22" s="23"/>
+      <c r="D22" s="23"/>
+      <c r="E22" s="23"/>
+      <c r="F22" s="23"/>
+      <c r="G22" s="23"/>
+      <c r="H22" s="23"/>
+      <c r="I22" s="23"/>
     </row>
     <row r="23" spans="1:10" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A23" s="33">
+      <c r="A23" s="28">
         <f t="shared" si="0"/>
         <v>22</v>
       </c>
-      <c r="B23" s="28"/>
-      <c r="C23" s="28"/>
-      <c r="D23" s="28"/>
-      <c r="E23" s="28"/>
-      <c r="F23" s="28"/>
-      <c r="G23" s="28"/>
-      <c r="H23" s="28"/>
-      <c r="I23" s="28"/>
+      <c r="B23" s="23"/>
+      <c r="C23" s="23"/>
+      <c r="D23" s="23"/>
+      <c r="E23" s="23"/>
+      <c r="F23" s="23"/>
+      <c r="G23" s="23"/>
+      <c r="H23" s="23"/>
+      <c r="I23" s="23"/>
     </row>
     <row r="24" spans="1:10" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A24" s="33">
+      <c r="A24" s="28">
         <f t="shared" si="0"/>
         <v>23</v>
       </c>
-      <c r="B24" s="28"/>
-      <c r="C24" s="28"/>
-      <c r="D24" s="28"/>
-      <c r="E24" s="28"/>
-      <c r="F24" s="28"/>
-      <c r="G24" s="28"/>
-      <c r="H24" s="28"/>
-      <c r="I24" s="28"/>
+      <c r="B24" s="23"/>
+      <c r="C24" s="23"/>
+      <c r="D24" s="23"/>
+      <c r="E24" s="23"/>
+      <c r="F24" s="23"/>
+      <c r="G24" s="23"/>
+      <c r="H24" s="23"/>
+      <c r="I24" s="23"/>
     </row>
     <row r="25" spans="1:10" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A25" s="33">
+      <c r="A25" s="28">
         <f t="shared" si="0"/>
         <v>24</v>
       </c>
-      <c r="B25" s="28"/>
-      <c r="C25" s="28"/>
-      <c r="D25" s="28"/>
-      <c r="E25" s="28"/>
-      <c r="F25" s="28"/>
-      <c r="G25" s="28"/>
-      <c r="H25" s="28"/>
-      <c r="I25" s="28"/>
+      <c r="B25" s="23"/>
+      <c r="C25" s="23"/>
+      <c r="D25" s="23"/>
+      <c r="E25" s="23"/>
+      <c r="F25" s="23"/>
+      <c r="G25" s="23"/>
+      <c r="H25" s="23"/>
+      <c r="I25" s="23"/>
     </row>
     <row r="26" spans="1:10" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A26" s="33">
+      <c r="A26" s="28">
         <f t="shared" si="0"/>
         <v>25</v>
       </c>
-      <c r="B26" s="28"/>
-      <c r="C26" s="28"/>
-      <c r="D26" s="28"/>
-      <c r="E26" s="28"/>
-      <c r="F26" s="28"/>
-      <c r="G26" s="28"/>
-      <c r="H26" s="28"/>
-      <c r="I26" s="28"/>
+      <c r="B26" s="23"/>
+      <c r="C26" s="23"/>
+      <c r="D26" s="23"/>
+      <c r="E26" s="23"/>
+      <c r="F26" s="23"/>
+      <c r="G26" s="23"/>
+      <c r="H26" s="23"/>
+      <c r="I26" s="23"/>
     </row>
     <row r="27" spans="1:10" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A27" s="33">
+      <c r="A27" s="28">
         <f t="shared" si="0"/>
         <v>26</v>
       </c>
-      <c r="B27" s="28"/>
-      <c r="C27" s="28"/>
-      <c r="D27" s="28"/>
-      <c r="E27" s="28"/>
-      <c r="F27" s="28"/>
-      <c r="G27" s="28"/>
-      <c r="H27" s="28"/>
-      <c r="I27" s="28"/>
+      <c r="B27" s="23"/>
+      <c r="C27" s="23"/>
+      <c r="D27" s="23"/>
+      <c r="E27" s="23"/>
+      <c r="F27" s="23"/>
+      <c r="G27" s="23"/>
+      <c r="H27" s="23"/>
+      <c r="I27" s="23"/>
     </row>
     <row r="28" spans="1:10" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A28" s="33">
+      <c r="A28" s="28">
         <f t="shared" si="0"/>
         <v>27</v>
       </c>
-      <c r="B28" s="28"/>
-      <c r="C28" s="28"/>
-      <c r="D28" s="28"/>
-      <c r="E28" s="28"/>
-      <c r="F28" s="28"/>
-      <c r="G28" s="28"/>
-      <c r="H28" s="28"/>
-      <c r="I28" s="28"/>
+      <c r="B28" s="23"/>
+      <c r="C28" s="23"/>
+      <c r="D28" s="23"/>
+      <c r="E28" s="23"/>
+      <c r="F28" s="23"/>
+      <c r="G28" s="23"/>
+      <c r="H28" s="23"/>
+      <c r="I28" s="23"/>
     </row>
     <row r="29" spans="1:10" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A29" s="33">
+      <c r="A29" s="28">
         <f t="shared" si="0"/>
         <v>28</v>
       </c>
-      <c r="B29" s="28"/>
-      <c r="C29" s="28"/>
-      <c r="D29" s="28"/>
-      <c r="E29" s="28"/>
-      <c r="F29" s="28"/>
-      <c r="G29" s="28"/>
-      <c r="H29" s="28"/>
-      <c r="I29" s="28"/>
+      <c r="B29" s="23"/>
+      <c r="C29" s="23"/>
+      <c r="D29" s="23"/>
+      <c r="E29" s="23"/>
+      <c r="F29" s="23"/>
+      <c r="G29" s="23"/>
+      <c r="H29" s="23"/>
+      <c r="I29" s="23"/>
     </row>
     <row r="30" spans="1:10" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A30" s="33">
+      <c r="A30" s="28">
         <f t="shared" si="0"/>
         <v>29</v>
       </c>
-      <c r="B30" s="27">
+      <c r="B30" s="22">
         <v>6351</v>
       </c>
-      <c r="C30" s="27">
+      <c r="C30" s="22">
         <v>8113</v>
       </c>
-      <c r="D30" s="27">
+      <c r="D30" s="22">
         <v>9260</v>
       </c>
-      <c r="E30" s="27">
+      <c r="E30" s="22">
         <v>11801</v>
       </c>
-      <c r="F30" s="27">
+      <c r="F30" s="22">
         <v>1270</v>
       </c>
-      <c r="G30" s="27">
+      <c r="G30" s="22">
         <v>3684</v>
       </c>
-      <c r="H30" s="27">
+      <c r="H30" s="22">
         <v>367</v>
       </c>
-      <c r="I30" s="27">
+      <c r="I30" s="22">
         <v>3316</v>
       </c>
     </row>
     <row r="31" spans="1:10" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A31" s="33">
+      <c r="A31" s="28">
         <f t="shared" si="0"/>
         <v>30</v>
       </c>
-      <c r="B31" s="27">
+      <c r="B31" s="22">
         <v>6375</v>
       </c>
-      <c r="C31" s="27">
+      <c r="C31" s="22">
         <v>8136</v>
       </c>
-      <c r="D31" s="27">
+      <c r="D31" s="22">
         <v>9263</v>
       </c>
-      <c r="E31" s="27">
+      <c r="E31" s="22">
         <v>11802</v>
       </c>
-      <c r="F31" s="27">
+      <c r="F31" s="22">
         <v>1270</v>
       </c>
-      <c r="G31" s="27">
+      <c r="G31" s="22">
         <v>3687</v>
       </c>
-      <c r="H31" s="27">
+      <c r="H31" s="22">
         <v>368</v>
       </c>
-      <c r="I31" s="27">
+      <c r="I31" s="22">
         <v>3318</v>
       </c>
     </row>
     <row r="32" spans="1:10" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A32" s="33">
+      <c r="A32" s="28">
         <f t="shared" si="0"/>
         <v>31</v>
       </c>
-      <c r="B32" s="34">
+      <c r="B32" s="29">
         <v>6407</v>
       </c>
-      <c r="C32" s="34">
+      <c r="C32" s="29">
         <v>8185</v>
       </c>
-      <c r="D32" s="34">
+      <c r="D32" s="29">
         <v>9265</v>
       </c>
-      <c r="E32" s="34">
+      <c r="E32" s="29">
         <v>11802</v>
       </c>
-      <c r="F32" s="34">
+      <c r="F32" s="29">
         <v>1271</v>
       </c>
-      <c r="G32" s="34">
+      <c r="G32" s="29">
         <v>3691</v>
       </c>
-      <c r="H32" s="34">
+      <c r="H32" s="29">
         <v>369</v>
       </c>
-      <c r="I32" s="34">
+      <c r="I32" s="29">
         <v>3321</v>
       </c>
     </row>
     <row r="33" spans="1:9" ht="12.75" x14ac:dyDescent="0.2"/>
     <row r="35" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A35" s="4"/>
-      <c r="B35" s="21"/>
-      <c r="C35" s="20"/>
-      <c r="D35" s="20"/>
-      <c r="E35" s="20"/>
-      <c r="F35" s="20"/>
-      <c r="G35" s="20"/>
-      <c r="H35" s="20"/>
-      <c r="I35" s="20"/>
+      <c r="B35" s="32"/>
+      <c r="C35" s="31"/>
+      <c r="D35" s="31"/>
+      <c r="E35" s="31"/>
+      <c r="F35" s="31"/>
+      <c r="G35" s="31"/>
+      <c r="H35" s="31"/>
+      <c r="I35" s="31"/>
     </row>
     <row r="36" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A36" s="4"/>
@@ -13827,15 +13832,15 @@
       <c r="I69" s="4"/>
     </row>
     <row r="70" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A70" s="21"/>
-      <c r="B70" s="20"/>
-      <c r="C70" s="20"/>
-      <c r="D70" s="20"/>
-      <c r="E70" s="20"/>
-      <c r="F70" s="20"/>
-      <c r="G70" s="20"/>
-      <c r="H70" s="20"/>
-      <c r="I70" s="20"/>
+      <c r="A70" s="32"/>
+      <c r="B70" s="31"/>
+      <c r="C70" s="31"/>
+      <c r="D70" s="31"/>
+      <c r="E70" s="31"/>
+      <c r="F70" s="31"/>
+      <c r="G70" s="31"/>
+      <c r="H70" s="31"/>
+      <c r="I70" s="31"/>
     </row>
     <row r="71" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A71" s="4"/>
@@ -13860,15 +13865,15 @@
       <c r="I72" s="6"/>
     </row>
     <row r="75" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A75" s="19"/>
-      <c r="B75" s="20"/>
-      <c r="C75" s="20"/>
-      <c r="D75" s="20"/>
-      <c r="E75" s="20"/>
-      <c r="F75" s="20"/>
-      <c r="G75" s="20"/>
-      <c r="H75" s="20"/>
-      <c r="I75" s="20"/>
+      <c r="A75" s="30"/>
+      <c r="B75" s="31"/>
+      <c r="C75" s="31"/>
+      <c r="D75" s="31"/>
+      <c r="E75" s="31"/>
+      <c r="F75" s="31"/>
+      <c r="G75" s="31"/>
+      <c r="H75" s="31"/>
+      <c r="I75" s="31"/>
     </row>
     <row r="76" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A76" s="4"/>
@@ -13904,15 +13909,15 @@
       <c r="I78" s="8"/>
     </row>
     <row r="79" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A79" s="22"/>
-      <c r="B79" s="20"/>
-      <c r="C79" s="20"/>
-      <c r="D79" s="20"/>
-      <c r="E79" s="20"/>
-      <c r="F79" s="20"/>
-      <c r="G79" s="20"/>
-      <c r="H79" s="20"/>
-      <c r="I79" s="20"/>
+      <c r="A79" s="33"/>
+      <c r="B79" s="31"/>
+      <c r="C79" s="31"/>
+      <c r="D79" s="31"/>
+      <c r="E79" s="31"/>
+      <c r="F79" s="31"/>
+      <c r="G79" s="31"/>
+      <c r="H79" s="31"/>
+      <c r="I79" s="31"/>
     </row>
     <row r="80" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A80" s="4"/>
@@ -13948,15 +13953,15 @@
       <c r="B85" s="6"/>
     </row>
     <row r="87" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A87" s="19"/>
-      <c r="B87" s="20"/>
-      <c r="C87" s="20"/>
-      <c r="D87" s="20"/>
-      <c r="E87" s="20"/>
-      <c r="F87" s="20"/>
-      <c r="G87" s="20"/>
-      <c r="H87" s="20"/>
-      <c r="I87" s="20"/>
+      <c r="A87" s="30"/>
+      <c r="B87" s="31"/>
+      <c r="C87" s="31"/>
+      <c r="D87" s="31"/>
+      <c r="E87" s="31"/>
+      <c r="F87" s="31"/>
+      <c r="G87" s="31"/>
+      <c r="H87" s="31"/>
+      <c r="I87" s="31"/>
     </row>
     <row r="88" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A88" s="4"/>
@@ -14059,15 +14064,15 @@
       <c r="B98" s="9"/>
     </row>
     <row r="100" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A100" s="21"/>
-      <c r="B100" s="20"/>
-      <c r="C100" s="20"/>
-      <c r="D100" s="20"/>
-      <c r="E100" s="20"/>
-      <c r="F100" s="20"/>
-      <c r="G100" s="20"/>
-      <c r="H100" s="20"/>
-      <c r="I100" s="20"/>
+      <c r="A100" s="32"/>
+      <c r="B100" s="31"/>
+      <c r="C100" s="31"/>
+      <c r="D100" s="31"/>
+      <c r="E100" s="31"/>
+      <c r="F100" s="31"/>
+      <c r="G100" s="31"/>
+      <c r="H100" s="31"/>
+      <c r="I100" s="31"/>
     </row>
     <row r="101" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A101" s="4"/>
@@ -15421,15 +15426,15 @@
       <c r="I68" s="4"/>
     </row>
     <row r="69" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A69" s="21"/>
-      <c r="B69" s="20"/>
-      <c r="C69" s="20"/>
-      <c r="D69" s="20"/>
-      <c r="E69" s="20"/>
-      <c r="F69" s="20"/>
-      <c r="G69" s="20"/>
-      <c r="H69" s="20"/>
-      <c r="I69" s="20"/>
+      <c r="A69" s="32"/>
+      <c r="B69" s="31"/>
+      <c r="C69" s="31"/>
+      <c r="D69" s="31"/>
+      <c r="E69" s="31"/>
+      <c r="F69" s="31"/>
+      <c r="G69" s="31"/>
+      <c r="H69" s="31"/>
+      <c r="I69" s="31"/>
     </row>
     <row r="70" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A70" s="4"/>
@@ -15454,15 +15459,15 @@
       <c r="I71" s="6"/>
     </row>
     <row r="74" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A74" s="19"/>
-      <c r="B74" s="20"/>
-      <c r="C74" s="20"/>
-      <c r="D74" s="20"/>
-      <c r="E74" s="20"/>
-      <c r="F74" s="20"/>
-      <c r="G74" s="20"/>
-      <c r="H74" s="20"/>
-      <c r="I74" s="20"/>
+      <c r="A74" s="30"/>
+      <c r="B74" s="31"/>
+      <c r="C74" s="31"/>
+      <c r="D74" s="31"/>
+      <c r="E74" s="31"/>
+      <c r="F74" s="31"/>
+      <c r="G74" s="31"/>
+      <c r="H74" s="31"/>
+      <c r="I74" s="31"/>
     </row>
     <row r="75" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A75" s="4"/>
@@ -15498,15 +15503,15 @@
       <c r="I77" s="8"/>
     </row>
     <row r="78" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A78" s="22"/>
-      <c r="B78" s="20"/>
-      <c r="C78" s="20"/>
-      <c r="D78" s="20"/>
-      <c r="E78" s="20"/>
-      <c r="F78" s="20"/>
-      <c r="G78" s="20"/>
-      <c r="H78" s="20"/>
-      <c r="I78" s="20"/>
+      <c r="A78" s="33"/>
+      <c r="B78" s="31"/>
+      <c r="C78" s="31"/>
+      <c r="D78" s="31"/>
+      <c r="E78" s="31"/>
+      <c r="F78" s="31"/>
+      <c r="G78" s="31"/>
+      <c r="H78" s="31"/>
+      <c r="I78" s="31"/>
     </row>
     <row r="79" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A79" s="4"/>
@@ -15542,15 +15547,15 @@
       <c r="B84" s="6"/>
     </row>
     <row r="86" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A86" s="19"/>
-      <c r="B86" s="20"/>
-      <c r="C86" s="20"/>
-      <c r="D86" s="20"/>
-      <c r="E86" s="20"/>
-      <c r="F86" s="20"/>
-      <c r="G86" s="20"/>
-      <c r="H86" s="20"/>
-      <c r="I86" s="20"/>
+      <c r="A86" s="30"/>
+      <c r="B86" s="31"/>
+      <c r="C86" s="31"/>
+      <c r="D86" s="31"/>
+      <c r="E86" s="31"/>
+      <c r="F86" s="31"/>
+      <c r="G86" s="31"/>
+      <c r="H86" s="31"/>
+      <c r="I86" s="31"/>
     </row>
     <row r="87" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A87" s="4"/>
@@ -15653,15 +15658,15 @@
       <c r="B97" s="9"/>
     </row>
     <row r="99" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A99" s="21"/>
-      <c r="B99" s="20"/>
-      <c r="C99" s="20"/>
-      <c r="D99" s="20"/>
-      <c r="E99" s="20"/>
-      <c r="F99" s="20"/>
-      <c r="G99" s="20"/>
-      <c r="H99" s="20"/>
-      <c r="I99" s="20"/>
+      <c r="A99" s="32"/>
+      <c r="B99" s="31"/>
+      <c r="C99" s="31"/>
+      <c r="D99" s="31"/>
+      <c r="E99" s="31"/>
+      <c r="F99" s="31"/>
+      <c r="G99" s="31"/>
+      <c r="H99" s="31"/>
+      <c r="I99" s="31"/>
     </row>
     <row r="100" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A100" s="4"/>

--- a/medicao_energia.xlsx
+++ b/medicao_energia.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\sgt.marquezzini\Documents\GitHub\Dashboardenergia\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{20C22391-3977-4BAC-BAFD-6185D1EF86D5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B939A4BD-AE5A-40F3-9312-B19D0A1CB5F4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="19080" yWindow="-120" windowWidth="19440" windowHeight="15000" firstSheet="5" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="19440" windowHeight="15000" firstSheet="5" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="DEZEMBRO" sheetId="23" r:id="rId1"/>
@@ -262,7 +262,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="34">
+  <cellXfs count="35">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -330,9 +330,6 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -353,6 +350,12 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1110,14 +1113,14 @@
     </row>
     <row r="34" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A34" s="4"/>
-      <c r="B34" s="32"/>
-      <c r="C34" s="31"/>
-      <c r="D34" s="31"/>
-      <c r="E34" s="31"/>
-      <c r="F34" s="31"/>
-      <c r="G34" s="31"/>
-      <c r="H34" s="31"/>
-      <c r="I34" s="31"/>
+      <c r="B34" s="31"/>
+      <c r="C34" s="30"/>
+      <c r="D34" s="30"/>
+      <c r="E34" s="30"/>
+      <c r="F34" s="30"/>
+      <c r="G34" s="30"/>
+      <c r="H34" s="30"/>
+      <c r="I34" s="30"/>
     </row>
     <row r="35" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A35" s="4"/>
@@ -1495,15 +1498,15 @@
       <c r="I68" s="4"/>
     </row>
     <row r="69" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A69" s="32"/>
-      <c r="B69" s="31"/>
-      <c r="C69" s="31"/>
-      <c r="D69" s="31"/>
-      <c r="E69" s="31"/>
-      <c r="F69" s="31"/>
-      <c r="G69" s="31"/>
-      <c r="H69" s="31"/>
-      <c r="I69" s="31"/>
+      <c r="A69" s="31"/>
+      <c r="B69" s="30"/>
+      <c r="C69" s="30"/>
+      <c r="D69" s="30"/>
+      <c r="E69" s="30"/>
+      <c r="F69" s="30"/>
+      <c r="G69" s="30"/>
+      <c r="H69" s="30"/>
+      <c r="I69" s="30"/>
     </row>
     <row r="70" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A70" s="4"/>
@@ -1528,15 +1531,15 @@
       <c r="I71" s="6"/>
     </row>
     <row r="74" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A74" s="30"/>
-      <c r="B74" s="31"/>
-      <c r="C74" s="31"/>
-      <c r="D74" s="31"/>
-      <c r="E74" s="31"/>
-      <c r="F74" s="31"/>
-      <c r="G74" s="31"/>
-      <c r="H74" s="31"/>
-      <c r="I74" s="31"/>
+      <c r="A74" s="29"/>
+      <c r="B74" s="30"/>
+      <c r="C74" s="30"/>
+      <c r="D74" s="30"/>
+      <c r="E74" s="30"/>
+      <c r="F74" s="30"/>
+      <c r="G74" s="30"/>
+      <c r="H74" s="30"/>
+      <c r="I74" s="30"/>
     </row>
     <row r="75" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A75" s="4"/>
@@ -1572,15 +1575,15 @@
       <c r="I77" s="8"/>
     </row>
     <row r="78" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A78" s="33"/>
-      <c r="B78" s="31"/>
-      <c r="C78" s="31"/>
-      <c r="D78" s="31"/>
-      <c r="E78" s="31"/>
-      <c r="F78" s="31"/>
-      <c r="G78" s="31"/>
-      <c r="H78" s="31"/>
-      <c r="I78" s="31"/>
+      <c r="A78" s="32"/>
+      <c r="B78" s="30"/>
+      <c r="C78" s="30"/>
+      <c r="D78" s="30"/>
+      <c r="E78" s="30"/>
+      <c r="F78" s="30"/>
+      <c r="G78" s="30"/>
+      <c r="H78" s="30"/>
+      <c r="I78" s="30"/>
     </row>
     <row r="79" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A79" s="4"/>
@@ -1616,15 +1619,15 @@
       <c r="B84" s="6"/>
     </row>
     <row r="86" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A86" s="30"/>
-      <c r="B86" s="31"/>
-      <c r="C86" s="31"/>
-      <c r="D86" s="31"/>
-      <c r="E86" s="31"/>
-      <c r="F86" s="31"/>
-      <c r="G86" s="31"/>
-      <c r="H86" s="31"/>
-      <c r="I86" s="31"/>
+      <c r="A86" s="29"/>
+      <c r="B86" s="30"/>
+      <c r="C86" s="30"/>
+      <c r="D86" s="30"/>
+      <c r="E86" s="30"/>
+      <c r="F86" s="30"/>
+      <c r="G86" s="30"/>
+      <c r="H86" s="30"/>
+      <c r="I86" s="30"/>
     </row>
     <row r="87" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A87" s="4"/>
@@ -1727,15 +1730,15 @@
       <c r="B97" s="9"/>
     </row>
     <row r="99" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A99" s="32"/>
-      <c r="B99" s="31"/>
-      <c r="C99" s="31"/>
-      <c r="D99" s="31"/>
-      <c r="E99" s="31"/>
-      <c r="F99" s="31"/>
-      <c r="G99" s="31"/>
-      <c r="H99" s="31"/>
-      <c r="I99" s="31"/>
+      <c r="A99" s="31"/>
+      <c r="B99" s="30"/>
+      <c r="C99" s="30"/>
+      <c r="D99" s="30"/>
+      <c r="E99" s="30"/>
+      <c r="F99" s="30"/>
+      <c r="G99" s="30"/>
+      <c r="H99" s="30"/>
+      <c r="I99" s="30"/>
     </row>
     <row r="100" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A100" s="4"/>
@@ -2703,14 +2706,14 @@
     <row r="33" spans="1:9" ht="12.75" x14ac:dyDescent="0.2"/>
     <row r="35" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A35" s="4"/>
-      <c r="B35" s="32"/>
-      <c r="C35" s="31"/>
-      <c r="D35" s="31"/>
-      <c r="E35" s="31"/>
-      <c r="F35" s="31"/>
-      <c r="G35" s="31"/>
-      <c r="H35" s="31"/>
-      <c r="I35" s="31"/>
+      <c r="B35" s="31"/>
+      <c r="C35" s="30"/>
+      <c r="D35" s="30"/>
+      <c r="E35" s="30"/>
+      <c r="F35" s="30"/>
+      <c r="G35" s="30"/>
+      <c r="H35" s="30"/>
+      <c r="I35" s="30"/>
     </row>
     <row r="36" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A36" s="4"/>
@@ -3087,15 +3090,15 @@
       <c r="I69" s="4"/>
     </row>
     <row r="70" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A70" s="32"/>
-      <c r="B70" s="31"/>
-      <c r="C70" s="31"/>
-      <c r="D70" s="31"/>
-      <c r="E70" s="31"/>
-      <c r="F70" s="31"/>
-      <c r="G70" s="31"/>
-      <c r="H70" s="31"/>
-      <c r="I70" s="31"/>
+      <c r="A70" s="31"/>
+      <c r="B70" s="30"/>
+      <c r="C70" s="30"/>
+      <c r="D70" s="30"/>
+      <c r="E70" s="30"/>
+      <c r="F70" s="30"/>
+      <c r="G70" s="30"/>
+      <c r="H70" s="30"/>
+      <c r="I70" s="30"/>
     </row>
     <row r="71" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A71" s="4"/>
@@ -3120,15 +3123,15 @@
       <c r="I72" s="6"/>
     </row>
     <row r="75" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A75" s="30"/>
-      <c r="B75" s="31"/>
-      <c r="C75" s="31"/>
-      <c r="D75" s="31"/>
-      <c r="E75" s="31"/>
-      <c r="F75" s="31"/>
-      <c r="G75" s="31"/>
-      <c r="H75" s="31"/>
-      <c r="I75" s="31"/>
+      <c r="A75" s="29"/>
+      <c r="B75" s="30"/>
+      <c r="C75" s="30"/>
+      <c r="D75" s="30"/>
+      <c r="E75" s="30"/>
+      <c r="F75" s="30"/>
+      <c r="G75" s="30"/>
+      <c r="H75" s="30"/>
+      <c r="I75" s="30"/>
     </row>
     <row r="76" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A76" s="4"/>
@@ -3164,15 +3167,15 @@
       <c r="I78" s="8"/>
     </row>
     <row r="79" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A79" s="33"/>
-      <c r="B79" s="31"/>
-      <c r="C79" s="31"/>
-      <c r="D79" s="31"/>
-      <c r="E79" s="31"/>
-      <c r="F79" s="31"/>
-      <c r="G79" s="31"/>
-      <c r="H79" s="31"/>
-      <c r="I79" s="31"/>
+      <c r="A79" s="32"/>
+      <c r="B79" s="30"/>
+      <c r="C79" s="30"/>
+      <c r="D79" s="30"/>
+      <c r="E79" s="30"/>
+      <c r="F79" s="30"/>
+      <c r="G79" s="30"/>
+      <c r="H79" s="30"/>
+      <c r="I79" s="30"/>
     </row>
     <row r="80" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A80" s="4"/>
@@ -3208,15 +3211,15 @@
       <c r="B85" s="6"/>
     </row>
     <row r="87" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A87" s="30"/>
-      <c r="B87" s="31"/>
-      <c r="C87" s="31"/>
-      <c r="D87" s="31"/>
-      <c r="E87" s="31"/>
-      <c r="F87" s="31"/>
-      <c r="G87" s="31"/>
-      <c r="H87" s="31"/>
-      <c r="I87" s="31"/>
+      <c r="A87" s="29"/>
+      <c r="B87" s="30"/>
+      <c r="C87" s="30"/>
+      <c r="D87" s="30"/>
+      <c r="E87" s="30"/>
+      <c r="F87" s="30"/>
+      <c r="G87" s="30"/>
+      <c r="H87" s="30"/>
+      <c r="I87" s="30"/>
     </row>
     <row r="88" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A88" s="4"/>
@@ -3319,15 +3322,15 @@
       <c r="B98" s="9"/>
     </row>
     <row r="100" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A100" s="32"/>
-      <c r="B100" s="31"/>
-      <c r="C100" s="31"/>
-      <c r="D100" s="31"/>
-      <c r="E100" s="31"/>
-      <c r="F100" s="31"/>
-      <c r="G100" s="31"/>
-      <c r="H100" s="31"/>
-      <c r="I100" s="31"/>
+      <c r="A100" s="31"/>
+      <c r="B100" s="30"/>
+      <c r="C100" s="30"/>
+      <c r="D100" s="30"/>
+      <c r="E100" s="30"/>
+      <c r="F100" s="30"/>
+      <c r="G100" s="30"/>
+      <c r="H100" s="30"/>
+      <c r="I100" s="30"/>
     </row>
     <row r="101" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A101" s="4"/>
@@ -3847,14 +3850,14 @@
     <row r="33" spans="1:9" ht="12.75" x14ac:dyDescent="0.2"/>
     <row r="35" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A35" s="4"/>
-      <c r="B35" s="32"/>
-      <c r="C35" s="31"/>
-      <c r="D35" s="31"/>
-      <c r="E35" s="31"/>
-      <c r="F35" s="31"/>
-      <c r="G35" s="31"/>
-      <c r="H35" s="31"/>
-      <c r="I35" s="31"/>
+      <c r="B35" s="31"/>
+      <c r="C35" s="30"/>
+      <c r="D35" s="30"/>
+      <c r="E35" s="30"/>
+      <c r="F35" s="30"/>
+      <c r="G35" s="30"/>
+      <c r="H35" s="30"/>
+      <c r="I35" s="30"/>
     </row>
     <row r="36" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A36" s="4"/>
@@ -4231,15 +4234,15 @@
       <c r="I69" s="4"/>
     </row>
     <row r="70" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A70" s="32"/>
-      <c r="B70" s="31"/>
-      <c r="C70" s="31"/>
-      <c r="D70" s="31"/>
-      <c r="E70" s="31"/>
-      <c r="F70" s="31"/>
-      <c r="G70" s="31"/>
-      <c r="H70" s="31"/>
-      <c r="I70" s="31"/>
+      <c r="A70" s="31"/>
+      <c r="B70" s="30"/>
+      <c r="C70" s="30"/>
+      <c r="D70" s="30"/>
+      <c r="E70" s="30"/>
+      <c r="F70" s="30"/>
+      <c r="G70" s="30"/>
+      <c r="H70" s="30"/>
+      <c r="I70" s="30"/>
     </row>
     <row r="71" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A71" s="4"/>
@@ -4264,15 +4267,15 @@
       <c r="I72" s="6"/>
     </row>
     <row r="75" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A75" s="30"/>
-      <c r="B75" s="31"/>
-      <c r="C75" s="31"/>
-      <c r="D75" s="31"/>
-      <c r="E75" s="31"/>
-      <c r="F75" s="31"/>
-      <c r="G75" s="31"/>
-      <c r="H75" s="31"/>
-      <c r="I75" s="31"/>
+      <c r="A75" s="29"/>
+      <c r="B75" s="30"/>
+      <c r="C75" s="30"/>
+      <c r="D75" s="30"/>
+      <c r="E75" s="30"/>
+      <c r="F75" s="30"/>
+      <c r="G75" s="30"/>
+      <c r="H75" s="30"/>
+      <c r="I75" s="30"/>
     </row>
     <row r="76" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A76" s="4"/>
@@ -4308,15 +4311,15 @@
       <c r="I78" s="8"/>
     </row>
     <row r="79" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A79" s="33"/>
-      <c r="B79" s="31"/>
-      <c r="C79" s="31"/>
-      <c r="D79" s="31"/>
-      <c r="E79" s="31"/>
-      <c r="F79" s="31"/>
-      <c r="G79" s="31"/>
-      <c r="H79" s="31"/>
-      <c r="I79" s="31"/>
+      <c r="A79" s="32"/>
+      <c r="B79" s="30"/>
+      <c r="C79" s="30"/>
+      <c r="D79" s="30"/>
+      <c r="E79" s="30"/>
+      <c r="F79" s="30"/>
+      <c r="G79" s="30"/>
+      <c r="H79" s="30"/>
+      <c r="I79" s="30"/>
     </row>
     <row r="80" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A80" s="4"/>
@@ -4352,15 +4355,15 @@
       <c r="B85" s="6"/>
     </row>
     <row r="87" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A87" s="30"/>
-      <c r="B87" s="31"/>
-      <c r="C87" s="31"/>
-      <c r="D87" s="31"/>
-      <c r="E87" s="31"/>
-      <c r="F87" s="31"/>
-      <c r="G87" s="31"/>
-      <c r="H87" s="31"/>
-      <c r="I87" s="31"/>
+      <c r="A87" s="29"/>
+      <c r="B87" s="30"/>
+      <c r="C87" s="30"/>
+      <c r="D87" s="30"/>
+      <c r="E87" s="30"/>
+      <c r="F87" s="30"/>
+      <c r="G87" s="30"/>
+      <c r="H87" s="30"/>
+      <c r="I87" s="30"/>
     </row>
     <row r="88" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A88" s="4"/>
@@ -4463,15 +4466,15 @@
       <c r="B98" s="9"/>
     </row>
     <row r="100" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A100" s="32"/>
-      <c r="B100" s="31"/>
-      <c r="C100" s="31"/>
-      <c r="D100" s="31"/>
-      <c r="E100" s="31"/>
-      <c r="F100" s="31"/>
-      <c r="G100" s="31"/>
-      <c r="H100" s="31"/>
-      <c r="I100" s="31"/>
+      <c r="A100" s="31"/>
+      <c r="B100" s="30"/>
+      <c r="C100" s="30"/>
+      <c r="D100" s="30"/>
+      <c r="E100" s="30"/>
+      <c r="F100" s="30"/>
+      <c r="G100" s="30"/>
+      <c r="H100" s="30"/>
+      <c r="I100" s="30"/>
     </row>
     <row r="101" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A101" s="4"/>
@@ -4990,14 +4993,14 @@
     <row r="33" spans="1:9" ht="12.75" x14ac:dyDescent="0.2"/>
     <row r="35" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A35" s="4"/>
-      <c r="B35" s="32"/>
-      <c r="C35" s="31"/>
-      <c r="D35" s="31"/>
-      <c r="E35" s="31"/>
-      <c r="F35" s="31"/>
-      <c r="G35" s="31"/>
-      <c r="H35" s="31"/>
-      <c r="I35" s="31"/>
+      <c r="B35" s="31"/>
+      <c r="C35" s="30"/>
+      <c r="D35" s="30"/>
+      <c r="E35" s="30"/>
+      <c r="F35" s="30"/>
+      <c r="G35" s="30"/>
+      <c r="H35" s="30"/>
+      <c r="I35" s="30"/>
     </row>
     <row r="36" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A36" s="4"/>
@@ -5374,15 +5377,15 @@
       <c r="I69" s="4"/>
     </row>
     <row r="70" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A70" s="32"/>
-      <c r="B70" s="31"/>
-      <c r="C70" s="31"/>
-      <c r="D70" s="31"/>
-      <c r="E70" s="31"/>
-      <c r="F70" s="31"/>
-      <c r="G70" s="31"/>
-      <c r="H70" s="31"/>
-      <c r="I70" s="31"/>
+      <c r="A70" s="31"/>
+      <c r="B70" s="30"/>
+      <c r="C70" s="30"/>
+      <c r="D70" s="30"/>
+      <c r="E70" s="30"/>
+      <c r="F70" s="30"/>
+      <c r="G70" s="30"/>
+      <c r="H70" s="30"/>
+      <c r="I70" s="30"/>
     </row>
     <row r="71" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A71" s="4"/>
@@ -5407,15 +5410,15 @@
       <c r="I72" s="6"/>
     </row>
     <row r="75" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A75" s="30"/>
-      <c r="B75" s="31"/>
-      <c r="C75" s="31"/>
-      <c r="D75" s="31"/>
-      <c r="E75" s="31"/>
-      <c r="F75" s="31"/>
-      <c r="G75" s="31"/>
-      <c r="H75" s="31"/>
-      <c r="I75" s="31"/>
+      <c r="A75" s="29"/>
+      <c r="B75" s="30"/>
+      <c r="C75" s="30"/>
+      <c r="D75" s="30"/>
+      <c r="E75" s="30"/>
+      <c r="F75" s="30"/>
+      <c r="G75" s="30"/>
+      <c r="H75" s="30"/>
+      <c r="I75" s="30"/>
     </row>
     <row r="76" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A76" s="4"/>
@@ -5451,15 +5454,15 @@
       <c r="I78" s="8"/>
     </row>
     <row r="79" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A79" s="33"/>
-      <c r="B79" s="31"/>
-      <c r="C79" s="31"/>
-      <c r="D79" s="31"/>
-      <c r="E79" s="31"/>
-      <c r="F79" s="31"/>
-      <c r="G79" s="31"/>
-      <c r="H79" s="31"/>
-      <c r="I79" s="31"/>
+      <c r="A79" s="32"/>
+      <c r="B79" s="30"/>
+      <c r="C79" s="30"/>
+      <c r="D79" s="30"/>
+      <c r="E79" s="30"/>
+      <c r="F79" s="30"/>
+      <c r="G79" s="30"/>
+      <c r="H79" s="30"/>
+      <c r="I79" s="30"/>
     </row>
     <row r="80" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A80" s="4"/>
@@ -5495,15 +5498,15 @@
       <c r="B85" s="6"/>
     </row>
     <row r="87" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A87" s="30"/>
-      <c r="B87" s="31"/>
-      <c r="C87" s="31"/>
-      <c r="D87" s="31"/>
-      <c r="E87" s="31"/>
-      <c r="F87" s="31"/>
-      <c r="G87" s="31"/>
-      <c r="H87" s="31"/>
-      <c r="I87" s="31"/>
+      <c r="A87" s="29"/>
+      <c r="B87" s="30"/>
+      <c r="C87" s="30"/>
+      <c r="D87" s="30"/>
+      <c r="E87" s="30"/>
+      <c r="F87" s="30"/>
+      <c r="G87" s="30"/>
+      <c r="H87" s="30"/>
+      <c r="I87" s="30"/>
     </row>
     <row r="88" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A88" s="4"/>
@@ -5606,15 +5609,15 @@
       <c r="B98" s="9"/>
     </row>
     <row r="100" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A100" s="32"/>
-      <c r="B100" s="31"/>
-      <c r="C100" s="31"/>
-      <c r="D100" s="31"/>
-      <c r="E100" s="31"/>
-      <c r="F100" s="31"/>
-      <c r="G100" s="31"/>
-      <c r="H100" s="31"/>
-      <c r="I100" s="31"/>
+      <c r="A100" s="31"/>
+      <c r="B100" s="30"/>
+      <c r="C100" s="30"/>
+      <c r="D100" s="30"/>
+      <c r="E100" s="30"/>
+      <c r="F100" s="30"/>
+      <c r="G100" s="30"/>
+      <c r="H100" s="30"/>
+      <c r="I100" s="30"/>
     </row>
     <row r="101" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A101" s="4"/>
@@ -6141,14 +6144,14 @@
     <row r="33" spans="1:9" ht="12.75" x14ac:dyDescent="0.2"/>
     <row r="35" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A35" s="4"/>
-      <c r="B35" s="32"/>
-      <c r="C35" s="31"/>
-      <c r="D35" s="31"/>
-      <c r="E35" s="31"/>
-      <c r="F35" s="31"/>
-      <c r="G35" s="31"/>
-      <c r="H35" s="31"/>
-      <c r="I35" s="31"/>
+      <c r="B35" s="31"/>
+      <c r="C35" s="30"/>
+      <c r="D35" s="30"/>
+      <c r="E35" s="30"/>
+      <c r="F35" s="30"/>
+      <c r="G35" s="30"/>
+      <c r="H35" s="30"/>
+      <c r="I35" s="30"/>
     </row>
     <row r="36" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A36" s="4"/>
@@ -6526,15 +6529,15 @@
       <c r="I69" s="4"/>
     </row>
     <row r="70" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A70" s="32"/>
-      <c r="B70" s="31"/>
-      <c r="C70" s="31"/>
-      <c r="D70" s="31"/>
-      <c r="E70" s="31"/>
-      <c r="F70" s="31"/>
-      <c r="G70" s="31"/>
-      <c r="H70" s="31"/>
-      <c r="I70" s="31"/>
+      <c r="A70" s="31"/>
+      <c r="B70" s="30"/>
+      <c r="C70" s="30"/>
+      <c r="D70" s="30"/>
+      <c r="E70" s="30"/>
+      <c r="F70" s="30"/>
+      <c r="G70" s="30"/>
+      <c r="H70" s="30"/>
+      <c r="I70" s="30"/>
     </row>
     <row r="71" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A71" s="4"/>
@@ -6559,15 +6562,15 @@
       <c r="I72" s="6"/>
     </row>
     <row r="75" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A75" s="30"/>
-      <c r="B75" s="31"/>
-      <c r="C75" s="31"/>
-      <c r="D75" s="31"/>
-      <c r="E75" s="31"/>
-      <c r="F75" s="31"/>
-      <c r="G75" s="31"/>
-      <c r="H75" s="31"/>
-      <c r="I75" s="31"/>
+      <c r="A75" s="29"/>
+      <c r="B75" s="30"/>
+      <c r="C75" s="30"/>
+      <c r="D75" s="30"/>
+      <c r="E75" s="30"/>
+      <c r="F75" s="30"/>
+      <c r="G75" s="30"/>
+      <c r="H75" s="30"/>
+      <c r="I75" s="30"/>
     </row>
     <row r="76" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A76" s="4"/>
@@ -6603,15 +6606,15 @@
       <c r="I78" s="8"/>
     </row>
     <row r="79" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A79" s="33"/>
-      <c r="B79" s="31"/>
-      <c r="C79" s="31"/>
-      <c r="D79" s="31"/>
-      <c r="E79" s="31"/>
-      <c r="F79" s="31"/>
-      <c r="G79" s="31"/>
-      <c r="H79" s="31"/>
-      <c r="I79" s="31"/>
+      <c r="A79" s="32"/>
+      <c r="B79" s="30"/>
+      <c r="C79" s="30"/>
+      <c r="D79" s="30"/>
+      <c r="E79" s="30"/>
+      <c r="F79" s="30"/>
+      <c r="G79" s="30"/>
+      <c r="H79" s="30"/>
+      <c r="I79" s="30"/>
     </row>
     <row r="80" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A80" s="4"/>
@@ -6647,15 +6650,15 @@
       <c r="B85" s="6"/>
     </row>
     <row r="87" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A87" s="30"/>
-      <c r="B87" s="31"/>
-      <c r="C87" s="31"/>
-      <c r="D87" s="31"/>
-      <c r="E87" s="31"/>
-      <c r="F87" s="31"/>
-      <c r="G87" s="31"/>
-      <c r="H87" s="31"/>
-      <c r="I87" s="31"/>
+      <c r="A87" s="29"/>
+      <c r="B87" s="30"/>
+      <c r="C87" s="30"/>
+      <c r="D87" s="30"/>
+      <c r="E87" s="30"/>
+      <c r="F87" s="30"/>
+      <c r="G87" s="30"/>
+      <c r="H87" s="30"/>
+      <c r="I87" s="30"/>
     </row>
     <row r="88" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A88" s="4"/>
@@ -6758,15 +6761,15 @@
       <c r="B98" s="9"/>
     </row>
     <row r="100" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A100" s="32"/>
-      <c r="B100" s="31"/>
-      <c r="C100" s="31"/>
-      <c r="D100" s="31"/>
-      <c r="E100" s="31"/>
-      <c r="F100" s="31"/>
-      <c r="G100" s="31"/>
-      <c r="H100" s="31"/>
-      <c r="I100" s="31"/>
+      <c r="A100" s="31"/>
+      <c r="B100" s="30"/>
+      <c r="C100" s="30"/>
+      <c r="D100" s="30"/>
+      <c r="E100" s="30"/>
+      <c r="F100" s="30"/>
+      <c r="G100" s="30"/>
+      <c r="H100" s="30"/>
+      <c r="I100" s="30"/>
     </row>
     <row r="101" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A101" s="4"/>
@@ -7293,14 +7296,14 @@
     <row r="33" spans="1:9" ht="12.75" x14ac:dyDescent="0.2"/>
     <row r="35" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A35" s="4"/>
-      <c r="B35" s="32"/>
-      <c r="C35" s="31"/>
-      <c r="D35" s="31"/>
-      <c r="E35" s="31"/>
-      <c r="F35" s="31"/>
-      <c r="G35" s="31"/>
-      <c r="H35" s="31"/>
-      <c r="I35" s="31"/>
+      <c r="B35" s="31"/>
+      <c r="C35" s="30"/>
+      <c r="D35" s="30"/>
+      <c r="E35" s="30"/>
+      <c r="F35" s="30"/>
+      <c r="G35" s="30"/>
+      <c r="H35" s="30"/>
+      <c r="I35" s="30"/>
     </row>
     <row r="36" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A36" s="4"/>
@@ -7678,15 +7681,15 @@
       <c r="I69" s="4"/>
     </row>
     <row r="70" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A70" s="32"/>
-      <c r="B70" s="31"/>
-      <c r="C70" s="31"/>
-      <c r="D70" s="31"/>
-      <c r="E70" s="31"/>
-      <c r="F70" s="31"/>
-      <c r="G70" s="31"/>
-      <c r="H70" s="31"/>
-      <c r="I70" s="31"/>
+      <c r="A70" s="31"/>
+      <c r="B70" s="30"/>
+      <c r="C70" s="30"/>
+      <c r="D70" s="30"/>
+      <c r="E70" s="30"/>
+      <c r="F70" s="30"/>
+      <c r="G70" s="30"/>
+      <c r="H70" s="30"/>
+      <c r="I70" s="30"/>
     </row>
     <row r="71" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A71" s="4"/>
@@ -7711,15 +7714,15 @@
       <c r="I72" s="6"/>
     </row>
     <row r="75" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A75" s="30"/>
-      <c r="B75" s="31"/>
-      <c r="C75" s="31"/>
-      <c r="D75" s="31"/>
-      <c r="E75" s="31"/>
-      <c r="F75" s="31"/>
-      <c r="G75" s="31"/>
-      <c r="H75" s="31"/>
-      <c r="I75" s="31"/>
+      <c r="A75" s="29"/>
+      <c r="B75" s="30"/>
+      <c r="C75" s="30"/>
+      <c r="D75" s="30"/>
+      <c r="E75" s="30"/>
+      <c r="F75" s="30"/>
+      <c r="G75" s="30"/>
+      <c r="H75" s="30"/>
+      <c r="I75" s="30"/>
     </row>
     <row r="76" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A76" s="4"/>
@@ -7755,15 +7758,15 @@
       <c r="I78" s="8"/>
     </row>
     <row r="79" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A79" s="33"/>
-      <c r="B79" s="31"/>
-      <c r="C79" s="31"/>
-      <c r="D79" s="31"/>
-      <c r="E79" s="31"/>
-      <c r="F79" s="31"/>
-      <c r="G79" s="31"/>
-      <c r="H79" s="31"/>
-      <c r="I79" s="31"/>
+      <c r="A79" s="32"/>
+      <c r="B79" s="30"/>
+      <c r="C79" s="30"/>
+      <c r="D79" s="30"/>
+      <c r="E79" s="30"/>
+      <c r="F79" s="30"/>
+      <c r="G79" s="30"/>
+      <c r="H79" s="30"/>
+      <c r="I79" s="30"/>
     </row>
     <row r="80" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A80" s="4"/>
@@ -7799,15 +7802,15 @@
       <c r="B85" s="6"/>
     </row>
     <row r="87" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A87" s="30"/>
-      <c r="B87" s="31"/>
-      <c r="C87" s="31"/>
-      <c r="D87" s="31"/>
-      <c r="E87" s="31"/>
-      <c r="F87" s="31"/>
-      <c r="G87" s="31"/>
-      <c r="H87" s="31"/>
-      <c r="I87" s="31"/>
+      <c r="A87" s="29"/>
+      <c r="B87" s="30"/>
+      <c r="C87" s="30"/>
+      <c r="D87" s="30"/>
+      <c r="E87" s="30"/>
+      <c r="F87" s="30"/>
+      <c r="G87" s="30"/>
+      <c r="H87" s="30"/>
+      <c r="I87" s="30"/>
     </row>
     <row r="88" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A88" s="4"/>
@@ -7910,15 +7913,15 @@
       <c r="B98" s="9"/>
     </row>
     <row r="100" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A100" s="32"/>
-      <c r="B100" s="31"/>
-      <c r="C100" s="31"/>
-      <c r="D100" s="31"/>
-      <c r="E100" s="31"/>
-      <c r="F100" s="31"/>
-      <c r="G100" s="31"/>
-      <c r="H100" s="31"/>
-      <c r="I100" s="31"/>
+      <c r="A100" s="31"/>
+      <c r="B100" s="30"/>
+      <c r="C100" s="30"/>
+      <c r="D100" s="30"/>
+      <c r="E100" s="30"/>
+      <c r="F100" s="30"/>
+      <c r="G100" s="30"/>
+      <c r="H100" s="30"/>
+      <c r="I100" s="30"/>
     </row>
     <row r="101" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A101" s="4"/>
@@ -8445,14 +8448,14 @@
     <row r="33" spans="1:9" ht="12.75" x14ac:dyDescent="0.2"/>
     <row r="35" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A35" s="4"/>
-      <c r="B35" s="32"/>
-      <c r="C35" s="31"/>
-      <c r="D35" s="31"/>
-      <c r="E35" s="31"/>
-      <c r="F35" s="31"/>
-      <c r="G35" s="31"/>
-      <c r="H35" s="31"/>
-      <c r="I35" s="31"/>
+      <c r="B35" s="31"/>
+      <c r="C35" s="30"/>
+      <c r="D35" s="30"/>
+      <c r="E35" s="30"/>
+      <c r="F35" s="30"/>
+      <c r="G35" s="30"/>
+      <c r="H35" s="30"/>
+      <c r="I35" s="30"/>
     </row>
     <row r="36" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A36" s="4"/>
@@ -8830,15 +8833,15 @@
       <c r="I69" s="4"/>
     </row>
     <row r="70" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A70" s="32"/>
-      <c r="B70" s="31"/>
-      <c r="C70" s="31"/>
-      <c r="D70" s="31"/>
-      <c r="E70" s="31"/>
-      <c r="F70" s="31"/>
-      <c r="G70" s="31"/>
-      <c r="H70" s="31"/>
-      <c r="I70" s="31"/>
+      <c r="A70" s="31"/>
+      <c r="B70" s="30"/>
+      <c r="C70" s="30"/>
+      <c r="D70" s="30"/>
+      <c r="E70" s="30"/>
+      <c r="F70" s="30"/>
+      <c r="G70" s="30"/>
+      <c r="H70" s="30"/>
+      <c r="I70" s="30"/>
     </row>
     <row r="71" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A71" s="4"/>
@@ -8863,15 +8866,15 @@
       <c r="I72" s="6"/>
     </row>
     <row r="75" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A75" s="30"/>
-      <c r="B75" s="31"/>
-      <c r="C75" s="31"/>
-      <c r="D75" s="31"/>
-      <c r="E75" s="31"/>
-      <c r="F75" s="31"/>
-      <c r="G75" s="31"/>
-      <c r="H75" s="31"/>
-      <c r="I75" s="31"/>
+      <c r="A75" s="29"/>
+      <c r="B75" s="30"/>
+      <c r="C75" s="30"/>
+      <c r="D75" s="30"/>
+      <c r="E75" s="30"/>
+      <c r="F75" s="30"/>
+      <c r="G75" s="30"/>
+      <c r="H75" s="30"/>
+      <c r="I75" s="30"/>
     </row>
     <row r="76" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A76" s="4"/>
@@ -8907,15 +8910,15 @@
       <c r="I78" s="8"/>
     </row>
     <row r="79" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A79" s="33"/>
-      <c r="B79" s="31"/>
-      <c r="C79" s="31"/>
-      <c r="D79" s="31"/>
-      <c r="E79" s="31"/>
-      <c r="F79" s="31"/>
-      <c r="G79" s="31"/>
-      <c r="H79" s="31"/>
-      <c r="I79" s="31"/>
+      <c r="A79" s="32"/>
+      <c r="B79" s="30"/>
+      <c r="C79" s="30"/>
+      <c r="D79" s="30"/>
+      <c r="E79" s="30"/>
+      <c r="F79" s="30"/>
+      <c r="G79" s="30"/>
+      <c r="H79" s="30"/>
+      <c r="I79" s="30"/>
     </row>
     <row r="80" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A80" s="4"/>
@@ -8951,15 +8954,15 @@
       <c r="B85" s="6"/>
     </row>
     <row r="87" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A87" s="30"/>
-      <c r="B87" s="31"/>
-      <c r="C87" s="31"/>
-      <c r="D87" s="31"/>
-      <c r="E87" s="31"/>
-      <c r="F87" s="31"/>
-      <c r="G87" s="31"/>
-      <c r="H87" s="31"/>
-      <c r="I87" s="31"/>
+      <c r="A87" s="29"/>
+      <c r="B87" s="30"/>
+      <c r="C87" s="30"/>
+      <c r="D87" s="30"/>
+      <c r="E87" s="30"/>
+      <c r="F87" s="30"/>
+      <c r="G87" s="30"/>
+      <c r="H87" s="30"/>
+      <c r="I87" s="30"/>
     </row>
     <row r="88" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A88" s="4"/>
@@ -9062,15 +9065,15 @@
       <c r="B98" s="9"/>
     </row>
     <row r="100" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A100" s="32"/>
-      <c r="B100" s="31"/>
-      <c r="C100" s="31"/>
-      <c r="D100" s="31"/>
-      <c r="E100" s="31"/>
-      <c r="F100" s="31"/>
-      <c r="G100" s="31"/>
-      <c r="H100" s="31"/>
-      <c r="I100" s="31"/>
+      <c r="A100" s="31"/>
+      <c r="B100" s="30"/>
+      <c r="C100" s="30"/>
+      <c r="D100" s="30"/>
+      <c r="E100" s="30"/>
+      <c r="F100" s="30"/>
+      <c r="G100" s="30"/>
+      <c r="H100" s="30"/>
+      <c r="I100" s="30"/>
     </row>
     <row r="101" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A101" s="4"/>
@@ -9597,14 +9600,14 @@
     <row r="33" spans="1:9" ht="12.75" x14ac:dyDescent="0.2"/>
     <row r="35" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A35" s="4"/>
-      <c r="B35" s="32"/>
-      <c r="C35" s="31"/>
-      <c r="D35" s="31"/>
-      <c r="E35" s="31"/>
-      <c r="F35" s="31"/>
-      <c r="G35" s="31"/>
-      <c r="H35" s="31"/>
-      <c r="I35" s="31"/>
+      <c r="B35" s="31"/>
+      <c r="C35" s="30"/>
+      <c r="D35" s="30"/>
+      <c r="E35" s="30"/>
+      <c r="F35" s="30"/>
+      <c r="G35" s="30"/>
+      <c r="H35" s="30"/>
+      <c r="I35" s="30"/>
     </row>
     <row r="36" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A36" s="4"/>
@@ -9982,15 +9985,15 @@
       <c r="I69" s="4"/>
     </row>
     <row r="70" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A70" s="32"/>
-      <c r="B70" s="31"/>
-      <c r="C70" s="31"/>
-      <c r="D70" s="31"/>
-      <c r="E70" s="31"/>
-      <c r="F70" s="31"/>
-      <c r="G70" s="31"/>
-      <c r="H70" s="31"/>
-      <c r="I70" s="31"/>
+      <c r="A70" s="31"/>
+      <c r="B70" s="30"/>
+      <c r="C70" s="30"/>
+      <c r="D70" s="30"/>
+      <c r="E70" s="30"/>
+      <c r="F70" s="30"/>
+      <c r="G70" s="30"/>
+      <c r="H70" s="30"/>
+      <c r="I70" s="30"/>
     </row>
     <row r="71" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A71" s="4"/>
@@ -10015,15 +10018,15 @@
       <c r="I72" s="6"/>
     </row>
     <row r="75" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A75" s="30"/>
-      <c r="B75" s="31"/>
-      <c r="C75" s="31"/>
-      <c r="D75" s="31"/>
-      <c r="E75" s="31"/>
-      <c r="F75" s="31"/>
-      <c r="G75" s="31"/>
-      <c r="H75" s="31"/>
-      <c r="I75" s="31"/>
+      <c r="A75" s="29"/>
+      <c r="B75" s="30"/>
+      <c r="C75" s="30"/>
+      <c r="D75" s="30"/>
+      <c r="E75" s="30"/>
+      <c r="F75" s="30"/>
+      <c r="G75" s="30"/>
+      <c r="H75" s="30"/>
+      <c r="I75" s="30"/>
     </row>
     <row r="76" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A76" s="4"/>
@@ -10059,15 +10062,15 @@
       <c r="I78" s="8"/>
     </row>
     <row r="79" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A79" s="33"/>
-      <c r="B79" s="31"/>
-      <c r="C79" s="31"/>
-      <c r="D79" s="31"/>
-      <c r="E79" s="31"/>
-      <c r="F79" s="31"/>
-      <c r="G79" s="31"/>
-      <c r="H79" s="31"/>
-      <c r="I79" s="31"/>
+      <c r="A79" s="32"/>
+      <c r="B79" s="30"/>
+      <c r="C79" s="30"/>
+      <c r="D79" s="30"/>
+      <c r="E79" s="30"/>
+      <c r="F79" s="30"/>
+      <c r="G79" s="30"/>
+      <c r="H79" s="30"/>
+      <c r="I79" s="30"/>
     </row>
     <row r="80" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A80" s="4"/>
@@ -10103,15 +10106,15 @@
       <c r="B85" s="6"/>
     </row>
     <row r="87" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A87" s="30"/>
-      <c r="B87" s="31"/>
-      <c r="C87" s="31"/>
-      <c r="D87" s="31"/>
-      <c r="E87" s="31"/>
-      <c r="F87" s="31"/>
-      <c r="G87" s="31"/>
-      <c r="H87" s="31"/>
-      <c r="I87" s="31"/>
+      <c r="A87" s="29"/>
+      <c r="B87" s="30"/>
+      <c r="C87" s="30"/>
+      <c r="D87" s="30"/>
+      <c r="E87" s="30"/>
+      <c r="F87" s="30"/>
+      <c r="G87" s="30"/>
+      <c r="H87" s="30"/>
+      <c r="I87" s="30"/>
     </row>
     <row r="88" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A88" s="4"/>
@@ -10214,15 +10217,15 @@
       <c r="B98" s="9"/>
     </row>
     <row r="100" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A100" s="32"/>
-      <c r="B100" s="31"/>
-      <c r="C100" s="31"/>
-      <c r="D100" s="31"/>
-      <c r="E100" s="31"/>
-      <c r="F100" s="31"/>
-      <c r="G100" s="31"/>
-      <c r="H100" s="31"/>
-      <c r="I100" s="31"/>
+      <c r="A100" s="31"/>
+      <c r="B100" s="30"/>
+      <c r="C100" s="30"/>
+      <c r="D100" s="30"/>
+      <c r="E100" s="30"/>
+      <c r="F100" s="30"/>
+      <c r="G100" s="30"/>
+      <c r="H100" s="30"/>
+      <c r="I100" s="30"/>
     </row>
     <row r="101" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A101" s="4"/>
@@ -10749,14 +10752,14 @@
     <row r="33" spans="1:9" ht="12.75" x14ac:dyDescent="0.2"/>
     <row r="35" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A35" s="4"/>
-      <c r="B35" s="32"/>
-      <c r="C35" s="31"/>
-      <c r="D35" s="31"/>
-      <c r="E35" s="31"/>
-      <c r="F35" s="31"/>
-      <c r="G35" s="31"/>
-      <c r="H35" s="31"/>
-      <c r="I35" s="31"/>
+      <c r="B35" s="31"/>
+      <c r="C35" s="30"/>
+      <c r="D35" s="30"/>
+      <c r="E35" s="30"/>
+      <c r="F35" s="30"/>
+      <c r="G35" s="30"/>
+      <c r="H35" s="30"/>
+      <c r="I35" s="30"/>
     </row>
     <row r="36" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A36" s="4"/>
@@ -11134,15 +11137,15 @@
       <c r="I69" s="4"/>
     </row>
     <row r="70" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A70" s="32"/>
-      <c r="B70" s="31"/>
-      <c r="C70" s="31"/>
-      <c r="D70" s="31"/>
-      <c r="E70" s="31"/>
-      <c r="F70" s="31"/>
-      <c r="G70" s="31"/>
-      <c r="H70" s="31"/>
-      <c r="I70" s="31"/>
+      <c r="A70" s="31"/>
+      <c r="B70" s="30"/>
+      <c r="C70" s="30"/>
+      <c r="D70" s="30"/>
+      <c r="E70" s="30"/>
+      <c r="F70" s="30"/>
+      <c r="G70" s="30"/>
+      <c r="H70" s="30"/>
+      <c r="I70" s="30"/>
     </row>
     <row r="71" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A71" s="4"/>
@@ -11167,15 +11170,15 @@
       <c r="I72" s="6"/>
     </row>
     <row r="75" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A75" s="30"/>
-      <c r="B75" s="31"/>
-      <c r="C75" s="31"/>
-      <c r="D75" s="31"/>
-      <c r="E75" s="31"/>
-      <c r="F75" s="31"/>
-      <c r="G75" s="31"/>
-      <c r="H75" s="31"/>
-      <c r="I75" s="31"/>
+      <c r="A75" s="29"/>
+      <c r="B75" s="30"/>
+      <c r="C75" s="30"/>
+      <c r="D75" s="30"/>
+      <c r="E75" s="30"/>
+      <c r="F75" s="30"/>
+      <c r="G75" s="30"/>
+      <c r="H75" s="30"/>
+      <c r="I75" s="30"/>
     </row>
     <row r="76" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A76" s="4"/>
@@ -11211,15 +11214,15 @@
       <c r="I78" s="8"/>
     </row>
     <row r="79" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A79" s="33"/>
-      <c r="B79" s="31"/>
-      <c r="C79" s="31"/>
-      <c r="D79" s="31"/>
-      <c r="E79" s="31"/>
-      <c r="F79" s="31"/>
-      <c r="G79" s="31"/>
-      <c r="H79" s="31"/>
-      <c r="I79" s="31"/>
+      <c r="A79" s="32"/>
+      <c r="B79" s="30"/>
+      <c r="C79" s="30"/>
+      <c r="D79" s="30"/>
+      <c r="E79" s="30"/>
+      <c r="F79" s="30"/>
+      <c r="G79" s="30"/>
+      <c r="H79" s="30"/>
+      <c r="I79" s="30"/>
     </row>
     <row r="80" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A80" s="4"/>
@@ -11255,15 +11258,15 @@
       <c r="B85" s="6"/>
     </row>
     <row r="87" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A87" s="30"/>
-      <c r="B87" s="31"/>
-      <c r="C87" s="31"/>
-      <c r="D87" s="31"/>
-      <c r="E87" s="31"/>
-      <c r="F87" s="31"/>
-      <c r="G87" s="31"/>
-      <c r="H87" s="31"/>
-      <c r="I87" s="31"/>
+      <c r="A87" s="29"/>
+      <c r="B87" s="30"/>
+      <c r="C87" s="30"/>
+      <c r="D87" s="30"/>
+      <c r="E87" s="30"/>
+      <c r="F87" s="30"/>
+      <c r="G87" s="30"/>
+      <c r="H87" s="30"/>
+      <c r="I87" s="30"/>
     </row>
     <row r="88" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A88" s="4"/>
@@ -11366,15 +11369,15 @@
       <c r="B98" s="9"/>
     </row>
     <row r="100" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A100" s="32"/>
-      <c r="B100" s="31"/>
-      <c r="C100" s="31"/>
-      <c r="D100" s="31"/>
-      <c r="E100" s="31"/>
-      <c r="F100" s="31"/>
-      <c r="G100" s="31"/>
-      <c r="H100" s="31"/>
-      <c r="I100" s="31"/>
+      <c r="A100" s="31"/>
+      <c r="B100" s="30"/>
+      <c r="C100" s="30"/>
+      <c r="D100" s="30"/>
+      <c r="E100" s="30"/>
+      <c r="F100" s="30"/>
+      <c r="G100" s="30"/>
+      <c r="H100" s="30"/>
+      <c r="I100" s="30"/>
     </row>
     <row r="101" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A101" s="4"/>
@@ -11764,118 +11767,134 @@
       </c>
     </row>
     <row r="12" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A12" s="1">
+      <c r="A12" s="19">
         <f t="shared" si="0"/>
         <v>11</v>
       </c>
-      <c r="B12" s="24">
+      <c r="B12" s="33">
         <v>6917</v>
       </c>
-      <c r="C12" s="25">
+      <c r="C12" s="34">
         <v>8710</v>
       </c>
-      <c r="D12" s="24">
+      <c r="D12" s="33">
         <v>9309</v>
       </c>
-      <c r="E12" s="24">
+      <c r="E12" s="33">
         <v>10811</v>
       </c>
-      <c r="F12" s="24">
+      <c r="F12" s="33">
         <v>1274</v>
       </c>
-      <c r="G12" s="24">
+      <c r="G12" s="33">
         <v>3734</v>
       </c>
-      <c r="H12" s="24">
+      <c r="H12" s="33">
         <v>373</v>
       </c>
-      <c r="I12" s="24">
+      <c r="I12" s="33">
         <v>3360</v>
       </c>
     </row>
     <row r="13" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A13" s="1">
+      <c r="A13" s="19">
         <f t="shared" si="0"/>
         <v>12</v>
       </c>
-      <c r="B13" s="2"/>
-      <c r="C13" s="2"/>
-      <c r="D13" s="2"/>
-      <c r="E13" s="2"/>
-      <c r="F13" s="2"/>
-      <c r="G13" s="2"/>
-      <c r="H13" s="2"/>
-      <c r="I13" s="2"/>
+      <c r="B13" s="22">
+        <v>7029</v>
+      </c>
+      <c r="C13" s="22">
+        <v>8819</v>
+      </c>
+      <c r="D13" s="22">
+        <v>9312</v>
+      </c>
+      <c r="E13" s="22">
+        <v>10811</v>
+      </c>
+      <c r="F13" s="22">
+        <v>1274</v>
+      </c>
+      <c r="G13" s="22">
+        <v>3738</v>
+      </c>
+      <c r="H13" s="22">
+        <v>374</v>
+      </c>
+      <c r="I13" s="22">
+        <v>3364</v>
+      </c>
     </row>
     <row r="14" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A14" s="1">
+      <c r="A14" s="19">
         <f t="shared" si="0"/>
         <v>13</v>
       </c>
-      <c r="B14" s="2"/>
-      <c r="C14" s="2"/>
-      <c r="D14" s="2"/>
-      <c r="E14" s="2"/>
-      <c r="F14" s="2"/>
-      <c r="G14" s="2"/>
-      <c r="H14" s="2"/>
-      <c r="I14" s="2"/>
+      <c r="B14" s="33"/>
+      <c r="C14" s="33"/>
+      <c r="D14" s="33"/>
+      <c r="E14" s="33"/>
+      <c r="F14" s="33"/>
+      <c r="G14" s="33"/>
+      <c r="H14" s="33"/>
+      <c r="I14" s="33"/>
     </row>
     <row r="15" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A15" s="1">
+      <c r="A15" s="19">
         <f t="shared" si="0"/>
         <v>14</v>
       </c>
-      <c r="B15" s="2"/>
-      <c r="C15" s="2"/>
-      <c r="D15" s="2"/>
-      <c r="E15" s="2"/>
-      <c r="F15" s="2"/>
-      <c r="G15" s="2"/>
-      <c r="H15" s="2"/>
-      <c r="I15" s="2"/>
+      <c r="B15" s="33"/>
+      <c r="C15" s="33"/>
+      <c r="D15" s="33"/>
+      <c r="E15" s="33"/>
+      <c r="F15" s="33"/>
+      <c r="G15" s="33"/>
+      <c r="H15" s="33"/>
+      <c r="I15" s="33"/>
     </row>
     <row r="16" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A16" s="1">
+      <c r="A16" s="19">
         <f t="shared" si="0"/>
         <v>15</v>
       </c>
-      <c r="B16" s="2"/>
-      <c r="C16" s="2"/>
-      <c r="D16" s="2"/>
-      <c r="E16" s="2"/>
-      <c r="F16" s="2"/>
-      <c r="G16" s="2"/>
-      <c r="H16" s="2"/>
-      <c r="I16" s="2"/>
+      <c r="B16" s="33"/>
+      <c r="C16" s="33"/>
+      <c r="D16" s="33"/>
+      <c r="E16" s="33"/>
+      <c r="F16" s="33"/>
+      <c r="G16" s="33"/>
+      <c r="H16" s="33"/>
+      <c r="I16" s="33"/>
     </row>
     <row r="17" spans="1:10" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A17" s="1">
+      <c r="A17" s="19">
         <f t="shared" si="0"/>
         <v>16</v>
       </c>
-      <c r="B17" s="2"/>
-      <c r="C17" s="2"/>
-      <c r="D17" s="2"/>
-      <c r="E17" s="2"/>
-      <c r="F17" s="2"/>
-      <c r="G17" s="2"/>
-      <c r="H17" s="2"/>
-      <c r="I17" s="2"/>
+      <c r="B17" s="33"/>
+      <c r="C17" s="33"/>
+      <c r="D17" s="33"/>
+      <c r="E17" s="33"/>
+      <c r="F17" s="33"/>
+      <c r="G17" s="33"/>
+      <c r="H17" s="33"/>
+      <c r="I17" s="33"/>
     </row>
     <row r="18" spans="1:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A18" s="1">
         <f t="shared" si="0"/>
         <v>17</v>
       </c>
-      <c r="B18" s="2"/>
-      <c r="C18" s="2"/>
-      <c r="D18" s="2"/>
-      <c r="E18" s="2"/>
-      <c r="F18" s="2"/>
-      <c r="G18" s="2"/>
-      <c r="H18" s="2"/>
-      <c r="I18" s="2"/>
+      <c r="B18" s="24"/>
+      <c r="C18" s="24"/>
+      <c r="D18" s="24"/>
+      <c r="E18" s="24"/>
+      <c r="F18" s="24"/>
+      <c r="G18" s="24"/>
+      <c r="H18" s="24"/>
+      <c r="I18" s="24"/>
       <c r="J18" s="3"/>
     </row>
     <row r="19" spans="1:10" ht="12.75" x14ac:dyDescent="0.2">
@@ -11963,128 +11982,128 @@
       <c r="I24" s="2"/>
     </row>
     <row r="25" spans="1:10" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A25" s="1">
+      <c r="A25" s="10">
         <f t="shared" si="0"/>
         <v>24</v>
       </c>
-      <c r="B25" s="2"/>
-      <c r="C25" s="2"/>
-      <c r="D25" s="2"/>
-      <c r="E25" s="2"/>
-      <c r="F25" s="2"/>
-      <c r="G25" s="2"/>
-      <c r="H25" s="2"/>
-      <c r="I25" s="2"/>
+      <c r="B25" s="11"/>
+      <c r="C25" s="11"/>
+      <c r="D25" s="11"/>
+      <c r="E25" s="11"/>
+      <c r="F25" s="11"/>
+      <c r="G25" s="11"/>
+      <c r="H25" s="11"/>
+      <c r="I25" s="11"/>
     </row>
     <row r="26" spans="1:10" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A26" s="1">
+      <c r="A26" s="27">
         <f t="shared" si="0"/>
         <v>25</v>
       </c>
-      <c r="B26" s="2"/>
-      <c r="C26" s="2"/>
-      <c r="D26" s="2"/>
-      <c r="E26" s="2"/>
-      <c r="F26" s="2"/>
-      <c r="G26" s="2"/>
-      <c r="H26" s="2"/>
-      <c r="I26" s="2"/>
+      <c r="B26" s="33"/>
+      <c r="C26" s="33"/>
+      <c r="D26" s="33"/>
+      <c r="E26" s="33"/>
+      <c r="F26" s="33"/>
+      <c r="G26" s="33"/>
+      <c r="H26" s="33"/>
+      <c r="I26" s="33"/>
     </row>
     <row r="27" spans="1:10" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A27" s="1">
+      <c r="A27" s="27">
         <f t="shared" si="0"/>
         <v>26</v>
       </c>
-      <c r="B27" s="2"/>
-      <c r="C27" s="2"/>
-      <c r="D27" s="2"/>
-      <c r="E27" s="2"/>
-      <c r="F27" s="2"/>
-      <c r="G27" s="2"/>
-      <c r="H27" s="2"/>
-      <c r="I27" s="2"/>
+      <c r="B27" s="33"/>
+      <c r="C27" s="33"/>
+      <c r="D27" s="33"/>
+      <c r="E27" s="33"/>
+      <c r="F27" s="33"/>
+      <c r="G27" s="33"/>
+      <c r="H27" s="33"/>
+      <c r="I27" s="33"/>
     </row>
     <row r="28" spans="1:10" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A28" s="1">
+      <c r="A28" s="27">
         <f t="shared" si="0"/>
         <v>27</v>
       </c>
-      <c r="B28" s="2"/>
-      <c r="C28" s="2"/>
-      <c r="D28" s="2"/>
-      <c r="E28" s="2"/>
-      <c r="F28" s="2"/>
-      <c r="G28" s="2"/>
-      <c r="H28" s="2"/>
-      <c r="I28" s="2"/>
+      <c r="B28" s="33"/>
+      <c r="C28" s="33"/>
+      <c r="D28" s="33"/>
+      <c r="E28" s="33"/>
+      <c r="F28" s="33"/>
+      <c r="G28" s="33"/>
+      <c r="H28" s="33"/>
+      <c r="I28" s="33"/>
     </row>
     <row r="29" spans="1:10" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A29" s="1">
+      <c r="A29" s="27">
         <f t="shared" si="0"/>
         <v>28</v>
       </c>
-      <c r="B29" s="2"/>
-      <c r="C29" s="2"/>
-      <c r="D29" s="2"/>
-      <c r="E29" s="2"/>
-      <c r="F29" s="2"/>
-      <c r="G29" s="2"/>
-      <c r="H29" s="2"/>
-      <c r="I29" s="2"/>
+      <c r="B29" s="33"/>
+      <c r="C29" s="33"/>
+      <c r="D29" s="33"/>
+      <c r="E29" s="33"/>
+      <c r="F29" s="33"/>
+      <c r="G29" s="33"/>
+      <c r="H29" s="33"/>
+      <c r="I29" s="33"/>
     </row>
     <row r="30" spans="1:10" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A30" s="1">
+      <c r="A30" s="27">
         <f t="shared" si="0"/>
         <v>29</v>
       </c>
-      <c r="B30" s="2"/>
-      <c r="C30" s="2"/>
-      <c r="D30" s="2"/>
-      <c r="E30" s="2"/>
-      <c r="F30" s="2"/>
-      <c r="G30" s="2"/>
-      <c r="H30" s="2"/>
-      <c r="I30" s="2"/>
+      <c r="B30" s="33"/>
+      <c r="C30" s="33"/>
+      <c r="D30" s="33"/>
+      <c r="E30" s="33"/>
+      <c r="F30" s="33"/>
+      <c r="G30" s="33"/>
+      <c r="H30" s="33"/>
+      <c r="I30" s="33"/>
     </row>
     <row r="31" spans="1:10" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A31" s="1">
+      <c r="A31" s="27">
         <f t="shared" si="0"/>
         <v>30</v>
       </c>
-      <c r="B31" s="2"/>
-      <c r="C31" s="2"/>
-      <c r="D31" s="2"/>
-      <c r="E31" s="2"/>
-      <c r="F31" s="2"/>
-      <c r="G31" s="2"/>
-      <c r="H31" s="2"/>
-      <c r="I31" s="2"/>
+      <c r="B31" s="33"/>
+      <c r="C31" s="33"/>
+      <c r="D31" s="33"/>
+      <c r="E31" s="33"/>
+      <c r="F31" s="33"/>
+      <c r="G31" s="33"/>
+      <c r="H31" s="33"/>
+      <c r="I31" s="33"/>
     </row>
     <row r="32" spans="1:10" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A32" s="10">
+      <c r="A32" s="27">
         <f t="shared" si="0"/>
         <v>31</v>
       </c>
-      <c r="B32" s="11"/>
-      <c r="C32" s="11"/>
-      <c r="D32" s="11"/>
-      <c r="E32" s="11"/>
-      <c r="F32" s="11"/>
-      <c r="G32" s="11"/>
-      <c r="H32" s="11"/>
-      <c r="I32" s="11"/>
+      <c r="B32" s="33"/>
+      <c r="C32" s="33"/>
+      <c r="D32" s="33"/>
+      <c r="E32" s="33"/>
+      <c r="F32" s="33"/>
+      <c r="G32" s="33"/>
+      <c r="H32" s="33"/>
+      <c r="I32" s="33"/>
     </row>
     <row r="33" spans="1:9" ht="12.75" x14ac:dyDescent="0.2"/>
     <row r="35" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A35" s="4"/>
-      <c r="B35" s="32"/>
-      <c r="C35" s="31"/>
-      <c r="D35" s="31"/>
-      <c r="E35" s="31"/>
-      <c r="F35" s="31"/>
-      <c r="G35" s="31"/>
-      <c r="H35" s="31"/>
-      <c r="I35" s="31"/>
+      <c r="B35" s="31"/>
+      <c r="C35" s="30"/>
+      <c r="D35" s="30"/>
+      <c r="E35" s="30"/>
+      <c r="F35" s="30"/>
+      <c r="G35" s="30"/>
+      <c r="H35" s="30"/>
+      <c r="I35" s="30"/>
     </row>
     <row r="36" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A36" s="4"/>
@@ -12462,15 +12481,15 @@
       <c r="I69" s="4"/>
     </row>
     <row r="70" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A70" s="32"/>
-      <c r="B70" s="31"/>
-      <c r="C70" s="31"/>
-      <c r="D70" s="31"/>
-      <c r="E70" s="31"/>
-      <c r="F70" s="31"/>
-      <c r="G70" s="31"/>
-      <c r="H70" s="31"/>
-      <c r="I70" s="31"/>
+      <c r="A70" s="31"/>
+      <c r="B70" s="30"/>
+      <c r="C70" s="30"/>
+      <c r="D70" s="30"/>
+      <c r="E70" s="30"/>
+      <c r="F70" s="30"/>
+      <c r="G70" s="30"/>
+      <c r="H70" s="30"/>
+      <c r="I70" s="30"/>
     </row>
     <row r="71" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A71" s="4"/>
@@ -12495,15 +12514,15 @@
       <c r="I72" s="6"/>
     </row>
     <row r="75" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A75" s="30"/>
-      <c r="B75" s="31"/>
-      <c r="C75" s="31"/>
-      <c r="D75" s="31"/>
-      <c r="E75" s="31"/>
-      <c r="F75" s="31"/>
-      <c r="G75" s="31"/>
-      <c r="H75" s="31"/>
-      <c r="I75" s="31"/>
+      <c r="A75" s="29"/>
+      <c r="B75" s="30"/>
+      <c r="C75" s="30"/>
+      <c r="D75" s="30"/>
+      <c r="E75" s="30"/>
+      <c r="F75" s="30"/>
+      <c r="G75" s="30"/>
+      <c r="H75" s="30"/>
+      <c r="I75" s="30"/>
     </row>
     <row r="76" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A76" s="4"/>
@@ -12539,15 +12558,15 @@
       <c r="I78" s="8"/>
     </row>
     <row r="79" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A79" s="33"/>
-      <c r="B79" s="31"/>
-      <c r="C79" s="31"/>
-      <c r="D79" s="31"/>
-      <c r="E79" s="31"/>
-      <c r="F79" s="31"/>
-      <c r="G79" s="31"/>
-      <c r="H79" s="31"/>
-      <c r="I79" s="31"/>
+      <c r="A79" s="32"/>
+      <c r="B79" s="30"/>
+      <c r="C79" s="30"/>
+      <c r="D79" s="30"/>
+      <c r="E79" s="30"/>
+      <c r="F79" s="30"/>
+      <c r="G79" s="30"/>
+      <c r="H79" s="30"/>
+      <c r="I79" s="30"/>
     </row>
     <row r="80" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A80" s="4"/>
@@ -12583,15 +12602,15 @@
       <c r="B85" s="6"/>
     </row>
     <row r="87" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A87" s="30"/>
-      <c r="B87" s="31"/>
-      <c r="C87" s="31"/>
-      <c r="D87" s="31"/>
-      <c r="E87" s="31"/>
-      <c r="F87" s="31"/>
-      <c r="G87" s="31"/>
-      <c r="H87" s="31"/>
-      <c r="I87" s="31"/>
+      <c r="A87" s="29"/>
+      <c r="B87" s="30"/>
+      <c r="C87" s="30"/>
+      <c r="D87" s="30"/>
+      <c r="E87" s="30"/>
+      <c r="F87" s="30"/>
+      <c r="G87" s="30"/>
+      <c r="H87" s="30"/>
+      <c r="I87" s="30"/>
     </row>
     <row r="88" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A88" s="4"/>
@@ -12694,15 +12713,15 @@
       <c r="B98" s="9"/>
     </row>
     <row r="100" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A100" s="32"/>
-      <c r="B100" s="31"/>
-      <c r="C100" s="31"/>
-      <c r="D100" s="31"/>
-      <c r="E100" s="31"/>
-      <c r="F100" s="31"/>
-      <c r="G100" s="31"/>
-      <c r="H100" s="31"/>
-      <c r="I100" s="31"/>
+      <c r="A100" s="31"/>
+      <c r="B100" s="30"/>
+      <c r="C100" s="30"/>
+      <c r="D100" s="30"/>
+      <c r="E100" s="30"/>
+      <c r="F100" s="30"/>
+      <c r="G100" s="30"/>
+      <c r="H100" s="30"/>
+      <c r="I100" s="30"/>
     </row>
     <row r="101" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A101" s="4"/>
@@ -12741,6 +12760,7 @@
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
 
@@ -12764,36 +12784,36 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A1" s="26" t="s">
+      <c r="A1" s="25" t="s">
         <v>8</v>
       </c>
-      <c r="B1" s="27" t="s">
+      <c r="B1" s="26" t="s">
         <v>0</v>
       </c>
-      <c r="C1" s="27" t="s">
+      <c r="C1" s="26" t="s">
         <v>1</v>
       </c>
-      <c r="D1" s="27" t="s">
+      <c r="D1" s="26" t="s">
         <v>2</v>
       </c>
-      <c r="E1" s="27" t="s">
+      <c r="E1" s="26" t="s">
         <v>3</v>
       </c>
-      <c r="F1" s="27" t="s">
+      <c r="F1" s="26" t="s">
         <v>4</v>
       </c>
-      <c r="G1" s="27" t="s">
+      <c r="G1" s="26" t="s">
         <v>5</v>
       </c>
-      <c r="H1" s="27" t="s">
+      <c r="H1" s="26" t="s">
         <v>6</v>
       </c>
-      <c r="I1" s="27" t="s">
+      <c r="I1" s="26" t="s">
         <v>7</v>
       </c>
     </row>
     <row r="2" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A2" s="28">
+      <c r="A2" s="27">
         <v>1</v>
       </c>
       <c r="B2" s="22">
@@ -12822,7 +12842,7 @@
       </c>
     </row>
     <row r="3" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A3" s="28">
+      <c r="A3" s="27">
         <f t="shared" ref="A3:A32" si="0">A2+1</f>
         <v>2</v>
       </c>
@@ -12836,7 +12856,7 @@
       <c r="I3" s="23"/>
     </row>
     <row r="4" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A4" s="28">
+      <c r="A4" s="27">
         <f t="shared" si="0"/>
         <v>3</v>
       </c>
@@ -12866,7 +12886,7 @@
       </c>
     </row>
     <row r="5" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A5" s="28">
+      <c r="A5" s="27">
         <f t="shared" si="0"/>
         <v>4</v>
       </c>
@@ -12896,7 +12916,7 @@
       </c>
     </row>
     <row r="6" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A6" s="28">
+      <c r="A6" s="27">
         <f t="shared" si="0"/>
         <v>5</v>
       </c>
@@ -12926,7 +12946,7 @@
       </c>
     </row>
     <row r="7" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A7" s="28">
+      <c r="A7" s="27">
         <f t="shared" si="0"/>
         <v>6</v>
       </c>
@@ -12956,7 +12976,7 @@
       </c>
     </row>
     <row r="8" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A8" s="28">
+      <c r="A8" s="27">
         <f t="shared" si="0"/>
         <v>7</v>
       </c>
@@ -12986,7 +13006,7 @@
       </c>
     </row>
     <row r="9" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A9" s="28">
+      <c r="A9" s="27">
         <f t="shared" si="0"/>
         <v>8</v>
       </c>
@@ -13000,7 +13020,7 @@
       <c r="I9" s="23"/>
     </row>
     <row r="10" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A10" s="28">
+      <c r="A10" s="27">
         <f t="shared" si="0"/>
         <v>9</v>
       </c>
@@ -13014,7 +13034,7 @@
       <c r="I10" s="23"/>
     </row>
     <row r="11" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A11" s="28">
+      <c r="A11" s="27">
         <f t="shared" si="0"/>
         <v>10</v>
       </c>
@@ -13044,7 +13064,7 @@
       </c>
     </row>
     <row r="12" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A12" s="28">
+      <c r="A12" s="27">
         <f t="shared" si="0"/>
         <v>11</v>
       </c>
@@ -13074,7 +13094,7 @@
       </c>
     </row>
     <row r="13" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A13" s="28">
+      <c r="A13" s="27">
         <f t="shared" si="0"/>
         <v>12</v>
       </c>
@@ -13104,7 +13124,7 @@
       </c>
     </row>
     <row r="14" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A14" s="28">
+      <c r="A14" s="27">
         <f t="shared" si="0"/>
         <v>13</v>
       </c>
@@ -13128,7 +13148,7 @@
       <c r="I14" s="23"/>
     </row>
     <row r="15" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A15" s="28">
+      <c r="A15" s="27">
         <f t="shared" si="0"/>
         <v>14</v>
       </c>
@@ -13142,7 +13162,7 @@
       <c r="I15" s="23"/>
     </row>
     <row r="16" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A16" s="28">
+      <c r="A16" s="27">
         <f t="shared" si="0"/>
         <v>15</v>
       </c>
@@ -13172,7 +13192,7 @@
       </c>
     </row>
     <row r="17" spans="1:10" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A17" s="28">
+      <c r="A17" s="27">
         <f t="shared" si="0"/>
         <v>16</v>
       </c>
@@ -13186,7 +13206,7 @@
       <c r="I17" s="23"/>
     </row>
     <row r="18" spans="1:10" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A18" s="28">
+      <c r="A18" s="27">
         <f t="shared" si="0"/>
         <v>17</v>
       </c>
@@ -13201,7 +13221,7 @@
       <c r="J18" s="3"/>
     </row>
     <row r="19" spans="1:10" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A19" s="28">
+      <c r="A19" s="27">
         <f t="shared" si="0"/>
         <v>18</v>
       </c>
@@ -13215,7 +13235,7 @@
       <c r="I19" s="23"/>
     </row>
     <row r="20" spans="1:10" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A20" s="28">
+      <c r="A20" s="27">
         <f t="shared" si="0"/>
         <v>19</v>
       </c>
@@ -13229,7 +13249,7 @@
       <c r="I20" s="23"/>
     </row>
     <row r="21" spans="1:10" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A21" s="28">
+      <c r="A21" s="27">
         <f t="shared" si="0"/>
         <v>20</v>
       </c>
@@ -13243,7 +13263,7 @@
       <c r="I21" s="23"/>
     </row>
     <row r="22" spans="1:10" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A22" s="28">
+      <c r="A22" s="27">
         <f t="shared" si="0"/>
         <v>21</v>
       </c>
@@ -13257,7 +13277,7 @@
       <c r="I22" s="23"/>
     </row>
     <row r="23" spans="1:10" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A23" s="28">
+      <c r="A23" s="27">
         <f t="shared" si="0"/>
         <v>22</v>
       </c>
@@ -13271,7 +13291,7 @@
       <c r="I23" s="23"/>
     </row>
     <row r="24" spans="1:10" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A24" s="28">
+      <c r="A24" s="27">
         <f t="shared" si="0"/>
         <v>23</v>
       </c>
@@ -13285,7 +13305,7 @@
       <c r="I24" s="23"/>
     </row>
     <row r="25" spans="1:10" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A25" s="28">
+      <c r="A25" s="27">
         <f t="shared" si="0"/>
         <v>24</v>
       </c>
@@ -13299,7 +13319,7 @@
       <c r="I25" s="23"/>
     </row>
     <row r="26" spans="1:10" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A26" s="28">
+      <c r="A26" s="27">
         <f t="shared" si="0"/>
         <v>25</v>
       </c>
@@ -13313,7 +13333,7 @@
       <c r="I26" s="23"/>
     </row>
     <row r="27" spans="1:10" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A27" s="28">
+      <c r="A27" s="27">
         <f t="shared" si="0"/>
         <v>26</v>
       </c>
@@ -13327,7 +13347,7 @@
       <c r="I27" s="23"/>
     </row>
     <row r="28" spans="1:10" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A28" s="28">
+      <c r="A28" s="27">
         <f t="shared" si="0"/>
         <v>27</v>
       </c>
@@ -13341,7 +13361,7 @@
       <c r="I28" s="23"/>
     </row>
     <row r="29" spans="1:10" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A29" s="28">
+      <c r="A29" s="27">
         <f t="shared" si="0"/>
         <v>28</v>
       </c>
@@ -13355,7 +13375,7 @@
       <c r="I29" s="23"/>
     </row>
     <row r="30" spans="1:10" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A30" s="28">
+      <c r="A30" s="27">
         <f t="shared" si="0"/>
         <v>29</v>
       </c>
@@ -13385,7 +13405,7 @@
       </c>
     </row>
     <row r="31" spans="1:10" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A31" s="28">
+      <c r="A31" s="27">
         <f t="shared" si="0"/>
         <v>30</v>
       </c>
@@ -13415,46 +13435,46 @@
       </c>
     </row>
     <row r="32" spans="1:10" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A32" s="28">
+      <c r="A32" s="27">
         <f t="shared" si="0"/>
         <v>31</v>
       </c>
-      <c r="B32" s="29">
+      <c r="B32" s="28">
         <v>6407</v>
       </c>
-      <c r="C32" s="29">
+      <c r="C32" s="28">
         <v>8185</v>
       </c>
-      <c r="D32" s="29">
+      <c r="D32" s="28">
         <v>9265</v>
       </c>
-      <c r="E32" s="29">
+      <c r="E32" s="28">
         <v>11802</v>
       </c>
-      <c r="F32" s="29">
+      <c r="F32" s="28">
         <v>1271</v>
       </c>
-      <c r="G32" s="29">
+      <c r="G32" s="28">
         <v>3691</v>
       </c>
-      <c r="H32" s="29">
+      <c r="H32" s="28">
         <v>369</v>
       </c>
-      <c r="I32" s="29">
+      <c r="I32" s="28">
         <v>3321</v>
       </c>
     </row>
     <row r="33" spans="1:9" ht="12.75" x14ac:dyDescent="0.2"/>
     <row r="35" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A35" s="4"/>
-      <c r="B35" s="32"/>
-      <c r="C35" s="31"/>
-      <c r="D35" s="31"/>
-      <c r="E35" s="31"/>
-      <c r="F35" s="31"/>
-      <c r="G35" s="31"/>
-      <c r="H35" s="31"/>
-      <c r="I35" s="31"/>
+      <c r="B35" s="31"/>
+      <c r="C35" s="30"/>
+      <c r="D35" s="30"/>
+      <c r="E35" s="30"/>
+      <c r="F35" s="30"/>
+      <c r="G35" s="30"/>
+      <c r="H35" s="30"/>
+      <c r="I35" s="30"/>
     </row>
     <row r="36" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A36" s="4"/>
@@ -13832,15 +13852,15 @@
       <c r="I69" s="4"/>
     </row>
     <row r="70" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A70" s="32"/>
-      <c r="B70" s="31"/>
-      <c r="C70" s="31"/>
-      <c r="D70" s="31"/>
-      <c r="E70" s="31"/>
-      <c r="F70" s="31"/>
-      <c r="G70" s="31"/>
-      <c r="H70" s="31"/>
-      <c r="I70" s="31"/>
+      <c r="A70" s="31"/>
+      <c r="B70" s="30"/>
+      <c r="C70" s="30"/>
+      <c r="D70" s="30"/>
+      <c r="E70" s="30"/>
+      <c r="F70" s="30"/>
+      <c r="G70" s="30"/>
+      <c r="H70" s="30"/>
+      <c r="I70" s="30"/>
     </row>
     <row r="71" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A71" s="4"/>
@@ -13865,15 +13885,15 @@
       <c r="I72" s="6"/>
     </row>
     <row r="75" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A75" s="30"/>
-      <c r="B75" s="31"/>
-      <c r="C75" s="31"/>
-      <c r="D75" s="31"/>
-      <c r="E75" s="31"/>
-      <c r="F75" s="31"/>
-      <c r="G75" s="31"/>
-      <c r="H75" s="31"/>
-      <c r="I75" s="31"/>
+      <c r="A75" s="29"/>
+      <c r="B75" s="30"/>
+      <c r="C75" s="30"/>
+      <c r="D75" s="30"/>
+      <c r="E75" s="30"/>
+      <c r="F75" s="30"/>
+      <c r="G75" s="30"/>
+      <c r="H75" s="30"/>
+      <c r="I75" s="30"/>
     </row>
     <row r="76" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A76" s="4"/>
@@ -13909,15 +13929,15 @@
       <c r="I78" s="8"/>
     </row>
     <row r="79" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A79" s="33"/>
-      <c r="B79" s="31"/>
-      <c r="C79" s="31"/>
-      <c r="D79" s="31"/>
-      <c r="E79" s="31"/>
-      <c r="F79" s="31"/>
-      <c r="G79" s="31"/>
-      <c r="H79" s="31"/>
-      <c r="I79" s="31"/>
+      <c r="A79" s="32"/>
+      <c r="B79" s="30"/>
+      <c r="C79" s="30"/>
+      <c r="D79" s="30"/>
+      <c r="E79" s="30"/>
+      <c r="F79" s="30"/>
+      <c r="G79" s="30"/>
+      <c r="H79" s="30"/>
+      <c r="I79" s="30"/>
     </row>
     <row r="80" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A80" s="4"/>
@@ -13953,15 +13973,15 @@
       <c r="B85" s="6"/>
     </row>
     <row r="87" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A87" s="30"/>
-      <c r="B87" s="31"/>
-      <c r="C87" s="31"/>
-      <c r="D87" s="31"/>
-      <c r="E87" s="31"/>
-      <c r="F87" s="31"/>
-      <c r="G87" s="31"/>
-      <c r="H87" s="31"/>
-      <c r="I87" s="31"/>
+      <c r="A87" s="29"/>
+      <c r="B87" s="30"/>
+      <c r="C87" s="30"/>
+      <c r="D87" s="30"/>
+      <c r="E87" s="30"/>
+      <c r="F87" s="30"/>
+      <c r="G87" s="30"/>
+      <c r="H87" s="30"/>
+      <c r="I87" s="30"/>
     </row>
     <row r="88" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A88" s="4"/>
@@ -14064,15 +14084,15 @@
       <c r="B98" s="9"/>
     </row>
     <row r="100" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A100" s="32"/>
-      <c r="B100" s="31"/>
-      <c r="C100" s="31"/>
-      <c r="D100" s="31"/>
-      <c r="E100" s="31"/>
-      <c r="F100" s="31"/>
-      <c r="G100" s="31"/>
-      <c r="H100" s="31"/>
-      <c r="I100" s="31"/>
+      <c r="A100" s="31"/>
+      <c r="B100" s="30"/>
+      <c r="C100" s="30"/>
+      <c r="D100" s="30"/>
+      <c r="E100" s="30"/>
+      <c r="F100" s="30"/>
+      <c r="G100" s="30"/>
+      <c r="H100" s="30"/>
+      <c r="I100" s="30"/>
     </row>
     <row r="101" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A101" s="4"/>
@@ -15426,15 +15446,15 @@
       <c r="I68" s="4"/>
     </row>
     <row r="69" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A69" s="32"/>
-      <c r="B69" s="31"/>
-      <c r="C69" s="31"/>
-      <c r="D69" s="31"/>
-      <c r="E69" s="31"/>
-      <c r="F69" s="31"/>
-      <c r="G69" s="31"/>
-      <c r="H69" s="31"/>
-      <c r="I69" s="31"/>
+      <c r="A69" s="31"/>
+      <c r="B69" s="30"/>
+      <c r="C69" s="30"/>
+      <c r="D69" s="30"/>
+      <c r="E69" s="30"/>
+      <c r="F69" s="30"/>
+      <c r="G69" s="30"/>
+      <c r="H69" s="30"/>
+      <c r="I69" s="30"/>
     </row>
     <row r="70" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A70" s="4"/>
@@ -15459,15 +15479,15 @@
       <c r="I71" s="6"/>
     </row>
     <row r="74" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A74" s="30"/>
-      <c r="B74" s="31"/>
-      <c r="C74" s="31"/>
-      <c r="D74" s="31"/>
-      <c r="E74" s="31"/>
-      <c r="F74" s="31"/>
-      <c r="G74" s="31"/>
-      <c r="H74" s="31"/>
-      <c r="I74" s="31"/>
+      <c r="A74" s="29"/>
+      <c r="B74" s="30"/>
+      <c r="C74" s="30"/>
+      <c r="D74" s="30"/>
+      <c r="E74" s="30"/>
+      <c r="F74" s="30"/>
+      <c r="G74" s="30"/>
+      <c r="H74" s="30"/>
+      <c r="I74" s="30"/>
     </row>
     <row r="75" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A75" s="4"/>
@@ -15503,15 +15523,15 @@
       <c r="I77" s="8"/>
     </row>
     <row r="78" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A78" s="33"/>
-      <c r="B78" s="31"/>
-      <c r="C78" s="31"/>
-      <c r="D78" s="31"/>
-      <c r="E78" s="31"/>
-      <c r="F78" s="31"/>
-      <c r="G78" s="31"/>
-      <c r="H78" s="31"/>
-      <c r="I78" s="31"/>
+      <c r="A78" s="32"/>
+      <c r="B78" s="30"/>
+      <c r="C78" s="30"/>
+      <c r="D78" s="30"/>
+      <c r="E78" s="30"/>
+      <c r="F78" s="30"/>
+      <c r="G78" s="30"/>
+      <c r="H78" s="30"/>
+      <c r="I78" s="30"/>
     </row>
     <row r="79" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A79" s="4"/>
@@ -15547,15 +15567,15 @@
       <c r="B84" s="6"/>
     </row>
     <row r="86" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A86" s="30"/>
-      <c r="B86" s="31"/>
-      <c r="C86" s="31"/>
-      <c r="D86" s="31"/>
-      <c r="E86" s="31"/>
-      <c r="F86" s="31"/>
-      <c r="G86" s="31"/>
-      <c r="H86" s="31"/>
-      <c r="I86" s="31"/>
+      <c r="A86" s="29"/>
+      <c r="B86" s="30"/>
+      <c r="C86" s="30"/>
+      <c r="D86" s="30"/>
+      <c r="E86" s="30"/>
+      <c r="F86" s="30"/>
+      <c r="G86" s="30"/>
+      <c r="H86" s="30"/>
+      <c r="I86" s="30"/>
     </row>
     <row r="87" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A87" s="4"/>
@@ -15658,15 +15678,15 @@
       <c r="B97" s="9"/>
     </row>
     <row r="99" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A99" s="32"/>
-      <c r="B99" s="31"/>
-      <c r="C99" s="31"/>
-      <c r="D99" s="31"/>
-      <c r="E99" s="31"/>
-      <c r="F99" s="31"/>
-      <c r="G99" s="31"/>
-      <c r="H99" s="31"/>
-      <c r="I99" s="31"/>
+      <c r="A99" s="31"/>
+      <c r="B99" s="30"/>
+      <c r="C99" s="30"/>
+      <c r="D99" s="30"/>
+      <c r="E99" s="30"/>
+      <c r="F99" s="30"/>
+      <c r="G99" s="30"/>
+      <c r="H99" s="30"/>
+      <c r="I99" s="30"/>
     </row>
     <row r="100" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A100" s="4"/>

--- a/medicao_energia.xlsx
+++ b/medicao_energia.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\sgt.marquezzini\Documents\GitHub\Dashboardenergia\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B939A4BD-AE5A-40F3-9312-B19D0A1CB5F4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{44390E53-CD28-4142-8756-BC4C586AE346}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="19440" windowHeight="15000" firstSheet="5" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="19440" windowHeight="15000" firstSheet="2" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="DEZEMBRO" sheetId="23" r:id="rId1"/>
@@ -144,7 +144,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="5">
+  <fills count="7">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -169,8 +169,20 @@
         <bgColor rgb="FF9FC5E8"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.39997558519241921"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.59999389629810485"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="7">
+  <borders count="9">
     <border>
       <left/>
       <right/>
@@ -258,11 +270,35 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF000000"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color rgb="FF000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="35">
+  <cellXfs count="40">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -342,6 +378,12 @@
     <xf numFmtId="0" fontId="7" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -350,10 +392,19 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="6" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -634,7 +685,7 @@
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
-  <dimension ref="A1:K101"/>
+  <dimension ref="A1:K102"/>
   <sheetFormatPr defaultColWidth="12.5703125" defaultRowHeight="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="19.42578125" customWidth="1"/>
@@ -648,7 +699,7 @@
     <col min="12" max="12" width="3.42578125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A1" s="12" t="s">
         <v>8</v>
       </c>
@@ -677,23 +728,22 @@
         <v>7</v>
       </c>
     </row>
-    <row r="2" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A2" s="1">
+    <row r="2" spans="1:10" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="A2" s="39">
+        <v>0</v>
+      </c>
+      <c r="B2" s="38"/>
+      <c r="C2" s="38"/>
+      <c r="D2" s="38"/>
+      <c r="E2" s="38"/>
+      <c r="F2" s="38"/>
+      <c r="G2" s="38"/>
+      <c r="H2" s="38"/>
+      <c r="I2" s="38"/>
+    </row>
+    <row r="3" spans="1:10" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="A3" s="1">
         <v>1</v>
-      </c>
-      <c r="B2" s="2"/>
-      <c r="C2" s="2"/>
-      <c r="D2" s="2"/>
-      <c r="E2" s="2"/>
-      <c r="F2" s="2"/>
-      <c r="G2" s="2"/>
-      <c r="H2" s="2"/>
-      <c r="I2" s="2"/>
-    </row>
-    <row r="3" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A3" s="1">
-        <f t="shared" ref="A3:A32" si="0">A2+1</f>
-        <v>2</v>
       </c>
       <c r="B3" s="2"/>
       <c r="C3" s="2"/>
@@ -704,10 +754,10 @@
       <c r="H3" s="2"/>
       <c r="I3" s="2"/>
     </row>
-    <row r="4" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A4" s="1">
-        <f t="shared" si="0"/>
-        <v>3</v>
+        <f t="shared" ref="A4:A33" si="0">A3+1</f>
+        <v>2</v>
       </c>
       <c r="B4" s="2"/>
       <c r="C4" s="2"/>
@@ -718,10 +768,10 @@
       <c r="H4" s="2"/>
       <c r="I4" s="2"/>
     </row>
-    <row r="5" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A5" s="1">
         <f t="shared" si="0"/>
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B5" s="2"/>
       <c r="C5" s="2"/>
@@ -732,10 +782,10 @@
       <c r="H5" s="2"/>
       <c r="I5" s="2"/>
     </row>
-    <row r="6" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A6" s="1">
         <f t="shared" si="0"/>
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B6" s="2"/>
       <c r="C6" s="2"/>
@@ -746,10 +796,10 @@
       <c r="H6" s="2"/>
       <c r="I6" s="2"/>
     </row>
-    <row r="7" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A7" s="1">
         <f t="shared" si="0"/>
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B7" s="2"/>
       <c r="C7" s="2"/>
@@ -760,10 +810,10 @@
       <c r="H7" s="2"/>
       <c r="I7" s="2"/>
     </row>
-    <row r="8" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A8" s="1">
         <f t="shared" si="0"/>
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B8" s="2"/>
       <c r="C8" s="2"/>
@@ -774,10 +824,10 @@
       <c r="H8" s="2"/>
       <c r="I8" s="2"/>
     </row>
-    <row r="9" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A9" s="1">
         <f t="shared" si="0"/>
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B9" s="2"/>
       <c r="C9" s="2"/>
@@ -788,10 +838,10 @@
       <c r="H9" s="2"/>
       <c r="I9" s="2"/>
     </row>
-    <row r="10" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A10" s="1">
         <f t="shared" si="0"/>
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B10" s="2"/>
       <c r="C10" s="2"/>
@@ -802,10 +852,10 @@
       <c r="H10" s="2"/>
       <c r="I10" s="2"/>
     </row>
-    <row r="11" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A11" s="1">
         <f t="shared" si="0"/>
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B11" s="2"/>
       <c r="C11" s="2"/>
@@ -816,13 +866,13 @@
       <c r="H11" s="2"/>
       <c r="I11" s="2"/>
     </row>
-    <row r="12" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A12" s="1">
         <f t="shared" si="0"/>
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B12" s="2"/>
-      <c r="C12" s="14"/>
+      <c r="C12" s="2"/>
       <c r="D12" s="2"/>
       <c r="E12" s="2"/>
       <c r="F12" s="2"/>
@@ -830,13 +880,13 @@
       <c r="H12" s="2"/>
       <c r="I12" s="2"/>
     </row>
-    <row r="13" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A13" s="1">
         <f t="shared" si="0"/>
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B13" s="2"/>
-      <c r="C13" s="2"/>
+      <c r="C13" s="14"/>
       <c r="D13" s="2"/>
       <c r="E13" s="2"/>
       <c r="F13" s="2"/>
@@ -844,10 +894,10 @@
       <c r="H13" s="2"/>
       <c r="I13" s="2"/>
     </row>
-    <row r="14" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A14" s="1">
         <f t="shared" si="0"/>
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B14" s="2"/>
       <c r="C14" s="2"/>
@@ -858,10 +908,10 @@
       <c r="H14" s="2"/>
       <c r="I14" s="2"/>
     </row>
-    <row r="15" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A15" s="1">
         <f t="shared" si="0"/>
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B15" s="2"/>
       <c r="C15" s="2"/>
@@ -871,11 +921,12 @@
       <c r="G15" s="2"/>
       <c r="H15" s="2"/>
       <c r="I15" s="2"/>
-    </row>
-    <row r="16" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="J15" s="18"/>
+    </row>
+    <row r="16" spans="1:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A16" s="1">
         <f t="shared" si="0"/>
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B16" s="2"/>
       <c r="C16" s="2"/>
@@ -889,7 +940,7 @@
     <row r="17" spans="1:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A17" s="1">
         <f t="shared" si="0"/>
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B17" s="2"/>
       <c r="C17" s="2"/>
@@ -903,7 +954,7 @@
     <row r="18" spans="1:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A18" s="1">
         <f t="shared" si="0"/>
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B18" s="2"/>
       <c r="C18" s="2"/>
@@ -913,12 +964,11 @@
       <c r="G18" s="2"/>
       <c r="H18" s="2"/>
       <c r="I18" s="2"/>
-      <c r="J18" s="3"/>
     </row>
     <row r="19" spans="1:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A19" s="1">
         <f t="shared" si="0"/>
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B19" s="2"/>
       <c r="C19" s="2"/>
@@ -928,11 +978,12 @@
       <c r="G19" s="2"/>
       <c r="H19" s="2"/>
       <c r="I19" s="2"/>
+      <c r="J19" s="3"/>
     </row>
     <row r="20" spans="1:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A20" s="1">
         <f t="shared" si="0"/>
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B20" s="2"/>
       <c r="C20" s="2"/>
@@ -946,7 +997,7 @@
     <row r="21" spans="1:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A21" s="1">
         <f t="shared" si="0"/>
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B21" s="2"/>
       <c r="C21" s="2"/>
@@ -960,7 +1011,7 @@
     <row r="22" spans="1:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A22" s="1">
         <f t="shared" si="0"/>
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="B22" s="2"/>
       <c r="C22" s="2"/>
@@ -974,7 +1025,7 @@
     <row r="23" spans="1:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A23" s="1">
         <f t="shared" si="0"/>
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B23" s="2"/>
       <c r="C23" s="2"/>
@@ -988,7 +1039,7 @@
     <row r="24" spans="1:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A24" s="1">
         <f t="shared" si="0"/>
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B24" s="2"/>
       <c r="C24" s="2"/>
@@ -1002,7 +1053,7 @@
     <row r="25" spans="1:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A25" s="1">
         <f t="shared" si="0"/>
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B25" s="2"/>
       <c r="C25" s="2"/>
@@ -1014,124 +1065,127 @@
       <c r="I25" s="2"/>
     </row>
     <row r="26" spans="1:10" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A26" s="1">
+      <c r="A26" s="10">
+        <f t="shared" si="0"/>
+        <v>24</v>
+      </c>
+      <c r="B26" s="11"/>
+      <c r="C26" s="11"/>
+      <c r="D26" s="11"/>
+      <c r="E26" s="11"/>
+      <c r="F26" s="11"/>
+      <c r="G26" s="11"/>
+      <c r="H26" s="11"/>
+      <c r="I26" s="11"/>
+    </row>
+    <row r="27" spans="1:10" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="A27" s="27">
         <f t="shared" si="0"/>
         <v>25</v>
       </c>
-      <c r="B26" s="2"/>
-      <c r="C26" s="2"/>
-      <c r="D26" s="2"/>
-      <c r="E26" s="2"/>
-      <c r="F26" s="2"/>
-      <c r="G26" s="2"/>
-      <c r="H26" s="2"/>
-      <c r="I26" s="2"/>
-    </row>
-    <row r="27" spans="1:10" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A27" s="1">
+      <c r="B27" s="29"/>
+      <c r="C27" s="29"/>
+      <c r="D27" s="29"/>
+      <c r="E27" s="29"/>
+      <c r="F27" s="29"/>
+      <c r="G27" s="29"/>
+      <c r="H27" s="29"/>
+      <c r="I27" s="29"/>
+    </row>
+    <row r="28" spans="1:10" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="A28" s="27">
         <f t="shared" si="0"/>
         <v>26</v>
       </c>
-      <c r="B27" s="2"/>
-      <c r="C27" s="2"/>
-      <c r="D27" s="2"/>
-      <c r="E27" s="2"/>
-      <c r="F27" s="2"/>
-      <c r="G27" s="2"/>
-      <c r="H27" s="2"/>
-      <c r="I27" s="2"/>
-    </row>
-    <row r="28" spans="1:10" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A28" s="1">
+      <c r="B28" s="29"/>
+      <c r="C28" s="29"/>
+      <c r="D28" s="29"/>
+      <c r="E28" s="29"/>
+      <c r="F28" s="29"/>
+      <c r="G28" s="29"/>
+      <c r="H28" s="29"/>
+      <c r="I28" s="29"/>
+    </row>
+    <row r="29" spans="1:10" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="A29" s="27">
         <f t="shared" si="0"/>
         <v>27</v>
       </c>
-      <c r="B28" s="2"/>
-      <c r="C28" s="2"/>
-      <c r="D28" s="2"/>
-      <c r="E28" s="2"/>
-      <c r="F28" s="2"/>
-      <c r="G28" s="2"/>
-      <c r="H28" s="2"/>
-      <c r="I28" s="2"/>
-    </row>
-    <row r="29" spans="1:10" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A29" s="1">
+      <c r="B29" s="29"/>
+      <c r="C29" s="29"/>
+      <c r="D29" s="29"/>
+      <c r="E29" s="29"/>
+      <c r="F29" s="29"/>
+      <c r="G29" s="29"/>
+      <c r="H29" s="29"/>
+      <c r="I29" s="29"/>
+    </row>
+    <row r="30" spans="1:10" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="A30" s="27">
         <f t="shared" si="0"/>
         <v>28</v>
       </c>
-      <c r="B29" s="2"/>
-      <c r="C29" s="2"/>
-      <c r="D29" s="2"/>
-      <c r="E29" s="2"/>
-      <c r="F29" s="2"/>
-      <c r="G29" s="2"/>
-      <c r="H29" s="2"/>
-      <c r="I29" s="2"/>
-    </row>
-    <row r="30" spans="1:10" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A30" s="1">
+      <c r="B30" s="29"/>
+      <c r="C30" s="29"/>
+      <c r="D30" s="29"/>
+      <c r="E30" s="29"/>
+      <c r="F30" s="29"/>
+      <c r="G30" s="29"/>
+      <c r="H30" s="29"/>
+      <c r="I30" s="29"/>
+    </row>
+    <row r="31" spans="1:10" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="A31" s="27">
         <f t="shared" si="0"/>
         <v>29</v>
       </c>
-      <c r="B30" s="2"/>
-      <c r="C30" s="2"/>
-      <c r="D30" s="2"/>
-      <c r="E30" s="2"/>
-      <c r="F30" s="2"/>
-      <c r="G30" s="2"/>
-      <c r="H30" s="2"/>
-      <c r="I30" s="2"/>
-    </row>
-    <row r="31" spans="1:10" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A31" s="1">
+      <c r="B31" s="29"/>
+      <c r="C31" s="29"/>
+      <c r="D31" s="29"/>
+      <c r="E31" s="29"/>
+      <c r="F31" s="29"/>
+      <c r="G31" s="29"/>
+      <c r="H31" s="29"/>
+      <c r="I31" s="29"/>
+    </row>
+    <row r="32" spans="1:10" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="A32" s="27">
         <f t="shared" si="0"/>
         <v>30</v>
       </c>
-      <c r="B31" s="2"/>
-      <c r="C31" s="2"/>
-      <c r="D31" s="2"/>
-      <c r="E31" s="2"/>
-      <c r="F31" s="2"/>
-      <c r="G31" s="2"/>
-      <c r="H31" s="2"/>
-      <c r="I31" s="2"/>
-    </row>
-    <row r="32" spans="1:10" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A32" s="10">
+      <c r="B32" s="29"/>
+      <c r="C32" s="29"/>
+      <c r="D32" s="29"/>
+      <c r="E32" s="29"/>
+      <c r="F32" s="29"/>
+      <c r="G32" s="29"/>
+      <c r="H32" s="29"/>
+      <c r="I32" s="29"/>
+    </row>
+    <row r="33" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="A33" s="27">
         <f t="shared" si="0"/>
         <v>31</v>
       </c>
-      <c r="B32" s="11"/>
-      <c r="C32" s="11"/>
-      <c r="D32" s="11"/>
-      <c r="E32" s="11"/>
-      <c r="F32" s="11"/>
-      <c r="G32" s="11"/>
-      <c r="H32" s="11"/>
-      <c r="I32" s="11"/>
-    </row>
-    <row r="34" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A34" s="4"/>
-      <c r="B34" s="31"/>
-      <c r="C34" s="30"/>
-      <c r="D34" s="30"/>
-      <c r="E34" s="30"/>
-      <c r="F34" s="30"/>
-      <c r="G34" s="30"/>
-      <c r="H34" s="30"/>
-      <c r="I34" s="30"/>
+      <c r="B33" s="29"/>
+      <c r="C33" s="29"/>
+      <c r="D33" s="29"/>
+      <c r="E33" s="29"/>
+      <c r="F33" s="29"/>
+      <c r="G33" s="29"/>
+      <c r="H33" s="29"/>
+      <c r="I33" s="29"/>
     </row>
     <row r="35" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A35" s="4"/>
-      <c r="B35" s="4"/>
-      <c r="C35" s="4"/>
-      <c r="D35" s="4"/>
-      <c r="E35" s="4"/>
-      <c r="F35" s="4"/>
-      <c r="G35" s="4"/>
-      <c r="H35" s="4"/>
-      <c r="I35" s="4"/>
+      <c r="B35" s="33"/>
+      <c r="C35" s="32"/>
+      <c r="D35" s="32"/>
+      <c r="E35" s="32"/>
+      <c r="F35" s="32"/>
+      <c r="G35" s="32"/>
+      <c r="H35" s="32"/>
+      <c r="I35" s="32"/>
     </row>
     <row r="36" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A36" s="4"/>
@@ -1308,7 +1362,6 @@
       <c r="G51" s="4"/>
       <c r="H51" s="4"/>
       <c r="I51" s="4"/>
-      <c r="K51" s="3"/>
     </row>
     <row r="52" spans="1:11" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A52" s="4"/>
@@ -1320,6 +1373,7 @@
       <c r="G52" s="4"/>
       <c r="H52" s="4"/>
       <c r="I52" s="4"/>
+      <c r="K52" s="3"/>
     </row>
     <row r="53" spans="1:11" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A53" s="4"/>
@@ -1475,7 +1529,7 @@
       <c r="H66" s="4"/>
       <c r="I66" s="4"/>
     </row>
-    <row r="67" spans="1:9" ht="12.75" hidden="1" x14ac:dyDescent="0.2">
+    <row r="67" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A67" s="4"/>
       <c r="B67" s="4"/>
       <c r="C67" s="4"/>
@@ -1486,7 +1540,7 @@
       <c r="H67" s="4"/>
       <c r="I67" s="4"/>
     </row>
-    <row r="68" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="68" spans="1:9" ht="12.75" hidden="1" x14ac:dyDescent="0.2">
       <c r="A68" s="4"/>
       <c r="B68" s="4"/>
       <c r="C68" s="4"/>
@@ -1498,29 +1552,29 @@
       <c r="I68" s="4"/>
     </row>
     <row r="69" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A69" s="31"/>
-      <c r="B69" s="30"/>
-      <c r="C69" s="30"/>
-      <c r="D69" s="30"/>
-      <c r="E69" s="30"/>
-      <c r="F69" s="30"/>
-      <c r="G69" s="30"/>
-      <c r="H69" s="30"/>
-      <c r="I69" s="30"/>
+      <c r="A69" s="4"/>
+      <c r="B69" s="4"/>
+      <c r="C69" s="4"/>
+      <c r="D69" s="4"/>
+      <c r="E69" s="4"/>
+      <c r="F69" s="4"/>
+      <c r="G69" s="4"/>
+      <c r="H69" s="4"/>
+      <c r="I69" s="4"/>
     </row>
     <row r="70" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A70" s="4"/>
-      <c r="B70" s="6"/>
-      <c r="C70" s="6"/>
-      <c r="D70" s="6"/>
-      <c r="E70" s="6"/>
-      <c r="F70" s="6"/>
-      <c r="G70" s="6"/>
-      <c r="H70" s="6"/>
-      <c r="I70" s="6"/>
+      <c r="A70" s="33"/>
+      <c r="B70" s="32"/>
+      <c r="C70" s="32"/>
+      <c r="D70" s="32"/>
+      <c r="E70" s="32"/>
+      <c r="F70" s="32"/>
+      <c r="G70" s="32"/>
+      <c r="H70" s="32"/>
+      <c r="I70" s="32"/>
     </row>
     <row r="71" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A71" s="6"/>
+      <c r="A71" s="4"/>
       <c r="B71" s="6"/>
       <c r="C71" s="6"/>
       <c r="D71" s="6"/>
@@ -1530,38 +1584,38 @@
       <c r="H71" s="6"/>
       <c r="I71" s="6"/>
     </row>
-    <row r="74" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A74" s="29"/>
-      <c r="B74" s="30"/>
-      <c r="C74" s="30"/>
-      <c r="D74" s="30"/>
-      <c r="E74" s="30"/>
-      <c r="F74" s="30"/>
-      <c r="G74" s="30"/>
-      <c r="H74" s="30"/>
-      <c r="I74" s="30"/>
+    <row r="72" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="A72" s="6"/>
+      <c r="B72" s="6"/>
+      <c r="C72" s="6"/>
+      <c r="D72" s="6"/>
+      <c r="E72" s="6"/>
+      <c r="F72" s="6"/>
+      <c r="G72" s="6"/>
+      <c r="H72" s="6"/>
+      <c r="I72" s="6"/>
     </row>
     <row r="75" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A75" s="4"/>
-      <c r="B75" s="7"/>
-      <c r="C75" s="7"/>
-      <c r="D75" s="7"/>
-      <c r="E75" s="7"/>
-      <c r="F75" s="7"/>
-      <c r="G75" s="7"/>
-      <c r="H75" s="7"/>
-      <c r="I75" s="7"/>
+      <c r="A75" s="31"/>
+      <c r="B75" s="32"/>
+      <c r="C75" s="32"/>
+      <c r="D75" s="32"/>
+      <c r="E75" s="32"/>
+      <c r="F75" s="32"/>
+      <c r="G75" s="32"/>
+      <c r="H75" s="32"/>
+      <c r="I75" s="32"/>
     </row>
     <row r="76" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A76" s="4"/>
-      <c r="B76" s="8"/>
-      <c r="C76" s="8"/>
-      <c r="D76" s="8"/>
-      <c r="E76" s="8"/>
-      <c r="F76" s="8"/>
-      <c r="G76" s="8"/>
-      <c r="H76" s="8"/>
-      <c r="I76" s="8"/>
+      <c r="B76" s="7"/>
+      <c r="C76" s="7"/>
+      <c r="D76" s="7"/>
+      <c r="E76" s="7"/>
+      <c r="F76" s="7"/>
+      <c r="G76" s="7"/>
+      <c r="H76" s="7"/>
+      <c r="I76" s="7"/>
     </row>
     <row r="77" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A77" s="4"/>
@@ -1575,26 +1629,26 @@
       <c r="I77" s="8"/>
     </row>
     <row r="78" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A78" s="32"/>
-      <c r="B78" s="30"/>
-      <c r="C78" s="30"/>
-      <c r="D78" s="30"/>
-      <c r="E78" s="30"/>
-      <c r="F78" s="30"/>
-      <c r="G78" s="30"/>
-      <c r="H78" s="30"/>
-      <c r="I78" s="30"/>
+      <c r="A78" s="4"/>
+      <c r="B78" s="8"/>
+      <c r="C78" s="8"/>
+      <c r="D78" s="8"/>
+      <c r="E78" s="8"/>
+      <c r="F78" s="8"/>
+      <c r="G78" s="8"/>
+      <c r="H78" s="8"/>
+      <c r="I78" s="8"/>
     </row>
     <row r="79" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A79" s="4"/>
-      <c r="B79" s="4"/>
-      <c r="C79" s="4"/>
-      <c r="D79" s="4"/>
-      <c r="E79" s="4"/>
-      <c r="F79" s="4"/>
-      <c r="G79" s="4"/>
-      <c r="H79" s="4"/>
-      <c r="I79" s="4"/>
+      <c r="A79" s="34"/>
+      <c r="B79" s="32"/>
+      <c r="C79" s="32"/>
+      <c r="D79" s="32"/>
+      <c r="E79" s="32"/>
+      <c r="F79" s="32"/>
+      <c r="G79" s="32"/>
+      <c r="H79" s="32"/>
+      <c r="I79" s="32"/>
     </row>
     <row r="80" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A80" s="4"/>
@@ -1607,38 +1661,38 @@
       <c r="H80" s="4"/>
       <c r="I80" s="4"/>
     </row>
-    <row r="82" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A82" s="4"/>
-      <c r="B82" s="4"/>
+    <row r="81" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="A81" s="4"/>
+      <c r="B81" s="4"/>
+      <c r="C81" s="4"/>
+      <c r="D81" s="4"/>
+      <c r="E81" s="4"/>
+      <c r="F81" s="4"/>
+      <c r="G81" s="4"/>
+      <c r="H81" s="4"/>
+      <c r="I81" s="4"/>
     </row>
     <row r="83" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A83" s="4"/>
+      <c r="B83" s="4"/>
     </row>
     <row r="84" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A84" s="4"/>
-      <c r="B84" s="6"/>
-    </row>
-    <row r="86" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A86" s="29"/>
-      <c r="B86" s="30"/>
-      <c r="C86" s="30"/>
-      <c r="D86" s="30"/>
-      <c r="E86" s="30"/>
-      <c r="F86" s="30"/>
-      <c r="G86" s="30"/>
-      <c r="H86" s="30"/>
-      <c r="I86" s="30"/>
+    </row>
+    <row r="85" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="A85" s="4"/>
+      <c r="B85" s="6"/>
     </row>
     <row r="87" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A87" s="4"/>
-      <c r="B87" s="9"/>
-      <c r="C87" s="9"/>
-      <c r="D87" s="9"/>
-      <c r="E87" s="9"/>
-      <c r="F87" s="9"/>
-      <c r="G87" s="9"/>
-      <c r="H87" s="9"/>
-      <c r="I87" s="9"/>
+      <c r="A87" s="31"/>
+      <c r="B87" s="32"/>
+      <c r="C87" s="32"/>
+      <c r="D87" s="32"/>
+      <c r="E87" s="32"/>
+      <c r="F87" s="32"/>
+      <c r="G87" s="32"/>
+      <c r="H87" s="32"/>
+      <c r="I87" s="32"/>
     </row>
     <row r="88" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A88" s="4"/>
@@ -1708,51 +1762,51 @@
     </row>
     <row r="94" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A94" s="4"/>
-      <c r="B94" s="4"/>
-      <c r="C94" s="4"/>
-      <c r="D94" s="4"/>
-      <c r="E94" s="4"/>
-      <c r="F94" s="4"/>
-      <c r="G94" s="4"/>
-      <c r="H94" s="4"/>
-      <c r="I94" s="4"/>
+      <c r="B94" s="9"/>
+      <c r="C94" s="9"/>
+      <c r="D94" s="9"/>
+      <c r="E94" s="9"/>
+      <c r="F94" s="9"/>
+      <c r="G94" s="9"/>
+      <c r="H94" s="9"/>
+      <c r="I94" s="9"/>
     </row>
     <row r="95" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A95" s="4"/>
-      <c r="B95" s="9"/>
+      <c r="B95" s="4"/>
+      <c r="C95" s="4"/>
+      <c r="D95" s="4"/>
+      <c r="E95" s="4"/>
+      <c r="F95" s="4"/>
+      <c r="G95" s="4"/>
+      <c r="H95" s="4"/>
+      <c r="I95" s="4"/>
     </row>
     <row r="96" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A96" s="4"/>
-      <c r="B96" s="4"/>
+      <c r="B96" s="9"/>
     </row>
     <row r="97" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A97" s="4"/>
-      <c r="B97" s="9"/>
-    </row>
-    <row r="99" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A99" s="31"/>
-      <c r="B99" s="30"/>
-      <c r="C99" s="30"/>
-      <c r="D99" s="30"/>
-      <c r="E99" s="30"/>
-      <c r="F99" s="30"/>
-      <c r="G99" s="30"/>
-      <c r="H99" s="30"/>
-      <c r="I99" s="30"/>
+      <c r="B97" s="4"/>
+    </row>
+    <row r="98" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="A98" s="4"/>
+      <c r="B98" s="9"/>
     </row>
     <row r="100" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A100" s="4"/>
-      <c r="B100" s="6"/>
-      <c r="C100" s="6"/>
-      <c r="D100" s="6"/>
-      <c r="E100" s="6"/>
-      <c r="F100" s="6"/>
-      <c r="G100" s="6"/>
-      <c r="H100" s="6"/>
-      <c r="I100" s="6"/>
+      <c r="A100" s="33"/>
+      <c r="B100" s="32"/>
+      <c r="C100" s="32"/>
+      <c r="D100" s="32"/>
+      <c r="E100" s="32"/>
+      <c r="F100" s="32"/>
+      <c r="G100" s="32"/>
+      <c r="H100" s="32"/>
+      <c r="I100" s="32"/>
     </row>
     <row r="101" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A101" s="6"/>
+      <c r="A101" s="4"/>
       <c r="B101" s="6"/>
       <c r="C101" s="6"/>
       <c r="D101" s="6"/>
@@ -1762,17 +1816,28 @@
       <c r="H101" s="6"/>
       <c r="I101" s="6"/>
     </row>
+    <row r="102" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="A102" s="6"/>
+      <c r="B102" s="6"/>
+      <c r="C102" s="6"/>
+      <c r="D102" s="6"/>
+      <c r="E102" s="6"/>
+      <c r="F102" s="6"/>
+      <c r="G102" s="6"/>
+      <c r="H102" s="6"/>
+      <c r="I102" s="6"/>
+    </row>
   </sheetData>
   <mergeCells count="6">
-    <mergeCell ref="A86:I86"/>
-    <mergeCell ref="A99:I99"/>
-    <mergeCell ref="B34:I34"/>
-    <mergeCell ref="A69:I69"/>
-    <mergeCell ref="A74:I74"/>
-    <mergeCell ref="A78:I78"/>
+    <mergeCell ref="A87:I87"/>
+    <mergeCell ref="A100:I100"/>
+    <mergeCell ref="B35:I35"/>
+    <mergeCell ref="A70:I70"/>
+    <mergeCell ref="A75:I75"/>
+    <mergeCell ref="A79:I79"/>
   </mergeCells>
   <dataValidations count="1">
-    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="A87" xr:uid="{F050F62C-8D86-46A3-AAB9-CE151BA0F32F}">
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="A88" xr:uid="{F050F62C-8D86-46A3-AAB9-CE151BA0F32F}">
       <formula1>"Bandeira,Verde,Amarela,Vermelha p1,Vermelha p2"</formula1>
     </dataValidation>
   </dataValidations>
@@ -1785,7 +1850,7 @@
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
-  <dimension ref="A1:J102"/>
+  <dimension ref="A1:J103"/>
   <sheetFormatPr defaultColWidth="12.5703125" defaultRowHeight="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="17.42578125" customWidth="1"/>
@@ -1822,47 +1887,30 @@
       </c>
     </row>
     <row r="2" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A2" s="19">
-        <v>1</v>
-      </c>
-      <c r="B2" s="22">
-        <v>594</v>
-      </c>
-      <c r="C2" s="22">
-        <v>1193</v>
-      </c>
-      <c r="D2" s="22">
-        <v>8925</v>
-      </c>
-      <c r="E2" s="22">
-        <v>10736</v>
-      </c>
-      <c r="F2" s="22">
-        <v>1256</v>
-      </c>
-      <c r="G2" s="22">
-        <v>3235</v>
-      </c>
-      <c r="H2" s="22">
-        <v>321</v>
-      </c>
-      <c r="I2" s="22">
-        <v>2913</v>
-      </c>
+      <c r="A2" s="39">
+        <v>0</v>
+      </c>
+      <c r="B2" s="38"/>
+      <c r="C2" s="38"/>
+      <c r="D2" s="38"/>
+      <c r="E2" s="38"/>
+      <c r="F2" s="38"/>
+      <c r="G2" s="38"/>
+      <c r="H2" s="38"/>
+      <c r="I2" s="38"/>
     </row>
     <row r="3" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A3" s="19">
-        <f t="shared" ref="A3:A32" si="0">A2+1</f>
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B3" s="22">
-        <v>671</v>
+        <v>594</v>
       </c>
       <c r="C3" s="22">
-        <v>1289</v>
+        <v>1193</v>
       </c>
       <c r="D3" s="22">
-        <v>8928</v>
+        <v>8925</v>
       </c>
       <c r="E3" s="22">
         <v>10736</v>
@@ -1871,28 +1919,28 @@
         <v>1256</v>
       </c>
       <c r="G3" s="22">
-        <v>3238</v>
+        <v>3235</v>
       </c>
       <c r="H3" s="22">
         <v>321</v>
       </c>
       <c r="I3" s="22">
-        <v>2917</v>
+        <v>2913</v>
       </c>
     </row>
     <row r="4" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A4" s="19">
-        <f t="shared" si="0"/>
-        <v>3</v>
+        <f t="shared" ref="A4:A33" si="0">A3+1</f>
+        <v>2</v>
       </c>
       <c r="B4" s="22">
-        <v>692</v>
+        <v>671</v>
       </c>
       <c r="C4" s="22">
-        <v>1453</v>
+        <v>1289</v>
       </c>
       <c r="D4" s="22">
-        <v>8931</v>
+        <v>8928</v>
       </c>
       <c r="E4" s="22">
         <v>10736</v>
@@ -1901,143 +1949,143 @@
         <v>1256</v>
       </c>
       <c r="G4" s="22">
-        <v>3243</v>
+        <v>3238</v>
       </c>
       <c r="H4" s="22">
         <v>321</v>
       </c>
       <c r="I4" s="22">
-        <v>2922</v>
+        <v>2917</v>
       </c>
     </row>
     <row r="5" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A5" s="19">
         <f t="shared" si="0"/>
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B5" s="22">
-        <v>728</v>
+        <v>692</v>
       </c>
       <c r="C5" s="22">
-        <v>1501</v>
+        <v>1453</v>
       </c>
       <c r="D5" s="22">
-        <v>8935</v>
+        <v>8931</v>
       </c>
       <c r="E5" s="22">
-        <v>10738</v>
+        <v>10736</v>
       </c>
       <c r="F5" s="22">
         <v>1256</v>
       </c>
       <c r="G5" s="22">
-        <v>3251</v>
+        <v>3243</v>
       </c>
       <c r="H5" s="22">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="I5" s="22">
-        <v>2928</v>
+        <v>2922</v>
       </c>
     </row>
     <row r="6" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A6" s="19">
         <f t="shared" si="0"/>
-        <v>5</v>
-      </c>
-      <c r="B6" s="23"/>
-      <c r="C6" s="23"/>
-      <c r="D6" s="23"/>
-      <c r="E6" s="23"/>
-      <c r="F6" s="23"/>
-      <c r="G6" s="23"/>
-      <c r="H6" s="23"/>
-      <c r="I6" s="23"/>
+        <v>4</v>
+      </c>
+      <c r="B6" s="22">
+        <v>728</v>
+      </c>
+      <c r="C6" s="22">
+        <v>1501</v>
+      </c>
+      <c r="D6" s="22">
+        <v>8935</v>
+      </c>
+      <c r="E6" s="22">
+        <v>10738</v>
+      </c>
+      <c r="F6" s="22">
+        <v>1256</v>
+      </c>
+      <c r="G6" s="22">
+        <v>3251</v>
+      </c>
+      <c r="H6" s="22">
+        <v>322</v>
+      </c>
+      <c r="I6" s="22">
+        <v>2928</v>
+      </c>
     </row>
     <row r="7" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A7" s="19">
         <f t="shared" si="0"/>
-        <v>6</v>
-      </c>
-      <c r="B7" s="22">
-        <v>882</v>
-      </c>
-      <c r="C7" s="22">
-        <v>1705</v>
-      </c>
-      <c r="D7" s="22">
-        <v>8946</v>
-      </c>
-      <c r="E7" s="22">
-        <v>10739</v>
-      </c>
-      <c r="F7" s="22">
-        <v>1256</v>
-      </c>
-      <c r="G7" s="22">
-        <v>3263</v>
-      </c>
-      <c r="H7" s="22">
-        <v>322</v>
-      </c>
-      <c r="I7" s="22">
-        <v>2928</v>
-      </c>
+        <v>5</v>
+      </c>
+      <c r="B7" s="23"/>
+      <c r="C7" s="23"/>
+      <c r="D7" s="23"/>
+      <c r="E7" s="23"/>
+      <c r="F7" s="23"/>
+      <c r="G7" s="23"/>
+      <c r="H7" s="23"/>
+      <c r="I7" s="23"/>
     </row>
     <row r="8" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A8" s="19">
         <f t="shared" si="0"/>
-        <v>7</v>
-      </c>
-      <c r="B8" s="23"/>
-      <c r="C8" s="23"/>
-      <c r="D8" s="23"/>
-      <c r="E8" s="23"/>
-      <c r="F8" s="23"/>
-      <c r="G8" s="23"/>
-      <c r="H8" s="23"/>
-      <c r="I8" s="23"/>
+        <v>6</v>
+      </c>
+      <c r="B8" s="22">
+        <v>882</v>
+      </c>
+      <c r="C8" s="22">
+        <v>1705</v>
+      </c>
+      <c r="D8" s="22">
+        <v>8946</v>
+      </c>
+      <c r="E8" s="22">
+        <v>10739</v>
+      </c>
+      <c r="F8" s="22">
+        <v>1256</v>
+      </c>
+      <c r="G8" s="22">
+        <v>3263</v>
+      </c>
+      <c r="H8" s="22">
+        <v>322</v>
+      </c>
+      <c r="I8" s="22">
+        <v>2928</v>
+      </c>
     </row>
     <row r="9" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A9" s="19">
         <f t="shared" si="0"/>
-        <v>8</v>
-      </c>
-      <c r="B9" s="22">
-        <v>1058</v>
-      </c>
-      <c r="C9" s="22">
-        <v>1995</v>
-      </c>
-      <c r="D9" s="22">
-        <v>8952</v>
-      </c>
-      <c r="E9" s="22">
-        <v>10741</v>
-      </c>
-      <c r="F9" s="22">
-        <v>1257</v>
-      </c>
-      <c r="G9" s="22">
-        <v>3274</v>
-      </c>
-      <c r="H9" s="22">
-        <v>325</v>
-      </c>
-      <c r="I9" s="22">
-        <v>2948</v>
-      </c>
+        <v>7</v>
+      </c>
+      <c r="B9" s="23"/>
+      <c r="C9" s="23"/>
+      <c r="D9" s="23"/>
+      <c r="E9" s="23"/>
+      <c r="F9" s="23"/>
+      <c r="G9" s="23"/>
+      <c r="H9" s="23"/>
+      <c r="I9" s="23"/>
     </row>
     <row r="10" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A10" s="19">
         <f t="shared" si="0"/>
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B10" s="22">
-        <v>1080</v>
+        <v>1058</v>
       </c>
       <c r="C10" s="22">
-        <v>2125</v>
+        <v>1995</v>
       </c>
       <c r="D10" s="22">
         <v>8952</v>
@@ -2049,61 +2097,61 @@
         <v>1257</v>
       </c>
       <c r="G10" s="22">
-        <v>3280</v>
+        <v>3274</v>
       </c>
       <c r="H10" s="22">
         <v>325</v>
       </c>
       <c r="I10" s="22">
-        <v>2955</v>
+        <v>2948</v>
       </c>
     </row>
     <row r="11" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A11" s="19">
         <f t="shared" si="0"/>
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B11" s="22">
-        <v>1135</v>
+        <v>1080</v>
       </c>
       <c r="C11" s="22">
-        <v>2301</v>
+        <v>2125</v>
       </c>
       <c r="D11" s="22">
-        <v>8960</v>
+        <v>8952</v>
       </c>
       <c r="E11" s="22">
-        <v>10742</v>
+        <v>10741</v>
       </c>
       <c r="F11" s="22">
         <v>1257</v>
       </c>
       <c r="G11" s="22">
-        <v>3287</v>
+        <v>3280</v>
       </c>
       <c r="H11" s="22">
         <v>325</v>
       </c>
       <c r="I11" s="22">
-        <v>2962</v>
+        <v>2955</v>
       </c>
     </row>
     <row r="12" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A12" s="19">
         <f t="shared" si="0"/>
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B12" s="22">
-        <v>1230</v>
+        <v>1135</v>
       </c>
       <c r="C12" s="22">
-        <v>2418</v>
+        <v>2301</v>
       </c>
       <c r="D12" s="22">
-        <v>8964</v>
+        <v>8960</v>
       </c>
       <c r="E12" s="22">
-        <v>10743</v>
+        <v>10742</v>
       </c>
       <c r="F12" s="22">
         <v>1257</v>
@@ -2121,150 +2169,150 @@
     <row r="13" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A13" s="19">
         <f t="shared" si="0"/>
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B13" s="22">
-        <v>1347</v>
+        <v>1230</v>
       </c>
       <c r="C13" s="22">
-        <v>2611</v>
+        <v>2418</v>
       </c>
       <c r="D13" s="22">
-        <v>8967</v>
+        <v>8964</v>
       </c>
       <c r="E13" s="22">
-        <v>10744</v>
+        <v>10743</v>
       </c>
       <c r="F13" s="22">
         <v>1257</v>
       </c>
       <c r="G13" s="22">
-        <v>3300</v>
+        <v>3287</v>
       </c>
       <c r="H13" s="22">
-        <v>327</v>
+        <v>325</v>
       </c>
       <c r="I13" s="22">
-        <v>2973</v>
+        <v>2962</v>
       </c>
     </row>
     <row r="14" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A14" s="19">
         <f t="shared" si="0"/>
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B14" s="22">
-        <v>1470</v>
+        <v>1347</v>
       </c>
       <c r="C14" s="22">
-        <v>2681</v>
+        <v>2611</v>
       </c>
       <c r="D14" s="22">
-        <v>8971</v>
+        <v>8967</v>
       </c>
       <c r="E14" s="22">
         <v>10744</v>
       </c>
       <c r="F14" s="22">
-        <v>1258</v>
+        <v>1257</v>
       </c>
       <c r="G14" s="22">
-        <v>3306</v>
+        <v>3300</v>
       </c>
       <c r="H14" s="22">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="I14" s="22">
-        <v>2977</v>
+        <v>2973</v>
       </c>
     </row>
     <row r="15" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A15" s="19">
         <f t="shared" si="0"/>
-        <v>14</v>
-      </c>
-      <c r="B15" s="23"/>
-      <c r="C15" s="23"/>
-      <c r="D15" s="23"/>
-      <c r="E15" s="23"/>
-      <c r="F15" s="23"/>
-      <c r="G15" s="23"/>
-      <c r="H15" s="23"/>
-      <c r="I15" s="23"/>
+        <v>13</v>
+      </c>
+      <c r="B15" s="22">
+        <v>1470</v>
+      </c>
+      <c r="C15" s="22">
+        <v>2681</v>
+      </c>
+      <c r="D15" s="22">
+        <v>8971</v>
+      </c>
+      <c r="E15" s="22">
+        <v>10744</v>
+      </c>
+      <c r="F15" s="22">
+        <v>1258</v>
+      </c>
+      <c r="G15" s="22">
+        <v>3306</v>
+      </c>
+      <c r="H15" s="22">
+        <v>328</v>
+      </c>
+      <c r="I15" s="22">
+        <v>2977</v>
+      </c>
     </row>
     <row r="16" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A16" s="19">
         <f t="shared" si="0"/>
-        <v>15</v>
-      </c>
-      <c r="B16" s="22">
-        <v>1674</v>
-      </c>
-      <c r="C16" s="22">
-        <v>2914</v>
-      </c>
-      <c r="D16" s="22">
-        <v>8979</v>
-      </c>
-      <c r="E16" s="22">
-        <v>10745</v>
-      </c>
-      <c r="F16" s="22">
-        <v>1258</v>
-      </c>
-      <c r="G16" s="22">
-        <v>3317</v>
-      </c>
-      <c r="H16" s="22">
-        <v>329</v>
-      </c>
-      <c r="I16" s="22">
-        <v>2988</v>
-      </c>
+        <v>14</v>
+      </c>
+      <c r="B16" s="23"/>
+      <c r="C16" s="23"/>
+      <c r="D16" s="23"/>
+      <c r="E16" s="23"/>
+      <c r="F16" s="23"/>
+      <c r="G16" s="23"/>
+      <c r="H16" s="23"/>
+      <c r="I16" s="23"/>
     </row>
     <row r="17" spans="1:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A17" s="19">
         <f t="shared" si="0"/>
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B17" s="22">
-        <v>1690</v>
+        <v>1674</v>
       </c>
       <c r="C17" s="22">
-        <v>2986</v>
+        <v>2914</v>
       </c>
       <c r="D17" s="22">
         <v>8979</v>
       </c>
       <c r="E17" s="22">
-        <v>10747</v>
+        <v>10745</v>
       </c>
       <c r="F17" s="22">
         <v>1258</v>
       </c>
       <c r="G17" s="22">
-        <v>3324</v>
+        <v>3317</v>
       </c>
       <c r="H17" s="22">
         <v>329</v>
       </c>
       <c r="I17" s="22">
-        <v>2994</v>
+        <v>2988</v>
       </c>
     </row>
     <row r="18" spans="1:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A18" s="19">
         <f t="shared" si="0"/>
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B18" s="22">
-        <v>1733</v>
+        <v>1690</v>
       </c>
       <c r="C18" s="22">
-        <v>3061</v>
+        <v>2986</v>
       </c>
       <c r="D18" s="22">
-        <v>8985</v>
+        <v>8979</v>
       </c>
       <c r="E18" s="22">
         <v>10747</v>
@@ -2273,89 +2321,89 @@
         <v>1258</v>
       </c>
       <c r="G18" s="22">
-        <v>3330</v>
+        <v>3324</v>
       </c>
       <c r="H18" s="22">
         <v>329</v>
       </c>
       <c r="I18" s="22">
-        <v>3000</v>
-      </c>
-      <c r="J18" s="3"/>
+        <v>2994</v>
+      </c>
     </row>
     <row r="19" spans="1:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A19" s="19">
         <f t="shared" si="0"/>
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B19" s="22">
-        <v>1859</v>
+        <v>1733</v>
       </c>
       <c r="C19" s="22">
-        <v>3301</v>
+        <v>3061</v>
       </c>
       <c r="D19" s="22">
-        <v>8988</v>
+        <v>8985</v>
       </c>
       <c r="E19" s="22">
-        <v>10748</v>
+        <v>10747</v>
       </c>
       <c r="F19" s="22">
         <v>1258</v>
       </c>
       <c r="G19" s="22">
-        <v>3336</v>
+        <v>3330</v>
       </c>
       <c r="H19" s="22">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="I19" s="22">
-        <v>3005</v>
-      </c>
+        <v>3000</v>
+      </c>
+      <c r="J19" s="3"/>
     </row>
     <row r="20" spans="1:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A20" s="19">
         <f t="shared" si="0"/>
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B20" s="22">
-        <v>1951</v>
+        <v>1859</v>
       </c>
       <c r="C20" s="22">
-        <v>3368</v>
+        <v>3301</v>
       </c>
       <c r="D20" s="22">
-        <v>8992</v>
+        <v>8988</v>
       </c>
       <c r="E20" s="22">
-        <v>10749</v>
+        <v>10748</v>
       </c>
       <c r="F20" s="22">
         <v>1258</v>
       </c>
       <c r="G20" s="22">
-        <v>3342</v>
+        <v>3336</v>
       </c>
       <c r="H20" s="22">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="I20" s="22">
-        <v>3010</v>
+        <v>3005</v>
       </c>
     </row>
     <row r="21" spans="1:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A21" s="19">
         <f t="shared" si="0"/>
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B21" s="22">
-        <v>2048</v>
+        <v>1951</v>
       </c>
       <c r="C21" s="22">
-        <v>3506</v>
+        <v>3368</v>
       </c>
       <c r="D21" s="22">
-        <v>8995</v>
+        <v>8992</v>
       </c>
       <c r="E21" s="22">
         <v>10749</v>
@@ -2364,28 +2412,28 @@
         <v>1258</v>
       </c>
       <c r="G21" s="22">
-        <v>3347</v>
+        <v>3342</v>
       </c>
       <c r="H21" s="22">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="I21" s="22">
-        <v>3015</v>
+        <v>3010</v>
       </c>
     </row>
     <row r="22" spans="1:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A22" s="19">
         <f t="shared" si="0"/>
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="B22" s="22">
-        <v>2170</v>
+        <v>2048</v>
       </c>
       <c r="C22" s="22">
-        <v>3628</v>
+        <v>3506</v>
       </c>
       <c r="D22" s="22">
-        <v>8985</v>
+        <v>8995</v>
       </c>
       <c r="E22" s="22">
         <v>10749</v>
@@ -2394,58 +2442,58 @@
         <v>1258</v>
       </c>
       <c r="G22" s="22">
-        <v>3350</v>
+        <v>3347</v>
       </c>
       <c r="H22" s="22">
-        <v>333</v>
+        <v>332</v>
       </c>
       <c r="I22" s="22">
-        <v>3017</v>
+        <v>3015</v>
       </c>
     </row>
     <row r="23" spans="1:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A23" s="19">
         <f t="shared" si="0"/>
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B23" s="22">
-        <v>2199</v>
+        <v>2170</v>
       </c>
       <c r="C23" s="22">
-        <v>3713</v>
+        <v>3628</v>
       </c>
       <c r="D23" s="22">
-        <v>8999</v>
+        <v>8985</v>
       </c>
       <c r="E23" s="22">
-        <v>10752</v>
+        <v>10749</v>
       </c>
       <c r="F23" s="22">
-        <v>1259</v>
+        <v>1258</v>
       </c>
       <c r="G23" s="22">
-        <v>3356</v>
+        <v>3350</v>
       </c>
       <c r="H23" s="22">
-        <v>334</v>
+        <v>333</v>
       </c>
       <c r="I23" s="22">
-        <v>3021</v>
+        <v>3017</v>
       </c>
     </row>
     <row r="24" spans="1:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A24" s="19">
         <f t="shared" si="0"/>
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B24" s="22">
-        <v>2248</v>
+        <v>2199</v>
       </c>
       <c r="C24" s="22">
-        <v>3790</v>
+        <v>3713</v>
       </c>
       <c r="D24" s="22">
-        <v>9004</v>
+        <v>8999</v>
       </c>
       <c r="E24" s="22">
         <v>10752</v>
@@ -2454,58 +2502,58 @@
         <v>1259</v>
       </c>
       <c r="G24" s="22">
-        <v>3364</v>
+        <v>3356</v>
       </c>
       <c r="H24" s="22">
         <v>334</v>
       </c>
       <c r="I24" s="22">
-        <v>3023</v>
+        <v>3021</v>
       </c>
     </row>
     <row r="25" spans="1:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A25" s="19">
         <f t="shared" si="0"/>
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B25" s="22">
-        <v>2286</v>
+        <v>2248</v>
       </c>
       <c r="C25" s="22">
         <v>3790</v>
       </c>
       <c r="D25" s="22">
-        <v>9009</v>
+        <v>9004</v>
       </c>
       <c r="E25" s="22">
-        <v>10753</v>
+        <v>10752</v>
       </c>
       <c r="F25" s="22">
         <v>1259</v>
       </c>
       <c r="G25" s="22">
-        <v>3369</v>
+        <v>3364</v>
       </c>
       <c r="H25" s="22">
         <v>334</v>
       </c>
       <c r="I25" s="22">
-        <v>3035</v>
+        <v>3023</v>
       </c>
     </row>
     <row r="26" spans="1:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A26" s="19">
         <f t="shared" si="0"/>
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B26" s="22">
-        <v>2384</v>
+        <v>2286</v>
       </c>
       <c r="C26" s="22">
-        <v>3934</v>
+        <v>3790</v>
       </c>
       <c r="D26" s="22">
-        <v>9011</v>
+        <v>9009</v>
       </c>
       <c r="E26" s="22">
         <v>10753</v>
@@ -2514,58 +2562,58 @@
         <v>1259</v>
       </c>
       <c r="G26" s="22">
-        <v>3371</v>
+        <v>3369</v>
       </c>
       <c r="H26" s="22">
         <v>334</v>
       </c>
       <c r="I26" s="22">
-        <v>3036</v>
+        <v>3035</v>
       </c>
     </row>
     <row r="27" spans="1:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A27" s="19">
         <f t="shared" si="0"/>
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B27" s="22">
-        <v>2452</v>
+        <v>2384</v>
       </c>
       <c r="C27" s="22">
-        <v>4054</v>
+        <v>3934</v>
       </c>
       <c r="D27" s="22">
-        <v>9015</v>
+        <v>9011</v>
       </c>
       <c r="E27" s="22">
-        <v>10755</v>
+        <v>10753</v>
       </c>
       <c r="F27" s="22">
         <v>1259</v>
       </c>
       <c r="G27" s="22">
-        <v>3379</v>
+        <v>3371</v>
       </c>
       <c r="H27" s="22">
-        <v>336</v>
+        <v>334</v>
       </c>
       <c r="I27" s="22">
-        <v>3043</v>
+        <v>3036</v>
       </c>
     </row>
     <row r="28" spans="1:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A28" s="19">
         <f t="shared" si="0"/>
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="B28" s="22">
-        <v>2601</v>
+        <v>2452</v>
       </c>
       <c r="C28" s="22">
-        <v>4174</v>
+        <v>4054</v>
       </c>
       <c r="D28" s="22">
-        <v>9017</v>
+        <v>9015</v>
       </c>
       <c r="E28" s="22">
         <v>10755</v>
@@ -2574,88 +2622,88 @@
         <v>1259</v>
       </c>
       <c r="G28" s="22">
-        <v>3384</v>
+        <v>3379</v>
       </c>
       <c r="H28" s="22">
         <v>336</v>
       </c>
       <c r="I28" s="22">
-        <v>3048</v>
+        <v>3043</v>
       </c>
     </row>
     <row r="29" spans="1:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A29" s="19">
         <f t="shared" si="0"/>
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="B29" s="22">
-        <v>2674</v>
+        <v>2601</v>
       </c>
       <c r="C29" s="22">
-        <v>4247</v>
+        <v>4174</v>
       </c>
       <c r="D29" s="22">
-        <v>9020</v>
+        <v>9017</v>
       </c>
       <c r="E29" s="22">
-        <v>10756</v>
+        <v>10755</v>
       </c>
       <c r="F29" s="22">
-        <v>1260</v>
+        <v>1259</v>
       </c>
       <c r="G29" s="22">
-        <v>3390</v>
+        <v>3384</v>
       </c>
       <c r="H29" s="22">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="I29" s="22">
-        <v>3052</v>
+        <v>3048</v>
       </c>
     </row>
     <row r="30" spans="1:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A30" s="19">
         <f t="shared" si="0"/>
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="B30" s="22">
-        <v>2742</v>
+        <v>2674</v>
       </c>
       <c r="C30" s="22">
-        <v>4306</v>
+        <v>4247</v>
       </c>
       <c r="D30" s="22">
         <v>9020</v>
       </c>
       <c r="E30" s="22">
-        <v>10757</v>
+        <v>10756</v>
       </c>
       <c r="F30" s="22">
         <v>1260</v>
       </c>
       <c r="G30" s="22">
-        <v>3395</v>
+        <v>3390</v>
       </c>
       <c r="H30" s="22">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="I30" s="22">
-        <v>3057</v>
+        <v>3052</v>
       </c>
     </row>
     <row r="31" spans="1:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A31" s="19">
         <f t="shared" si="0"/>
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B31" s="22">
-        <v>2801</v>
+        <v>2742</v>
       </c>
       <c r="C31" s="22">
-        <v>4403</v>
+        <v>4306</v>
       </c>
       <c r="D31" s="22">
-        <v>9034</v>
+        <v>9020</v>
       </c>
       <c r="E31" s="22">
         <v>10757</v>
@@ -2664,67 +2712,86 @@
         <v>1260</v>
       </c>
       <c r="G31" s="22">
-        <v>3402</v>
+        <v>3395</v>
       </c>
       <c r="H31" s="22">
         <v>338</v>
       </c>
       <c r="I31" s="22">
-        <v>3063</v>
+        <v>3057</v>
       </c>
     </row>
     <row r="32" spans="1:10" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A32" s="20">
-        <f t="shared" si="0"/>
-        <v>31</v>
+      <c r="A32" s="19">
+        <f t="shared" si="0"/>
+        <v>30</v>
       </c>
       <c r="B32" s="22">
-        <v>2812</v>
+        <v>2801</v>
       </c>
       <c r="C32" s="22">
-        <v>4489</v>
+        <v>4403</v>
       </c>
       <c r="D32" s="22">
-        <v>9036</v>
+        <v>9034</v>
       </c>
       <c r="E32" s="22">
-        <v>10758</v>
+        <v>10757</v>
       </c>
       <c r="F32" s="22">
         <v>1260</v>
       </c>
       <c r="G32" s="22">
-        <v>3408</v>
+        <v>3402</v>
       </c>
       <c r="H32" s="22">
         <v>338</v>
       </c>
       <c r="I32" s="22">
+        <v>3063</v>
+      </c>
+    </row>
+    <row r="33" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="A33" s="20">
+        <f t="shared" si="0"/>
+        <v>31</v>
+      </c>
+      <c r="B33" s="22">
+        <v>2812</v>
+      </c>
+      <c r="C33" s="22">
+        <v>4489</v>
+      </c>
+      <c r="D33" s="22">
+        <v>9036</v>
+      </c>
+      <c r="E33" s="22">
+        <v>10758</v>
+      </c>
+      <c r="F33" s="22">
+        <v>1260</v>
+      </c>
+      <c r="G33" s="22">
+        <v>3408</v>
+      </c>
+      <c r="H33" s="22">
+        <v>338</v>
+      </c>
+      <c r="I33" s="22">
         <v>3069</v>
       </c>
     </row>
-    <row r="33" spans="1:9" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="35" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A35" s="4"/>
-      <c r="B35" s="31"/>
-      <c r="C35" s="30"/>
-      <c r="D35" s="30"/>
-      <c r="E35" s="30"/>
-      <c r="F35" s="30"/>
-      <c r="G35" s="30"/>
-      <c r="H35" s="30"/>
-      <c r="I35" s="30"/>
-    </row>
+    <row r="34" spans="1:9" ht="12.75" x14ac:dyDescent="0.2"/>
     <row r="36" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A36" s="4"/>
-      <c r="B36" s="4"/>
-      <c r="C36" s="4"/>
-      <c r="D36" s="4"/>
-      <c r="E36" s="4"/>
-      <c r="F36" s="4"/>
-      <c r="G36" s="4"/>
-      <c r="H36" s="4"/>
-      <c r="I36" s="4"/>
+      <c r="B36" s="33"/>
+      <c r="C36" s="32"/>
+      <c r="D36" s="32"/>
+      <c r="E36" s="32"/>
+      <c r="F36" s="32"/>
+      <c r="G36" s="32"/>
+      <c r="H36" s="32"/>
+      <c r="I36" s="32"/>
     </row>
     <row r="37" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A37" s="4"/>
@@ -3090,29 +3157,29 @@
       <c r="I69" s="4"/>
     </row>
     <row r="70" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A70" s="31"/>
-      <c r="B70" s="30"/>
-      <c r="C70" s="30"/>
-      <c r="D70" s="30"/>
-      <c r="E70" s="30"/>
-      <c r="F70" s="30"/>
-      <c r="G70" s="30"/>
-      <c r="H70" s="30"/>
-      <c r="I70" s="30"/>
+      <c r="A70" s="4"/>
+      <c r="B70" s="4"/>
+      <c r="C70" s="4"/>
+      <c r="D70" s="4"/>
+      <c r="E70" s="4"/>
+      <c r="F70" s="4"/>
+      <c r="G70" s="4"/>
+      <c r="H70" s="4"/>
+      <c r="I70" s="4"/>
     </row>
     <row r="71" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A71" s="4"/>
-      <c r="B71" s="6"/>
-      <c r="C71" s="6"/>
-      <c r="D71" s="6"/>
-      <c r="E71" s="6"/>
-      <c r="F71" s="6"/>
-      <c r="G71" s="6"/>
-      <c r="H71" s="6"/>
-      <c r="I71" s="6"/>
+      <c r="A71" s="33"/>
+      <c r="B71" s="32"/>
+      <c r="C71" s="32"/>
+      <c r="D71" s="32"/>
+      <c r="E71" s="32"/>
+      <c r="F71" s="32"/>
+      <c r="G71" s="32"/>
+      <c r="H71" s="32"/>
+      <c r="I71" s="32"/>
     </row>
     <row r="72" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A72" s="6"/>
+      <c r="A72" s="4"/>
       <c r="B72" s="6"/>
       <c r="C72" s="6"/>
       <c r="D72" s="6"/>
@@ -3122,38 +3189,38 @@
       <c r="H72" s="6"/>
       <c r="I72" s="6"/>
     </row>
-    <row r="75" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A75" s="29"/>
-      <c r="B75" s="30"/>
-      <c r="C75" s="30"/>
-      <c r="D75" s="30"/>
-      <c r="E75" s="30"/>
-      <c r="F75" s="30"/>
-      <c r="G75" s="30"/>
-      <c r="H75" s="30"/>
-      <c r="I75" s="30"/>
+    <row r="73" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="A73" s="6"/>
+      <c r="B73" s="6"/>
+      <c r="C73" s="6"/>
+      <c r="D73" s="6"/>
+      <c r="E73" s="6"/>
+      <c r="F73" s="6"/>
+      <c r="G73" s="6"/>
+      <c r="H73" s="6"/>
+      <c r="I73" s="6"/>
     </row>
     <row r="76" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A76" s="4"/>
-      <c r="B76" s="7"/>
-      <c r="C76" s="7"/>
-      <c r="D76" s="7"/>
-      <c r="E76" s="7"/>
-      <c r="F76" s="7"/>
-      <c r="G76" s="7"/>
-      <c r="H76" s="7"/>
-      <c r="I76" s="7"/>
+      <c r="A76" s="31"/>
+      <c r="B76" s="32"/>
+      <c r="C76" s="32"/>
+      <c r="D76" s="32"/>
+      <c r="E76" s="32"/>
+      <c r="F76" s="32"/>
+      <c r="G76" s="32"/>
+      <c r="H76" s="32"/>
+      <c r="I76" s="32"/>
     </row>
     <row r="77" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A77" s="4"/>
-      <c r="B77" s="8"/>
-      <c r="C77" s="8"/>
-      <c r="D77" s="8"/>
-      <c r="E77" s="8"/>
-      <c r="F77" s="8"/>
-      <c r="G77" s="8"/>
-      <c r="H77" s="8"/>
-      <c r="I77" s="8"/>
+      <c r="B77" s="7"/>
+      <c r="C77" s="7"/>
+      <c r="D77" s="7"/>
+      <c r="E77" s="7"/>
+      <c r="F77" s="7"/>
+      <c r="G77" s="7"/>
+      <c r="H77" s="7"/>
+      <c r="I77" s="7"/>
     </row>
     <row r="78" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A78" s="4"/>
@@ -3167,26 +3234,26 @@
       <c r="I78" s="8"/>
     </row>
     <row r="79" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A79" s="32"/>
-      <c r="B79" s="30"/>
-      <c r="C79" s="30"/>
-      <c r="D79" s="30"/>
-      <c r="E79" s="30"/>
-      <c r="F79" s="30"/>
-      <c r="G79" s="30"/>
-      <c r="H79" s="30"/>
-      <c r="I79" s="30"/>
+      <c r="A79" s="4"/>
+      <c r="B79" s="8"/>
+      <c r="C79" s="8"/>
+      <c r="D79" s="8"/>
+      <c r="E79" s="8"/>
+      <c r="F79" s="8"/>
+      <c r="G79" s="8"/>
+      <c r="H79" s="8"/>
+      <c r="I79" s="8"/>
     </row>
     <row r="80" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A80" s="4"/>
-      <c r="B80" s="4"/>
-      <c r="C80" s="4"/>
-      <c r="D80" s="4"/>
-      <c r="E80" s="4"/>
-      <c r="F80" s="4"/>
-      <c r="G80" s="4"/>
-      <c r="H80" s="4"/>
-      <c r="I80" s="4"/>
+      <c r="A80" s="34"/>
+      <c r="B80" s="32"/>
+      <c r="C80" s="32"/>
+      <c r="D80" s="32"/>
+      <c r="E80" s="32"/>
+      <c r="F80" s="32"/>
+      <c r="G80" s="32"/>
+      <c r="H80" s="32"/>
+      <c r="I80" s="32"/>
     </row>
     <row r="81" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A81" s="4"/>
@@ -3199,38 +3266,38 @@
       <c r="H81" s="4"/>
       <c r="I81" s="4"/>
     </row>
-    <row r="83" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A83" s="4"/>
-      <c r="B83" s="4"/>
+    <row r="82" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="A82" s="4"/>
+      <c r="B82" s="4"/>
+      <c r="C82" s="4"/>
+      <c r="D82" s="4"/>
+      <c r="E82" s="4"/>
+      <c r="F82" s="4"/>
+      <c r="G82" s="4"/>
+      <c r="H82" s="4"/>
+      <c r="I82" s="4"/>
     </row>
     <row r="84" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A84" s="4"/>
+      <c r="B84" s="4"/>
     </row>
     <row r="85" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A85" s="4"/>
-      <c r="B85" s="6"/>
-    </row>
-    <row r="87" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A87" s="29"/>
-      <c r="B87" s="30"/>
-      <c r="C87" s="30"/>
-      <c r="D87" s="30"/>
-      <c r="E87" s="30"/>
-      <c r="F87" s="30"/>
-      <c r="G87" s="30"/>
-      <c r="H87" s="30"/>
-      <c r="I87" s="30"/>
+    </row>
+    <row r="86" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="A86" s="4"/>
+      <c r="B86" s="6"/>
     </row>
     <row r="88" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A88" s="4"/>
-      <c r="B88" s="9"/>
-      <c r="C88" s="9"/>
-      <c r="D88" s="9"/>
-      <c r="E88" s="9"/>
-      <c r="F88" s="9"/>
-      <c r="G88" s="9"/>
-      <c r="H88" s="9"/>
-      <c r="I88" s="9"/>
+      <c r="A88" s="31"/>
+      <c r="B88" s="32"/>
+      <c r="C88" s="32"/>
+      <c r="D88" s="32"/>
+      <c r="E88" s="32"/>
+      <c r="F88" s="32"/>
+      <c r="G88" s="32"/>
+      <c r="H88" s="32"/>
+      <c r="I88" s="32"/>
     </row>
     <row r="89" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A89" s="4"/>
@@ -3300,51 +3367,51 @@
     </row>
     <row r="95" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A95" s="4"/>
-      <c r="B95" s="4"/>
-      <c r="C95" s="4"/>
-      <c r="D95" s="4"/>
-      <c r="E95" s="4"/>
-      <c r="F95" s="4"/>
-      <c r="G95" s="4"/>
-      <c r="H95" s="4"/>
-      <c r="I95" s="4"/>
+      <c r="B95" s="9"/>
+      <c r="C95" s="9"/>
+      <c r="D95" s="9"/>
+      <c r="E95" s="9"/>
+      <c r="F95" s="9"/>
+      <c r="G95" s="9"/>
+      <c r="H95" s="9"/>
+      <c r="I95" s="9"/>
     </row>
     <row r="96" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A96" s="4"/>
-      <c r="B96" s="9"/>
+      <c r="B96" s="4"/>
+      <c r="C96" s="4"/>
+      <c r="D96" s="4"/>
+      <c r="E96" s="4"/>
+      <c r="F96" s="4"/>
+      <c r="G96" s="4"/>
+      <c r="H96" s="4"/>
+      <c r="I96" s="4"/>
     </row>
     <row r="97" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A97" s="4"/>
-      <c r="B97" s="4"/>
+      <c r="B97" s="9"/>
     </row>
     <row r="98" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A98" s="4"/>
-      <c r="B98" s="9"/>
-    </row>
-    <row r="100" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A100" s="31"/>
-      <c r="B100" s="30"/>
-      <c r="C100" s="30"/>
-      <c r="D100" s="30"/>
-      <c r="E100" s="30"/>
-      <c r="F100" s="30"/>
-      <c r="G100" s="30"/>
-      <c r="H100" s="30"/>
-      <c r="I100" s="30"/>
+      <c r="B98" s="4"/>
+    </row>
+    <row r="99" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="A99" s="4"/>
+      <c r="B99" s="9"/>
     </row>
     <row r="101" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A101" s="4"/>
-      <c r="B101" s="6"/>
-      <c r="C101" s="6"/>
-      <c r="D101" s="6"/>
-      <c r="E101" s="6"/>
-      <c r="F101" s="6"/>
-      <c r="G101" s="6"/>
-      <c r="H101" s="6"/>
-      <c r="I101" s="6"/>
+      <c r="A101" s="33"/>
+      <c r="B101" s="32"/>
+      <c r="C101" s="32"/>
+      <c r="D101" s="32"/>
+      <c r="E101" s="32"/>
+      <c r="F101" s="32"/>
+      <c r="G101" s="32"/>
+      <c r="H101" s="32"/>
+      <c r="I101" s="32"/>
     </row>
     <row r="102" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A102" s="6"/>
+      <c r="A102" s="4"/>
       <c r="B102" s="6"/>
       <c r="C102" s="6"/>
       <c r="D102" s="6"/>
@@ -3354,17 +3421,28 @@
       <c r="H102" s="6"/>
       <c r="I102" s="6"/>
     </row>
+    <row r="103" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="A103" s="6"/>
+      <c r="B103" s="6"/>
+      <c r="C103" s="6"/>
+      <c r="D103" s="6"/>
+      <c r="E103" s="6"/>
+      <c r="F103" s="6"/>
+      <c r="G103" s="6"/>
+      <c r="H103" s="6"/>
+      <c r="I103" s="6"/>
+    </row>
   </sheetData>
   <mergeCells count="6">
-    <mergeCell ref="A79:I79"/>
-    <mergeCell ref="A87:I87"/>
-    <mergeCell ref="A100:I100"/>
-    <mergeCell ref="B35:I35"/>
-    <mergeCell ref="A70:I70"/>
-    <mergeCell ref="A75:I75"/>
+    <mergeCell ref="A80:I80"/>
+    <mergeCell ref="A88:I88"/>
+    <mergeCell ref="A101:I101"/>
+    <mergeCell ref="B36:I36"/>
+    <mergeCell ref="A71:I71"/>
+    <mergeCell ref="A76:I76"/>
   </mergeCells>
   <dataValidations count="1">
-    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="A88" xr:uid="{00000000-0002-0000-0B00-000000000000}">
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="A89" xr:uid="{00000000-0002-0000-0B00-000000000000}">
       <formula1>"Bandeira,Verde,Amarela,Vermelha p1,Vermelha p2"</formula1>
     </dataValidation>
   </dataValidations>
@@ -3377,7 +3455,7 @@
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
-  <dimension ref="A1:J102"/>
+  <dimension ref="A1:J100"/>
   <sheetFormatPr defaultColWidth="12.5703125" defaultRowHeight="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="17.7109375" customWidth="1"/>
@@ -3414,22 +3492,21 @@
       </c>
     </row>
     <row r="2" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A2" s="1">
-        <v>1</v>
-      </c>
-      <c r="B2" s="2"/>
-      <c r="C2" s="2"/>
-      <c r="D2" s="2"/>
-      <c r="E2" s="2"/>
-      <c r="F2" s="2"/>
-      <c r="G2" s="2"/>
-      <c r="H2" s="2"/>
-      <c r="I2" s="2"/>
+      <c r="A2" s="39">
+        <v>0</v>
+      </c>
+      <c r="B2" s="38"/>
+      <c r="C2" s="38"/>
+      <c r="D2" s="38"/>
+      <c r="E2" s="38"/>
+      <c r="F2" s="38"/>
+      <c r="G2" s="38"/>
+      <c r="H2" s="38"/>
+      <c r="I2" s="38"/>
     </row>
     <row r="3" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A3" s="1">
-        <f t="shared" ref="A3:A32" si="0">A2+1</f>
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B3" s="2"/>
       <c r="C3" s="2"/>
@@ -3442,8 +3519,8 @@
     </row>
     <row r="4" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A4" s="1">
-        <f t="shared" si="0"/>
-        <v>3</v>
+        <f t="shared" ref="A4:A30" si="0">A3+1</f>
+        <v>2</v>
       </c>
       <c r="B4" s="2"/>
       <c r="C4" s="2"/>
@@ -3457,7 +3534,7 @@
     <row r="5" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A5" s="1">
         <f t="shared" si="0"/>
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B5" s="2"/>
       <c r="C5" s="2"/>
@@ -3471,7 +3548,7 @@
     <row r="6" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A6" s="1">
         <f t="shared" si="0"/>
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B6" s="2"/>
       <c r="C6" s="2"/>
@@ -3485,7 +3562,7 @@
     <row r="7" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A7" s="1">
         <f t="shared" si="0"/>
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B7" s="2"/>
       <c r="C7" s="2"/>
@@ -3499,7 +3576,7 @@
     <row r="8" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A8" s="1">
         <f t="shared" si="0"/>
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B8" s="2"/>
       <c r="C8" s="2"/>
@@ -3513,7 +3590,7 @@
     <row r="9" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A9" s="1">
         <f t="shared" si="0"/>
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B9" s="2"/>
       <c r="C9" s="2"/>
@@ -3527,7 +3604,7 @@
     <row r="10" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A10" s="1">
         <f t="shared" si="0"/>
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B10" s="2"/>
       <c r="C10" s="2"/>
@@ -3541,7 +3618,7 @@
     <row r="11" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A11" s="1">
         <f t="shared" si="0"/>
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B11" s="2"/>
       <c r="C11" s="2"/>
@@ -3555,10 +3632,10 @@
     <row r="12" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A12" s="1">
         <f t="shared" si="0"/>
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B12" s="2"/>
-      <c r="C12" s="14"/>
+      <c r="C12" s="2"/>
       <c r="D12" s="2"/>
       <c r="E12" s="2"/>
       <c r="F12" s="2"/>
@@ -3569,10 +3646,10 @@
     <row r="13" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A13" s="1">
         <f t="shared" si="0"/>
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B13" s="2"/>
-      <c r="C13" s="2"/>
+      <c r="C13" s="14"/>
       <c r="D13" s="2"/>
       <c r="E13" s="2"/>
       <c r="F13" s="2"/>
@@ -3583,7 +3660,7 @@
     <row r="14" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A14" s="1">
         <f t="shared" si="0"/>
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B14" s="2"/>
       <c r="C14" s="2"/>
@@ -3597,7 +3674,7 @@
     <row r="15" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A15" s="1">
         <f t="shared" si="0"/>
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B15" s="2"/>
       <c r="C15" s="2"/>
@@ -3611,7 +3688,7 @@
     <row r="16" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A16" s="1">
         <f t="shared" si="0"/>
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B16" s="2"/>
       <c r="C16" s="2"/>
@@ -3625,7 +3702,7 @@
     <row r="17" spans="1:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A17" s="1">
         <f t="shared" si="0"/>
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B17" s="2"/>
       <c r="C17" s="2"/>
@@ -3639,7 +3716,7 @@
     <row r="18" spans="1:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A18" s="1">
         <f t="shared" si="0"/>
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B18" s="2"/>
       <c r="C18" s="2"/>
@@ -3649,12 +3726,11 @@
       <c r="G18" s="2"/>
       <c r="H18" s="2"/>
       <c r="I18" s="2"/>
-      <c r="J18" s="3"/>
     </row>
     <row r="19" spans="1:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A19" s="1">
         <f t="shared" si="0"/>
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B19" s="2"/>
       <c r="C19" s="2"/>
@@ -3664,11 +3740,12 @@
       <c r="G19" s="2"/>
       <c r="H19" s="2"/>
       <c r="I19" s="2"/>
+      <c r="J19" s="3"/>
     </row>
     <row r="20" spans="1:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A20" s="1">
         <f t="shared" si="0"/>
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B20" s="2"/>
       <c r="C20" s="2"/>
@@ -3682,7 +3759,7 @@
     <row r="21" spans="1:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A21" s="1">
         <f t="shared" si="0"/>
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B21" s="2"/>
       <c r="C21" s="2"/>
@@ -3696,7 +3773,7 @@
     <row r="22" spans="1:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A22" s="1">
         <f t="shared" si="0"/>
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="B22" s="2"/>
       <c r="C22" s="2"/>
@@ -3710,7 +3787,7 @@
     <row r="23" spans="1:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A23" s="1">
         <f t="shared" si="0"/>
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B23" s="2"/>
       <c r="C23" s="2"/>
@@ -3724,7 +3801,7 @@
     <row r="24" spans="1:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A24" s="1">
         <f t="shared" si="0"/>
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B24" s="2"/>
       <c r="C24" s="2"/>
@@ -3738,7 +3815,7 @@
     <row r="25" spans="1:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A25" s="1">
         <f t="shared" si="0"/>
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B25" s="2"/>
       <c r="C25" s="2"/>
@@ -3752,7 +3829,7 @@
     <row r="26" spans="1:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A26" s="1">
         <f t="shared" si="0"/>
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B26" s="2"/>
       <c r="C26" s="2"/>
@@ -3766,7 +3843,7 @@
     <row r="27" spans="1:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A27" s="1">
         <f t="shared" si="0"/>
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B27" s="2"/>
       <c r="C27" s="2"/>
@@ -3780,7 +3857,7 @@
     <row r="28" spans="1:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A28" s="1">
         <f t="shared" si="0"/>
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="B28" s="2"/>
       <c r="C28" s="2"/>
@@ -3794,7 +3871,7 @@
     <row r="29" spans="1:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A29" s="1">
         <f t="shared" si="0"/>
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="B29" s="2"/>
       <c r="C29" s="2"/>
@@ -3808,7 +3885,7 @@
     <row r="30" spans="1:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A30" s="1">
         <f t="shared" si="0"/>
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="B30" s="2"/>
       <c r="C30" s="2"/>
@@ -3819,45 +3896,39 @@
       <c r="H30" s="2"/>
       <c r="I30" s="2"/>
     </row>
-    <row r="31" spans="1:10" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A31" s="1">
-        <f t="shared" si="0"/>
-        <v>30</v>
-      </c>
-      <c r="B31" s="2"/>
-      <c r="C31" s="2"/>
-      <c r="D31" s="2"/>
-      <c r="E31" s="2"/>
-      <c r="F31" s="2"/>
-      <c r="G31" s="2"/>
-      <c r="H31" s="2"/>
-      <c r="I31" s="2"/>
-    </row>
-    <row r="32" spans="1:10" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A32" s="10">
-        <f t="shared" si="0"/>
-        <v>31</v>
-      </c>
-      <c r="B32" s="11"/>
-      <c r="C32" s="11"/>
-      <c r="D32" s="11"/>
-      <c r="E32" s="11"/>
-      <c r="F32" s="11"/>
-      <c r="G32" s="11"/>
-      <c r="H32" s="11"/>
-      <c r="I32" s="11"/>
-    </row>
-    <row r="33" spans="1:9" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="31" spans="1:10" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="33" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="A33" s="4"/>
+      <c r="B33" s="33"/>
+      <c r="C33" s="32"/>
+      <c r="D33" s="32"/>
+      <c r="E33" s="32"/>
+      <c r="F33" s="32"/>
+      <c r="G33" s="32"/>
+      <c r="H33" s="32"/>
+      <c r="I33" s="32"/>
+    </row>
+    <row r="34" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="A34" s="4"/>
+      <c r="B34" s="4"/>
+      <c r="C34" s="4"/>
+      <c r="D34" s="4"/>
+      <c r="E34" s="4"/>
+      <c r="F34" s="4"/>
+      <c r="G34" s="4"/>
+      <c r="H34" s="4"/>
+      <c r="I34" s="4"/>
+    </row>
     <row r="35" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A35" s="4"/>
-      <c r="B35" s="31"/>
-      <c r="C35" s="30"/>
-      <c r="D35" s="30"/>
-      <c r="E35" s="30"/>
-      <c r="F35" s="30"/>
-      <c r="G35" s="30"/>
-      <c r="H35" s="30"/>
-      <c r="I35" s="30"/>
+      <c r="B35" s="4"/>
+      <c r="C35" s="4"/>
+      <c r="D35" s="4"/>
+      <c r="E35" s="4"/>
+      <c r="F35" s="4"/>
+      <c r="G35" s="4"/>
+      <c r="H35" s="4"/>
+      <c r="I35" s="4"/>
     </row>
     <row r="36" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A36" s="4"/>
@@ -4212,158 +4283,158 @@
       <c r="I67" s="4"/>
     </row>
     <row r="68" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A68" s="4"/>
-      <c r="B68" s="4"/>
-      <c r="C68" s="4"/>
-      <c r="D68" s="4"/>
-      <c r="E68" s="4"/>
-      <c r="F68" s="4"/>
-      <c r="G68" s="4"/>
-      <c r="H68" s="4"/>
-      <c r="I68" s="4"/>
+      <c r="A68" s="33"/>
+      <c r="B68" s="32"/>
+      <c r="C68" s="32"/>
+      <c r="D68" s="32"/>
+      <c r="E68" s="32"/>
+      <c r="F68" s="32"/>
+      <c r="G68" s="32"/>
+      <c r="H68" s="32"/>
+      <c r="I68" s="32"/>
     </row>
     <row r="69" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A69" s="4"/>
-      <c r="B69" s="4"/>
-      <c r="C69" s="4"/>
-      <c r="D69" s="4"/>
-      <c r="E69" s="4"/>
-      <c r="F69" s="4"/>
-      <c r="G69" s="4"/>
-      <c r="H69" s="4"/>
-      <c r="I69" s="4"/>
+      <c r="B69" s="6"/>
+      <c r="C69" s="6"/>
+      <c r="D69" s="6"/>
+      <c r="E69" s="6"/>
+      <c r="F69" s="6"/>
+      <c r="G69" s="6"/>
+      <c r="H69" s="6"/>
+      <c r="I69" s="6"/>
     </row>
     <row r="70" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A70" s="31"/>
-      <c r="B70" s="30"/>
-      <c r="C70" s="30"/>
-      <c r="D70" s="30"/>
-      <c r="E70" s="30"/>
-      <c r="F70" s="30"/>
-      <c r="G70" s="30"/>
-      <c r="H70" s="30"/>
-      <c r="I70" s="30"/>
-    </row>
-    <row r="71" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A71" s="4"/>
-      <c r="B71" s="6"/>
-      <c r="C71" s="6"/>
-      <c r="D71" s="6"/>
-      <c r="E71" s="6"/>
-      <c r="F71" s="6"/>
-      <c r="G71" s="6"/>
-      <c r="H71" s="6"/>
-      <c r="I71" s="6"/>
-    </row>
-    <row r="72" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A72" s="6"/>
-      <c r="B72" s="6"/>
-      <c r="C72" s="6"/>
-      <c r="D72" s="6"/>
-      <c r="E72" s="6"/>
-      <c r="F72" s="6"/>
-      <c r="G72" s="6"/>
-      <c r="H72" s="6"/>
-      <c r="I72" s="6"/>
+      <c r="A70" s="6"/>
+      <c r="B70" s="6"/>
+      <c r="C70" s="6"/>
+      <c r="D70" s="6"/>
+      <c r="E70" s="6"/>
+      <c r="F70" s="6"/>
+      <c r="G70" s="6"/>
+      <c r="H70" s="6"/>
+      <c r="I70" s="6"/>
+    </row>
+    <row r="73" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="A73" s="31"/>
+      <c r="B73" s="32"/>
+      <c r="C73" s="32"/>
+      <c r="D73" s="32"/>
+      <c r="E73" s="32"/>
+      <c r="F73" s="32"/>
+      <c r="G73" s="32"/>
+      <c r="H73" s="32"/>
+      <c r="I73" s="32"/>
+    </row>
+    <row r="74" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="A74" s="4"/>
+      <c r="B74" s="7"/>
+      <c r="C74" s="7"/>
+      <c r="D74" s="7"/>
+      <c r="E74" s="7"/>
+      <c r="F74" s="7"/>
+      <c r="G74" s="7"/>
+      <c r="H74" s="7"/>
+      <c r="I74" s="7"/>
     </row>
     <row r="75" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A75" s="29"/>
-      <c r="B75" s="30"/>
-      <c r="C75" s="30"/>
-      <c r="D75" s="30"/>
-      <c r="E75" s="30"/>
-      <c r="F75" s="30"/>
-      <c r="G75" s="30"/>
-      <c r="H75" s="30"/>
-      <c r="I75" s="30"/>
+      <c r="A75" s="4"/>
+      <c r="B75" s="8"/>
+      <c r="C75" s="8"/>
+      <c r="D75" s="8"/>
+      <c r="E75" s="8"/>
+      <c r="F75" s="8"/>
+      <c r="G75" s="8"/>
+      <c r="H75" s="8"/>
+      <c r="I75" s="8"/>
     </row>
     <row r="76" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A76" s="4"/>
-      <c r="B76" s="7"/>
-      <c r="C76" s="7"/>
-      <c r="D76" s="7"/>
-      <c r="E76" s="7"/>
-      <c r="F76" s="7"/>
-      <c r="G76" s="7"/>
-      <c r="H76" s="7"/>
-      <c r="I76" s="7"/>
+      <c r="B76" s="8"/>
+      <c r="C76" s="8"/>
+      <c r="D76" s="8"/>
+      <c r="E76" s="8"/>
+      <c r="F76" s="8"/>
+      <c r="G76" s="8"/>
+      <c r="H76" s="8"/>
+      <c r="I76" s="8"/>
     </row>
     <row r="77" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A77" s="4"/>
-      <c r="B77" s="8"/>
-      <c r="C77" s="8"/>
-      <c r="D77" s="8"/>
-      <c r="E77" s="8"/>
-      <c r="F77" s="8"/>
-      <c r="G77" s="8"/>
-      <c r="H77" s="8"/>
-      <c r="I77" s="8"/>
+      <c r="A77" s="34"/>
+      <c r="B77" s="32"/>
+      <c r="C77" s="32"/>
+      <c r="D77" s="32"/>
+      <c r="E77" s="32"/>
+      <c r="F77" s="32"/>
+      <c r="G77" s="32"/>
+      <c r="H77" s="32"/>
+      <c r="I77" s="32"/>
     </row>
     <row r="78" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A78" s="4"/>
-      <c r="B78" s="8"/>
-      <c r="C78" s="8"/>
-      <c r="D78" s="8"/>
-      <c r="E78" s="8"/>
-      <c r="F78" s="8"/>
-      <c r="G78" s="8"/>
-      <c r="H78" s="8"/>
-      <c r="I78" s="8"/>
+      <c r="B78" s="4"/>
+      <c r="C78" s="4"/>
+      <c r="D78" s="4"/>
+      <c r="E78" s="4"/>
+      <c r="F78" s="4"/>
+      <c r="G78" s="4"/>
+      <c r="H78" s="4"/>
+      <c r="I78" s="4"/>
     </row>
     <row r="79" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A79" s="32"/>
-      <c r="B79" s="30"/>
-      <c r="C79" s="30"/>
-      <c r="D79" s="30"/>
-      <c r="E79" s="30"/>
-      <c r="F79" s="30"/>
-      <c r="G79" s="30"/>
-      <c r="H79" s="30"/>
-      <c r="I79" s="30"/>
-    </row>
-    <row r="80" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A80" s="4"/>
-      <c r="B80" s="4"/>
-      <c r="C80" s="4"/>
-      <c r="D80" s="4"/>
-      <c r="E80" s="4"/>
-      <c r="F80" s="4"/>
-      <c r="G80" s="4"/>
-      <c r="H80" s="4"/>
-      <c r="I80" s="4"/>
+      <c r="A79" s="4"/>
+      <c r="B79" s="4"/>
+      <c r="C79" s="4"/>
+      <c r="D79" s="4"/>
+      <c r="E79" s="4"/>
+      <c r="F79" s="4"/>
+      <c r="G79" s="4"/>
+      <c r="H79" s="4"/>
+      <c r="I79" s="4"/>
     </row>
     <row r="81" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A81" s="4"/>
       <c r="B81" s="4"/>
-      <c r="C81" s="4"/>
-      <c r="D81" s="4"/>
-      <c r="E81" s="4"/>
-      <c r="F81" s="4"/>
-      <c r="G81" s="4"/>
-      <c r="H81" s="4"/>
-      <c r="I81" s="4"/>
+    </row>
+    <row r="82" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="A82" s="4"/>
     </row>
     <row r="83" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A83" s="4"/>
-      <c r="B83" s="4"/>
-    </row>
-    <row r="84" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A84" s="4"/>
+      <c r="B83" s="6"/>
     </row>
     <row r="85" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A85" s="4"/>
-      <c r="B85" s="6"/>
+      <c r="A85" s="31"/>
+      <c r="B85" s="32"/>
+      <c r="C85" s="32"/>
+      <c r="D85" s="32"/>
+      <c r="E85" s="32"/>
+      <c r="F85" s="32"/>
+      <c r="G85" s="32"/>
+      <c r="H85" s="32"/>
+      <c r="I85" s="32"/>
+    </row>
+    <row r="86" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="A86" s="4"/>
+      <c r="B86" s="9"/>
+      <c r="C86" s="9"/>
+      <c r="D86" s="9"/>
+      <c r="E86" s="9"/>
+      <c r="F86" s="9"/>
+      <c r="G86" s="9"/>
+      <c r="H86" s="9"/>
+      <c r="I86" s="9"/>
     </row>
     <row r="87" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A87" s="29"/>
-      <c r="B87" s="30"/>
-      <c r="C87" s="30"/>
-      <c r="D87" s="30"/>
-      <c r="E87" s="30"/>
-      <c r="F87" s="30"/>
-      <c r="G87" s="30"/>
-      <c r="H87" s="30"/>
-      <c r="I87" s="30"/>
+      <c r="A87" s="4"/>
+      <c r="B87" s="9"/>
+      <c r="C87" s="9"/>
+      <c r="D87" s="9"/>
+      <c r="E87" s="9"/>
+      <c r="F87" s="9"/>
+      <c r="G87" s="9"/>
+      <c r="H87" s="9"/>
+      <c r="I87" s="9"/>
     </row>
     <row r="88" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A88" s="4"/>
@@ -4422,93 +4493,71 @@
     </row>
     <row r="93" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A93" s="4"/>
-      <c r="B93" s="9"/>
-      <c r="C93" s="9"/>
-      <c r="D93" s="9"/>
-      <c r="E93" s="9"/>
-      <c r="F93" s="9"/>
-      <c r="G93" s="9"/>
-      <c r="H93" s="9"/>
-      <c r="I93" s="9"/>
+      <c r="B93" s="4"/>
+      <c r="C93" s="4"/>
+      <c r="D93" s="4"/>
+      <c r="E93" s="4"/>
+      <c r="F93" s="4"/>
+      <c r="G93" s="4"/>
+      <c r="H93" s="4"/>
+      <c r="I93" s="4"/>
     </row>
     <row r="94" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A94" s="4"/>
       <c r="B94" s="9"/>
-      <c r="C94" s="9"/>
-      <c r="D94" s="9"/>
-      <c r="E94" s="9"/>
-      <c r="F94" s="9"/>
-      <c r="G94" s="9"/>
-      <c r="H94" s="9"/>
-      <c r="I94" s="9"/>
     </row>
     <row r="95" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A95" s="4"/>
       <c r="B95" s="4"/>
-      <c r="C95" s="4"/>
-      <c r="D95" s="4"/>
-      <c r="E95" s="4"/>
-      <c r="F95" s="4"/>
-      <c r="G95" s="4"/>
-      <c r="H95" s="4"/>
-      <c r="I95" s="4"/>
     </row>
     <row r="96" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A96" s="4"/>
       <c r="B96" s="9"/>
     </row>
-    <row r="97" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A97" s="4"/>
-      <c r="B97" s="4"/>
-    </row>
     <row r="98" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A98" s="4"/>
-      <c r="B98" s="9"/>
+      <c r="A98" s="33"/>
+      <c r="B98" s="32"/>
+      <c r="C98" s="32"/>
+      <c r="D98" s="32"/>
+      <c r="E98" s="32"/>
+      <c r="F98" s="32"/>
+      <c r="G98" s="32"/>
+      <c r="H98" s="32"/>
+      <c r="I98" s="32"/>
+    </row>
+    <row r="99" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="A99" s="4"/>
+      <c r="B99" s="6"/>
+      <c r="C99" s="6"/>
+      <c r="D99" s="6"/>
+      <c r="E99" s="6"/>
+      <c r="F99" s="6"/>
+      <c r="G99" s="6"/>
+      <c r="H99" s="6"/>
+      <c r="I99" s="6"/>
     </row>
     <row r="100" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A100" s="31"/>
-      <c r="B100" s="30"/>
-      <c r="C100" s="30"/>
-      <c r="D100" s="30"/>
-      <c r="E100" s="30"/>
-      <c r="F100" s="30"/>
-      <c r="G100" s="30"/>
-      <c r="H100" s="30"/>
-      <c r="I100" s="30"/>
-    </row>
-    <row r="101" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A101" s="4"/>
-      <c r="B101" s="6"/>
-      <c r="C101" s="6"/>
-      <c r="D101" s="6"/>
-      <c r="E101" s="6"/>
-      <c r="F101" s="6"/>
-      <c r="G101" s="6"/>
-      <c r="H101" s="6"/>
-      <c r="I101" s="6"/>
-    </row>
-    <row r="102" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A102" s="6"/>
-      <c r="B102" s="6"/>
-      <c r="C102" s="6"/>
-      <c r="D102" s="6"/>
-      <c r="E102" s="6"/>
-      <c r="F102" s="6"/>
-      <c r="G102" s="6"/>
-      <c r="H102" s="6"/>
-      <c r="I102" s="6"/>
+      <c r="A100" s="6"/>
+      <c r="B100" s="6"/>
+      <c r="C100" s="6"/>
+      <c r="D100" s="6"/>
+      <c r="E100" s="6"/>
+      <c r="F100" s="6"/>
+      <c r="G100" s="6"/>
+      <c r="H100" s="6"/>
+      <c r="I100" s="6"/>
     </row>
   </sheetData>
   <mergeCells count="6">
-    <mergeCell ref="A79:I79"/>
-    <mergeCell ref="A87:I87"/>
-    <mergeCell ref="A100:I100"/>
-    <mergeCell ref="B35:I35"/>
-    <mergeCell ref="A70:I70"/>
-    <mergeCell ref="A75:I75"/>
+    <mergeCell ref="A77:I77"/>
+    <mergeCell ref="A85:I85"/>
+    <mergeCell ref="A98:I98"/>
+    <mergeCell ref="B33:I33"/>
+    <mergeCell ref="A68:I68"/>
+    <mergeCell ref="A73:I73"/>
   </mergeCells>
   <dataValidations count="1">
-    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="A88" xr:uid="{00000000-0002-0000-0C00-000000000000}">
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="A86" xr:uid="{00000000-0002-0000-0C00-000000000000}">
       <formula1>"Bandeira,Verde,Amarela,Vermelha p1,Vermelha p2"</formula1>
     </dataValidation>
   </dataValidations>
@@ -4521,7 +4570,7 @@
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
-  <dimension ref="A1:J102"/>
+  <dimension ref="A1:J103"/>
   <sheetFormatPr defaultColWidth="12.5703125" defaultRowHeight="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="12" max="12" width="3.42578125" customWidth="1"/>
@@ -4557,22 +4606,21 @@
       </c>
     </row>
     <row r="2" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A2" s="1">
-        <v>1</v>
-      </c>
-      <c r="B2" s="2"/>
-      <c r="C2" s="2"/>
-      <c r="D2" s="2"/>
-      <c r="E2" s="2"/>
-      <c r="F2" s="2"/>
-      <c r="G2" s="2"/>
-      <c r="H2" s="2"/>
-      <c r="I2" s="2"/>
+      <c r="A2" s="39">
+        <v>0</v>
+      </c>
+      <c r="B2" s="38"/>
+      <c r="C2" s="38"/>
+      <c r="D2" s="38"/>
+      <c r="E2" s="38"/>
+      <c r="F2" s="38"/>
+      <c r="G2" s="38"/>
+      <c r="H2" s="38"/>
+      <c r="I2" s="38"/>
     </row>
     <row r="3" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A3" s="1">
-        <f t="shared" ref="A3:A32" si="0">A2+1</f>
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B3" s="2"/>
       <c r="C3" s="2"/>
@@ -4585,8 +4633,8 @@
     </row>
     <row r="4" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A4" s="1">
-        <f t="shared" si="0"/>
-        <v>3</v>
+        <f t="shared" ref="A4:A33" si="0">A3+1</f>
+        <v>2</v>
       </c>
       <c r="B4" s="2"/>
       <c r="C4" s="2"/>
@@ -4600,7 +4648,7 @@
     <row r="5" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A5" s="1">
         <f t="shared" si="0"/>
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B5" s="2"/>
       <c r="C5" s="2"/>
@@ -4614,7 +4662,7 @@
     <row r="6" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A6" s="1">
         <f t="shared" si="0"/>
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B6" s="2"/>
       <c r="C6" s="2"/>
@@ -4628,7 +4676,7 @@
     <row r="7" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A7" s="1">
         <f t="shared" si="0"/>
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B7" s="2"/>
       <c r="C7" s="2"/>
@@ -4642,7 +4690,7 @@
     <row r="8" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A8" s="1">
         <f t="shared" si="0"/>
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B8" s="2"/>
       <c r="C8" s="2"/>
@@ -4656,7 +4704,7 @@
     <row r="9" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A9" s="1">
         <f t="shared" si="0"/>
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B9" s="2"/>
       <c r="C9" s="2"/>
@@ -4670,7 +4718,7 @@
     <row r="10" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A10" s="1">
         <f t="shared" si="0"/>
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B10" s="2"/>
       <c r="C10" s="2"/>
@@ -4684,7 +4732,7 @@
     <row r="11" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A11" s="1">
         <f t="shared" si="0"/>
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B11" s="2"/>
       <c r="C11" s="2"/>
@@ -4698,10 +4746,10 @@
     <row r="12" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A12" s="1">
         <f t="shared" si="0"/>
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B12" s="2"/>
-      <c r="C12" s="14"/>
+      <c r="C12" s="2"/>
       <c r="D12" s="2"/>
       <c r="E12" s="2"/>
       <c r="F12" s="2"/>
@@ -4712,10 +4760,10 @@
     <row r="13" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A13" s="1">
         <f t="shared" si="0"/>
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B13" s="2"/>
-      <c r="C13" s="2"/>
+      <c r="C13" s="14"/>
       <c r="D13" s="2"/>
       <c r="E13" s="2"/>
       <c r="F13" s="2"/>
@@ -4726,7 +4774,7 @@
     <row r="14" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A14" s="1">
         <f t="shared" si="0"/>
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B14" s="2"/>
       <c r="C14" s="2"/>
@@ -4740,7 +4788,7 @@
     <row r="15" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A15" s="1">
         <f t="shared" si="0"/>
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B15" s="2"/>
       <c r="C15" s="2"/>
@@ -4754,7 +4802,7 @@
     <row r="16" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A16" s="1">
         <f t="shared" si="0"/>
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B16" s="2"/>
       <c r="C16" s="2"/>
@@ -4768,7 +4816,7 @@
     <row r="17" spans="1:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A17" s="1">
         <f t="shared" si="0"/>
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B17" s="2"/>
       <c r="C17" s="2"/>
@@ -4782,7 +4830,7 @@
     <row r="18" spans="1:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A18" s="1">
         <f t="shared" si="0"/>
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B18" s="2"/>
       <c r="C18" s="2"/>
@@ -4792,12 +4840,11 @@
       <c r="G18" s="2"/>
       <c r="H18" s="2"/>
       <c r="I18" s="2"/>
-      <c r="J18" s="3"/>
     </row>
     <row r="19" spans="1:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A19" s="1">
         <f t="shared" si="0"/>
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B19" s="2"/>
       <c r="C19" s="2"/>
@@ -4807,11 +4854,12 @@
       <c r="G19" s="2"/>
       <c r="H19" s="2"/>
       <c r="I19" s="2"/>
+      <c r="J19" s="3"/>
     </row>
     <row r="20" spans="1:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A20" s="1">
         <f t="shared" si="0"/>
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B20" s="2"/>
       <c r="C20" s="2"/>
@@ -4825,7 +4873,7 @@
     <row r="21" spans="1:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A21" s="1">
         <f t="shared" si="0"/>
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B21" s="2"/>
       <c r="C21" s="2"/>
@@ -4839,7 +4887,7 @@
     <row r="22" spans="1:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A22" s="1">
         <f t="shared" si="0"/>
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="B22" s="2"/>
       <c r="C22" s="2"/>
@@ -4853,7 +4901,7 @@
     <row r="23" spans="1:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A23" s="1">
         <f t="shared" si="0"/>
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B23" s="2"/>
       <c r="C23" s="2"/>
@@ -4867,7 +4915,7 @@
     <row r="24" spans="1:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A24" s="1">
         <f t="shared" si="0"/>
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B24" s="2"/>
       <c r="C24" s="2"/>
@@ -4881,7 +4929,7 @@
     <row r="25" spans="1:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A25" s="1">
         <f t="shared" si="0"/>
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B25" s="2"/>
       <c r="C25" s="2"/>
@@ -4895,7 +4943,7 @@
     <row r="26" spans="1:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A26" s="1">
         <f t="shared" si="0"/>
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B26" s="2"/>
       <c r="C26" s="2"/>
@@ -4909,7 +4957,7 @@
     <row r="27" spans="1:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A27" s="1">
         <f t="shared" si="0"/>
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B27" s="2"/>
       <c r="C27" s="2"/>
@@ -4923,7 +4971,7 @@
     <row r="28" spans="1:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A28" s="1">
         <f t="shared" si="0"/>
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="B28" s="2"/>
       <c r="C28" s="2"/>
@@ -4937,7 +4985,7 @@
     <row r="29" spans="1:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A29" s="1">
         <f t="shared" si="0"/>
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="B29" s="2"/>
       <c r="C29" s="2"/>
@@ -4951,7 +4999,7 @@
     <row r="30" spans="1:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A30" s="1">
         <f t="shared" si="0"/>
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="B30" s="2"/>
       <c r="C30" s="2"/>
@@ -4965,7 +5013,7 @@
     <row r="31" spans="1:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A31" s="1">
         <f t="shared" si="0"/>
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B31" s="2"/>
       <c r="C31" s="2"/>
@@ -4977,41 +5025,44 @@
       <c r="I31" s="2"/>
     </row>
     <row r="32" spans="1:10" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A32" s="10">
+      <c r="A32" s="1">
+        <f t="shared" si="0"/>
+        <v>30</v>
+      </c>
+      <c r="B32" s="2"/>
+      <c r="C32" s="2"/>
+      <c r="D32" s="2"/>
+      <c r="E32" s="2"/>
+      <c r="F32" s="2"/>
+      <c r="G32" s="2"/>
+      <c r="H32" s="2"/>
+      <c r="I32" s="2"/>
+    </row>
+    <row r="33" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="A33" s="10">
         <f t="shared" si="0"/>
         <v>31</v>
       </c>
-      <c r="B32" s="11"/>
-      <c r="C32" s="11"/>
-      <c r="D32" s="11"/>
-      <c r="E32" s="11"/>
-      <c r="F32" s="11"/>
-      <c r="G32" s="11"/>
-      <c r="H32" s="11"/>
-      <c r="I32" s="11"/>
-    </row>
-    <row r="33" spans="1:9" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="35" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A35" s="4"/>
-      <c r="B35" s="31"/>
-      <c r="C35" s="30"/>
-      <c r="D35" s="30"/>
-      <c r="E35" s="30"/>
-      <c r="F35" s="30"/>
-      <c r="G35" s="30"/>
-      <c r="H35" s="30"/>
-      <c r="I35" s="30"/>
-    </row>
+      <c r="B33" s="11"/>
+      <c r="C33" s="11"/>
+      <c r="D33" s="11"/>
+      <c r="E33" s="11"/>
+      <c r="F33" s="11"/>
+      <c r="G33" s="11"/>
+      <c r="H33" s="11"/>
+      <c r="I33" s="11"/>
+    </row>
+    <row r="34" spans="1:9" ht="12.75" x14ac:dyDescent="0.2"/>
     <row r="36" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A36" s="4"/>
-      <c r="B36" s="4"/>
-      <c r="C36" s="4"/>
-      <c r="D36" s="4"/>
-      <c r="E36" s="4"/>
-      <c r="F36" s="4"/>
-      <c r="G36" s="4"/>
-      <c r="H36" s="4"/>
-      <c r="I36" s="4"/>
+      <c r="B36" s="33"/>
+      <c r="C36" s="32"/>
+      <c r="D36" s="32"/>
+      <c r="E36" s="32"/>
+      <c r="F36" s="32"/>
+      <c r="G36" s="32"/>
+      <c r="H36" s="32"/>
+      <c r="I36" s="32"/>
     </row>
     <row r="37" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A37" s="4"/>
@@ -5377,29 +5428,29 @@
       <c r="I69" s="4"/>
     </row>
     <row r="70" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A70" s="31"/>
-      <c r="B70" s="30"/>
-      <c r="C70" s="30"/>
-      <c r="D70" s="30"/>
-      <c r="E70" s="30"/>
-      <c r="F70" s="30"/>
-      <c r="G70" s="30"/>
-      <c r="H70" s="30"/>
-      <c r="I70" s="30"/>
+      <c r="A70" s="4"/>
+      <c r="B70" s="4"/>
+      <c r="C70" s="4"/>
+      <c r="D70" s="4"/>
+      <c r="E70" s="4"/>
+      <c r="F70" s="4"/>
+      <c r="G70" s="4"/>
+      <c r="H70" s="4"/>
+      <c r="I70" s="4"/>
     </row>
     <row r="71" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A71" s="4"/>
-      <c r="B71" s="6"/>
-      <c r="C71" s="6"/>
-      <c r="D71" s="6"/>
-      <c r="E71" s="6"/>
-      <c r="F71" s="6"/>
-      <c r="G71" s="6"/>
-      <c r="H71" s="6"/>
-      <c r="I71" s="6"/>
+      <c r="A71" s="33"/>
+      <c r="B71" s="32"/>
+      <c r="C71" s="32"/>
+      <c r="D71" s="32"/>
+      <c r="E71" s="32"/>
+      <c r="F71" s="32"/>
+      <c r="G71" s="32"/>
+      <c r="H71" s="32"/>
+      <c r="I71" s="32"/>
     </row>
     <row r="72" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A72" s="6"/>
+      <c r="A72" s="4"/>
       <c r="B72" s="6"/>
       <c r="C72" s="6"/>
       <c r="D72" s="6"/>
@@ -5409,38 +5460,38 @@
       <c r="H72" s="6"/>
       <c r="I72" s="6"/>
     </row>
-    <row r="75" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A75" s="29"/>
-      <c r="B75" s="30"/>
-      <c r="C75" s="30"/>
-      <c r="D75" s="30"/>
-      <c r="E75" s="30"/>
-      <c r="F75" s="30"/>
-      <c r="G75" s="30"/>
-      <c r="H75" s="30"/>
-      <c r="I75" s="30"/>
+    <row r="73" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="A73" s="6"/>
+      <c r="B73" s="6"/>
+      <c r="C73" s="6"/>
+      <c r="D73" s="6"/>
+      <c r="E73" s="6"/>
+      <c r="F73" s="6"/>
+      <c r="G73" s="6"/>
+      <c r="H73" s="6"/>
+      <c r="I73" s="6"/>
     </row>
     <row r="76" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A76" s="4"/>
-      <c r="B76" s="7"/>
-      <c r="C76" s="7"/>
-      <c r="D76" s="7"/>
-      <c r="E76" s="7"/>
-      <c r="F76" s="7"/>
-      <c r="G76" s="7"/>
-      <c r="H76" s="7"/>
-      <c r="I76" s="7"/>
+      <c r="A76" s="31"/>
+      <c r="B76" s="32"/>
+      <c r="C76" s="32"/>
+      <c r="D76" s="32"/>
+      <c r="E76" s="32"/>
+      <c r="F76" s="32"/>
+      <c r="G76" s="32"/>
+      <c r="H76" s="32"/>
+      <c r="I76" s="32"/>
     </row>
     <row r="77" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A77" s="4"/>
-      <c r="B77" s="8"/>
-      <c r="C77" s="8"/>
-      <c r="D77" s="8"/>
-      <c r="E77" s="8"/>
-      <c r="F77" s="8"/>
-      <c r="G77" s="8"/>
-      <c r="H77" s="8"/>
-      <c r="I77" s="8"/>
+      <c r="B77" s="7"/>
+      <c r="C77" s="7"/>
+      <c r="D77" s="7"/>
+      <c r="E77" s="7"/>
+      <c r="F77" s="7"/>
+      <c r="G77" s="7"/>
+      <c r="H77" s="7"/>
+      <c r="I77" s="7"/>
     </row>
     <row r="78" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A78" s="4"/>
@@ -5454,26 +5505,26 @@
       <c r="I78" s="8"/>
     </row>
     <row r="79" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A79" s="32"/>
-      <c r="B79" s="30"/>
-      <c r="C79" s="30"/>
-      <c r="D79" s="30"/>
-      <c r="E79" s="30"/>
-      <c r="F79" s="30"/>
-      <c r="G79" s="30"/>
-      <c r="H79" s="30"/>
-      <c r="I79" s="30"/>
+      <c r="A79" s="4"/>
+      <c r="B79" s="8"/>
+      <c r="C79" s="8"/>
+      <c r="D79" s="8"/>
+      <c r="E79" s="8"/>
+      <c r="F79" s="8"/>
+      <c r="G79" s="8"/>
+      <c r="H79" s="8"/>
+      <c r="I79" s="8"/>
     </row>
     <row r="80" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A80" s="4"/>
-      <c r="B80" s="4"/>
-      <c r="C80" s="4"/>
-      <c r="D80" s="4"/>
-      <c r="E80" s="4"/>
-      <c r="F80" s="4"/>
-      <c r="G80" s="4"/>
-      <c r="H80" s="4"/>
-      <c r="I80" s="4"/>
+      <c r="A80" s="34"/>
+      <c r="B80" s="32"/>
+      <c r="C80" s="32"/>
+      <c r="D80" s="32"/>
+      <c r="E80" s="32"/>
+      <c r="F80" s="32"/>
+      <c r="G80" s="32"/>
+      <c r="H80" s="32"/>
+      <c r="I80" s="32"/>
     </row>
     <row r="81" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A81" s="4"/>
@@ -5486,38 +5537,38 @@
       <c r="H81" s="4"/>
       <c r="I81" s="4"/>
     </row>
-    <row r="83" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A83" s="4"/>
-      <c r="B83" s="4"/>
+    <row r="82" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="A82" s="4"/>
+      <c r="B82" s="4"/>
+      <c r="C82" s="4"/>
+      <c r="D82" s="4"/>
+      <c r="E82" s="4"/>
+      <c r="F82" s="4"/>
+      <c r="G82" s="4"/>
+      <c r="H82" s="4"/>
+      <c r="I82" s="4"/>
     </row>
     <row r="84" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A84" s="4"/>
+      <c r="B84" s="4"/>
     </row>
     <row r="85" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A85" s="4"/>
-      <c r="B85" s="6"/>
-    </row>
-    <row r="87" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A87" s="29"/>
-      <c r="B87" s="30"/>
-      <c r="C87" s="30"/>
-      <c r="D87" s="30"/>
-      <c r="E87" s="30"/>
-      <c r="F87" s="30"/>
-      <c r="G87" s="30"/>
-      <c r="H87" s="30"/>
-      <c r="I87" s="30"/>
+    </row>
+    <row r="86" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="A86" s="4"/>
+      <c r="B86" s="6"/>
     </row>
     <row r="88" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A88" s="4"/>
-      <c r="B88" s="9"/>
-      <c r="C88" s="9"/>
-      <c r="D88" s="9"/>
-      <c r="E88" s="9"/>
-      <c r="F88" s="9"/>
-      <c r="G88" s="9"/>
-      <c r="H88" s="9"/>
-      <c r="I88" s="9"/>
+      <c r="A88" s="31"/>
+      <c r="B88" s="32"/>
+      <c r="C88" s="32"/>
+      <c r="D88" s="32"/>
+      <c r="E88" s="32"/>
+      <c r="F88" s="32"/>
+      <c r="G88" s="32"/>
+      <c r="H88" s="32"/>
+      <c r="I88" s="32"/>
     </row>
     <row r="89" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A89" s="4"/>
@@ -5587,51 +5638,51 @@
     </row>
     <row r="95" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A95" s="4"/>
-      <c r="B95" s="4"/>
-      <c r="C95" s="4"/>
-      <c r="D95" s="4"/>
-      <c r="E95" s="4"/>
-      <c r="F95" s="4"/>
-      <c r="G95" s="4"/>
-      <c r="H95" s="4"/>
-      <c r="I95" s="4"/>
+      <c r="B95" s="9"/>
+      <c r="C95" s="9"/>
+      <c r="D95" s="9"/>
+      <c r="E95" s="9"/>
+      <c r="F95" s="9"/>
+      <c r="G95" s="9"/>
+      <c r="H95" s="9"/>
+      <c r="I95" s="9"/>
     </row>
     <row r="96" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A96" s="4"/>
-      <c r="B96" s="9"/>
+      <c r="B96" s="4"/>
+      <c r="C96" s="4"/>
+      <c r="D96" s="4"/>
+      <c r="E96" s="4"/>
+      <c r="F96" s="4"/>
+      <c r="G96" s="4"/>
+      <c r="H96" s="4"/>
+      <c r="I96" s="4"/>
     </row>
     <row r="97" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A97" s="4"/>
-      <c r="B97" s="4"/>
+      <c r="B97" s="9"/>
     </row>
     <row r="98" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A98" s="4"/>
-      <c r="B98" s="9"/>
-    </row>
-    <row r="100" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A100" s="31"/>
-      <c r="B100" s="30"/>
-      <c r="C100" s="30"/>
-      <c r="D100" s="30"/>
-      <c r="E100" s="30"/>
-      <c r="F100" s="30"/>
-      <c r="G100" s="30"/>
-      <c r="H100" s="30"/>
-      <c r="I100" s="30"/>
+      <c r="B98" s="4"/>
+    </row>
+    <row r="99" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="A99" s="4"/>
+      <c r="B99" s="9"/>
     </row>
     <row r="101" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A101" s="4"/>
-      <c r="B101" s="6"/>
-      <c r="C101" s="6"/>
-      <c r="D101" s="6"/>
-      <c r="E101" s="6"/>
-      <c r="F101" s="6"/>
-      <c r="G101" s="6"/>
-      <c r="H101" s="6"/>
-      <c r="I101" s="6"/>
+      <c r="A101" s="33"/>
+      <c r="B101" s="32"/>
+      <c r="C101" s="32"/>
+      <c r="D101" s="32"/>
+      <c r="E101" s="32"/>
+      <c r="F101" s="32"/>
+      <c r="G101" s="32"/>
+      <c r="H101" s="32"/>
+      <c r="I101" s="32"/>
     </row>
     <row r="102" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A102" s="6"/>
+      <c r="A102" s="4"/>
       <c r="B102" s="6"/>
       <c r="C102" s="6"/>
       <c r="D102" s="6"/>
@@ -5641,17 +5692,28 @@
       <c r="H102" s="6"/>
       <c r="I102" s="6"/>
     </row>
+    <row r="103" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="A103" s="6"/>
+      <c r="B103" s="6"/>
+      <c r="C103" s="6"/>
+      <c r="D103" s="6"/>
+      <c r="E103" s="6"/>
+      <c r="F103" s="6"/>
+      <c r="G103" s="6"/>
+      <c r="H103" s="6"/>
+      <c r="I103" s="6"/>
+    </row>
   </sheetData>
   <mergeCells count="6">
-    <mergeCell ref="A79:I79"/>
-    <mergeCell ref="A87:I87"/>
-    <mergeCell ref="A100:I100"/>
-    <mergeCell ref="B35:I35"/>
-    <mergeCell ref="A70:I70"/>
-    <mergeCell ref="A75:I75"/>
+    <mergeCell ref="A80:I80"/>
+    <mergeCell ref="A88:I88"/>
+    <mergeCell ref="A101:I101"/>
+    <mergeCell ref="B36:I36"/>
+    <mergeCell ref="A71:I71"/>
+    <mergeCell ref="A76:I76"/>
   </mergeCells>
   <dataValidations count="1">
-    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="A88" xr:uid="{00000000-0002-0000-0D00-000000000000}">
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="A89" xr:uid="{00000000-0002-0000-0D00-000000000000}">
       <formula1>"Bandeira,Verde,Amarela,Vermelha p1,Vermelha p2"</formula1>
     </dataValidation>
   </dataValidations>
@@ -5708,22 +5770,21 @@
       </c>
     </row>
     <row r="2" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A2" s="1">
-        <v>1</v>
-      </c>
-      <c r="B2" s="2"/>
-      <c r="C2" s="2"/>
-      <c r="D2" s="2"/>
-      <c r="E2" s="2"/>
-      <c r="F2" s="2"/>
-      <c r="G2" s="2"/>
-      <c r="H2" s="2"/>
-      <c r="I2" s="2"/>
+      <c r="A2" s="39">
+        <v>0</v>
+      </c>
+      <c r="B2" s="38"/>
+      <c r="C2" s="38"/>
+      <c r="D2" s="38"/>
+      <c r="E2" s="38"/>
+      <c r="F2" s="38"/>
+      <c r="G2" s="38"/>
+      <c r="H2" s="38"/>
+      <c r="I2" s="38"/>
     </row>
     <row r="3" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A3" s="1">
-        <f t="shared" ref="A3:A32" si="0">A2+1</f>
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B3" s="2"/>
       <c r="C3" s="2"/>
@@ -5736,8 +5797,8 @@
     </row>
     <row r="4" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A4" s="1">
-        <f t="shared" si="0"/>
-        <v>3</v>
+        <f t="shared" ref="A4:A32" si="0">A3+1</f>
+        <v>2</v>
       </c>
       <c r="B4" s="2"/>
       <c r="C4" s="2"/>
@@ -5751,7 +5812,7 @@
     <row r="5" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A5" s="1">
         <f t="shared" si="0"/>
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B5" s="2"/>
       <c r="C5" s="2"/>
@@ -5765,7 +5826,7 @@
     <row r="6" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A6" s="1">
         <f t="shared" si="0"/>
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B6" s="2"/>
       <c r="C6" s="2"/>
@@ -5779,7 +5840,7 @@
     <row r="7" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A7" s="1">
         <f t="shared" si="0"/>
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B7" s="2"/>
       <c r="C7" s="2"/>
@@ -5793,7 +5854,7 @@
     <row r="8" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A8" s="1">
         <f t="shared" si="0"/>
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B8" s="2"/>
       <c r="C8" s="2"/>
@@ -5807,7 +5868,7 @@
     <row r="9" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A9" s="1">
         <f t="shared" si="0"/>
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B9" s="2"/>
       <c r="C9" s="2"/>
@@ -5821,7 +5882,7 @@
     <row r="10" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A10" s="1">
         <f t="shared" si="0"/>
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B10" s="2"/>
       <c r="C10" s="2"/>
@@ -5835,7 +5896,7 @@
     <row r="11" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A11" s="1">
         <f t="shared" si="0"/>
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B11" s="2"/>
       <c r="C11" s="2"/>
@@ -5849,10 +5910,10 @@
     <row r="12" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A12" s="1">
         <f t="shared" si="0"/>
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B12" s="2"/>
-      <c r="C12" s="14"/>
+      <c r="C12" s="2"/>
       <c r="D12" s="2"/>
       <c r="E12" s="2"/>
       <c r="F12" s="2"/>
@@ -5863,10 +5924,10 @@
     <row r="13" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A13" s="1">
         <f t="shared" si="0"/>
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B13" s="2"/>
-      <c r="C13" s="2"/>
+      <c r="C13" s="14"/>
       <c r="D13" s="2"/>
       <c r="E13" s="2"/>
       <c r="F13" s="2"/>
@@ -5877,7 +5938,7 @@
     <row r="14" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A14" s="1">
         <f t="shared" si="0"/>
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B14" s="2"/>
       <c r="C14" s="2"/>
@@ -5891,7 +5952,7 @@
     <row r="15" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A15" s="1">
         <f t="shared" si="0"/>
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B15" s="2"/>
       <c r="C15" s="2"/>
@@ -5905,7 +5966,7 @@
     <row r="16" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A16" s="1">
         <f t="shared" si="0"/>
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B16" s="2"/>
       <c r="C16" s="2"/>
@@ -5919,7 +5980,7 @@
     <row r="17" spans="1:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A17" s="1">
         <f t="shared" si="0"/>
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B17" s="2"/>
       <c r="C17" s="2"/>
@@ -5933,7 +5994,7 @@
     <row r="18" spans="1:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A18" s="1">
         <f t="shared" si="0"/>
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B18" s="2"/>
       <c r="C18" s="2"/>
@@ -5943,12 +6004,11 @@
       <c r="G18" s="2"/>
       <c r="H18" s="2"/>
       <c r="I18" s="2"/>
-      <c r="J18" s="3"/>
     </row>
     <row r="19" spans="1:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A19" s="1">
         <f t="shared" si="0"/>
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B19" s="2"/>
       <c r="C19" s="2"/>
@@ -5958,11 +6018,12 @@
       <c r="G19" s="2"/>
       <c r="H19" s="2"/>
       <c r="I19" s="2"/>
+      <c r="J19" s="3"/>
     </row>
     <row r="20" spans="1:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A20" s="1">
         <f t="shared" si="0"/>
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B20" s="2"/>
       <c r="C20" s="2"/>
@@ -5976,7 +6037,7 @@
     <row r="21" spans="1:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A21" s="1">
         <f t="shared" si="0"/>
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B21" s="2"/>
       <c r="C21" s="2"/>
@@ -5990,7 +6051,7 @@
     <row r="22" spans="1:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A22" s="1">
         <f t="shared" si="0"/>
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="B22" s="2"/>
       <c r="C22" s="2"/>
@@ -6004,7 +6065,7 @@
     <row r="23" spans="1:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A23" s="1">
         <f t="shared" si="0"/>
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B23" s="2"/>
       <c r="C23" s="2"/>
@@ -6018,7 +6079,7 @@
     <row r="24" spans="1:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A24" s="1">
         <f t="shared" si="0"/>
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B24" s="2"/>
       <c r="C24" s="2"/>
@@ -6032,7 +6093,7 @@
     <row r="25" spans="1:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A25" s="1">
         <f t="shared" si="0"/>
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B25" s="2"/>
       <c r="C25" s="2"/>
@@ -6046,7 +6107,7 @@
     <row r="26" spans="1:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A26" s="1">
         <f t="shared" si="0"/>
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B26" s="2"/>
       <c r="C26" s="2"/>
@@ -6060,7 +6121,7 @@
     <row r="27" spans="1:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A27" s="1">
         <f t="shared" si="0"/>
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B27" s="2"/>
       <c r="C27" s="2"/>
@@ -6074,7 +6135,7 @@
     <row r="28" spans="1:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A28" s="1">
         <f t="shared" si="0"/>
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="B28" s="2"/>
       <c r="C28" s="2"/>
@@ -6088,7 +6149,7 @@
     <row r="29" spans="1:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A29" s="1">
         <f t="shared" si="0"/>
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="B29" s="2"/>
       <c r="C29" s="2"/>
@@ -6102,7 +6163,7 @@
     <row r="30" spans="1:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A30" s="1">
         <f t="shared" si="0"/>
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="B30" s="2"/>
       <c r="C30" s="2"/>
@@ -6116,7 +6177,7 @@
     <row r="31" spans="1:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A31" s="1">
         <f t="shared" si="0"/>
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B31" s="2"/>
       <c r="C31" s="2"/>
@@ -6128,30 +6189,30 @@
       <c r="I31" s="2"/>
     </row>
     <row r="32" spans="1:10" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A32" s="10">
-        <f t="shared" si="0"/>
-        <v>31</v>
-      </c>
-      <c r="B32" s="11"/>
-      <c r="C32" s="11"/>
-      <c r="D32" s="11"/>
-      <c r="E32" s="11"/>
-      <c r="F32" s="11"/>
-      <c r="G32" s="11"/>
-      <c r="H32" s="11"/>
-      <c r="I32" s="11"/>
+      <c r="A32" s="1">
+        <f t="shared" si="0"/>
+        <v>30</v>
+      </c>
+      <c r="B32" s="2"/>
+      <c r="C32" s="2"/>
+      <c r="D32" s="2"/>
+      <c r="E32" s="2"/>
+      <c r="F32" s="2"/>
+      <c r="G32" s="2"/>
+      <c r="H32" s="2"/>
+      <c r="I32" s="2"/>
     </row>
     <row r="33" spans="1:9" ht="12.75" x14ac:dyDescent="0.2"/>
     <row r="35" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A35" s="4"/>
-      <c r="B35" s="31"/>
-      <c r="C35" s="30"/>
-      <c r="D35" s="30"/>
-      <c r="E35" s="30"/>
-      <c r="F35" s="30"/>
-      <c r="G35" s="30"/>
-      <c r="H35" s="30"/>
-      <c r="I35" s="30"/>
+      <c r="B35" s="33"/>
+      <c r="C35" s="32"/>
+      <c r="D35" s="32"/>
+      <c r="E35" s="32"/>
+      <c r="F35" s="32"/>
+      <c r="G35" s="32"/>
+      <c r="H35" s="32"/>
+      <c r="I35" s="32"/>
     </row>
     <row r="36" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A36" s="4"/>
@@ -6529,15 +6590,15 @@
       <c r="I69" s="4"/>
     </row>
     <row r="70" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A70" s="31"/>
-      <c r="B70" s="30"/>
-      <c r="C70" s="30"/>
-      <c r="D70" s="30"/>
-      <c r="E70" s="30"/>
-      <c r="F70" s="30"/>
-      <c r="G70" s="30"/>
-      <c r="H70" s="30"/>
-      <c r="I70" s="30"/>
+      <c r="A70" s="33"/>
+      <c r="B70" s="32"/>
+      <c r="C70" s="32"/>
+      <c r="D70" s="32"/>
+      <c r="E70" s="32"/>
+      <c r="F70" s="32"/>
+      <c r="G70" s="32"/>
+      <c r="H70" s="32"/>
+      <c r="I70" s="32"/>
     </row>
     <row r="71" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A71" s="4"/>
@@ -6562,15 +6623,15 @@
       <c r="I72" s="6"/>
     </row>
     <row r="75" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A75" s="29"/>
-      <c r="B75" s="30"/>
-      <c r="C75" s="30"/>
-      <c r="D75" s="30"/>
-      <c r="E75" s="30"/>
-      <c r="F75" s="30"/>
-      <c r="G75" s="30"/>
-      <c r="H75" s="30"/>
-      <c r="I75" s="30"/>
+      <c r="A75" s="31"/>
+      <c r="B75" s="32"/>
+      <c r="C75" s="32"/>
+      <c r="D75" s="32"/>
+      <c r="E75" s="32"/>
+      <c r="F75" s="32"/>
+      <c r="G75" s="32"/>
+      <c r="H75" s="32"/>
+      <c r="I75" s="32"/>
     </row>
     <row r="76" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A76" s="4"/>
@@ -6606,15 +6667,15 @@
       <c r="I78" s="8"/>
     </row>
     <row r="79" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A79" s="32"/>
-      <c r="B79" s="30"/>
-      <c r="C79" s="30"/>
-      <c r="D79" s="30"/>
-      <c r="E79" s="30"/>
-      <c r="F79" s="30"/>
-      <c r="G79" s="30"/>
-      <c r="H79" s="30"/>
-      <c r="I79" s="30"/>
+      <c r="A79" s="34"/>
+      <c r="B79" s="32"/>
+      <c r="C79" s="32"/>
+      <c r="D79" s="32"/>
+      <c r="E79" s="32"/>
+      <c r="F79" s="32"/>
+      <c r="G79" s="32"/>
+      <c r="H79" s="32"/>
+      <c r="I79" s="32"/>
     </row>
     <row r="80" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A80" s="4"/>
@@ -6650,15 +6711,15 @@
       <c r="B85" s="6"/>
     </row>
     <row r="87" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A87" s="29"/>
-      <c r="B87" s="30"/>
-      <c r="C87" s="30"/>
-      <c r="D87" s="30"/>
-      <c r="E87" s="30"/>
-      <c r="F87" s="30"/>
-      <c r="G87" s="30"/>
-      <c r="H87" s="30"/>
-      <c r="I87" s="30"/>
+      <c r="A87" s="31"/>
+      <c r="B87" s="32"/>
+      <c r="C87" s="32"/>
+      <c r="D87" s="32"/>
+      <c r="E87" s="32"/>
+      <c r="F87" s="32"/>
+      <c r="G87" s="32"/>
+      <c r="H87" s="32"/>
+      <c r="I87" s="32"/>
     </row>
     <row r="88" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A88" s="4"/>
@@ -6761,15 +6822,15 @@
       <c r="B98" s="9"/>
     </row>
     <row r="100" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A100" s="31"/>
-      <c r="B100" s="30"/>
-      <c r="C100" s="30"/>
-      <c r="D100" s="30"/>
-      <c r="E100" s="30"/>
-      <c r="F100" s="30"/>
-      <c r="G100" s="30"/>
-      <c r="H100" s="30"/>
-      <c r="I100" s="30"/>
+      <c r="A100" s="33"/>
+      <c r="B100" s="32"/>
+      <c r="C100" s="32"/>
+      <c r="D100" s="32"/>
+      <c r="E100" s="32"/>
+      <c r="F100" s="32"/>
+      <c r="G100" s="32"/>
+      <c r="H100" s="32"/>
+      <c r="I100" s="32"/>
     </row>
     <row r="101" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A101" s="4"/>
@@ -6816,7 +6877,7 @@
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
-  <dimension ref="A1:K102"/>
+  <dimension ref="A1:K103"/>
   <sheetFormatPr defaultColWidth="12.5703125" defaultRowHeight="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="19.42578125" customWidth="1"/>
@@ -6860,22 +6921,21 @@
       </c>
     </row>
     <row r="2" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A2" s="1">
-        <v>1</v>
-      </c>
-      <c r="B2" s="2"/>
-      <c r="C2" s="2"/>
-      <c r="D2" s="2"/>
-      <c r="E2" s="2"/>
-      <c r="F2" s="2"/>
-      <c r="G2" s="2"/>
-      <c r="H2" s="2"/>
-      <c r="I2" s="2"/>
+      <c r="A2" s="39">
+        <v>0</v>
+      </c>
+      <c r="B2" s="38"/>
+      <c r="C2" s="38"/>
+      <c r="D2" s="38"/>
+      <c r="E2" s="38"/>
+      <c r="F2" s="38"/>
+      <c r="G2" s="38"/>
+      <c r="H2" s="38"/>
+      <c r="I2" s="38"/>
     </row>
     <row r="3" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A3" s="1">
-        <f t="shared" ref="A3:A32" si="0">A2+1</f>
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B3" s="2"/>
       <c r="C3" s="2"/>
@@ -6888,8 +6948,8 @@
     </row>
     <row r="4" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A4" s="1">
-        <f t="shared" si="0"/>
-        <v>3</v>
+        <f t="shared" ref="A4:A33" si="0">A3+1</f>
+        <v>2</v>
       </c>
       <c r="B4" s="2"/>
       <c r="C4" s="2"/>
@@ -6903,7 +6963,7 @@
     <row r="5" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A5" s="1">
         <f t="shared" si="0"/>
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B5" s="2"/>
       <c r="C5" s="2"/>
@@ -6917,7 +6977,7 @@
     <row r="6" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A6" s="1">
         <f t="shared" si="0"/>
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B6" s="2"/>
       <c r="C6" s="2"/>
@@ -6931,7 +6991,7 @@
     <row r="7" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A7" s="1">
         <f t="shared" si="0"/>
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B7" s="2"/>
       <c r="C7" s="2"/>
@@ -6945,7 +7005,7 @@
     <row r="8" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A8" s="1">
         <f t="shared" si="0"/>
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B8" s="2"/>
       <c r="C8" s="2"/>
@@ -6959,7 +7019,7 @@
     <row r="9" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A9" s="1">
         <f t="shared" si="0"/>
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B9" s="2"/>
       <c r="C9" s="2"/>
@@ -6973,7 +7033,7 @@
     <row r="10" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A10" s="1">
         <f t="shared" si="0"/>
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B10" s="2"/>
       <c r="C10" s="2"/>
@@ -6987,7 +7047,7 @@
     <row r="11" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A11" s="1">
         <f t="shared" si="0"/>
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B11" s="2"/>
       <c r="C11" s="2"/>
@@ -7001,10 +7061,10 @@
     <row r="12" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A12" s="1">
         <f t="shared" si="0"/>
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B12" s="2"/>
-      <c r="C12" s="14"/>
+      <c r="C12" s="2"/>
       <c r="D12" s="2"/>
       <c r="E12" s="2"/>
       <c r="F12" s="2"/>
@@ -7015,10 +7075,10 @@
     <row r="13" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A13" s="1">
         <f t="shared" si="0"/>
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B13" s="2"/>
-      <c r="C13" s="2"/>
+      <c r="C13" s="14"/>
       <c r="D13" s="2"/>
       <c r="E13" s="2"/>
       <c r="F13" s="2"/>
@@ -7029,7 +7089,7 @@
     <row r="14" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A14" s="1">
         <f t="shared" si="0"/>
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B14" s="2"/>
       <c r="C14" s="2"/>
@@ -7043,7 +7103,7 @@
     <row r="15" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A15" s="1">
         <f t="shared" si="0"/>
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B15" s="2"/>
       <c r="C15" s="2"/>
@@ -7057,7 +7117,7 @@
     <row r="16" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A16" s="1">
         <f t="shared" si="0"/>
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B16" s="2"/>
       <c r="C16" s="2"/>
@@ -7071,7 +7131,7 @@
     <row r="17" spans="1:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A17" s="1">
         <f t="shared" si="0"/>
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B17" s="2"/>
       <c r="C17" s="2"/>
@@ -7085,7 +7145,7 @@
     <row r="18" spans="1:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A18" s="1">
         <f t="shared" si="0"/>
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B18" s="2"/>
       <c r="C18" s="2"/>
@@ -7095,12 +7155,11 @@
       <c r="G18" s="2"/>
       <c r="H18" s="2"/>
       <c r="I18" s="2"/>
-      <c r="J18" s="3"/>
     </row>
     <row r="19" spans="1:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A19" s="1">
         <f t="shared" si="0"/>
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B19" s="2"/>
       <c r="C19" s="2"/>
@@ -7110,11 +7169,12 @@
       <c r="G19" s="2"/>
       <c r="H19" s="2"/>
       <c r="I19" s="2"/>
+      <c r="J19" s="3"/>
     </row>
     <row r="20" spans="1:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A20" s="1">
         <f t="shared" si="0"/>
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B20" s="2"/>
       <c r="C20" s="2"/>
@@ -7128,7 +7188,7 @@
     <row r="21" spans="1:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A21" s="1">
         <f t="shared" si="0"/>
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B21" s="2"/>
       <c r="C21" s="2"/>
@@ -7142,7 +7202,7 @@
     <row r="22" spans="1:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A22" s="1">
         <f t="shared" si="0"/>
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="B22" s="2"/>
       <c r="C22" s="2"/>
@@ -7156,7 +7216,7 @@
     <row r="23" spans="1:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A23" s="1">
         <f t="shared" si="0"/>
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B23" s="2"/>
       <c r="C23" s="2"/>
@@ -7170,7 +7230,7 @@
     <row r="24" spans="1:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A24" s="1">
         <f t="shared" si="0"/>
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B24" s="2"/>
       <c r="C24" s="2"/>
@@ -7184,7 +7244,7 @@
     <row r="25" spans="1:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A25" s="1">
         <f t="shared" si="0"/>
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B25" s="2"/>
       <c r="C25" s="2"/>
@@ -7198,7 +7258,7 @@
     <row r="26" spans="1:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A26" s="1">
         <f t="shared" si="0"/>
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B26" s="2"/>
       <c r="C26" s="2"/>
@@ -7212,7 +7272,7 @@
     <row r="27" spans="1:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A27" s="1">
         <f t="shared" si="0"/>
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B27" s="2"/>
       <c r="C27" s="2"/>
@@ -7226,7 +7286,7 @@
     <row r="28" spans="1:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A28" s="1">
         <f t="shared" si="0"/>
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="B28" s="2"/>
       <c r="C28" s="2"/>
@@ -7240,7 +7300,7 @@
     <row r="29" spans="1:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A29" s="1">
         <f t="shared" si="0"/>
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="B29" s="2"/>
       <c r="C29" s="2"/>
@@ -7254,7 +7314,7 @@
     <row r="30" spans="1:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A30" s="1">
         <f t="shared" si="0"/>
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="B30" s="2"/>
       <c r="C30" s="2"/>
@@ -7268,7 +7328,7 @@
     <row r="31" spans="1:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A31" s="1">
         <f t="shared" si="0"/>
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B31" s="2"/>
       <c r="C31" s="2"/>
@@ -7280,41 +7340,44 @@
       <c r="I31" s="2"/>
     </row>
     <row r="32" spans="1:10" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A32" s="10">
+      <c r="A32" s="1">
+        <f t="shared" si="0"/>
+        <v>30</v>
+      </c>
+      <c r="B32" s="2"/>
+      <c r="C32" s="2"/>
+      <c r="D32" s="2"/>
+      <c r="E32" s="2"/>
+      <c r="F32" s="2"/>
+      <c r="G32" s="2"/>
+      <c r="H32" s="2"/>
+      <c r="I32" s="2"/>
+    </row>
+    <row r="33" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="A33" s="10">
         <f t="shared" si="0"/>
         <v>31</v>
       </c>
-      <c r="B32" s="11"/>
-      <c r="C32" s="11"/>
-      <c r="D32" s="11"/>
-      <c r="E32" s="11"/>
-      <c r="F32" s="11"/>
-      <c r="G32" s="11"/>
-      <c r="H32" s="11"/>
-      <c r="I32" s="11"/>
-    </row>
-    <row r="33" spans="1:9" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="35" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A35" s="4"/>
-      <c r="B35" s="31"/>
-      <c r="C35" s="30"/>
-      <c r="D35" s="30"/>
-      <c r="E35" s="30"/>
-      <c r="F35" s="30"/>
-      <c r="G35" s="30"/>
-      <c r="H35" s="30"/>
-      <c r="I35" s="30"/>
-    </row>
+      <c r="B33" s="11"/>
+      <c r="C33" s="11"/>
+      <c r="D33" s="11"/>
+      <c r="E33" s="11"/>
+      <c r="F33" s="11"/>
+      <c r="G33" s="11"/>
+      <c r="H33" s="11"/>
+      <c r="I33" s="11"/>
+    </row>
+    <row r="34" spans="1:9" ht="12.75" x14ac:dyDescent="0.2"/>
     <row r="36" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A36" s="4"/>
-      <c r="B36" s="4"/>
-      <c r="C36" s="4"/>
-      <c r="D36" s="4"/>
-      <c r="E36" s="4"/>
-      <c r="F36" s="4"/>
-      <c r="G36" s="4"/>
-      <c r="H36" s="4"/>
-      <c r="I36" s="4"/>
+      <c r="B36" s="33"/>
+      <c r="C36" s="32"/>
+      <c r="D36" s="32"/>
+      <c r="E36" s="32"/>
+      <c r="F36" s="32"/>
+      <c r="G36" s="32"/>
+      <c r="H36" s="32"/>
+      <c r="I36" s="32"/>
     </row>
     <row r="37" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A37" s="4"/>
@@ -7491,7 +7554,6 @@
       <c r="G52" s="4"/>
       <c r="H52" s="4"/>
       <c r="I52" s="4"/>
-      <c r="K52" s="3"/>
     </row>
     <row r="53" spans="1:11" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A53" s="4"/>
@@ -7503,6 +7565,7 @@
       <c r="G53" s="4"/>
       <c r="H53" s="4"/>
       <c r="I53" s="4"/>
+      <c r="K53" s="3"/>
     </row>
     <row r="54" spans="1:11" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A54" s="4"/>
@@ -7658,7 +7721,7 @@
       <c r="H67" s="4"/>
       <c r="I67" s="4"/>
     </row>
-    <row r="68" spans="1:9" ht="12.75" hidden="1" x14ac:dyDescent="0.2">
+    <row r="68" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A68" s="4"/>
       <c r="B68" s="4"/>
       <c r="C68" s="4"/>
@@ -7669,7 +7732,7 @@
       <c r="H68" s="4"/>
       <c r="I68" s="4"/>
     </row>
-    <row r="69" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="69" spans="1:9" ht="12.75" hidden="1" x14ac:dyDescent="0.2">
       <c r="A69" s="4"/>
       <c r="B69" s="4"/>
       <c r="C69" s="4"/>
@@ -7681,29 +7744,29 @@
       <c r="I69" s="4"/>
     </row>
     <row r="70" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A70" s="31"/>
-      <c r="B70" s="30"/>
-      <c r="C70" s="30"/>
-      <c r="D70" s="30"/>
-      <c r="E70" s="30"/>
-      <c r="F70" s="30"/>
-      <c r="G70" s="30"/>
-      <c r="H70" s="30"/>
-      <c r="I70" s="30"/>
+      <c r="A70" s="4"/>
+      <c r="B70" s="4"/>
+      <c r="C70" s="4"/>
+      <c r="D70" s="4"/>
+      <c r="E70" s="4"/>
+      <c r="F70" s="4"/>
+      <c r="G70" s="4"/>
+      <c r="H70" s="4"/>
+      <c r="I70" s="4"/>
     </row>
     <row r="71" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A71" s="4"/>
-      <c r="B71" s="6"/>
-      <c r="C71" s="6"/>
-      <c r="D71" s="6"/>
-      <c r="E71" s="6"/>
-      <c r="F71" s="6"/>
-      <c r="G71" s="6"/>
-      <c r="H71" s="6"/>
-      <c r="I71" s="6"/>
+      <c r="A71" s="33"/>
+      <c r="B71" s="32"/>
+      <c r="C71" s="32"/>
+      <c r="D71" s="32"/>
+      <c r="E71" s="32"/>
+      <c r="F71" s="32"/>
+      <c r="G71" s="32"/>
+      <c r="H71" s="32"/>
+      <c r="I71" s="32"/>
     </row>
     <row r="72" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A72" s="6"/>
+      <c r="A72" s="4"/>
       <c r="B72" s="6"/>
       <c r="C72" s="6"/>
       <c r="D72" s="6"/>
@@ -7713,38 +7776,38 @@
       <c r="H72" s="6"/>
       <c r="I72" s="6"/>
     </row>
-    <row r="75" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A75" s="29"/>
-      <c r="B75" s="30"/>
-      <c r="C75" s="30"/>
-      <c r="D75" s="30"/>
-      <c r="E75" s="30"/>
-      <c r="F75" s="30"/>
-      <c r="G75" s="30"/>
-      <c r="H75" s="30"/>
-      <c r="I75" s="30"/>
+    <row r="73" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="A73" s="6"/>
+      <c r="B73" s="6"/>
+      <c r="C73" s="6"/>
+      <c r="D73" s="6"/>
+      <c r="E73" s="6"/>
+      <c r="F73" s="6"/>
+      <c r="G73" s="6"/>
+      <c r="H73" s="6"/>
+      <c r="I73" s="6"/>
     </row>
     <row r="76" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A76" s="4"/>
-      <c r="B76" s="7"/>
-      <c r="C76" s="7"/>
-      <c r="D76" s="7"/>
-      <c r="E76" s="7"/>
-      <c r="F76" s="7"/>
-      <c r="G76" s="7"/>
-      <c r="H76" s="7"/>
-      <c r="I76" s="7"/>
+      <c r="A76" s="31"/>
+      <c r="B76" s="32"/>
+      <c r="C76" s="32"/>
+      <c r="D76" s="32"/>
+      <c r="E76" s="32"/>
+      <c r="F76" s="32"/>
+      <c r="G76" s="32"/>
+      <c r="H76" s="32"/>
+      <c r="I76" s="32"/>
     </row>
     <row r="77" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A77" s="4"/>
-      <c r="B77" s="8"/>
-      <c r="C77" s="8"/>
-      <c r="D77" s="8"/>
-      <c r="E77" s="8"/>
-      <c r="F77" s="8"/>
-      <c r="G77" s="8"/>
-      <c r="H77" s="8"/>
-      <c r="I77" s="8"/>
+      <c r="B77" s="7"/>
+      <c r="C77" s="7"/>
+      <c r="D77" s="7"/>
+      <c r="E77" s="7"/>
+      <c r="F77" s="7"/>
+      <c r="G77" s="7"/>
+      <c r="H77" s="7"/>
+      <c r="I77" s="7"/>
     </row>
     <row r="78" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A78" s="4"/>
@@ -7758,26 +7821,26 @@
       <c r="I78" s="8"/>
     </row>
     <row r="79" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A79" s="32"/>
-      <c r="B79" s="30"/>
-      <c r="C79" s="30"/>
-      <c r="D79" s="30"/>
-      <c r="E79" s="30"/>
-      <c r="F79" s="30"/>
-      <c r="G79" s="30"/>
-      <c r="H79" s="30"/>
-      <c r="I79" s="30"/>
+      <c r="A79" s="4"/>
+      <c r="B79" s="8"/>
+      <c r="C79" s="8"/>
+      <c r="D79" s="8"/>
+      <c r="E79" s="8"/>
+      <c r="F79" s="8"/>
+      <c r="G79" s="8"/>
+      <c r="H79" s="8"/>
+      <c r="I79" s="8"/>
     </row>
     <row r="80" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A80" s="4"/>
-      <c r="B80" s="4"/>
-      <c r="C80" s="4"/>
-      <c r="D80" s="4"/>
-      <c r="E80" s="4"/>
-      <c r="F80" s="4"/>
-      <c r="G80" s="4"/>
-      <c r="H80" s="4"/>
-      <c r="I80" s="4"/>
+      <c r="A80" s="34"/>
+      <c r="B80" s="32"/>
+      <c r="C80" s="32"/>
+      <c r="D80" s="32"/>
+      <c r="E80" s="32"/>
+      <c r="F80" s="32"/>
+      <c r="G80" s="32"/>
+      <c r="H80" s="32"/>
+      <c r="I80" s="32"/>
     </row>
     <row r="81" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A81" s="4"/>
@@ -7790,38 +7853,38 @@
       <c r="H81" s="4"/>
       <c r="I81" s="4"/>
     </row>
-    <row r="83" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A83" s="4"/>
-      <c r="B83" s="4"/>
+    <row r="82" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="A82" s="4"/>
+      <c r="B82" s="4"/>
+      <c r="C82" s="4"/>
+      <c r="D82" s="4"/>
+      <c r="E82" s="4"/>
+      <c r="F82" s="4"/>
+      <c r="G82" s="4"/>
+      <c r="H82" s="4"/>
+      <c r="I82" s="4"/>
     </row>
     <row r="84" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A84" s="4"/>
+      <c r="B84" s="4"/>
     </row>
     <row r="85" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A85" s="4"/>
-      <c r="B85" s="6"/>
-    </row>
-    <row r="87" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A87" s="29"/>
-      <c r="B87" s="30"/>
-      <c r="C87" s="30"/>
-      <c r="D87" s="30"/>
-      <c r="E87" s="30"/>
-      <c r="F87" s="30"/>
-      <c r="G87" s="30"/>
-      <c r="H87" s="30"/>
-      <c r="I87" s="30"/>
+    </row>
+    <row r="86" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="A86" s="4"/>
+      <c r="B86" s="6"/>
     </row>
     <row r="88" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A88" s="4"/>
-      <c r="B88" s="9"/>
-      <c r="C88" s="9"/>
-      <c r="D88" s="9"/>
-      <c r="E88" s="9"/>
-      <c r="F88" s="9"/>
-      <c r="G88" s="9"/>
-      <c r="H88" s="9"/>
-      <c r="I88" s="9"/>
+      <c r="A88" s="31"/>
+      <c r="B88" s="32"/>
+      <c r="C88" s="32"/>
+      <c r="D88" s="32"/>
+      <c r="E88" s="32"/>
+      <c r="F88" s="32"/>
+      <c r="G88" s="32"/>
+      <c r="H88" s="32"/>
+      <c r="I88" s="32"/>
     </row>
     <row r="89" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A89" s="4"/>
@@ -7891,51 +7954,51 @@
     </row>
     <row r="95" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A95" s="4"/>
-      <c r="B95" s="4"/>
-      <c r="C95" s="4"/>
-      <c r="D95" s="4"/>
-      <c r="E95" s="4"/>
-      <c r="F95" s="4"/>
-      <c r="G95" s="4"/>
-      <c r="H95" s="4"/>
-      <c r="I95" s="4"/>
+      <c r="B95" s="9"/>
+      <c r="C95" s="9"/>
+      <c r="D95" s="9"/>
+      <c r="E95" s="9"/>
+      <c r="F95" s="9"/>
+      <c r="G95" s="9"/>
+      <c r="H95" s="9"/>
+      <c r="I95" s="9"/>
     </row>
     <row r="96" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A96" s="4"/>
-      <c r="B96" s="9"/>
+      <c r="B96" s="4"/>
+      <c r="C96" s="4"/>
+      <c r="D96" s="4"/>
+      <c r="E96" s="4"/>
+      <c r="F96" s="4"/>
+      <c r="G96" s="4"/>
+      <c r="H96" s="4"/>
+      <c r="I96" s="4"/>
     </row>
     <row r="97" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A97" s="4"/>
-      <c r="B97" s="4"/>
+      <c r="B97" s="9"/>
     </row>
     <row r="98" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A98" s="4"/>
-      <c r="B98" s="9"/>
-    </row>
-    <row r="100" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A100" s="31"/>
-      <c r="B100" s="30"/>
-      <c r="C100" s="30"/>
-      <c r="D100" s="30"/>
-      <c r="E100" s="30"/>
-      <c r="F100" s="30"/>
-      <c r="G100" s="30"/>
-      <c r="H100" s="30"/>
-      <c r="I100" s="30"/>
+      <c r="B98" s="4"/>
+    </row>
+    <row r="99" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="A99" s="4"/>
+      <c r="B99" s="9"/>
     </row>
     <row r="101" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A101" s="4"/>
-      <c r="B101" s="6"/>
-      <c r="C101" s="6"/>
-      <c r="D101" s="6"/>
-      <c r="E101" s="6"/>
-      <c r="F101" s="6"/>
-      <c r="G101" s="6"/>
-      <c r="H101" s="6"/>
-      <c r="I101" s="6"/>
+      <c r="A101" s="33"/>
+      <c r="B101" s="32"/>
+      <c r="C101" s="32"/>
+      <c r="D101" s="32"/>
+      <c r="E101" s="32"/>
+      <c r="F101" s="32"/>
+      <c r="G101" s="32"/>
+      <c r="H101" s="32"/>
+      <c r="I101" s="32"/>
     </row>
     <row r="102" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A102" s="6"/>
+      <c r="A102" s="4"/>
       <c r="B102" s="6"/>
       <c r="C102" s="6"/>
       <c r="D102" s="6"/>
@@ -7945,17 +8008,28 @@
       <c r="H102" s="6"/>
       <c r="I102" s="6"/>
     </row>
+    <row r="103" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="A103" s="6"/>
+      <c r="B103" s="6"/>
+      <c r="C103" s="6"/>
+      <c r="D103" s="6"/>
+      <c r="E103" s="6"/>
+      <c r="F103" s="6"/>
+      <c r="G103" s="6"/>
+      <c r="H103" s="6"/>
+      <c r="I103" s="6"/>
+    </row>
   </sheetData>
   <mergeCells count="6">
-    <mergeCell ref="A87:I87"/>
-    <mergeCell ref="A100:I100"/>
-    <mergeCell ref="B35:I35"/>
-    <mergeCell ref="A70:I70"/>
-    <mergeCell ref="A75:I75"/>
-    <mergeCell ref="A79:I79"/>
+    <mergeCell ref="A88:I88"/>
+    <mergeCell ref="A101:I101"/>
+    <mergeCell ref="B36:I36"/>
+    <mergeCell ref="A71:I71"/>
+    <mergeCell ref="A76:I76"/>
+    <mergeCell ref="A80:I80"/>
   </mergeCells>
   <dataValidations count="1">
-    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="A88" xr:uid="{7528D64E-4704-4E96-BA2D-746370B2BE4A}">
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="A89" xr:uid="{7528D64E-4704-4E96-BA2D-746370B2BE4A}">
       <formula1>"Bandeira,Verde,Amarela,Vermelha p1,Vermelha p2"</formula1>
     </dataValidation>
   </dataValidations>
@@ -8012,22 +8086,21 @@
       </c>
     </row>
     <row r="2" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A2" s="1">
-        <v>1</v>
-      </c>
-      <c r="B2" s="2"/>
-      <c r="C2" s="2"/>
-      <c r="D2" s="2"/>
-      <c r="E2" s="2"/>
-      <c r="F2" s="2"/>
-      <c r="G2" s="2"/>
-      <c r="H2" s="2"/>
-      <c r="I2" s="2"/>
+      <c r="A2" s="39">
+        <v>0</v>
+      </c>
+      <c r="B2" s="38"/>
+      <c r="C2" s="38"/>
+      <c r="D2" s="38"/>
+      <c r="E2" s="38"/>
+      <c r="F2" s="38"/>
+      <c r="G2" s="38"/>
+      <c r="H2" s="38"/>
+      <c r="I2" s="38"/>
     </row>
     <row r="3" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A3" s="1">
-        <f t="shared" ref="A3:A32" si="0">A2+1</f>
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B3" s="2"/>
       <c r="C3" s="2"/>
@@ -8040,8 +8113,8 @@
     </row>
     <row r="4" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A4" s="1">
-        <f t="shared" si="0"/>
-        <v>3</v>
+        <f t="shared" ref="A4:A32" si="0">A3+1</f>
+        <v>2</v>
       </c>
       <c r="B4" s="2"/>
       <c r="C4" s="2"/>
@@ -8055,7 +8128,7 @@
     <row r="5" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A5" s="1">
         <f t="shared" si="0"/>
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B5" s="2"/>
       <c r="C5" s="2"/>
@@ -8069,7 +8142,7 @@
     <row r="6" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A6" s="1">
         <f t="shared" si="0"/>
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B6" s="2"/>
       <c r="C6" s="2"/>
@@ -8083,7 +8156,7 @@
     <row r="7" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A7" s="1">
         <f t="shared" si="0"/>
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B7" s="2"/>
       <c r="C7" s="2"/>
@@ -8097,7 +8170,7 @@
     <row r="8" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A8" s="1">
         <f t="shared" si="0"/>
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B8" s="2"/>
       <c r="C8" s="2"/>
@@ -8111,7 +8184,7 @@
     <row r="9" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A9" s="1">
         <f t="shared" si="0"/>
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B9" s="2"/>
       <c r="C9" s="2"/>
@@ -8125,7 +8198,7 @@
     <row r="10" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A10" s="1">
         <f t="shared" si="0"/>
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B10" s="2"/>
       <c r="C10" s="2"/>
@@ -8139,7 +8212,7 @@
     <row r="11" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A11" s="1">
         <f t="shared" si="0"/>
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B11" s="2"/>
       <c r="C11" s="2"/>
@@ -8153,10 +8226,10 @@
     <row r="12" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A12" s="1">
         <f t="shared" si="0"/>
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B12" s="2"/>
-      <c r="C12" s="14"/>
+      <c r="C12" s="2"/>
       <c r="D12" s="2"/>
       <c r="E12" s="2"/>
       <c r="F12" s="2"/>
@@ -8167,10 +8240,10 @@
     <row r="13" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A13" s="1">
         <f t="shared" si="0"/>
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B13" s="2"/>
-      <c r="C13" s="2"/>
+      <c r="C13" s="14"/>
       <c r="D13" s="2"/>
       <c r="E13" s="2"/>
       <c r="F13" s="2"/>
@@ -8181,7 +8254,7 @@
     <row r="14" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A14" s="1">
         <f t="shared" si="0"/>
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B14" s="2"/>
       <c r="C14" s="2"/>
@@ -8195,7 +8268,7 @@
     <row r="15" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A15" s="1">
         <f t="shared" si="0"/>
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B15" s="2"/>
       <c r="C15" s="2"/>
@@ -8209,7 +8282,7 @@
     <row r="16" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A16" s="1">
         <f t="shared" si="0"/>
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B16" s="2"/>
       <c r="C16" s="2"/>
@@ -8223,7 +8296,7 @@
     <row r="17" spans="1:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A17" s="1">
         <f t="shared" si="0"/>
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B17" s="2"/>
       <c r="C17" s="2"/>
@@ -8237,7 +8310,7 @@
     <row r="18" spans="1:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A18" s="1">
         <f t="shared" si="0"/>
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B18" s="2"/>
       <c r="C18" s="2"/>
@@ -8247,12 +8320,11 @@
       <c r="G18" s="2"/>
       <c r="H18" s="2"/>
       <c r="I18" s="2"/>
-      <c r="J18" s="3"/>
     </row>
     <row r="19" spans="1:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A19" s="1">
         <f t="shared" si="0"/>
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B19" s="2"/>
       <c r="C19" s="2"/>
@@ -8262,11 +8334,12 @@
       <c r="G19" s="2"/>
       <c r="H19" s="2"/>
       <c r="I19" s="2"/>
+      <c r="J19" s="3"/>
     </row>
     <row r="20" spans="1:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A20" s="1">
         <f t="shared" si="0"/>
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B20" s="2"/>
       <c r="C20" s="2"/>
@@ -8280,7 +8353,7 @@
     <row r="21" spans="1:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A21" s="1">
         <f t="shared" si="0"/>
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B21" s="2"/>
       <c r="C21" s="2"/>
@@ -8294,7 +8367,7 @@
     <row r="22" spans="1:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A22" s="1">
         <f t="shared" si="0"/>
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="B22" s="2"/>
       <c r="C22" s="2"/>
@@ -8308,7 +8381,7 @@
     <row r="23" spans="1:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A23" s="1">
         <f t="shared" si="0"/>
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B23" s="2"/>
       <c r="C23" s="2"/>
@@ -8322,7 +8395,7 @@
     <row r="24" spans="1:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A24" s="1">
         <f t="shared" si="0"/>
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B24" s="2"/>
       <c r="C24" s="2"/>
@@ -8336,7 +8409,7 @@
     <row r="25" spans="1:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A25" s="1">
         <f t="shared" si="0"/>
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B25" s="2"/>
       <c r="C25" s="2"/>
@@ -8350,7 +8423,7 @@
     <row r="26" spans="1:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A26" s="1">
         <f t="shared" si="0"/>
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B26" s="2"/>
       <c r="C26" s="2"/>
@@ -8364,7 +8437,7 @@
     <row r="27" spans="1:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A27" s="1">
         <f t="shared" si="0"/>
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B27" s="2"/>
       <c r="C27" s="2"/>
@@ -8378,7 +8451,7 @@
     <row r="28" spans="1:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A28" s="1">
         <f t="shared" si="0"/>
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="B28" s="2"/>
       <c r="C28" s="2"/>
@@ -8392,7 +8465,7 @@
     <row r="29" spans="1:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A29" s="1">
         <f t="shared" si="0"/>
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="B29" s="2"/>
       <c r="C29" s="2"/>
@@ -8406,7 +8479,7 @@
     <row r="30" spans="1:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A30" s="1">
         <f t="shared" si="0"/>
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="B30" s="2"/>
       <c r="C30" s="2"/>
@@ -8420,7 +8493,7 @@
     <row r="31" spans="1:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A31" s="1">
         <f t="shared" si="0"/>
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B31" s="2"/>
       <c r="C31" s="2"/>
@@ -8432,30 +8505,30 @@
       <c r="I31" s="2"/>
     </row>
     <row r="32" spans="1:10" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A32" s="10">
-        <f t="shared" si="0"/>
-        <v>31</v>
-      </c>
-      <c r="B32" s="11"/>
-      <c r="C32" s="11"/>
-      <c r="D32" s="11"/>
-      <c r="E32" s="11"/>
-      <c r="F32" s="11"/>
-      <c r="G32" s="11"/>
-      <c r="H32" s="11"/>
-      <c r="I32" s="11"/>
+      <c r="A32" s="1">
+        <f t="shared" si="0"/>
+        <v>30</v>
+      </c>
+      <c r="B32" s="2"/>
+      <c r="C32" s="2"/>
+      <c r="D32" s="2"/>
+      <c r="E32" s="2"/>
+      <c r="F32" s="2"/>
+      <c r="G32" s="2"/>
+      <c r="H32" s="2"/>
+      <c r="I32" s="2"/>
     </row>
     <row r="33" spans="1:9" ht="12.75" x14ac:dyDescent="0.2"/>
     <row r="35" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A35" s="4"/>
-      <c r="B35" s="31"/>
-      <c r="C35" s="30"/>
-      <c r="D35" s="30"/>
-      <c r="E35" s="30"/>
-      <c r="F35" s="30"/>
-      <c r="G35" s="30"/>
-      <c r="H35" s="30"/>
-      <c r="I35" s="30"/>
+      <c r="B35" s="33"/>
+      <c r="C35" s="32"/>
+      <c r="D35" s="32"/>
+      <c r="E35" s="32"/>
+      <c r="F35" s="32"/>
+      <c r="G35" s="32"/>
+      <c r="H35" s="32"/>
+      <c r="I35" s="32"/>
     </row>
     <row r="36" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A36" s="4"/>
@@ -8833,15 +8906,15 @@
       <c r="I69" s="4"/>
     </row>
     <row r="70" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A70" s="31"/>
-      <c r="B70" s="30"/>
-      <c r="C70" s="30"/>
-      <c r="D70" s="30"/>
-      <c r="E70" s="30"/>
-      <c r="F70" s="30"/>
-      <c r="G70" s="30"/>
-      <c r="H70" s="30"/>
-      <c r="I70" s="30"/>
+      <c r="A70" s="33"/>
+      <c r="B70" s="32"/>
+      <c r="C70" s="32"/>
+      <c r="D70" s="32"/>
+      <c r="E70" s="32"/>
+      <c r="F70" s="32"/>
+      <c r="G70" s="32"/>
+      <c r="H70" s="32"/>
+      <c r="I70" s="32"/>
     </row>
     <row r="71" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A71" s="4"/>
@@ -8866,15 +8939,15 @@
       <c r="I72" s="6"/>
     </row>
     <row r="75" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A75" s="29"/>
-      <c r="B75" s="30"/>
-      <c r="C75" s="30"/>
-      <c r="D75" s="30"/>
-      <c r="E75" s="30"/>
-      <c r="F75" s="30"/>
-      <c r="G75" s="30"/>
-      <c r="H75" s="30"/>
-      <c r="I75" s="30"/>
+      <c r="A75" s="31"/>
+      <c r="B75" s="32"/>
+      <c r="C75" s="32"/>
+      <c r="D75" s="32"/>
+      <c r="E75" s="32"/>
+      <c r="F75" s="32"/>
+      <c r="G75" s="32"/>
+      <c r="H75" s="32"/>
+      <c r="I75" s="32"/>
     </row>
     <row r="76" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A76" s="4"/>
@@ -8910,15 +8983,15 @@
       <c r="I78" s="8"/>
     </row>
     <row r="79" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A79" s="32"/>
-      <c r="B79" s="30"/>
-      <c r="C79" s="30"/>
-      <c r="D79" s="30"/>
-      <c r="E79" s="30"/>
-      <c r="F79" s="30"/>
-      <c r="G79" s="30"/>
-      <c r="H79" s="30"/>
-      <c r="I79" s="30"/>
+      <c r="A79" s="34"/>
+      <c r="B79" s="32"/>
+      <c r="C79" s="32"/>
+      <c r="D79" s="32"/>
+      <c r="E79" s="32"/>
+      <c r="F79" s="32"/>
+      <c r="G79" s="32"/>
+      <c r="H79" s="32"/>
+      <c r="I79" s="32"/>
     </row>
     <row r="80" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A80" s="4"/>
@@ -8954,15 +9027,15 @@
       <c r="B85" s="6"/>
     </row>
     <row r="87" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A87" s="29"/>
-      <c r="B87" s="30"/>
-      <c r="C87" s="30"/>
-      <c r="D87" s="30"/>
-      <c r="E87" s="30"/>
-      <c r="F87" s="30"/>
-      <c r="G87" s="30"/>
-      <c r="H87" s="30"/>
-      <c r="I87" s="30"/>
+      <c r="A87" s="31"/>
+      <c r="B87" s="32"/>
+      <c r="C87" s="32"/>
+      <c r="D87" s="32"/>
+      <c r="E87" s="32"/>
+      <c r="F87" s="32"/>
+      <c r="G87" s="32"/>
+      <c r="H87" s="32"/>
+      <c r="I87" s="32"/>
     </row>
     <row r="88" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A88" s="4"/>
@@ -9065,15 +9138,15 @@
       <c r="B98" s="9"/>
     </row>
     <row r="100" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A100" s="31"/>
-      <c r="B100" s="30"/>
-      <c r="C100" s="30"/>
-      <c r="D100" s="30"/>
-      <c r="E100" s="30"/>
-      <c r="F100" s="30"/>
-      <c r="G100" s="30"/>
-      <c r="H100" s="30"/>
-      <c r="I100" s="30"/>
+      <c r="A100" s="33"/>
+      <c r="B100" s="32"/>
+      <c r="C100" s="32"/>
+      <c r="D100" s="32"/>
+      <c r="E100" s="32"/>
+      <c r="F100" s="32"/>
+      <c r="G100" s="32"/>
+      <c r="H100" s="32"/>
+      <c r="I100" s="32"/>
     </row>
     <row r="101" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A101" s="4"/>
@@ -9164,22 +9237,21 @@
       </c>
     </row>
     <row r="2" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A2" s="1">
-        <v>1</v>
-      </c>
-      <c r="B2" s="2"/>
-      <c r="C2" s="2"/>
-      <c r="D2" s="2"/>
-      <c r="E2" s="2"/>
-      <c r="F2" s="2"/>
-      <c r="G2" s="2"/>
-      <c r="H2" s="2"/>
-      <c r="I2" s="2"/>
+      <c r="A2" s="39">
+        <v>0</v>
+      </c>
+      <c r="B2" s="38"/>
+      <c r="C2" s="38"/>
+      <c r="D2" s="38"/>
+      <c r="E2" s="38"/>
+      <c r="F2" s="38"/>
+      <c r="G2" s="38"/>
+      <c r="H2" s="38"/>
+      <c r="I2" s="38"/>
     </row>
     <row r="3" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A3" s="1">
-        <f t="shared" ref="A3:A32" si="0">A2+1</f>
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B3" s="2"/>
       <c r="C3" s="2"/>
@@ -9192,8 +9264,8 @@
     </row>
     <row r="4" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A4" s="1">
-        <f t="shared" si="0"/>
-        <v>3</v>
+        <f t="shared" ref="A4:A33" si="0">A3+1</f>
+        <v>2</v>
       </c>
       <c r="B4" s="2"/>
       <c r="C4" s="2"/>
@@ -9207,7 +9279,7 @@
     <row r="5" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A5" s="1">
         <f t="shared" si="0"/>
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B5" s="2"/>
       <c r="C5" s="2"/>
@@ -9221,7 +9293,7 @@
     <row r="6" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A6" s="1">
         <f t="shared" si="0"/>
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B6" s="2"/>
       <c r="C6" s="2"/>
@@ -9235,7 +9307,7 @@
     <row r="7" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A7" s="1">
         <f t="shared" si="0"/>
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B7" s="2"/>
       <c r="C7" s="2"/>
@@ -9249,7 +9321,7 @@
     <row r="8" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A8" s="1">
         <f t="shared" si="0"/>
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B8" s="2"/>
       <c r="C8" s="2"/>
@@ -9263,7 +9335,7 @@
     <row r="9" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A9" s="1">
         <f t="shared" si="0"/>
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B9" s="2"/>
       <c r="C9" s="2"/>
@@ -9277,7 +9349,7 @@
     <row r="10" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A10" s="1">
         <f t="shared" si="0"/>
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B10" s="2"/>
       <c r="C10" s="2"/>
@@ -9291,7 +9363,7 @@
     <row r="11" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A11" s="1">
         <f t="shared" si="0"/>
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B11" s="2"/>
       <c r="C11" s="2"/>
@@ -9305,10 +9377,10 @@
     <row r="12" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A12" s="1">
         <f t="shared" si="0"/>
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B12" s="2"/>
-      <c r="C12" s="14"/>
+      <c r="C12" s="2"/>
       <c r="D12" s="2"/>
       <c r="E12" s="2"/>
       <c r="F12" s="2"/>
@@ -9319,10 +9391,10 @@
     <row r="13" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A13" s="1">
         <f t="shared" si="0"/>
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B13" s="2"/>
-      <c r="C13" s="2"/>
+      <c r="C13" s="14"/>
       <c r="D13" s="2"/>
       <c r="E13" s="2"/>
       <c r="F13" s="2"/>
@@ -9333,7 +9405,7 @@
     <row r="14" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A14" s="1">
         <f t="shared" si="0"/>
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B14" s="2"/>
       <c r="C14" s="2"/>
@@ -9347,7 +9419,7 @@
     <row r="15" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A15" s="1">
         <f t="shared" si="0"/>
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B15" s="2"/>
       <c r="C15" s="2"/>
@@ -9361,7 +9433,7 @@
     <row r="16" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A16" s="1">
         <f t="shared" si="0"/>
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B16" s="2"/>
       <c r="C16" s="2"/>
@@ -9375,7 +9447,7 @@
     <row r="17" spans="1:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A17" s="1">
         <f t="shared" si="0"/>
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B17" s="2"/>
       <c r="C17" s="2"/>
@@ -9389,7 +9461,7 @@
     <row r="18" spans="1:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A18" s="1">
         <f t="shared" si="0"/>
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B18" s="2"/>
       <c r="C18" s="2"/>
@@ -9399,12 +9471,11 @@
       <c r="G18" s="2"/>
       <c r="H18" s="2"/>
       <c r="I18" s="2"/>
-      <c r="J18" s="3"/>
     </row>
     <row r="19" spans="1:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A19" s="1">
         <f t="shared" si="0"/>
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B19" s="2"/>
       <c r="C19" s="2"/>
@@ -9414,11 +9485,12 @@
       <c r="G19" s="2"/>
       <c r="H19" s="2"/>
       <c r="I19" s="2"/>
+      <c r="J19" s="3"/>
     </row>
     <row r="20" spans="1:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A20" s="1">
         <f t="shared" si="0"/>
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B20" s="2"/>
       <c r="C20" s="2"/>
@@ -9432,7 +9504,7 @@
     <row r="21" spans="1:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A21" s="1">
         <f t="shared" si="0"/>
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B21" s="2"/>
       <c r="C21" s="2"/>
@@ -9446,7 +9518,7 @@
     <row r="22" spans="1:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A22" s="1">
         <f t="shared" si="0"/>
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="B22" s="2"/>
       <c r="C22" s="2"/>
@@ -9460,7 +9532,7 @@
     <row r="23" spans="1:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A23" s="1">
         <f t="shared" si="0"/>
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B23" s="2"/>
       <c r="C23" s="2"/>
@@ -9474,7 +9546,7 @@
     <row r="24" spans="1:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A24" s="1">
         <f t="shared" si="0"/>
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B24" s="2"/>
       <c r="C24" s="2"/>
@@ -9488,7 +9560,7 @@
     <row r="25" spans="1:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A25" s="1">
         <f t="shared" si="0"/>
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B25" s="2"/>
       <c r="C25" s="2"/>
@@ -9502,7 +9574,7 @@
     <row r="26" spans="1:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A26" s="1">
         <f t="shared" si="0"/>
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B26" s="2"/>
       <c r="C26" s="2"/>
@@ -9516,7 +9588,7 @@
     <row r="27" spans="1:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A27" s="1">
         <f t="shared" si="0"/>
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B27" s="2"/>
       <c r="C27" s="2"/>
@@ -9530,7 +9602,7 @@
     <row r="28" spans="1:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A28" s="1">
         <f t="shared" si="0"/>
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="B28" s="2"/>
       <c r="C28" s="2"/>
@@ -9544,7 +9616,7 @@
     <row r="29" spans="1:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A29" s="1">
         <f t="shared" si="0"/>
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="B29" s="2"/>
       <c r="C29" s="2"/>
@@ -9558,7 +9630,7 @@
     <row r="30" spans="1:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A30" s="1">
         <f t="shared" si="0"/>
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="B30" s="2"/>
       <c r="C30" s="2"/>
@@ -9572,7 +9644,7 @@
     <row r="31" spans="1:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A31" s="1">
         <f t="shared" si="0"/>
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B31" s="2"/>
       <c r="C31" s="2"/>
@@ -9584,30 +9656,43 @@
       <c r="I31" s="2"/>
     </row>
     <row r="32" spans="1:10" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A32" s="10">
+      <c r="A32" s="1">
+        <f t="shared" si="0"/>
+        <v>30</v>
+      </c>
+      <c r="B32" s="2"/>
+      <c r="C32" s="2"/>
+      <c r="D32" s="2"/>
+      <c r="E32" s="2"/>
+      <c r="F32" s="2"/>
+      <c r="G32" s="2"/>
+      <c r="H32" s="2"/>
+      <c r="I32" s="2"/>
+    </row>
+    <row r="33" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="A33" s="10">
         <f t="shared" si="0"/>
         <v>31</v>
       </c>
-      <c r="B32" s="11"/>
-      <c r="C32" s="11"/>
-      <c r="D32" s="11"/>
-      <c r="E32" s="11"/>
-      <c r="F32" s="11"/>
-      <c r="G32" s="11"/>
-      <c r="H32" s="11"/>
-      <c r="I32" s="11"/>
-    </row>
-    <row r="33" spans="1:9" ht="12.75" x14ac:dyDescent="0.2"/>
+      <c r="B33" s="11"/>
+      <c r="C33" s="11"/>
+      <c r="D33" s="11"/>
+      <c r="E33" s="11"/>
+      <c r="F33" s="11"/>
+      <c r="G33" s="11"/>
+      <c r="H33" s="11"/>
+      <c r="I33" s="11"/>
+    </row>
     <row r="35" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A35" s="4"/>
-      <c r="B35" s="31"/>
-      <c r="C35" s="30"/>
-      <c r="D35" s="30"/>
-      <c r="E35" s="30"/>
-      <c r="F35" s="30"/>
-      <c r="G35" s="30"/>
-      <c r="H35" s="30"/>
-      <c r="I35" s="30"/>
+      <c r="B35" s="33"/>
+      <c r="C35" s="32"/>
+      <c r="D35" s="32"/>
+      <c r="E35" s="32"/>
+      <c r="F35" s="32"/>
+      <c r="G35" s="32"/>
+      <c r="H35" s="32"/>
+      <c r="I35" s="32"/>
     </row>
     <row r="36" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A36" s="4"/>
@@ -9985,15 +10070,15 @@
       <c r="I69" s="4"/>
     </row>
     <row r="70" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A70" s="31"/>
-      <c r="B70" s="30"/>
-      <c r="C70" s="30"/>
-      <c r="D70" s="30"/>
-      <c r="E70" s="30"/>
-      <c r="F70" s="30"/>
-      <c r="G70" s="30"/>
-      <c r="H70" s="30"/>
-      <c r="I70" s="30"/>
+      <c r="A70" s="33"/>
+      <c r="B70" s="32"/>
+      <c r="C70" s="32"/>
+      <c r="D70" s="32"/>
+      <c r="E70" s="32"/>
+      <c r="F70" s="32"/>
+      <c r="G70" s="32"/>
+      <c r="H70" s="32"/>
+      <c r="I70" s="32"/>
     </row>
     <row r="71" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A71" s="4"/>
@@ -10018,15 +10103,15 @@
       <c r="I72" s="6"/>
     </row>
     <row r="75" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A75" s="29"/>
-      <c r="B75" s="30"/>
-      <c r="C75" s="30"/>
-      <c r="D75" s="30"/>
-      <c r="E75" s="30"/>
-      <c r="F75" s="30"/>
-      <c r="G75" s="30"/>
-      <c r="H75" s="30"/>
-      <c r="I75" s="30"/>
+      <c r="A75" s="31"/>
+      <c r="B75" s="32"/>
+      <c r="C75" s="32"/>
+      <c r="D75" s="32"/>
+      <c r="E75" s="32"/>
+      <c r="F75" s="32"/>
+      <c r="G75" s="32"/>
+      <c r="H75" s="32"/>
+      <c r="I75" s="32"/>
     </row>
     <row r="76" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A76" s="4"/>
@@ -10062,15 +10147,15 @@
       <c r="I78" s="8"/>
     </row>
     <row r="79" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A79" s="32"/>
-      <c r="B79" s="30"/>
-      <c r="C79" s="30"/>
-      <c r="D79" s="30"/>
-      <c r="E79" s="30"/>
-      <c r="F79" s="30"/>
-      <c r="G79" s="30"/>
-      <c r="H79" s="30"/>
-      <c r="I79" s="30"/>
+      <c r="A79" s="34"/>
+      <c r="B79" s="32"/>
+      <c r="C79" s="32"/>
+      <c r="D79" s="32"/>
+      <c r="E79" s="32"/>
+      <c r="F79" s="32"/>
+      <c r="G79" s="32"/>
+      <c r="H79" s="32"/>
+      <c r="I79" s="32"/>
     </row>
     <row r="80" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A80" s="4"/>
@@ -10106,15 +10191,15 @@
       <c r="B85" s="6"/>
     </row>
     <row r="87" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A87" s="29"/>
-      <c r="B87" s="30"/>
-      <c r="C87" s="30"/>
-      <c r="D87" s="30"/>
-      <c r="E87" s="30"/>
-      <c r="F87" s="30"/>
-      <c r="G87" s="30"/>
-      <c r="H87" s="30"/>
-      <c r="I87" s="30"/>
+      <c r="A87" s="31"/>
+      <c r="B87" s="32"/>
+      <c r="C87" s="32"/>
+      <c r="D87" s="32"/>
+      <c r="E87" s="32"/>
+      <c r="F87" s="32"/>
+      <c r="G87" s="32"/>
+      <c r="H87" s="32"/>
+      <c r="I87" s="32"/>
     </row>
     <row r="88" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A88" s="4"/>
@@ -10217,15 +10302,15 @@
       <c r="B98" s="9"/>
     </row>
     <row r="100" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A100" s="31"/>
-      <c r="B100" s="30"/>
-      <c r="C100" s="30"/>
-      <c r="D100" s="30"/>
-      <c r="E100" s="30"/>
-      <c r="F100" s="30"/>
-      <c r="G100" s="30"/>
-      <c r="H100" s="30"/>
-      <c r="I100" s="30"/>
+      <c r="A100" s="33"/>
+      <c r="B100" s="32"/>
+      <c r="C100" s="32"/>
+      <c r="D100" s="32"/>
+      <c r="E100" s="32"/>
+      <c r="F100" s="32"/>
+      <c r="G100" s="32"/>
+      <c r="H100" s="32"/>
+      <c r="I100" s="32"/>
     </row>
     <row r="101" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A101" s="4"/>
@@ -10272,7 +10357,7 @@
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
-  <dimension ref="A1:K102"/>
+  <dimension ref="A1:K103"/>
   <sheetFormatPr defaultColWidth="12.5703125" defaultRowHeight="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="19.42578125" customWidth="1"/>
@@ -10316,22 +10401,21 @@
       </c>
     </row>
     <row r="2" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A2" s="1">
-        <v>1</v>
-      </c>
-      <c r="B2" s="2"/>
-      <c r="C2" s="2"/>
-      <c r="D2" s="2"/>
-      <c r="E2" s="2"/>
-      <c r="F2" s="2"/>
-      <c r="G2" s="2"/>
-      <c r="H2" s="2"/>
-      <c r="I2" s="2"/>
+      <c r="A2" s="39">
+        <v>0</v>
+      </c>
+      <c r="B2" s="38"/>
+      <c r="C2" s="38"/>
+      <c r="D2" s="38"/>
+      <c r="E2" s="38"/>
+      <c r="F2" s="38"/>
+      <c r="G2" s="38"/>
+      <c r="H2" s="38"/>
+      <c r="I2" s="38"/>
     </row>
     <row r="3" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A3" s="1">
-        <f t="shared" ref="A3:A32" si="0">A2+1</f>
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B3" s="2"/>
       <c r="C3" s="2"/>
@@ -10344,8 +10428,8 @@
     </row>
     <row r="4" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A4" s="1">
-        <f t="shared" si="0"/>
-        <v>3</v>
+        <f t="shared" ref="A4:A33" si="0">A3+1</f>
+        <v>2</v>
       </c>
       <c r="B4" s="2"/>
       <c r="C4" s="2"/>
@@ -10359,7 +10443,7 @@
     <row r="5" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A5" s="1">
         <f t="shared" si="0"/>
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B5" s="2"/>
       <c r="C5" s="2"/>
@@ -10373,7 +10457,7 @@
     <row r="6" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A6" s="1">
         <f t="shared" si="0"/>
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B6" s="2"/>
       <c r="C6" s="2"/>
@@ -10387,7 +10471,7 @@
     <row r="7" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A7" s="1">
         <f t="shared" si="0"/>
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B7" s="2"/>
       <c r="C7" s="2"/>
@@ -10401,7 +10485,7 @@
     <row r="8" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A8" s="1">
         <f t="shared" si="0"/>
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B8" s="2"/>
       <c r="C8" s="2"/>
@@ -10415,7 +10499,7 @@
     <row r="9" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A9" s="1">
         <f t="shared" si="0"/>
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B9" s="2"/>
       <c r="C9" s="2"/>
@@ -10429,7 +10513,7 @@
     <row r="10" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A10" s="1">
         <f t="shared" si="0"/>
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B10" s="2"/>
       <c r="C10" s="2"/>
@@ -10443,7 +10527,7 @@
     <row r="11" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A11" s="1">
         <f t="shared" si="0"/>
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B11" s="2"/>
       <c r="C11" s="2"/>
@@ -10457,10 +10541,10 @@
     <row r="12" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A12" s="1">
         <f t="shared" si="0"/>
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B12" s="2"/>
-      <c r="C12" s="14"/>
+      <c r="C12" s="2"/>
       <c r="D12" s="2"/>
       <c r="E12" s="2"/>
       <c r="F12" s="2"/>
@@ -10471,10 +10555,10 @@
     <row r="13" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A13" s="1">
         <f t="shared" si="0"/>
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B13" s="2"/>
-      <c r="C13" s="2"/>
+      <c r="C13" s="14"/>
       <c r="D13" s="2"/>
       <c r="E13" s="2"/>
       <c r="F13" s="2"/>
@@ -10485,7 +10569,7 @@
     <row r="14" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A14" s="1">
         <f t="shared" si="0"/>
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B14" s="2"/>
       <c r="C14" s="2"/>
@@ -10499,7 +10583,7 @@
     <row r="15" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A15" s="1">
         <f t="shared" si="0"/>
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B15" s="2"/>
       <c r="C15" s="2"/>
@@ -10513,7 +10597,7 @@
     <row r="16" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A16" s="1">
         <f t="shared" si="0"/>
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B16" s="2"/>
       <c r="C16" s="2"/>
@@ -10527,7 +10611,7 @@
     <row r="17" spans="1:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A17" s="1">
         <f t="shared" si="0"/>
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B17" s="2"/>
       <c r="C17" s="2"/>
@@ -10541,7 +10625,7 @@
     <row r="18" spans="1:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A18" s="1">
         <f t="shared" si="0"/>
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B18" s="2"/>
       <c r="C18" s="2"/>
@@ -10551,12 +10635,11 @@
       <c r="G18" s="2"/>
       <c r="H18" s="2"/>
       <c r="I18" s="2"/>
-      <c r="J18" s="3"/>
     </row>
     <row r="19" spans="1:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A19" s="1">
         <f t="shared" si="0"/>
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B19" s="2"/>
       <c r="C19" s="2"/>
@@ -10566,11 +10649,12 @@
       <c r="G19" s="2"/>
       <c r="H19" s="2"/>
       <c r="I19" s="2"/>
+      <c r="J19" s="3"/>
     </row>
     <row r="20" spans="1:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A20" s="1">
         <f t="shared" si="0"/>
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B20" s="2"/>
       <c r="C20" s="2"/>
@@ -10584,7 +10668,7 @@
     <row r="21" spans="1:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A21" s="1">
         <f t="shared" si="0"/>
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B21" s="2"/>
       <c r="C21" s="2"/>
@@ -10598,7 +10682,7 @@
     <row r="22" spans="1:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A22" s="1">
         <f t="shared" si="0"/>
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="B22" s="2"/>
       <c r="C22" s="2"/>
@@ -10612,7 +10696,7 @@
     <row r="23" spans="1:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A23" s="1">
         <f t="shared" si="0"/>
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B23" s="2"/>
       <c r="C23" s="2"/>
@@ -10626,7 +10710,7 @@
     <row r="24" spans="1:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A24" s="1">
         <f t="shared" si="0"/>
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B24" s="2"/>
       <c r="C24" s="2"/>
@@ -10640,7 +10724,7 @@
     <row r="25" spans="1:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A25" s="1">
         <f t="shared" si="0"/>
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B25" s="2"/>
       <c r="C25" s="2"/>
@@ -10654,7 +10738,7 @@
     <row r="26" spans="1:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A26" s="1">
         <f t="shared" si="0"/>
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B26" s="2"/>
       <c r="C26" s="2"/>
@@ -10668,7 +10752,7 @@
     <row r="27" spans="1:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A27" s="1">
         <f t="shared" si="0"/>
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B27" s="2"/>
       <c r="C27" s="2"/>
@@ -10682,7 +10766,7 @@
     <row r="28" spans="1:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A28" s="1">
         <f t="shared" si="0"/>
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="B28" s="2"/>
       <c r="C28" s="2"/>
@@ -10696,7 +10780,7 @@
     <row r="29" spans="1:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A29" s="1">
         <f t="shared" si="0"/>
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="B29" s="2"/>
       <c r="C29" s="2"/>
@@ -10710,7 +10794,7 @@
     <row r="30" spans="1:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A30" s="1">
         <f t="shared" si="0"/>
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="B30" s="2"/>
       <c r="C30" s="2"/>
@@ -10724,7 +10808,7 @@
     <row r="31" spans="1:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A31" s="1">
         <f t="shared" si="0"/>
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B31" s="2"/>
       <c r="C31" s="2"/>
@@ -10736,41 +10820,43 @@
       <c r="I31" s="2"/>
     </row>
     <row r="32" spans="1:10" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A32" s="10">
+      <c r="A32" s="1">
+        <f t="shared" si="0"/>
+        <v>30</v>
+      </c>
+      <c r="B32" s="2"/>
+      <c r="C32" s="2"/>
+      <c r="D32" s="2"/>
+      <c r="E32" s="2"/>
+      <c r="F32" s="2"/>
+      <c r="G32" s="2"/>
+      <c r="H32" s="2"/>
+      <c r="I32" s="2"/>
+    </row>
+    <row r="33" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="A33" s="10">
         <f t="shared" si="0"/>
         <v>31</v>
       </c>
-      <c r="B32" s="11"/>
-      <c r="C32" s="11"/>
-      <c r="D32" s="11"/>
-      <c r="E32" s="11"/>
-      <c r="F32" s="11"/>
-      <c r="G32" s="11"/>
-      <c r="H32" s="11"/>
-      <c r="I32" s="11"/>
-    </row>
-    <row r="33" spans="1:9" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="35" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A35" s="4"/>
-      <c r="B35" s="31"/>
-      <c r="C35" s="30"/>
-      <c r="D35" s="30"/>
-      <c r="E35" s="30"/>
-      <c r="F35" s="30"/>
-      <c r="G35" s="30"/>
-      <c r="H35" s="30"/>
-      <c r="I35" s="30"/>
+      <c r="B33" s="11"/>
+      <c r="C33" s="11"/>
+      <c r="D33" s="11"/>
+      <c r="E33" s="11"/>
+      <c r="F33" s="11"/>
+      <c r="G33" s="11"/>
+      <c r="H33" s="11"/>
+      <c r="I33" s="11"/>
     </row>
     <row r="36" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A36" s="4"/>
-      <c r="B36" s="4"/>
-      <c r="C36" s="4"/>
-      <c r="D36" s="4"/>
-      <c r="E36" s="4"/>
-      <c r="F36" s="4"/>
-      <c r="G36" s="4"/>
-      <c r="H36" s="4"/>
-      <c r="I36" s="4"/>
+      <c r="B36" s="33"/>
+      <c r="C36" s="32"/>
+      <c r="D36" s="32"/>
+      <c r="E36" s="32"/>
+      <c r="F36" s="32"/>
+      <c r="G36" s="32"/>
+      <c r="H36" s="32"/>
+      <c r="I36" s="32"/>
     </row>
     <row r="37" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A37" s="4"/>
@@ -10947,7 +11033,6 @@
       <c r="G52" s="4"/>
       <c r="H52" s="4"/>
       <c r="I52" s="4"/>
-      <c r="K52" s="3"/>
     </row>
     <row r="53" spans="1:11" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A53" s="4"/>
@@ -10959,6 +11044,7 @@
       <c r="G53" s="4"/>
       <c r="H53" s="4"/>
       <c r="I53" s="4"/>
+      <c r="K53" s="3"/>
     </row>
     <row r="54" spans="1:11" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A54" s="4"/>
@@ -11114,7 +11200,7 @@
       <c r="H67" s="4"/>
       <c r="I67" s="4"/>
     </row>
-    <row r="68" spans="1:9" ht="12.75" hidden="1" x14ac:dyDescent="0.2">
+    <row r="68" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A68" s="4"/>
       <c r="B68" s="4"/>
       <c r="C68" s="4"/>
@@ -11125,7 +11211,7 @@
       <c r="H68" s="4"/>
       <c r="I68" s="4"/>
     </row>
-    <row r="69" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="69" spans="1:9" ht="12.75" hidden="1" x14ac:dyDescent="0.2">
       <c r="A69" s="4"/>
       <c r="B69" s="4"/>
       <c r="C69" s="4"/>
@@ -11137,29 +11223,29 @@
       <c r="I69" s="4"/>
     </row>
     <row r="70" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A70" s="31"/>
-      <c r="B70" s="30"/>
-      <c r="C70" s="30"/>
-      <c r="D70" s="30"/>
-      <c r="E70" s="30"/>
-      <c r="F70" s="30"/>
-      <c r="G70" s="30"/>
-      <c r="H70" s="30"/>
-      <c r="I70" s="30"/>
+      <c r="A70" s="4"/>
+      <c r="B70" s="4"/>
+      <c r="C70" s="4"/>
+      <c r="D70" s="4"/>
+      <c r="E70" s="4"/>
+      <c r="F70" s="4"/>
+      <c r="G70" s="4"/>
+      <c r="H70" s="4"/>
+      <c r="I70" s="4"/>
     </row>
     <row r="71" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A71" s="4"/>
-      <c r="B71" s="6"/>
-      <c r="C71" s="6"/>
-      <c r="D71" s="6"/>
-      <c r="E71" s="6"/>
-      <c r="F71" s="6"/>
-      <c r="G71" s="6"/>
-      <c r="H71" s="6"/>
-      <c r="I71" s="6"/>
+      <c r="A71" s="33"/>
+      <c r="B71" s="32"/>
+      <c r="C71" s="32"/>
+      <c r="D71" s="32"/>
+      <c r="E71" s="32"/>
+      <c r="F71" s="32"/>
+      <c r="G71" s="32"/>
+      <c r="H71" s="32"/>
+      <c r="I71" s="32"/>
     </row>
     <row r="72" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A72" s="6"/>
+      <c r="A72" s="4"/>
       <c r="B72" s="6"/>
       <c r="C72" s="6"/>
       <c r="D72" s="6"/>
@@ -11169,38 +11255,38 @@
       <c r="H72" s="6"/>
       <c r="I72" s="6"/>
     </row>
-    <row r="75" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A75" s="29"/>
-      <c r="B75" s="30"/>
-      <c r="C75" s="30"/>
-      <c r="D75" s="30"/>
-      <c r="E75" s="30"/>
-      <c r="F75" s="30"/>
-      <c r="G75" s="30"/>
-      <c r="H75" s="30"/>
-      <c r="I75" s="30"/>
+    <row r="73" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="A73" s="6"/>
+      <c r="B73" s="6"/>
+      <c r="C73" s="6"/>
+      <c r="D73" s="6"/>
+      <c r="E73" s="6"/>
+      <c r="F73" s="6"/>
+      <c r="G73" s="6"/>
+      <c r="H73" s="6"/>
+      <c r="I73" s="6"/>
     </row>
     <row r="76" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A76" s="4"/>
-      <c r="B76" s="7"/>
-      <c r="C76" s="7"/>
-      <c r="D76" s="7"/>
-      <c r="E76" s="7"/>
-      <c r="F76" s="7"/>
-      <c r="G76" s="7"/>
-      <c r="H76" s="7"/>
-      <c r="I76" s="7"/>
+      <c r="A76" s="31"/>
+      <c r="B76" s="32"/>
+      <c r="C76" s="32"/>
+      <c r="D76" s="32"/>
+      <c r="E76" s="32"/>
+      <c r="F76" s="32"/>
+      <c r="G76" s="32"/>
+      <c r="H76" s="32"/>
+      <c r="I76" s="32"/>
     </row>
     <row r="77" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A77" s="4"/>
-      <c r="B77" s="8"/>
-      <c r="C77" s="8"/>
-      <c r="D77" s="8"/>
-      <c r="E77" s="8"/>
-      <c r="F77" s="8"/>
-      <c r="G77" s="8"/>
-      <c r="H77" s="8"/>
-      <c r="I77" s="8"/>
+      <c r="B77" s="7"/>
+      <c r="C77" s="7"/>
+      <c r="D77" s="7"/>
+      <c r="E77" s="7"/>
+      <c r="F77" s="7"/>
+      <c r="G77" s="7"/>
+      <c r="H77" s="7"/>
+      <c r="I77" s="7"/>
     </row>
     <row r="78" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A78" s="4"/>
@@ -11214,26 +11300,26 @@
       <c r="I78" s="8"/>
     </row>
     <row r="79" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A79" s="32"/>
-      <c r="B79" s="30"/>
-      <c r="C79" s="30"/>
-      <c r="D79" s="30"/>
-      <c r="E79" s="30"/>
-      <c r="F79" s="30"/>
-      <c r="G79" s="30"/>
-      <c r="H79" s="30"/>
-      <c r="I79" s="30"/>
+      <c r="A79" s="4"/>
+      <c r="B79" s="8"/>
+      <c r="C79" s="8"/>
+      <c r="D79" s="8"/>
+      <c r="E79" s="8"/>
+      <c r="F79" s="8"/>
+      <c r="G79" s="8"/>
+      <c r="H79" s="8"/>
+      <c r="I79" s="8"/>
     </row>
     <row r="80" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A80" s="4"/>
-      <c r="B80" s="4"/>
-      <c r="C80" s="4"/>
-      <c r="D80" s="4"/>
-      <c r="E80" s="4"/>
-      <c r="F80" s="4"/>
-      <c r="G80" s="4"/>
-      <c r="H80" s="4"/>
-      <c r="I80" s="4"/>
+      <c r="A80" s="34"/>
+      <c r="B80" s="32"/>
+      <c r="C80" s="32"/>
+      <c r="D80" s="32"/>
+      <c r="E80" s="32"/>
+      <c r="F80" s="32"/>
+      <c r="G80" s="32"/>
+      <c r="H80" s="32"/>
+      <c r="I80" s="32"/>
     </row>
     <row r="81" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A81" s="4"/>
@@ -11246,38 +11332,38 @@
       <c r="H81" s="4"/>
       <c r="I81" s="4"/>
     </row>
-    <row r="83" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A83" s="4"/>
-      <c r="B83" s="4"/>
+    <row r="82" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="A82" s="4"/>
+      <c r="B82" s="4"/>
+      <c r="C82" s="4"/>
+      <c r="D82" s="4"/>
+      <c r="E82" s="4"/>
+      <c r="F82" s="4"/>
+      <c r="G82" s="4"/>
+      <c r="H82" s="4"/>
+      <c r="I82" s="4"/>
     </row>
     <row r="84" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A84" s="4"/>
+      <c r="B84" s="4"/>
     </row>
     <row r="85" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A85" s="4"/>
-      <c r="B85" s="6"/>
-    </row>
-    <row r="87" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A87" s="29"/>
-      <c r="B87" s="30"/>
-      <c r="C87" s="30"/>
-      <c r="D87" s="30"/>
-      <c r="E87" s="30"/>
-      <c r="F87" s="30"/>
-      <c r="G87" s="30"/>
-      <c r="H87" s="30"/>
-      <c r="I87" s="30"/>
+    </row>
+    <row r="86" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="A86" s="4"/>
+      <c r="B86" s="6"/>
     </row>
     <row r="88" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A88" s="4"/>
-      <c r="B88" s="9"/>
-      <c r="C88" s="9"/>
-      <c r="D88" s="9"/>
-      <c r="E88" s="9"/>
-      <c r="F88" s="9"/>
-      <c r="G88" s="9"/>
-      <c r="H88" s="9"/>
-      <c r="I88" s="9"/>
+      <c r="A88" s="31"/>
+      <c r="B88" s="32"/>
+      <c r="C88" s="32"/>
+      <c r="D88" s="32"/>
+      <c r="E88" s="32"/>
+      <c r="F88" s="32"/>
+      <c r="G88" s="32"/>
+      <c r="H88" s="32"/>
+      <c r="I88" s="32"/>
     </row>
     <row r="89" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A89" s="4"/>
@@ -11347,51 +11433,51 @@
     </row>
     <row r="95" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A95" s="4"/>
-      <c r="B95" s="4"/>
-      <c r="C95" s="4"/>
-      <c r="D95" s="4"/>
-      <c r="E95" s="4"/>
-      <c r="F95" s="4"/>
-      <c r="G95" s="4"/>
-      <c r="H95" s="4"/>
-      <c r="I95" s="4"/>
+      <c r="B95" s="9"/>
+      <c r="C95" s="9"/>
+      <c r="D95" s="9"/>
+      <c r="E95" s="9"/>
+      <c r="F95" s="9"/>
+      <c r="G95" s="9"/>
+      <c r="H95" s="9"/>
+      <c r="I95" s="9"/>
     </row>
     <row r="96" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A96" s="4"/>
-      <c r="B96" s="9"/>
+      <c r="B96" s="4"/>
+      <c r="C96" s="4"/>
+      <c r="D96" s="4"/>
+      <c r="E96" s="4"/>
+      <c r="F96" s="4"/>
+      <c r="G96" s="4"/>
+      <c r="H96" s="4"/>
+      <c r="I96" s="4"/>
     </row>
     <row r="97" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A97" s="4"/>
-      <c r="B97" s="4"/>
+      <c r="B97" s="9"/>
     </row>
     <row r="98" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A98" s="4"/>
-      <c r="B98" s="9"/>
-    </row>
-    <row r="100" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A100" s="31"/>
-      <c r="B100" s="30"/>
-      <c r="C100" s="30"/>
-      <c r="D100" s="30"/>
-      <c r="E100" s="30"/>
-      <c r="F100" s="30"/>
-      <c r="G100" s="30"/>
-      <c r="H100" s="30"/>
-      <c r="I100" s="30"/>
+      <c r="B98" s="4"/>
+    </row>
+    <row r="99" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="A99" s="4"/>
+      <c r="B99" s="9"/>
     </row>
     <row r="101" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A101" s="4"/>
-      <c r="B101" s="6"/>
-      <c r="C101" s="6"/>
-      <c r="D101" s="6"/>
-      <c r="E101" s="6"/>
-      <c r="F101" s="6"/>
-      <c r="G101" s="6"/>
-      <c r="H101" s="6"/>
-      <c r="I101" s="6"/>
+      <c r="A101" s="33"/>
+      <c r="B101" s="32"/>
+      <c r="C101" s="32"/>
+      <c r="D101" s="32"/>
+      <c r="E101" s="32"/>
+      <c r="F101" s="32"/>
+      <c r="G101" s="32"/>
+      <c r="H101" s="32"/>
+      <c r="I101" s="32"/>
     </row>
     <row r="102" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A102" s="6"/>
+      <c r="A102" s="4"/>
       <c r="B102" s="6"/>
       <c r="C102" s="6"/>
       <c r="D102" s="6"/>
@@ -11401,17 +11487,28 @@
       <c r="H102" s="6"/>
       <c r="I102" s="6"/>
     </row>
+    <row r="103" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="A103" s="6"/>
+      <c r="B103" s="6"/>
+      <c r="C103" s="6"/>
+      <c r="D103" s="6"/>
+      <c r="E103" s="6"/>
+      <c r="F103" s="6"/>
+      <c r="G103" s="6"/>
+      <c r="H103" s="6"/>
+      <c r="I103" s="6"/>
+    </row>
   </sheetData>
   <mergeCells count="6">
-    <mergeCell ref="A87:I87"/>
-    <mergeCell ref="A100:I100"/>
-    <mergeCell ref="B35:I35"/>
-    <mergeCell ref="A70:I70"/>
-    <mergeCell ref="A75:I75"/>
-    <mergeCell ref="A79:I79"/>
+    <mergeCell ref="A88:I88"/>
+    <mergeCell ref="A101:I101"/>
+    <mergeCell ref="B36:I36"/>
+    <mergeCell ref="A71:I71"/>
+    <mergeCell ref="A76:I76"/>
+    <mergeCell ref="A80:I80"/>
   </mergeCells>
   <dataValidations count="1">
-    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="A88" xr:uid="{2D697F35-6929-4839-AC7F-B0ED5D02B6A8}">
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="A89" xr:uid="{2D697F35-6929-4839-AC7F-B0ED5D02B6A8}">
       <formula1>"Bandeira,Verde,Amarela,Vermelha p1,Vermelha p2"</formula1>
     </dataValidation>
   </dataValidations>
@@ -11439,106 +11536,105 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A1" s="12" t="s">
+      <c r="A1" s="25" t="s">
         <v>8</v>
       </c>
-      <c r="B1" s="21" t="s">
+      <c r="B1" s="26" t="s">
         <v>0</v>
       </c>
-      <c r="C1" s="21" t="s">
+      <c r="C1" s="26" t="s">
         <v>1</v>
       </c>
-      <c r="D1" s="21" t="s">
+      <c r="D1" s="26" t="s">
         <v>2</v>
       </c>
-      <c r="E1" s="21" t="s">
+      <c r="E1" s="26" t="s">
         <v>3</v>
       </c>
-      <c r="F1" s="21" t="s">
+      <c r="F1" s="26" t="s">
         <v>4</v>
       </c>
-      <c r="G1" s="21" t="s">
+      <c r="G1" s="26" t="s">
         <v>5</v>
       </c>
-      <c r="H1" s="21" t="s">
+      <c r="H1" s="26" t="s">
         <v>6</v>
       </c>
-      <c r="I1" s="21" t="s">
+      <c r="I1" s="26" t="s">
         <v>7</v>
       </c>
     </row>
     <row r="2" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A2" s="19">
+      <c r="A2" s="37">
+        <v>0</v>
+      </c>
+      <c r="B2" s="28">
+        <v>6407</v>
+      </c>
+      <c r="C2" s="28">
+        <v>8185</v>
+      </c>
+      <c r="D2" s="28">
+        <v>9265</v>
+      </c>
+      <c r="E2" s="28">
+        <v>10802</v>
+      </c>
+      <c r="F2" s="28">
+        <v>1271</v>
+      </c>
+      <c r="G2" s="28">
+        <v>3691</v>
+      </c>
+      <c r="H2" s="28">
+        <v>369</v>
+      </c>
+      <c r="I2" s="28">
+        <v>3321</v>
+      </c>
+    </row>
+    <row r="3" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="A3" s="35">
         <v>1</v>
       </c>
-      <c r="B2" s="22">
+      <c r="B3" s="36">
         <v>6429</v>
       </c>
-      <c r="C2" s="22">
+      <c r="C3" s="36">
         <v>8198</v>
       </c>
-      <c r="D2" s="22">
+      <c r="D3" s="36">
         <v>9269</v>
       </c>
-      <c r="E2" s="22">
+      <c r="E3" s="36">
         <v>10803</v>
       </c>
-      <c r="F2" s="22">
+      <c r="F3" s="36">
         <v>1271</v>
       </c>
-      <c r="G2" s="22">
+      <c r="G3" s="36">
         <v>3694</v>
       </c>
-      <c r="H2" s="22">
+      <c r="H3" s="36">
         <v>369</v>
       </c>
-      <c r="I2" s="22">
+      <c r="I3" s="36">
         <v>3325</v>
-      </c>
-    </row>
-    <row r="3" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A3" s="19">
-        <f t="shared" ref="A3:A32" si="0">A2+1</f>
-        <v>2</v>
-      </c>
-      <c r="B3" s="22">
-        <v>6461</v>
-      </c>
-      <c r="C3" s="22">
-        <v>8283</v>
-      </c>
-      <c r="D3" s="22">
-        <v>9272</v>
-      </c>
-      <c r="E3" s="22">
-        <v>10804</v>
-      </c>
-      <c r="F3" s="22">
-        <v>1271</v>
-      </c>
-      <c r="G3" s="22">
-        <v>3697</v>
-      </c>
-      <c r="H3" s="22">
-        <v>369</v>
-      </c>
-      <c r="I3" s="22">
-        <v>3328</v>
       </c>
     </row>
     <row r="4" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A4" s="19">
-        <f t="shared" si="0"/>
-        <v>3</v>
+        <f t="shared" ref="A4:A32" si="0">A3+1</f>
+        <v>2</v>
       </c>
       <c r="B4" s="22">
-        <v>6524</v>
+        <v>6461</v>
       </c>
       <c r="C4" s="22">
-        <v>8298</v>
+        <v>8283</v>
       </c>
       <c r="D4" s="22">
-        <v>9275</v>
+        <v>9272</v>
       </c>
       <c r="E4" s="22">
         <v>10804</v>
@@ -11547,145 +11643,145 @@
         <v>1271</v>
       </c>
       <c r="G4" s="22">
-        <v>3702</v>
+        <v>3697</v>
       </c>
       <c r="H4" s="22">
         <v>369</v>
       </c>
       <c r="I4" s="22">
-        <v>3333</v>
+        <v>3328</v>
       </c>
     </row>
     <row r="5" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A5" s="19">
         <f t="shared" si="0"/>
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B5" s="22">
-        <v>6619</v>
+        <v>6524</v>
       </c>
       <c r="C5" s="22">
-        <v>8371</v>
+        <v>8298</v>
       </c>
       <c r="D5" s="22">
-        <v>9279</v>
+        <v>9275</v>
       </c>
       <c r="E5" s="22">
-        <v>10805</v>
+        <v>10804</v>
       </c>
       <c r="F5" s="22">
         <v>1271</v>
       </c>
       <c r="G5" s="22">
-        <v>3707</v>
+        <v>3702</v>
       </c>
       <c r="H5" s="22">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="I5" s="22">
-        <v>3336</v>
+        <v>3333</v>
       </c>
     </row>
     <row r="6" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A6" s="19">
         <f t="shared" si="0"/>
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B6" s="22">
-        <v>6676</v>
+        <v>6619</v>
       </c>
       <c r="C6" s="22">
-        <v>8399</v>
+        <v>8371</v>
       </c>
       <c r="D6" s="22">
-        <v>9281</v>
+        <v>9279</v>
       </c>
       <c r="E6" s="22">
-        <v>10806</v>
+        <v>10805</v>
       </c>
       <c r="F6" s="22">
         <v>1271</v>
       </c>
       <c r="G6" s="22">
-        <v>3711</v>
+        <v>3707</v>
       </c>
       <c r="H6" s="22">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="I6" s="22">
-        <v>3340</v>
+        <v>3336</v>
       </c>
     </row>
     <row r="7" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A7" s="19">
         <f t="shared" si="0"/>
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B7" s="22">
-        <v>6759</v>
+        <v>6676</v>
       </c>
       <c r="C7" s="22">
-        <v>8479</v>
+        <v>8399</v>
       </c>
       <c r="D7" s="22">
-        <v>9287</v>
+        <v>9281</v>
       </c>
       <c r="E7" s="22">
-        <v>10807</v>
+        <v>10806</v>
       </c>
       <c r="F7" s="22">
-        <v>1272</v>
+        <v>1271</v>
       </c>
       <c r="G7" s="22">
-        <v>3712</v>
+        <v>3711</v>
       </c>
       <c r="H7" s="22">
         <v>371</v>
       </c>
       <c r="I7" s="22">
-        <v>3343</v>
+        <v>3340</v>
       </c>
     </row>
     <row r="8" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A8" s="19">
         <f t="shared" si="0"/>
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B8" s="22">
-        <v>6793</v>
+        <v>6759</v>
       </c>
       <c r="C8" s="22">
-        <v>8509</v>
+        <v>8479</v>
       </c>
       <c r="D8" s="22">
-        <v>9291</v>
+        <v>9287</v>
       </c>
       <c r="E8" s="22">
-        <v>10808</v>
+        <v>10807</v>
       </c>
       <c r="F8" s="22">
-        <v>1273</v>
+        <v>1272</v>
       </c>
       <c r="G8" s="22">
-        <v>3719</v>
+        <v>3712</v>
       </c>
       <c r="H8" s="22">
-        <v>372</v>
+        <v>371</v>
       </c>
       <c r="I8" s="22">
-        <v>3347</v>
+        <v>3343</v>
       </c>
     </row>
     <row r="9" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A9" s="19">
         <f t="shared" si="0"/>
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B9" s="22">
-        <v>6840</v>
+        <v>6793</v>
       </c>
       <c r="C9" s="22">
-        <v>8572</v>
+        <v>8509</v>
       </c>
       <c r="D9" s="22">
         <v>9291</v>
@@ -11697,224 +11793,240 @@
         <v>1273</v>
       </c>
       <c r="G9" s="22">
-        <v>3723</v>
+        <v>3719</v>
       </c>
       <c r="H9" s="22">
         <v>372</v>
       </c>
       <c r="I9" s="22">
-        <v>3351</v>
+        <v>3347</v>
       </c>
     </row>
     <row r="10" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A10" s="19">
         <f t="shared" si="0"/>
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B10" s="22">
-        <v>6845</v>
+        <v>6840</v>
       </c>
       <c r="C10" s="22">
-        <v>8607</v>
+        <v>8572</v>
       </c>
       <c r="D10" s="22">
-        <v>9299</v>
+        <v>9291</v>
       </c>
       <c r="E10" s="22">
-        <v>10809</v>
+        <v>10808</v>
       </c>
       <c r="F10" s="22">
         <v>1273</v>
       </c>
       <c r="G10" s="22">
-        <v>3726</v>
+        <v>3723</v>
       </c>
       <c r="H10" s="22">
-        <v>373</v>
+        <v>372</v>
       </c>
       <c r="I10" s="22">
-        <v>3349</v>
+        <v>3351</v>
       </c>
     </row>
     <row r="11" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A11" s="19">
         <f t="shared" si="0"/>
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B11" s="22">
-        <v>6902</v>
+        <v>6845</v>
       </c>
       <c r="C11" s="22">
-        <v>8690</v>
+        <v>8607</v>
       </c>
       <c r="D11" s="22">
-        <v>9302</v>
+        <v>9299</v>
       </c>
       <c r="E11" s="22">
-        <v>10810</v>
+        <v>10809</v>
       </c>
       <c r="F11" s="22">
         <v>1273</v>
       </c>
       <c r="G11" s="22">
-        <v>3733</v>
+        <v>3726</v>
       </c>
       <c r="H11" s="22">
         <v>373</v>
       </c>
       <c r="I11" s="22">
-        <v>3359</v>
+        <v>3349</v>
       </c>
     </row>
     <row r="12" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A12" s="19">
         <f t="shared" si="0"/>
-        <v>11</v>
-      </c>
-      <c r="B12" s="33">
-        <v>6917</v>
-      </c>
-      <c r="C12" s="34">
-        <v>8710</v>
-      </c>
-      <c r="D12" s="33">
-        <v>9309</v>
-      </c>
-      <c r="E12" s="33">
-        <v>10811</v>
-      </c>
-      <c r="F12" s="33">
-        <v>1274</v>
-      </c>
-      <c r="G12" s="33">
-        <v>3734</v>
-      </c>
-      <c r="H12" s="33">
+        <v>10</v>
+      </c>
+      <c r="B12" s="22">
+        <v>6902</v>
+      </c>
+      <c r="C12" s="22">
+        <v>8690</v>
+      </c>
+      <c r="D12" s="22">
+        <v>9302</v>
+      </c>
+      <c r="E12" s="22">
+        <v>10810</v>
+      </c>
+      <c r="F12" s="22">
+        <v>1273</v>
+      </c>
+      <c r="G12" s="22">
+        <v>3733</v>
+      </c>
+      <c r="H12" s="22">
         <v>373</v>
       </c>
-      <c r="I12" s="33">
-        <v>3360</v>
+      <c r="I12" s="22">
+        <v>3359</v>
       </c>
     </row>
     <row r="13" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A13" s="19">
         <f t="shared" si="0"/>
-        <v>12</v>
-      </c>
-      <c r="B13" s="22">
-        <v>7029</v>
-      </c>
-      <c r="C13" s="22">
-        <v>8819</v>
-      </c>
-      <c r="D13" s="22">
-        <v>9312</v>
-      </c>
-      <c r="E13" s="22">
+        <v>11</v>
+      </c>
+      <c r="B13" s="29">
+        <v>6917</v>
+      </c>
+      <c r="C13" s="30">
+        <v>8710</v>
+      </c>
+      <c r="D13" s="29">
+        <v>9309</v>
+      </c>
+      <c r="E13" s="29">
         <v>10811</v>
       </c>
-      <c r="F13" s="22">
+      <c r="F13" s="29">
         <v>1274</v>
       </c>
-      <c r="G13" s="22">
-        <v>3738</v>
-      </c>
-      <c r="H13" s="22">
-        <v>374</v>
-      </c>
-      <c r="I13" s="22">
-        <v>3364</v>
+      <c r="G13" s="29">
+        <v>3734</v>
+      </c>
+      <c r="H13" s="29">
+        <v>373</v>
+      </c>
+      <c r="I13" s="29">
+        <v>3360</v>
       </c>
     </row>
     <row r="14" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A14" s="19">
         <f t="shared" si="0"/>
-        <v>13</v>
-      </c>
-      <c r="B14" s="33"/>
-      <c r="C14" s="33"/>
-      <c r="D14" s="33"/>
-      <c r="E14" s="33"/>
-      <c r="F14" s="33"/>
-      <c r="G14" s="33"/>
-      <c r="H14" s="33"/>
-      <c r="I14" s="33"/>
+        <v>12</v>
+      </c>
+      <c r="B14" s="22">
+        <v>7029</v>
+      </c>
+      <c r="C14" s="22">
+        <v>8819</v>
+      </c>
+      <c r="D14" s="22">
+        <v>9312</v>
+      </c>
+      <c r="E14" s="22">
+        <v>10811</v>
+      </c>
+      <c r="F14" s="22">
+        <v>1274</v>
+      </c>
+      <c r="G14" s="22">
+        <v>3738</v>
+      </c>
+      <c r="H14" s="22">
+        <v>374</v>
+      </c>
+      <c r="I14" s="22">
+        <v>3364</v>
+      </c>
     </row>
     <row r="15" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A15" s="19">
         <f t="shared" si="0"/>
-        <v>14</v>
-      </c>
-      <c r="B15" s="33"/>
-      <c r="C15" s="33"/>
-      <c r="D15" s="33"/>
-      <c r="E15" s="33"/>
-      <c r="F15" s="33"/>
-      <c r="G15" s="33"/>
-      <c r="H15" s="33"/>
-      <c r="I15" s="33"/>
+        <v>13</v>
+      </c>
+      <c r="B15" s="29"/>
+      <c r="C15" s="29"/>
+      <c r="D15" s="29"/>
+      <c r="E15" s="29"/>
+      <c r="F15" s="29"/>
+      <c r="G15" s="29"/>
+      <c r="H15" s="29"/>
+      <c r="I15" s="29"/>
     </row>
     <row r="16" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A16" s="19">
         <f t="shared" si="0"/>
-        <v>15</v>
-      </c>
-      <c r="B16" s="33"/>
-      <c r="C16" s="33"/>
-      <c r="D16" s="33"/>
-      <c r="E16" s="33"/>
-      <c r="F16" s="33"/>
-      <c r="G16" s="33"/>
-      <c r="H16" s="33"/>
-      <c r="I16" s="33"/>
+        <v>14</v>
+      </c>
+      <c r="B16" s="29"/>
+      <c r="C16" s="29"/>
+      <c r="D16" s="29"/>
+      <c r="E16" s="29"/>
+      <c r="F16" s="29"/>
+      <c r="G16" s="29"/>
+      <c r="H16" s="29"/>
+      <c r="I16" s="29"/>
     </row>
     <row r="17" spans="1:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A17" s="19">
         <f t="shared" si="0"/>
+        <v>15</v>
+      </c>
+      <c r="B17" s="29"/>
+      <c r="C17" s="29"/>
+      <c r="D17" s="29"/>
+      <c r="E17" s="29"/>
+      <c r="F17" s="29"/>
+      <c r="G17" s="29"/>
+      <c r="H17" s="29"/>
+      <c r="I17" s="29"/>
+    </row>
+    <row r="18" spans="1:10" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="A18" s="19">
+        <f t="shared" si="0"/>
         <v>16</v>
       </c>
-      <c r="B17" s="33"/>
-      <c r="C17" s="33"/>
-      <c r="D17" s="33"/>
-      <c r="E17" s="33"/>
-      <c r="F17" s="33"/>
-      <c r="G17" s="33"/>
-      <c r="H17" s="33"/>
-      <c r="I17" s="33"/>
-    </row>
-    <row r="18" spans="1:10" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A18" s="1">
-        <f t="shared" si="0"/>
-        <v>17</v>
-      </c>
-      <c r="B18" s="24"/>
-      <c r="C18" s="24"/>
-      <c r="D18" s="24"/>
-      <c r="E18" s="24"/>
-      <c r="F18" s="24"/>
-      <c r="G18" s="24"/>
-      <c r="H18" s="24"/>
-      <c r="I18" s="24"/>
-      <c r="J18" s="3"/>
+      <c r="B18" s="29"/>
+      <c r="C18" s="29"/>
+      <c r="D18" s="29"/>
+      <c r="E18" s="29"/>
+      <c r="F18" s="29"/>
+      <c r="G18" s="29"/>
+      <c r="H18" s="29"/>
+      <c r="I18" s="29"/>
     </row>
     <row r="19" spans="1:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A19" s="1">
         <f t="shared" si="0"/>
-        <v>18</v>
-      </c>
-      <c r="B19" s="2"/>
-      <c r="C19" s="2"/>
-      <c r="D19" s="2"/>
-      <c r="E19" s="2"/>
-      <c r="F19" s="2"/>
-      <c r="G19" s="2"/>
-      <c r="H19" s="2"/>
-      <c r="I19" s="2"/>
+        <v>17</v>
+      </c>
+      <c r="B19" s="24"/>
+      <c r="C19" s="24"/>
+      <c r="D19" s="24"/>
+      <c r="E19" s="24"/>
+      <c r="F19" s="24"/>
+      <c r="G19" s="24"/>
+      <c r="H19" s="24"/>
+      <c r="I19" s="24"/>
+      <c r="J19" s="3"/>
     </row>
     <row r="20" spans="1:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A20" s="1">
         <f t="shared" si="0"/>
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B20" s="2"/>
       <c r="C20" s="2"/>
@@ -11928,7 +12040,7 @@
     <row r="21" spans="1:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A21" s="1">
         <f t="shared" si="0"/>
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B21" s="2"/>
       <c r="C21" s="2"/>
@@ -11942,7 +12054,7 @@
     <row r="22" spans="1:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A22" s="1">
         <f t="shared" si="0"/>
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="B22" s="2"/>
       <c r="C22" s="2"/>
@@ -11956,7 +12068,7 @@
     <row r="23" spans="1:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A23" s="1">
         <f t="shared" si="0"/>
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B23" s="2"/>
       <c r="C23" s="2"/>
@@ -11970,7 +12082,7 @@
     <row r="24" spans="1:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A24" s="1">
         <f t="shared" si="0"/>
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B24" s="2"/>
       <c r="C24" s="2"/>
@@ -11982,128 +12094,128 @@
       <c r="I24" s="2"/>
     </row>
     <row r="25" spans="1:10" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A25" s="10">
+      <c r="A25" s="1">
+        <f t="shared" si="0"/>
+        <v>23</v>
+      </c>
+      <c r="B25" s="2"/>
+      <c r="C25" s="2"/>
+      <c r="D25" s="2"/>
+      <c r="E25" s="2"/>
+      <c r="F25" s="2"/>
+      <c r="G25" s="2"/>
+      <c r="H25" s="2"/>
+      <c r="I25" s="2"/>
+    </row>
+    <row r="26" spans="1:10" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="A26" s="10">
         <f t="shared" si="0"/>
         <v>24</v>
       </c>
-      <c r="B25" s="11"/>
-      <c r="C25" s="11"/>
-      <c r="D25" s="11"/>
-      <c r="E25" s="11"/>
-      <c r="F25" s="11"/>
-      <c r="G25" s="11"/>
-      <c r="H25" s="11"/>
-      <c r="I25" s="11"/>
-    </row>
-    <row r="26" spans="1:10" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A26" s="27">
-        <f t="shared" si="0"/>
-        <v>25</v>
-      </c>
-      <c r="B26" s="33"/>
-      <c r="C26" s="33"/>
-      <c r="D26" s="33"/>
-      <c r="E26" s="33"/>
-      <c r="F26" s="33"/>
-      <c r="G26" s="33"/>
-      <c r="H26" s="33"/>
-      <c r="I26" s="33"/>
+      <c r="B26" s="11"/>
+      <c r="C26" s="11"/>
+      <c r="D26" s="11"/>
+      <c r="E26" s="11"/>
+      <c r="F26" s="11"/>
+      <c r="G26" s="11"/>
+      <c r="H26" s="11"/>
+      <c r="I26" s="11"/>
     </row>
     <row r="27" spans="1:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A27" s="27">
         <f t="shared" si="0"/>
-        <v>26</v>
-      </c>
-      <c r="B27" s="33"/>
-      <c r="C27" s="33"/>
-      <c r="D27" s="33"/>
-      <c r="E27" s="33"/>
-      <c r="F27" s="33"/>
-      <c r="G27" s="33"/>
-      <c r="H27" s="33"/>
-      <c r="I27" s="33"/>
+        <v>25</v>
+      </c>
+      <c r="B27" s="29"/>
+      <c r="C27" s="29"/>
+      <c r="D27" s="29"/>
+      <c r="E27" s="29"/>
+      <c r="F27" s="29"/>
+      <c r="G27" s="29"/>
+      <c r="H27" s="29"/>
+      <c r="I27" s="29"/>
     </row>
     <row r="28" spans="1:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A28" s="27">
         <f t="shared" si="0"/>
-        <v>27</v>
-      </c>
-      <c r="B28" s="33"/>
-      <c r="C28" s="33"/>
-      <c r="D28" s="33"/>
-      <c r="E28" s="33"/>
-      <c r="F28" s="33"/>
-      <c r="G28" s="33"/>
-      <c r="H28" s="33"/>
-      <c r="I28" s="33"/>
+        <v>26</v>
+      </c>
+      <c r="B28" s="29"/>
+      <c r="C28" s="29"/>
+      <c r="D28" s="29"/>
+      <c r="E28" s="29"/>
+      <c r="F28" s="29"/>
+      <c r="G28" s="29"/>
+      <c r="H28" s="29"/>
+      <c r="I28" s="29"/>
     </row>
     <row r="29" spans="1:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A29" s="27">
         <f t="shared" si="0"/>
-        <v>28</v>
-      </c>
-      <c r="B29" s="33"/>
-      <c r="C29" s="33"/>
-      <c r="D29" s="33"/>
-      <c r="E29" s="33"/>
-      <c r="F29" s="33"/>
-      <c r="G29" s="33"/>
-      <c r="H29" s="33"/>
-      <c r="I29" s="33"/>
+        <v>27</v>
+      </c>
+      <c r="B29" s="29"/>
+      <c r="C29" s="29"/>
+      <c r="D29" s="29"/>
+      <c r="E29" s="29"/>
+      <c r="F29" s="29"/>
+      <c r="G29" s="29"/>
+      <c r="H29" s="29"/>
+      <c r="I29" s="29"/>
     </row>
     <row r="30" spans="1:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A30" s="27">
         <f t="shared" si="0"/>
-        <v>29</v>
-      </c>
-      <c r="B30" s="33"/>
-      <c r="C30" s="33"/>
-      <c r="D30" s="33"/>
-      <c r="E30" s="33"/>
-      <c r="F30" s="33"/>
-      <c r="G30" s="33"/>
-      <c r="H30" s="33"/>
-      <c r="I30" s="33"/>
+        <v>28</v>
+      </c>
+      <c r="B30" s="29"/>
+      <c r="C30" s="29"/>
+      <c r="D30" s="29"/>
+      <c r="E30" s="29"/>
+      <c r="F30" s="29"/>
+      <c r="G30" s="29"/>
+      <c r="H30" s="29"/>
+      <c r="I30" s="29"/>
     </row>
     <row r="31" spans="1:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A31" s="27">
         <f t="shared" si="0"/>
-        <v>30</v>
-      </c>
-      <c r="B31" s="33"/>
-      <c r="C31" s="33"/>
-      <c r="D31" s="33"/>
-      <c r="E31" s="33"/>
-      <c r="F31" s="33"/>
-      <c r="G31" s="33"/>
-      <c r="H31" s="33"/>
-      <c r="I31" s="33"/>
+        <v>29</v>
+      </c>
+      <c r="B31" s="29"/>
+      <c r="C31" s="29"/>
+      <c r="D31" s="29"/>
+      <c r="E31" s="29"/>
+      <c r="F31" s="29"/>
+      <c r="G31" s="29"/>
+      <c r="H31" s="29"/>
+      <c r="I31" s="29"/>
     </row>
     <row r="32" spans="1:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A32" s="27">
         <f t="shared" si="0"/>
-        <v>31</v>
-      </c>
-      <c r="B32" s="33"/>
-      <c r="C32" s="33"/>
-      <c r="D32" s="33"/>
-      <c r="E32" s="33"/>
-      <c r="F32" s="33"/>
-      <c r="G32" s="33"/>
-      <c r="H32" s="33"/>
-      <c r="I32" s="33"/>
+        <v>30</v>
+      </c>
+      <c r="B32" s="29"/>
+      <c r="C32" s="29"/>
+      <c r="D32" s="29"/>
+      <c r="E32" s="29"/>
+      <c r="F32" s="29"/>
+      <c r="G32" s="29"/>
+      <c r="H32" s="29"/>
+      <c r="I32" s="29"/>
     </row>
     <row r="33" spans="1:9" ht="12.75" x14ac:dyDescent="0.2"/>
     <row r="35" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A35" s="4"/>
-      <c r="B35" s="31"/>
-      <c r="C35" s="30"/>
-      <c r="D35" s="30"/>
-      <c r="E35" s="30"/>
-      <c r="F35" s="30"/>
-      <c r="G35" s="30"/>
-      <c r="H35" s="30"/>
-      <c r="I35" s="30"/>
+      <c r="B35" s="33"/>
+      <c r="C35" s="32"/>
+      <c r="D35" s="32"/>
+      <c r="E35" s="32"/>
+      <c r="F35" s="32"/>
+      <c r="G35" s="32"/>
+      <c r="H35" s="32"/>
+      <c r="I35" s="32"/>
     </row>
     <row r="36" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A36" s="4"/>
@@ -12481,15 +12593,15 @@
       <c r="I69" s="4"/>
     </row>
     <row r="70" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A70" s="31"/>
-      <c r="B70" s="30"/>
-      <c r="C70" s="30"/>
-      <c r="D70" s="30"/>
-      <c r="E70" s="30"/>
-      <c r="F70" s="30"/>
-      <c r="G70" s="30"/>
-      <c r="H70" s="30"/>
-      <c r="I70" s="30"/>
+      <c r="A70" s="33"/>
+      <c r="B70" s="32"/>
+      <c r="C70" s="32"/>
+      <c r="D70" s="32"/>
+      <c r="E70" s="32"/>
+      <c r="F70" s="32"/>
+      <c r="G70" s="32"/>
+      <c r="H70" s="32"/>
+      <c r="I70" s="32"/>
     </row>
     <row r="71" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A71" s="4"/>
@@ -12514,15 +12626,15 @@
       <c r="I72" s="6"/>
     </row>
     <row r="75" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A75" s="29"/>
-      <c r="B75" s="30"/>
-      <c r="C75" s="30"/>
-      <c r="D75" s="30"/>
-      <c r="E75" s="30"/>
-      <c r="F75" s="30"/>
-      <c r="G75" s="30"/>
-      <c r="H75" s="30"/>
-      <c r="I75" s="30"/>
+      <c r="A75" s="31"/>
+      <c r="B75" s="32"/>
+      <c r="C75" s="32"/>
+      <c r="D75" s="32"/>
+      <c r="E75" s="32"/>
+      <c r="F75" s="32"/>
+      <c r="G75" s="32"/>
+      <c r="H75" s="32"/>
+      <c r="I75" s="32"/>
     </row>
     <row r="76" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A76" s="4"/>
@@ -12558,15 +12670,15 @@
       <c r="I78" s="8"/>
     </row>
     <row r="79" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A79" s="32"/>
-      <c r="B79" s="30"/>
-      <c r="C79" s="30"/>
-      <c r="D79" s="30"/>
-      <c r="E79" s="30"/>
-      <c r="F79" s="30"/>
-      <c r="G79" s="30"/>
-      <c r="H79" s="30"/>
-      <c r="I79" s="30"/>
+      <c r="A79" s="34"/>
+      <c r="B79" s="32"/>
+      <c r="C79" s="32"/>
+      <c r="D79" s="32"/>
+      <c r="E79" s="32"/>
+      <c r="F79" s="32"/>
+      <c r="G79" s="32"/>
+      <c r="H79" s="32"/>
+      <c r="I79" s="32"/>
     </row>
     <row r="80" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A80" s="4"/>
@@ -12602,15 +12714,15 @@
       <c r="B85" s="6"/>
     </row>
     <row r="87" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A87" s="29"/>
-      <c r="B87" s="30"/>
-      <c r="C87" s="30"/>
-      <c r="D87" s="30"/>
-      <c r="E87" s="30"/>
-      <c r="F87" s="30"/>
-      <c r="G87" s="30"/>
-      <c r="H87" s="30"/>
-      <c r="I87" s="30"/>
+      <c r="A87" s="31"/>
+      <c r="B87" s="32"/>
+      <c r="C87" s="32"/>
+      <c r="D87" s="32"/>
+      <c r="E87" s="32"/>
+      <c r="F87" s="32"/>
+      <c r="G87" s="32"/>
+      <c r="H87" s="32"/>
+      <c r="I87" s="32"/>
     </row>
     <row r="88" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A88" s="4"/>
@@ -12713,15 +12825,15 @@
       <c r="B98" s="9"/>
     </row>
     <row r="100" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A100" s="31"/>
-      <c r="B100" s="30"/>
-      <c r="C100" s="30"/>
-      <c r="D100" s="30"/>
-      <c r="E100" s="30"/>
-      <c r="F100" s="30"/>
-      <c r="G100" s="30"/>
-      <c r="H100" s="30"/>
-      <c r="I100" s="30"/>
+      <c r="A100" s="33"/>
+      <c r="B100" s="32"/>
+      <c r="C100" s="32"/>
+      <c r="D100" s="32"/>
+      <c r="E100" s="32"/>
+      <c r="F100" s="32"/>
+      <c r="G100" s="32"/>
+      <c r="H100" s="32"/>
+      <c r="I100" s="32"/>
     </row>
     <row r="101" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A101" s="4"/>
@@ -12769,7 +12881,7 @@
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
-  <dimension ref="A1:K102"/>
+  <dimension ref="A1:K103"/>
   <sheetFormatPr defaultColWidth="12.5703125" defaultRowHeight="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="19.42578125" customWidth="1"/>
@@ -12813,91 +12925,74 @@
       </c>
     </row>
     <row r="2" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A2" s="27">
-        <v>1</v>
-      </c>
-      <c r="B2" s="22">
-        <v>4909</v>
-      </c>
-      <c r="C2" s="22">
-        <v>6810</v>
-      </c>
-      <c r="D2" s="22">
-        <v>9145</v>
-      </c>
-      <c r="E2" s="22">
-        <v>10783</v>
-      </c>
-      <c r="F2" s="22">
-        <v>1266</v>
-      </c>
-      <c r="G2" s="22">
-        <v>3565</v>
-      </c>
-      <c r="H2" s="22">
-        <v>354</v>
-      </c>
-      <c r="I2" s="22">
-        <v>3210</v>
-      </c>
+      <c r="A2" s="39">
+        <v>0</v>
+      </c>
+      <c r="B2" s="38"/>
+      <c r="C2" s="38"/>
+      <c r="D2" s="38"/>
+      <c r="E2" s="38"/>
+      <c r="F2" s="38"/>
+      <c r="G2" s="38"/>
+      <c r="H2" s="38"/>
+      <c r="I2" s="38"/>
     </row>
     <row r="3" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A3" s="27">
-        <f t="shared" ref="A3:A32" si="0">A2+1</f>
-        <v>2</v>
-      </c>
-      <c r="B3" s="23"/>
-      <c r="C3" s="23"/>
-      <c r="D3" s="23"/>
-      <c r="E3" s="23"/>
-      <c r="F3" s="23"/>
-      <c r="G3" s="23"/>
-      <c r="H3" s="23"/>
-      <c r="I3" s="23"/>
+        <v>1</v>
+      </c>
+      <c r="B3" s="22">
+        <v>4909</v>
+      </c>
+      <c r="C3" s="22">
+        <v>6810</v>
+      </c>
+      <c r="D3" s="22">
+        <v>9145</v>
+      </c>
+      <c r="E3" s="22">
+        <v>10783</v>
+      </c>
+      <c r="F3" s="22">
+        <v>1266</v>
+      </c>
+      <c r="G3" s="22">
+        <v>3565</v>
+      </c>
+      <c r="H3" s="22">
+        <v>354</v>
+      </c>
+      <c r="I3" s="22">
+        <v>3210</v>
+      </c>
     </row>
     <row r="4" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A4" s="27">
-        <f t="shared" si="0"/>
-        <v>3</v>
-      </c>
-      <c r="B4" s="22">
-        <v>5009</v>
-      </c>
-      <c r="C4" s="22">
-        <v>6932</v>
-      </c>
-      <c r="D4" s="22">
-        <v>9157</v>
-      </c>
-      <c r="E4" s="22">
-        <v>10784</v>
-      </c>
-      <c r="F4" s="22">
-        <v>1267</v>
-      </c>
-      <c r="G4" s="22">
-        <v>3574</v>
-      </c>
-      <c r="H4" s="22">
-        <v>355</v>
-      </c>
-      <c r="I4" s="22">
-        <v>3218</v>
-      </c>
+        <f t="shared" ref="A4:A33" si="0">A3+1</f>
+        <v>2</v>
+      </c>
+      <c r="B4" s="23"/>
+      <c r="C4" s="23"/>
+      <c r="D4" s="23"/>
+      <c r="E4" s="23"/>
+      <c r="F4" s="23"/>
+      <c r="G4" s="23"/>
+      <c r="H4" s="23"/>
+      <c r="I4" s="23"/>
     </row>
     <row r="5" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A5" s="27">
         <f t="shared" si="0"/>
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B5" s="22">
-        <v>5025</v>
+        <v>5009</v>
       </c>
       <c r="C5" s="22">
         <v>6932</v>
       </c>
       <c r="D5" s="22">
-        <v>9158</v>
+        <v>9157</v>
       </c>
       <c r="E5" s="22">
         <v>10784</v>
@@ -12906,28 +13001,28 @@
         <v>1267</v>
       </c>
       <c r="G5" s="22">
-        <v>3578</v>
+        <v>3574</v>
       </c>
       <c r="H5" s="22">
         <v>355</v>
       </c>
       <c r="I5" s="22">
-        <v>3223</v>
+        <v>3218</v>
       </c>
     </row>
     <row r="6" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A6" s="27">
         <f t="shared" si="0"/>
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B6" s="22">
-        <v>5069</v>
+        <v>5025</v>
       </c>
       <c r="C6" s="22">
-        <v>6997</v>
+        <v>6932</v>
       </c>
       <c r="D6" s="22">
-        <v>9168</v>
+        <v>9158</v>
       </c>
       <c r="E6" s="22">
         <v>10784</v>
@@ -12936,93 +13031,109 @@
         <v>1267</v>
       </c>
       <c r="G6" s="22">
-        <v>3583</v>
+        <v>3578</v>
       </c>
       <c r="H6" s="22">
         <v>355</v>
       </c>
       <c r="I6" s="22">
-        <v>3227</v>
+        <v>3223</v>
       </c>
     </row>
     <row r="7" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A7" s="27">
         <f t="shared" si="0"/>
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B7" s="22">
-        <v>5127</v>
+        <v>5069</v>
       </c>
       <c r="C7" s="22">
-        <v>7107</v>
+        <v>6997</v>
       </c>
       <c r="D7" s="22">
-        <v>9172</v>
+        <v>9168</v>
       </c>
       <c r="E7" s="22">
-        <v>10785</v>
+        <v>10784</v>
       </c>
       <c r="F7" s="22">
         <v>1267</v>
       </c>
       <c r="G7" s="22">
-        <v>3584</v>
+        <v>3583</v>
       </c>
       <c r="H7" s="22">
         <v>355</v>
       </c>
       <c r="I7" s="22">
-        <v>3228</v>
+        <v>3227</v>
       </c>
     </row>
     <row r="8" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A8" s="27">
         <f t="shared" si="0"/>
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B8" s="22">
-        <v>5130</v>
+        <v>5127</v>
       </c>
       <c r="C8" s="22">
-        <v>7110</v>
+        <v>7107</v>
       </c>
       <c r="D8" s="22">
-        <v>9176</v>
+        <v>9172</v>
       </c>
       <c r="E8" s="22">
-        <v>10787</v>
+        <v>10785</v>
       </c>
       <c r="F8" s="22">
-        <v>1268</v>
+        <v>1267</v>
       </c>
       <c r="G8" s="22">
-        <v>3590</v>
+        <v>3584</v>
       </c>
       <c r="H8" s="22">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="I8" s="22">
-        <v>3233</v>
+        <v>3228</v>
       </c>
     </row>
     <row r="9" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A9" s="27">
         <f t="shared" si="0"/>
-        <v>8</v>
-      </c>
-      <c r="B9" s="23"/>
-      <c r="C9" s="23"/>
-      <c r="D9" s="23"/>
-      <c r="E9" s="23"/>
-      <c r="F9" s="23"/>
-      <c r="G9" s="23"/>
-      <c r="H9" s="23"/>
-      <c r="I9" s="23"/>
+        <v>7</v>
+      </c>
+      <c r="B9" s="22">
+        <v>5130</v>
+      </c>
+      <c r="C9" s="22">
+        <v>7110</v>
+      </c>
+      <c r="D9" s="22">
+        <v>9176</v>
+      </c>
+      <c r="E9" s="22">
+        <v>10787</v>
+      </c>
+      <c r="F9" s="22">
+        <v>1268</v>
+      </c>
+      <c r="G9" s="22">
+        <v>3590</v>
+      </c>
+      <c r="H9" s="22">
+        <v>356</v>
+      </c>
+      <c r="I9" s="22">
+        <v>3233</v>
+      </c>
     </row>
     <row r="10" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A10" s="27">
         <f t="shared" si="0"/>
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B10" s="23"/>
       <c r="C10" s="23"/>
@@ -13036,106 +13147,90 @@
     <row r="11" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A11" s="27">
         <f t="shared" si="0"/>
-        <v>10</v>
-      </c>
-      <c r="B11" s="22">
-        <v>5416</v>
-      </c>
-      <c r="C11" s="22">
-        <v>7409</v>
-      </c>
-      <c r="D11" s="22">
-        <v>9192</v>
-      </c>
-      <c r="E11" s="22">
-        <v>10787</v>
-      </c>
-      <c r="F11" s="22">
-        <v>1269</v>
-      </c>
-      <c r="G11" s="22">
-        <v>3604</v>
-      </c>
-      <c r="H11" s="22">
-        <v>358</v>
-      </c>
-      <c r="I11" s="22">
-        <v>3245</v>
-      </c>
+        <v>9</v>
+      </c>
+      <c r="B11" s="23"/>
+      <c r="C11" s="23"/>
+      <c r="D11" s="23"/>
+      <c r="E11" s="23"/>
+      <c r="F11" s="23"/>
+      <c r="G11" s="23"/>
+      <c r="H11" s="23"/>
+      <c r="I11" s="23"/>
     </row>
     <row r="12" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A12" s="27">
         <f t="shared" si="0"/>
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B12" s="22">
-        <v>5429</v>
+        <v>5416</v>
       </c>
       <c r="C12" s="22">
-        <v>7435</v>
+        <v>7409</v>
       </c>
       <c r="D12" s="22">
-        <v>9195</v>
+        <v>9192</v>
       </c>
       <c r="E12" s="22">
-        <v>10788</v>
+        <v>10787</v>
       </c>
       <c r="F12" s="22">
         <v>1269</v>
       </c>
       <c r="G12" s="22">
-        <v>3609</v>
+        <v>3604</v>
       </c>
       <c r="H12" s="22">
         <v>358</v>
       </c>
       <c r="I12" s="22">
-        <v>3250</v>
+        <v>3245</v>
       </c>
     </row>
     <row r="13" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A13" s="27">
         <f t="shared" si="0"/>
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B13" s="22">
-        <v>5458</v>
+        <v>5429</v>
       </c>
       <c r="C13" s="22">
-        <v>7553</v>
+        <v>7435</v>
       </c>
       <c r="D13" s="22">
-        <v>9200</v>
+        <v>9195</v>
       </c>
       <c r="E13" s="22">
-        <v>10789</v>
+        <v>10788</v>
       </c>
       <c r="F13" s="22">
         <v>1269</v>
       </c>
       <c r="G13" s="22">
-        <v>3614</v>
+        <v>3609</v>
       </c>
       <c r="H13" s="22">
         <v>358</v>
       </c>
       <c r="I13" s="22">
-        <v>3255</v>
+        <v>3250</v>
       </c>
     </row>
     <row r="14" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A14" s="27">
         <f t="shared" si="0"/>
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B14" s="22">
-        <v>5553</v>
+        <v>5458</v>
       </c>
       <c r="C14" s="22">
-        <v>7571</v>
+        <v>7553</v>
       </c>
       <c r="D14" s="22">
-        <v>9201</v>
+        <v>9200</v>
       </c>
       <c r="E14" s="22">
         <v>10789</v>
@@ -13143,20 +13238,36 @@
       <c r="F14" s="22">
         <v>1269</v>
       </c>
-      <c r="G14" s="23"/>
-      <c r="H14" s="23"/>
-      <c r="I14" s="23"/>
+      <c r="G14" s="22">
+        <v>3614</v>
+      </c>
+      <c r="H14" s="22">
+        <v>358</v>
+      </c>
+      <c r="I14" s="22">
+        <v>3255</v>
+      </c>
     </row>
     <row r="15" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A15" s="27">
         <f t="shared" si="0"/>
-        <v>14</v>
-      </c>
-      <c r="B15" s="23"/>
-      <c r="C15" s="23"/>
-      <c r="D15" s="23"/>
-      <c r="E15" s="23"/>
-      <c r="F15" s="23"/>
+        <v>13</v>
+      </c>
+      <c r="B15" s="22">
+        <v>5553</v>
+      </c>
+      <c r="C15" s="22">
+        <v>7571</v>
+      </c>
+      <c r="D15" s="22">
+        <v>9201</v>
+      </c>
+      <c r="E15" s="22">
+        <v>10789</v>
+      </c>
+      <c r="F15" s="22">
+        <v>1269</v>
+      </c>
       <c r="G15" s="23"/>
       <c r="H15" s="23"/>
       <c r="I15" s="23"/>
@@ -13164,51 +13275,51 @@
     <row r="16" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A16" s="27">
         <f t="shared" si="0"/>
-        <v>15</v>
-      </c>
-      <c r="B16" s="22">
-        <v>5695</v>
-      </c>
-      <c r="C16" s="22">
-        <v>7647</v>
-      </c>
-      <c r="D16" s="22">
-        <v>9209</v>
-      </c>
-      <c r="E16" s="22">
-        <v>10791</v>
-      </c>
-      <c r="F16" s="22">
-        <v>1269</v>
-      </c>
-      <c r="G16" s="22">
-        <v>3627</v>
-      </c>
-      <c r="H16" s="22">
-        <v>360</v>
-      </c>
-      <c r="I16" s="22">
-        <v>3266</v>
-      </c>
+        <v>14</v>
+      </c>
+      <c r="B16" s="23"/>
+      <c r="C16" s="23"/>
+      <c r="D16" s="23"/>
+      <c r="E16" s="23"/>
+      <c r="F16" s="23"/>
+      <c r="G16" s="23"/>
+      <c r="H16" s="23"/>
+      <c r="I16" s="23"/>
     </row>
     <row r="17" spans="1:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A17" s="27">
         <f t="shared" si="0"/>
-        <v>16</v>
-      </c>
-      <c r="B17" s="23"/>
-      <c r="C17" s="23"/>
-      <c r="D17" s="23"/>
-      <c r="E17" s="23"/>
-      <c r="F17" s="23"/>
-      <c r="G17" s="23"/>
-      <c r="H17" s="23"/>
-      <c r="I17" s="23"/>
+        <v>15</v>
+      </c>
+      <c r="B17" s="22">
+        <v>5695</v>
+      </c>
+      <c r="C17" s="22">
+        <v>7647</v>
+      </c>
+      <c r="D17" s="22">
+        <v>9209</v>
+      </c>
+      <c r="E17" s="22">
+        <v>10791</v>
+      </c>
+      <c r="F17" s="22">
+        <v>1269</v>
+      </c>
+      <c r="G17" s="22">
+        <v>3627</v>
+      </c>
+      <c r="H17" s="22">
+        <v>360</v>
+      </c>
+      <c r="I17" s="22">
+        <v>3266</v>
+      </c>
     </row>
     <row r="18" spans="1:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A18" s="27">
         <f t="shared" si="0"/>
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B18" s="23"/>
       <c r="C18" s="23"/>
@@ -13218,12 +13329,11 @@
       <c r="G18" s="23"/>
       <c r="H18" s="23"/>
       <c r="I18" s="23"/>
-      <c r="J18" s="3"/>
     </row>
     <row r="19" spans="1:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A19" s="27">
         <f t="shared" si="0"/>
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B19" s="23"/>
       <c r="C19" s="23"/>
@@ -13233,11 +13343,12 @@
       <c r="G19" s="23"/>
       <c r="H19" s="23"/>
       <c r="I19" s="23"/>
+      <c r="J19" s="3"/>
     </row>
     <row r="20" spans="1:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A20" s="27">
         <f t="shared" si="0"/>
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B20" s="23"/>
       <c r="C20" s="23"/>
@@ -13251,7 +13362,7 @@
     <row r="21" spans="1:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A21" s="27">
         <f t="shared" si="0"/>
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B21" s="23"/>
       <c r="C21" s="23"/>
@@ -13265,7 +13376,7 @@
     <row r="22" spans="1:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A22" s="27">
         <f t="shared" si="0"/>
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="B22" s="23"/>
       <c r="C22" s="23"/>
@@ -13279,7 +13390,7 @@
     <row r="23" spans="1:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A23" s="27">
         <f t="shared" si="0"/>
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B23" s="23"/>
       <c r="C23" s="23"/>
@@ -13293,7 +13404,7 @@
     <row r="24" spans="1:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A24" s="27">
         <f t="shared" si="0"/>
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B24" s="23"/>
       <c r="C24" s="23"/>
@@ -13307,7 +13418,7 @@
     <row r="25" spans="1:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A25" s="27">
         <f t="shared" si="0"/>
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B25" s="23"/>
       <c r="C25" s="23"/>
@@ -13321,7 +13432,7 @@
     <row r="26" spans="1:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A26" s="27">
         <f t="shared" si="0"/>
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B26" s="23"/>
       <c r="C26" s="23"/>
@@ -13335,7 +13446,7 @@
     <row r="27" spans="1:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A27" s="27">
         <f t="shared" si="0"/>
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B27" s="23"/>
       <c r="C27" s="23"/>
@@ -13349,7 +13460,7 @@
     <row r="28" spans="1:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A28" s="27">
         <f t="shared" si="0"/>
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="B28" s="23"/>
       <c r="C28" s="23"/>
@@ -13363,7 +13474,7 @@
     <row r="29" spans="1:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A29" s="27">
         <f t="shared" si="0"/>
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="B29" s="23"/>
       <c r="C29" s="23"/>
@@ -13377,115 +13488,118 @@
     <row r="30" spans="1:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A30" s="27">
         <f t="shared" si="0"/>
-        <v>29</v>
-      </c>
-      <c r="B30" s="22">
-        <v>6351</v>
-      </c>
-      <c r="C30" s="22">
-        <v>8113</v>
-      </c>
-      <c r="D30" s="22">
-        <v>9260</v>
-      </c>
-      <c r="E30" s="22">
-        <v>11801</v>
-      </c>
-      <c r="F30" s="22">
-        <v>1270</v>
-      </c>
-      <c r="G30" s="22">
-        <v>3684</v>
-      </c>
-      <c r="H30" s="22">
-        <v>367</v>
-      </c>
-      <c r="I30" s="22">
-        <v>3316</v>
-      </c>
+        <v>28</v>
+      </c>
+      <c r="B30" s="23"/>
+      <c r="C30" s="23"/>
+      <c r="D30" s="23"/>
+      <c r="E30" s="23"/>
+      <c r="F30" s="23"/>
+      <c r="G30" s="23"/>
+      <c r="H30" s="23"/>
+      <c r="I30" s="23"/>
     </row>
     <row r="31" spans="1:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A31" s="27">
         <f t="shared" si="0"/>
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B31" s="22">
-        <v>6375</v>
+        <v>6351</v>
       </c>
       <c r="C31" s="22">
-        <v>8136</v>
+        <v>8113</v>
       </c>
       <c r="D31" s="22">
-        <v>9263</v>
+        <v>9260</v>
       </c>
       <c r="E31" s="22">
-        <v>11802</v>
+        <v>10801</v>
       </c>
       <c r="F31" s="22">
         <v>1270</v>
       </c>
       <c r="G31" s="22">
-        <v>3687</v>
+        <v>3684</v>
       </c>
       <c r="H31" s="22">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="I31" s="22">
-        <v>3318</v>
+        <v>3316</v>
       </c>
     </row>
     <row r="32" spans="1:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A32" s="27">
         <f t="shared" si="0"/>
+        <v>30</v>
+      </c>
+      <c r="B32" s="22">
+        <v>6375</v>
+      </c>
+      <c r="C32" s="22">
+        <v>8136</v>
+      </c>
+      <c r="D32" s="22">
+        <v>9263</v>
+      </c>
+      <c r="E32" s="22">
+        <v>10802</v>
+      </c>
+      <c r="F32" s="22">
+        <v>1270</v>
+      </c>
+      <c r="G32" s="22">
+        <v>3687</v>
+      </c>
+      <c r="H32" s="22">
+        <v>368</v>
+      </c>
+      <c r="I32" s="22">
+        <v>3318</v>
+      </c>
+    </row>
+    <row r="33" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="A33" s="27">
+        <f t="shared" si="0"/>
         <v>31</v>
       </c>
-      <c r="B32" s="28">
+      <c r="B33" s="28">
         <v>6407</v>
       </c>
-      <c r="C32" s="28">
+      <c r="C33" s="28">
         <v>8185</v>
       </c>
-      <c r="D32" s="28">
+      <c r="D33" s="28">
         <v>9265</v>
       </c>
-      <c r="E32" s="28">
-        <v>11802</v>
-      </c>
-      <c r="F32" s="28">
+      <c r="E33" s="28">
+        <v>10802</v>
+      </c>
+      <c r="F33" s="28">
         <v>1271</v>
       </c>
-      <c r="G32" s="28">
+      <c r="G33" s="28">
         <v>3691</v>
       </c>
-      <c r="H32" s="28">
+      <c r="H33" s="28">
         <v>369</v>
       </c>
-      <c r="I32" s="28">
+      <c r="I33" s="28">
         <v>3321</v>
       </c>
     </row>
-    <row r="33" spans="1:9" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="35" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A35" s="4"/>
-      <c r="B35" s="31"/>
-      <c r="C35" s="30"/>
-      <c r="D35" s="30"/>
-      <c r="E35" s="30"/>
-      <c r="F35" s="30"/>
-      <c r="G35" s="30"/>
-      <c r="H35" s="30"/>
-      <c r="I35" s="30"/>
-    </row>
+    <row r="34" spans="1:9" ht="12.75" x14ac:dyDescent="0.2"/>
     <row r="36" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A36" s="4"/>
-      <c r="B36" s="4"/>
-      <c r="C36" s="4"/>
-      <c r="D36" s="4"/>
-      <c r="E36" s="4"/>
-      <c r="F36" s="4"/>
-      <c r="G36" s="4"/>
-      <c r="H36" s="4"/>
-      <c r="I36" s="4"/>
+      <c r="B36" s="33"/>
+      <c r="C36" s="32"/>
+      <c r="D36" s="32"/>
+      <c r="E36" s="32"/>
+      <c r="F36" s="32"/>
+      <c r="G36" s="32"/>
+      <c r="H36" s="32"/>
+      <c r="I36" s="32"/>
     </row>
     <row r="37" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A37" s="4"/>
@@ -13662,7 +13776,6 @@
       <c r="G52" s="4"/>
       <c r="H52" s="4"/>
       <c r="I52" s="4"/>
-      <c r="K52" s="3"/>
     </row>
     <row r="53" spans="1:11" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A53" s="4"/>
@@ -13674,6 +13787,7 @@
       <c r="G53" s="4"/>
       <c r="H53" s="4"/>
       <c r="I53" s="4"/>
+      <c r="K53" s="3"/>
     </row>
     <row r="54" spans="1:11" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A54" s="4"/>
@@ -13829,7 +13943,7 @@
       <c r="H67" s="4"/>
       <c r="I67" s="4"/>
     </row>
-    <row r="68" spans="1:9" ht="12.75" hidden="1" x14ac:dyDescent="0.2">
+    <row r="68" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A68" s="4"/>
       <c r="B68" s="4"/>
       <c r="C68" s="4"/>
@@ -13840,7 +13954,7 @@
       <c r="H68" s="4"/>
       <c r="I68" s="4"/>
     </row>
-    <row r="69" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="69" spans="1:9" ht="12.75" hidden="1" x14ac:dyDescent="0.2">
       <c r="A69" s="4"/>
       <c r="B69" s="4"/>
       <c r="C69" s="4"/>
@@ -13852,29 +13966,29 @@
       <c r="I69" s="4"/>
     </row>
     <row r="70" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A70" s="31"/>
-      <c r="B70" s="30"/>
-      <c r="C70" s="30"/>
-      <c r="D70" s="30"/>
-      <c r="E70" s="30"/>
-      <c r="F70" s="30"/>
-      <c r="G70" s="30"/>
-      <c r="H70" s="30"/>
-      <c r="I70" s="30"/>
+      <c r="A70" s="4"/>
+      <c r="B70" s="4"/>
+      <c r="C70" s="4"/>
+      <c r="D70" s="4"/>
+      <c r="E70" s="4"/>
+      <c r="F70" s="4"/>
+      <c r="G70" s="4"/>
+      <c r="H70" s="4"/>
+      <c r="I70" s="4"/>
     </row>
     <row r="71" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A71" s="4"/>
-      <c r="B71" s="6"/>
-      <c r="C71" s="6"/>
-      <c r="D71" s="6"/>
-      <c r="E71" s="6"/>
-      <c r="F71" s="6"/>
-      <c r="G71" s="6"/>
-      <c r="H71" s="6"/>
-      <c r="I71" s="6"/>
+      <c r="A71" s="33"/>
+      <c r="B71" s="32"/>
+      <c r="C71" s="32"/>
+      <c r="D71" s="32"/>
+      <c r="E71" s="32"/>
+      <c r="F71" s="32"/>
+      <c r="G71" s="32"/>
+      <c r="H71" s="32"/>
+      <c r="I71" s="32"/>
     </row>
     <row r="72" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A72" s="6"/>
+      <c r="A72" s="4"/>
       <c r="B72" s="6"/>
       <c r="C72" s="6"/>
       <c r="D72" s="6"/>
@@ -13884,38 +13998,38 @@
       <c r="H72" s="6"/>
       <c r="I72" s="6"/>
     </row>
-    <row r="75" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A75" s="29"/>
-      <c r="B75" s="30"/>
-      <c r="C75" s="30"/>
-      <c r="D75" s="30"/>
-      <c r="E75" s="30"/>
-      <c r="F75" s="30"/>
-      <c r="G75" s="30"/>
-      <c r="H75" s="30"/>
-      <c r="I75" s="30"/>
+    <row r="73" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="A73" s="6"/>
+      <c r="B73" s="6"/>
+      <c r="C73" s="6"/>
+      <c r="D73" s="6"/>
+      <c r="E73" s="6"/>
+      <c r="F73" s="6"/>
+      <c r="G73" s="6"/>
+      <c r="H73" s="6"/>
+      <c r="I73" s="6"/>
     </row>
     <row r="76" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A76" s="4"/>
-      <c r="B76" s="7"/>
-      <c r="C76" s="7"/>
-      <c r="D76" s="7"/>
-      <c r="E76" s="7"/>
-      <c r="F76" s="7"/>
-      <c r="G76" s="7"/>
-      <c r="H76" s="7"/>
-      <c r="I76" s="7"/>
+      <c r="A76" s="31"/>
+      <c r="B76" s="32"/>
+      <c r="C76" s="32"/>
+      <c r="D76" s="32"/>
+      <c r="E76" s="32"/>
+      <c r="F76" s="32"/>
+      <c r="G76" s="32"/>
+      <c r="H76" s="32"/>
+      <c r="I76" s="32"/>
     </row>
     <row r="77" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A77" s="4"/>
-      <c r="B77" s="8"/>
-      <c r="C77" s="8"/>
-      <c r="D77" s="8"/>
-      <c r="E77" s="8"/>
-      <c r="F77" s="8"/>
-      <c r="G77" s="8"/>
-      <c r="H77" s="8"/>
-      <c r="I77" s="8"/>
+      <c r="B77" s="7"/>
+      <c r="C77" s="7"/>
+      <c r="D77" s="7"/>
+      <c r="E77" s="7"/>
+      <c r="F77" s="7"/>
+      <c r="G77" s="7"/>
+      <c r="H77" s="7"/>
+      <c r="I77" s="7"/>
     </row>
     <row r="78" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A78" s="4"/>
@@ -13929,26 +14043,26 @@
       <c r="I78" s="8"/>
     </row>
     <row r="79" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A79" s="32"/>
-      <c r="B79" s="30"/>
-      <c r="C79" s="30"/>
-      <c r="D79" s="30"/>
-      <c r="E79" s="30"/>
-      <c r="F79" s="30"/>
-      <c r="G79" s="30"/>
-      <c r="H79" s="30"/>
-      <c r="I79" s="30"/>
+      <c r="A79" s="4"/>
+      <c r="B79" s="8"/>
+      <c r="C79" s="8"/>
+      <c r="D79" s="8"/>
+      <c r="E79" s="8"/>
+      <c r="F79" s="8"/>
+      <c r="G79" s="8"/>
+      <c r="H79" s="8"/>
+      <c r="I79" s="8"/>
     </row>
     <row r="80" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A80" s="4"/>
-      <c r="B80" s="4"/>
-      <c r="C80" s="4"/>
-      <c r="D80" s="4"/>
-      <c r="E80" s="4"/>
-      <c r="F80" s="4"/>
-      <c r="G80" s="4"/>
-      <c r="H80" s="4"/>
-      <c r="I80" s="4"/>
+      <c r="A80" s="34"/>
+      <c r="B80" s="32"/>
+      <c r="C80" s="32"/>
+      <c r="D80" s="32"/>
+      <c r="E80" s="32"/>
+      <c r="F80" s="32"/>
+      <c r="G80" s="32"/>
+      <c r="H80" s="32"/>
+      <c r="I80" s="32"/>
     </row>
     <row r="81" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A81" s="4"/>
@@ -13961,38 +14075,38 @@
       <c r="H81" s="4"/>
       <c r="I81" s="4"/>
     </row>
-    <row r="83" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A83" s="4"/>
-      <c r="B83" s="4"/>
+    <row r="82" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="A82" s="4"/>
+      <c r="B82" s="4"/>
+      <c r="C82" s="4"/>
+      <c r="D82" s="4"/>
+      <c r="E82" s="4"/>
+      <c r="F82" s="4"/>
+      <c r="G82" s="4"/>
+      <c r="H82" s="4"/>
+      <c r="I82" s="4"/>
     </row>
     <row r="84" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A84" s="4"/>
+      <c r="B84" s="4"/>
     </row>
     <row r="85" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A85" s="4"/>
-      <c r="B85" s="6"/>
-    </row>
-    <row r="87" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A87" s="29"/>
-      <c r="B87" s="30"/>
-      <c r="C87" s="30"/>
-      <c r="D87" s="30"/>
-      <c r="E87" s="30"/>
-      <c r="F87" s="30"/>
-      <c r="G87" s="30"/>
-      <c r="H87" s="30"/>
-      <c r="I87" s="30"/>
+    </row>
+    <row r="86" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="A86" s="4"/>
+      <c r="B86" s="6"/>
     </row>
     <row r="88" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A88" s="4"/>
-      <c r="B88" s="9"/>
-      <c r="C88" s="9"/>
-      <c r="D88" s="9"/>
-      <c r="E88" s="9"/>
-      <c r="F88" s="9"/>
-      <c r="G88" s="9"/>
-      <c r="H88" s="9"/>
-      <c r="I88" s="9"/>
+      <c r="A88" s="31"/>
+      <c r="B88" s="32"/>
+      <c r="C88" s="32"/>
+      <c r="D88" s="32"/>
+      <c r="E88" s="32"/>
+      <c r="F88" s="32"/>
+      <c r="G88" s="32"/>
+      <c r="H88" s="32"/>
+      <c r="I88" s="32"/>
     </row>
     <row r="89" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A89" s="4"/>
@@ -14062,51 +14176,51 @@
     </row>
     <row r="95" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A95" s="4"/>
-      <c r="B95" s="4"/>
-      <c r="C95" s="4"/>
-      <c r="D95" s="4"/>
-      <c r="E95" s="4"/>
-      <c r="F95" s="4"/>
-      <c r="G95" s="4"/>
-      <c r="H95" s="4"/>
-      <c r="I95" s="4"/>
+      <c r="B95" s="9"/>
+      <c r="C95" s="9"/>
+      <c r="D95" s="9"/>
+      <c r="E95" s="9"/>
+      <c r="F95" s="9"/>
+      <c r="G95" s="9"/>
+      <c r="H95" s="9"/>
+      <c r="I95" s="9"/>
     </row>
     <row r="96" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A96" s="4"/>
-      <c r="B96" s="9"/>
+      <c r="B96" s="4"/>
+      <c r="C96" s="4"/>
+      <c r="D96" s="4"/>
+      <c r="E96" s="4"/>
+      <c r="F96" s="4"/>
+      <c r="G96" s="4"/>
+      <c r="H96" s="4"/>
+      <c r="I96" s="4"/>
     </row>
     <row r="97" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A97" s="4"/>
-      <c r="B97" s="4"/>
+      <c r="B97" s="9"/>
     </row>
     <row r="98" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A98" s="4"/>
-      <c r="B98" s="9"/>
-    </row>
-    <row r="100" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A100" s="31"/>
-      <c r="B100" s="30"/>
-      <c r="C100" s="30"/>
-      <c r="D100" s="30"/>
-      <c r="E100" s="30"/>
-      <c r="F100" s="30"/>
-      <c r="G100" s="30"/>
-      <c r="H100" s="30"/>
-      <c r="I100" s="30"/>
+      <c r="B98" s="4"/>
+    </row>
+    <row r="99" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="A99" s="4"/>
+      <c r="B99" s="9"/>
     </row>
     <row r="101" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A101" s="4"/>
-      <c r="B101" s="6"/>
-      <c r="C101" s="6"/>
-      <c r="D101" s="6"/>
-      <c r="E101" s="6"/>
-      <c r="F101" s="6"/>
-      <c r="G101" s="6"/>
-      <c r="H101" s="6"/>
-      <c r="I101" s="6"/>
+      <c r="A101" s="33"/>
+      <c r="B101" s="32"/>
+      <c r="C101" s="32"/>
+      <c r="D101" s="32"/>
+      <c r="E101" s="32"/>
+      <c r="F101" s="32"/>
+      <c r="G101" s="32"/>
+      <c r="H101" s="32"/>
+      <c r="I101" s="32"/>
     </row>
     <row r="102" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A102" s="6"/>
+      <c r="A102" s="4"/>
       <c r="B102" s="6"/>
       <c r="C102" s="6"/>
       <c r="D102" s="6"/>
@@ -14116,17 +14230,28 @@
       <c r="H102" s="6"/>
       <c r="I102" s="6"/>
     </row>
+    <row r="103" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="A103" s="6"/>
+      <c r="B103" s="6"/>
+      <c r="C103" s="6"/>
+      <c r="D103" s="6"/>
+      <c r="E103" s="6"/>
+      <c r="F103" s="6"/>
+      <c r="G103" s="6"/>
+      <c r="H103" s="6"/>
+      <c r="I103" s="6"/>
+    </row>
   </sheetData>
   <mergeCells count="6">
-    <mergeCell ref="A87:I87"/>
-    <mergeCell ref="A100:I100"/>
-    <mergeCell ref="B35:I35"/>
-    <mergeCell ref="A70:I70"/>
-    <mergeCell ref="A75:I75"/>
-    <mergeCell ref="A79:I79"/>
+    <mergeCell ref="A88:I88"/>
+    <mergeCell ref="A101:I101"/>
+    <mergeCell ref="B36:I36"/>
+    <mergeCell ref="A71:I71"/>
+    <mergeCell ref="A76:I76"/>
+    <mergeCell ref="A80:I80"/>
   </mergeCells>
   <dataValidations count="1">
-    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="A88" xr:uid="{FDFFC2D5-0871-4A1A-88C7-2B7E5B59E96A}">
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="A89" xr:uid="{FDFFC2D5-0871-4A1A-88C7-2B7E5B59E96A}">
       <formula1>"Bandeira,Verde,Amarela,Vermelha p1,Vermelha p2"</formula1>
     </dataValidation>
   </dataValidations>
@@ -14197,47 +14322,22 @@
       <c r="S1" s="5"/>
     </row>
     <row r="2" spans="1:19" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A2" s="1">
-        <v>1</v>
-      </c>
-      <c r="B2" s="2">
-        <v>2930</v>
-      </c>
-      <c r="C2" s="2">
-        <v>4611</v>
-      </c>
-      <c r="D2" s="2">
-        <v>9038</v>
-      </c>
-      <c r="E2" s="2">
-        <v>10758</v>
-      </c>
-      <c r="F2" s="2">
-        <v>1260</v>
-      </c>
-      <c r="G2" s="2">
-        <v>3413</v>
-      </c>
-      <c r="H2" s="2">
-        <v>339</v>
-      </c>
-      <c r="I2" s="2">
-        <v>3073</v>
-      </c>
-      <c r="K2" s="4"/>
-      <c r="L2" s="4"/>
-      <c r="M2" s="4"/>
-      <c r="N2" s="4"/>
-      <c r="O2" s="4"/>
-      <c r="P2" s="4"/>
-      <c r="Q2" s="4"/>
-      <c r="R2" s="4"/>
-      <c r="S2" s="4"/>
+      <c r="A2" s="39">
+        <v>0</v>
+      </c>
+      <c r="B2" s="38"/>
+      <c r="C2" s="38"/>
+      <c r="D2" s="38"/>
+      <c r="E2" s="38"/>
+      <c r="F2" s="38"/>
+      <c r="G2" s="38"/>
+      <c r="H2" s="38"/>
+      <c r="I2" s="38"/>
     </row>
     <row r="3" spans="1:19" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A3" s="1">
         <f t="shared" ref="A3:A32" si="0">A2+1</f>
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B3" s="2">
         <v>3025</v>
@@ -14276,7 +14376,7 @@
     <row r="4" spans="1:19" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A4" s="1">
         <f t="shared" si="0"/>
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B4" s="2">
         <v>3146</v>
@@ -14315,7 +14415,7 @@
     <row r="5" spans="1:19" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A5" s="1">
         <f t="shared" si="0"/>
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B5" s="2">
         <v>3240</v>
@@ -14354,7 +14454,7 @@
     <row r="6" spans="1:19" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A6" s="1">
         <f t="shared" si="0"/>
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B6" s="2">
         <v>3301</v>
@@ -14393,7 +14493,7 @@
     <row r="7" spans="1:19" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A7" s="1">
         <f t="shared" si="0"/>
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B7" s="2">
         <v>3332</v>
@@ -14432,7 +14532,7 @@
     <row r="8" spans="1:19" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A8" s="1">
         <f t="shared" si="0"/>
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B8" s="2">
         <v>3369</v>
@@ -14471,7 +14571,7 @@
     <row r="9" spans="1:19" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A9" s="1">
         <f t="shared" si="0"/>
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B9" s="2">
         <v>3461</v>
@@ -14510,7 +14610,7 @@
     <row r="10" spans="1:19" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A10" s="1">
         <f t="shared" si="0"/>
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B10" s="2">
         <v>3541</v>
@@ -14549,7 +14649,7 @@
     <row r="11" spans="1:19" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A11" s="1">
         <f t="shared" si="0"/>
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B11" s="2">
         <v>3647</v>
@@ -14588,7 +14688,7 @@
     <row r="12" spans="1:19" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A12" s="1">
         <f t="shared" si="0"/>
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B12" s="2">
         <v>3717</v>
@@ -14627,7 +14727,7 @@
     <row r="13" spans="1:19" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A13" s="1">
         <f t="shared" si="0"/>
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B13" s="2">
         <v>3819</v>
@@ -14666,7 +14766,7 @@
     <row r="14" spans="1:19" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A14" s="1">
         <f t="shared" si="0"/>
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B14" s="2">
         <v>3835</v>
@@ -14705,7 +14805,7 @@
     <row r="15" spans="1:19" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A15" s="1">
         <f t="shared" si="0"/>
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B15" s="2">
         <v>3879</v>
@@ -14744,7 +14844,7 @@
     <row r="16" spans="1:19" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A16" s="1">
         <f t="shared" si="0"/>
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B16" s="2">
         <v>3959</v>
@@ -14783,7 +14883,7 @@
     <row r="17" spans="1:19" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A17" s="1">
         <f t="shared" si="0"/>
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B17" s="2">
         <v>4062</v>
@@ -14823,7 +14923,7 @@
     <row r="18" spans="1:19" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A18" s="1">
         <f t="shared" si="0"/>
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B18" s="2">
         <v>4205</v>
@@ -14862,7 +14962,7 @@
     <row r="19" spans="1:19" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A19" s="1">
         <f t="shared" si="0"/>
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B19" s="2">
         <v>4205</v>
@@ -14901,7 +15001,7 @@
     <row r="20" spans="1:19" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A20" s="1">
         <f t="shared" si="0"/>
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B20" s="2">
         <v>4216</v>
@@ -14940,7 +15040,7 @@
     <row r="21" spans="1:19" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A21" s="1">
         <f t="shared" si="0"/>
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B21" s="2">
         <v>4216</v>
@@ -14979,7 +15079,7 @@
     <row r="22" spans="1:19" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A22" s="1">
         <f t="shared" si="0"/>
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="B22" s="2">
         <v>4276</v>
@@ -15018,7 +15118,7 @@
     <row r="23" spans="1:19" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A23" s="1">
         <f t="shared" si="0"/>
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B23" s="2">
         <v>4310</v>
@@ -15057,7 +15157,7 @@
     <row r="24" spans="1:19" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A24" s="1">
         <f t="shared" si="0"/>
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B24" s="2">
         <v>4401</v>
@@ -15096,7 +15196,7 @@
     <row r="25" spans="1:19" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A25" s="1">
         <f t="shared" si="0"/>
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B25" s="2">
         <v>4494</v>
@@ -15135,7 +15235,7 @@
     <row r="26" spans="1:19" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A26" s="1">
         <f t="shared" si="0"/>
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B26" s="2">
         <v>4569</v>
@@ -15174,7 +15274,7 @@
     <row r="27" spans="1:19" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A27" s="1">
         <f t="shared" si="0"/>
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B27" s="2">
         <v>4603</v>
@@ -15214,7 +15314,7 @@
     <row r="28" spans="1:19" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A28" s="1">
         <f t="shared" si="0"/>
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="B28" s="2">
         <v>4660</v>
@@ -15253,7 +15353,7 @@
     <row r="29" spans="1:19" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A29" s="1">
         <f t="shared" si="0"/>
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="B29" s="2">
         <v>4672</v>
@@ -15292,7 +15392,7 @@
     <row r="30" spans="1:19" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A30" s="1">
         <f t="shared" si="0"/>
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="B30" s="2">
         <v>4765</v>
@@ -15331,7 +15431,7 @@
     <row r="31" spans="1:19" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A31" s="1">
         <f t="shared" si="0"/>
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B31" s="2"/>
       <c r="C31" s="2"/>
@@ -15354,7 +15454,7 @@
     <row r="32" spans="1:19" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A32" s="1">
         <f t="shared" si="0"/>
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="B32" s="2"/>
       <c r="C32" s="2"/>
@@ -15446,15 +15546,15 @@
       <c r="I68" s="4"/>
     </row>
     <row r="69" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A69" s="31"/>
-      <c r="B69" s="30"/>
-      <c r="C69" s="30"/>
-      <c r="D69" s="30"/>
-      <c r="E69" s="30"/>
-      <c r="F69" s="30"/>
-      <c r="G69" s="30"/>
-      <c r="H69" s="30"/>
-      <c r="I69" s="30"/>
+      <c r="A69" s="33"/>
+      <c r="B69" s="32"/>
+      <c r="C69" s="32"/>
+      <c r="D69" s="32"/>
+      <c r="E69" s="32"/>
+      <c r="F69" s="32"/>
+      <c r="G69" s="32"/>
+      <c r="H69" s="32"/>
+      <c r="I69" s="32"/>
     </row>
     <row r="70" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A70" s="4"/>
@@ -15479,15 +15579,15 @@
       <c r="I71" s="6"/>
     </row>
     <row r="74" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A74" s="29"/>
-      <c r="B74" s="30"/>
-      <c r="C74" s="30"/>
-      <c r="D74" s="30"/>
-      <c r="E74" s="30"/>
-      <c r="F74" s="30"/>
-      <c r="G74" s="30"/>
-      <c r="H74" s="30"/>
-      <c r="I74" s="30"/>
+      <c r="A74" s="31"/>
+      <c r="B74" s="32"/>
+      <c r="C74" s="32"/>
+      <c r="D74" s="32"/>
+      <c r="E74" s="32"/>
+      <c r="F74" s="32"/>
+      <c r="G74" s="32"/>
+      <c r="H74" s="32"/>
+      <c r="I74" s="32"/>
     </row>
     <row r="75" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A75" s="4"/>
@@ -15523,15 +15623,15 @@
       <c r="I77" s="8"/>
     </row>
     <row r="78" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A78" s="32"/>
-      <c r="B78" s="30"/>
-      <c r="C78" s="30"/>
-      <c r="D78" s="30"/>
-      <c r="E78" s="30"/>
-      <c r="F78" s="30"/>
-      <c r="G78" s="30"/>
-      <c r="H78" s="30"/>
-      <c r="I78" s="30"/>
+      <c r="A78" s="34"/>
+      <c r="B78" s="32"/>
+      <c r="C78" s="32"/>
+      <c r="D78" s="32"/>
+      <c r="E78" s="32"/>
+      <c r="F78" s="32"/>
+      <c r="G78" s="32"/>
+      <c r="H78" s="32"/>
+      <c r="I78" s="32"/>
     </row>
     <row r="79" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A79" s="4"/>
@@ -15567,15 +15667,15 @@
       <c r="B84" s="6"/>
     </row>
     <row r="86" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A86" s="29"/>
-      <c r="B86" s="30"/>
-      <c r="C86" s="30"/>
-      <c r="D86" s="30"/>
-      <c r="E86" s="30"/>
-      <c r="F86" s="30"/>
-      <c r="G86" s="30"/>
-      <c r="H86" s="30"/>
-      <c r="I86" s="30"/>
+      <c r="A86" s="31"/>
+      <c r="B86" s="32"/>
+      <c r="C86" s="32"/>
+      <c r="D86" s="32"/>
+      <c r="E86" s="32"/>
+      <c r="F86" s="32"/>
+      <c r="G86" s="32"/>
+      <c r="H86" s="32"/>
+      <c r="I86" s="32"/>
     </row>
     <row r="87" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A87" s="4"/>
@@ -15678,15 +15778,15 @@
       <c r="B97" s="9"/>
     </row>
     <row r="99" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A99" s="31"/>
-      <c r="B99" s="30"/>
-      <c r="C99" s="30"/>
-      <c r="D99" s="30"/>
-      <c r="E99" s="30"/>
-      <c r="F99" s="30"/>
-      <c r="G99" s="30"/>
-      <c r="H99" s="30"/>
-      <c r="I99" s="30"/>
+      <c r="A99" s="33"/>
+      <c r="B99" s="32"/>
+      <c r="C99" s="32"/>
+      <c r="D99" s="32"/>
+      <c r="E99" s="32"/>
+      <c r="F99" s="32"/>
+      <c r="G99" s="32"/>
+      <c r="H99" s="32"/>
+      <c r="I99" s="32"/>
     </row>
     <row r="100" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A100" s="4"/>

--- a/medicao_energia.xlsx
+++ b/medicao_energia.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\sgt.marquezzini\Documents\GitHub\Dashboardenergia\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{44390E53-CD28-4142-8756-BC4C586AE346}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{134FABA0-BDD6-47D6-8E69-7901A8A198CD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="19440" windowHeight="15000" firstSheet="2" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="19080" yWindow="-120" windowWidth="19440" windowHeight="15000" firstSheet="6" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="DEZEMBRO" sheetId="23" r:id="rId1"/>
@@ -25,6 +25,7 @@
     <sheet name="MARÇO" sheetId="12" r:id="rId10"/>
     <sheet name="FEVEREIRO" sheetId="13" r:id="rId11"/>
     <sheet name="JANEIRO" sheetId="14" r:id="rId12"/>
+    <sheet name="Planilha1" sheetId="24" r:id="rId13"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -41,8 +42,30 @@
 </workbook>
 </file>
 
+<file path=xl/metadata.xml><?xml version="1.0" encoding="utf-8"?>
+<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
+  <metadataTypes count="1">
+    <metadataType name="XLDAPR" minSupportedVersion="120000" copy="1" pasteAll="1" pasteValues="1" merge="1" splitFirst="1" rowColShift="1" clearFormats="1" clearComments="1" assign="1" coerce="1" cellMeta="1"/>
+  </metadataTypes>
+  <futureMetadata name="XLDAPR" count="1">
+    <bk>
+      <extLst>
+        <ext uri="{bdbb8cdc-fa1e-496e-a857-3c3f30c029c3}">
+          <xda:dynamicArrayProperties fDynamic="1" fCollapsed="0"/>
+        </ext>
+      </extLst>
+    </bk>
+  </futureMetadata>
+  <cellMetadata count="1">
+    <bk>
+      <rc t="1" v="0"/>
+    </bk>
+  </cellMetadata>
+</metadata>
+</file>
+
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="108" uniqueCount="9">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="123" uniqueCount="15">
   <si>
     <t>HTS</t>
   </si>
@@ -70,15 +93,35 @@
   <si>
     <t>Data</t>
   </si>
+  <si>
+    <t>Bandeira</t>
+  </si>
+  <si>
+    <t>Vermelha P1</t>
+  </si>
+  <si>
+    <t>Valor</t>
+  </si>
+  <si>
+    <t>Verde</t>
+  </si>
+  <si>
+    <t>Amarela</t>
+  </si>
+  <si>
+    <t>Vermelha P2</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="x14ac x16r2 xr xr9">
-  <numFmts count="1">
+  <numFmts count="3">
+    <numFmt numFmtId="44" formatCode="_-&quot;R$&quot;\ * #,##0.00_-;\-&quot;R$&quot;\ * #,##0.00_-;_-&quot;R$&quot;\ * &quot;-&quot;??_-;_-@_-"/>
     <numFmt numFmtId="164" formatCode="[$R$ -416]#,##0.00"/>
+    <numFmt numFmtId="166" formatCode="_-&quot;R$&quot;\ * #,##0.000_-;\-&quot;R$&quot;\ * #,##0.000_-;_-&quot;R$&quot;\ * &quot;-&quot;??_-;_-@_-"/>
   </numFmts>
-  <fonts count="9" x14ac:knownFonts="1">
+  <fonts count="11" x14ac:knownFonts="1">
     <font>
       <sz val="10"/>
       <color rgb="FF000000"/>
@@ -139,6 +182,21 @@
       <u/>
       <sz val="10"/>
       <color rgb="FF000000"/>
+      <name val="Arial"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FF000000"/>
+      <name val="Arial"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <u/>
+      <sz val="10"/>
+      <color theme="1"/>
       <name val="Arial"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -295,10 +353,11 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="44" fontId="9" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="40">
+  <cellXfs count="44">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -338,9 +397,6 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -384,14 +440,6 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -401,14 +449,34 @@
     <xf numFmtId="0" fontId="2" fillId="5" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="6" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="5" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="2">
+    <cellStyle name="Moeda" xfId="1" builtinId="4"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="6">
@@ -729,17 +797,17 @@
       </c>
     </row>
     <row r="2" spans="1:10" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A2" s="39">
+      <c r="A2" s="34">
         <v>0</v>
       </c>
-      <c r="B2" s="38"/>
-      <c r="C2" s="38"/>
-      <c r="D2" s="38"/>
-      <c r="E2" s="38"/>
-      <c r="F2" s="38"/>
-      <c r="G2" s="38"/>
-      <c r="H2" s="38"/>
-      <c r="I2" s="38"/>
+      <c r="B2" s="33"/>
+      <c r="C2" s="33"/>
+      <c r="D2" s="33"/>
+      <c r="E2" s="33"/>
+      <c r="F2" s="33"/>
+      <c r="G2" s="33"/>
+      <c r="H2" s="33"/>
+      <c r="I2" s="33"/>
     </row>
     <row r="3" spans="1:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A3" s="1">
@@ -921,7 +989,7 @@
       <c r="G15" s="2"/>
       <c r="H15" s="2"/>
       <c r="I15" s="2"/>
-      <c r="J15" s="18"/>
+      <c r="J15" s="17"/>
     </row>
     <row r="16" spans="1:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A16" s="1">
@@ -1079,113 +1147,113 @@
       <c r="I26" s="11"/>
     </row>
     <row r="27" spans="1:10" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A27" s="27">
+      <c r="A27" s="26">
         <f t="shared" si="0"/>
         <v>25</v>
       </c>
-      <c r="B27" s="29"/>
-      <c r="C27" s="29"/>
-      <c r="D27" s="29"/>
-      <c r="E27" s="29"/>
-      <c r="F27" s="29"/>
-      <c r="G27" s="29"/>
-      <c r="H27" s="29"/>
-      <c r="I27" s="29"/>
+      <c r="B27" s="28"/>
+      <c r="C27" s="28"/>
+      <c r="D27" s="28"/>
+      <c r="E27" s="28"/>
+      <c r="F27" s="28"/>
+      <c r="G27" s="28"/>
+      <c r="H27" s="28"/>
+      <c r="I27" s="28"/>
     </row>
     <row r="28" spans="1:10" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A28" s="27">
+      <c r="A28" s="26">
         <f t="shared" si="0"/>
         <v>26</v>
       </c>
-      <c r="B28" s="29"/>
-      <c r="C28" s="29"/>
-      <c r="D28" s="29"/>
-      <c r="E28" s="29"/>
-      <c r="F28" s="29"/>
-      <c r="G28" s="29"/>
-      <c r="H28" s="29"/>
-      <c r="I28" s="29"/>
+      <c r="B28" s="28"/>
+      <c r="C28" s="28"/>
+      <c r="D28" s="28"/>
+      <c r="E28" s="28"/>
+      <c r="F28" s="28"/>
+      <c r="G28" s="28"/>
+      <c r="H28" s="28"/>
+      <c r="I28" s="28"/>
     </row>
     <row r="29" spans="1:10" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A29" s="27">
+      <c r="A29" s="26">
         <f t="shared" si="0"/>
         <v>27</v>
       </c>
-      <c r="B29" s="29"/>
-      <c r="C29" s="29"/>
-      <c r="D29" s="29"/>
-      <c r="E29" s="29"/>
-      <c r="F29" s="29"/>
-      <c r="G29" s="29"/>
-      <c r="H29" s="29"/>
-      <c r="I29" s="29"/>
+      <c r="B29" s="28"/>
+      <c r="C29" s="28"/>
+      <c r="D29" s="28"/>
+      <c r="E29" s="28"/>
+      <c r="F29" s="28"/>
+      <c r="G29" s="28"/>
+      <c r="H29" s="28"/>
+      <c r="I29" s="28"/>
     </row>
     <row r="30" spans="1:10" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A30" s="27">
+      <c r="A30" s="26">
         <f t="shared" si="0"/>
         <v>28</v>
       </c>
-      <c r="B30" s="29"/>
-      <c r="C30" s="29"/>
-      <c r="D30" s="29"/>
-      <c r="E30" s="29"/>
-      <c r="F30" s="29"/>
-      <c r="G30" s="29"/>
-      <c r="H30" s="29"/>
-      <c r="I30" s="29"/>
+      <c r="B30" s="28"/>
+      <c r="C30" s="28"/>
+      <c r="D30" s="28"/>
+      <c r="E30" s="28"/>
+      <c r="F30" s="28"/>
+      <c r="G30" s="28"/>
+      <c r="H30" s="28"/>
+      <c r="I30" s="28"/>
     </row>
     <row r="31" spans="1:10" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A31" s="27">
+      <c r="A31" s="26">
         <f t="shared" si="0"/>
         <v>29</v>
       </c>
-      <c r="B31" s="29"/>
-      <c r="C31" s="29"/>
-      <c r="D31" s="29"/>
-      <c r="E31" s="29"/>
-      <c r="F31" s="29"/>
-      <c r="G31" s="29"/>
-      <c r="H31" s="29"/>
-      <c r="I31" s="29"/>
+      <c r="B31" s="28"/>
+      <c r="C31" s="28"/>
+      <c r="D31" s="28"/>
+      <c r="E31" s="28"/>
+      <c r="F31" s="28"/>
+      <c r="G31" s="28"/>
+      <c r="H31" s="28"/>
+      <c r="I31" s="28"/>
     </row>
     <row r="32" spans="1:10" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A32" s="27">
+      <c r="A32" s="26">
         <f t="shared" si="0"/>
         <v>30</v>
       </c>
-      <c r="B32" s="29"/>
-      <c r="C32" s="29"/>
-      <c r="D32" s="29"/>
-      <c r="E32" s="29"/>
-      <c r="F32" s="29"/>
-      <c r="G32" s="29"/>
-      <c r="H32" s="29"/>
-      <c r="I32" s="29"/>
+      <c r="B32" s="28"/>
+      <c r="C32" s="28"/>
+      <c r="D32" s="28"/>
+      <c r="E32" s="28"/>
+      <c r="F32" s="28"/>
+      <c r="G32" s="28"/>
+      <c r="H32" s="28"/>
+      <c r="I32" s="28"/>
     </row>
     <row r="33" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A33" s="27">
+      <c r="A33" s="26">
         <f t="shared" si="0"/>
         <v>31</v>
       </c>
-      <c r="B33" s="29"/>
-      <c r="C33" s="29"/>
-      <c r="D33" s="29"/>
-      <c r="E33" s="29"/>
-      <c r="F33" s="29"/>
-      <c r="G33" s="29"/>
-      <c r="H33" s="29"/>
-      <c r="I33" s="29"/>
+      <c r="B33" s="28"/>
+      <c r="C33" s="28"/>
+      <c r="D33" s="28"/>
+      <c r="E33" s="28"/>
+      <c r="F33" s="28"/>
+      <c r="G33" s="28"/>
+      <c r="H33" s="28"/>
+      <c r="I33" s="28"/>
     </row>
     <row r="35" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A35" s="4"/>
-      <c r="B35" s="33"/>
-      <c r="C35" s="32"/>
-      <c r="D35" s="32"/>
-      <c r="E35" s="32"/>
-      <c r="F35" s="32"/>
-      <c r="G35" s="32"/>
-      <c r="H35" s="32"/>
-      <c r="I35" s="32"/>
+      <c r="B35" s="37"/>
+      <c r="C35" s="36"/>
+      <c r="D35" s="36"/>
+      <c r="E35" s="36"/>
+      <c r="F35" s="36"/>
+      <c r="G35" s="36"/>
+      <c r="H35" s="36"/>
+      <c r="I35" s="36"/>
     </row>
     <row r="36" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A36" s="4"/>
@@ -1563,15 +1631,15 @@
       <c r="I69" s="4"/>
     </row>
     <row r="70" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A70" s="33"/>
-      <c r="B70" s="32"/>
-      <c r="C70" s="32"/>
-      <c r="D70" s="32"/>
-      <c r="E70" s="32"/>
-      <c r="F70" s="32"/>
-      <c r="G70" s="32"/>
-      <c r="H70" s="32"/>
-      <c r="I70" s="32"/>
+      <c r="A70" s="37"/>
+      <c r="B70" s="36"/>
+      <c r="C70" s="36"/>
+      <c r="D70" s="36"/>
+      <c r="E70" s="36"/>
+      <c r="F70" s="36"/>
+      <c r="G70" s="36"/>
+      <c r="H70" s="36"/>
+      <c r="I70" s="36"/>
     </row>
     <row r="71" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A71" s="4"/>
@@ -1596,15 +1664,15 @@
       <c r="I72" s="6"/>
     </row>
     <row r="75" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A75" s="31"/>
-      <c r="B75" s="32"/>
-      <c r="C75" s="32"/>
-      <c r="D75" s="32"/>
-      <c r="E75" s="32"/>
-      <c r="F75" s="32"/>
-      <c r="G75" s="32"/>
-      <c r="H75" s="32"/>
-      <c r="I75" s="32"/>
+      <c r="A75" s="35"/>
+      <c r="B75" s="36"/>
+      <c r="C75" s="36"/>
+      <c r="D75" s="36"/>
+      <c r="E75" s="36"/>
+      <c r="F75" s="36"/>
+      <c r="G75" s="36"/>
+      <c r="H75" s="36"/>
+      <c r="I75" s="36"/>
     </row>
     <row r="76" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A76" s="4"/>
@@ -1640,15 +1708,15 @@
       <c r="I78" s="8"/>
     </row>
     <row r="79" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A79" s="34"/>
-      <c r="B79" s="32"/>
-      <c r="C79" s="32"/>
-      <c r="D79" s="32"/>
-      <c r="E79" s="32"/>
-      <c r="F79" s="32"/>
-      <c r="G79" s="32"/>
-      <c r="H79" s="32"/>
-      <c r="I79" s="32"/>
+      <c r="A79" s="38"/>
+      <c r="B79" s="36"/>
+      <c r="C79" s="36"/>
+      <c r="D79" s="36"/>
+      <c r="E79" s="36"/>
+      <c r="F79" s="36"/>
+      <c r="G79" s="36"/>
+      <c r="H79" s="36"/>
+      <c r="I79" s="36"/>
     </row>
     <row r="80" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A80" s="4"/>
@@ -1684,15 +1752,15 @@
       <c r="B85" s="6"/>
     </row>
     <row r="87" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A87" s="31"/>
-      <c r="B87" s="32"/>
-      <c r="C87" s="32"/>
-      <c r="D87" s="32"/>
-      <c r="E87" s="32"/>
-      <c r="F87" s="32"/>
-      <c r="G87" s="32"/>
-      <c r="H87" s="32"/>
-      <c r="I87" s="32"/>
+      <c r="A87" s="35"/>
+      <c r="B87" s="36"/>
+      <c r="C87" s="36"/>
+      <c r="D87" s="36"/>
+      <c r="E87" s="36"/>
+      <c r="F87" s="36"/>
+      <c r="G87" s="36"/>
+      <c r="H87" s="36"/>
+      <c r="I87" s="36"/>
     </row>
     <row r="88" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A88" s="4"/>
@@ -1795,15 +1863,15 @@
       <c r="B98" s="9"/>
     </row>
     <row r="100" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A100" s="33"/>
-      <c r="B100" s="32"/>
-      <c r="C100" s="32"/>
-      <c r="D100" s="32"/>
-      <c r="E100" s="32"/>
-      <c r="F100" s="32"/>
-      <c r="G100" s="32"/>
-      <c r="H100" s="32"/>
-      <c r="I100" s="32"/>
+      <c r="A100" s="37"/>
+      <c r="B100" s="36"/>
+      <c r="C100" s="36"/>
+      <c r="D100" s="36"/>
+      <c r="E100" s="36"/>
+      <c r="F100" s="36"/>
+      <c r="G100" s="36"/>
+      <c r="H100" s="36"/>
+      <c r="I100" s="36"/>
     </row>
     <row r="101" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A101" s="4"/>
@@ -1861,937 +1929,937 @@
       <c r="A1" s="12" t="s">
         <v>8</v>
       </c>
-      <c r="B1" s="21" t="s">
+      <c r="B1" s="20" t="s">
         <v>0</v>
       </c>
-      <c r="C1" s="21" t="s">
+      <c r="C1" s="20" t="s">
         <v>1</v>
       </c>
-      <c r="D1" s="21" t="s">
+      <c r="D1" s="20" t="s">
         <v>2</v>
       </c>
-      <c r="E1" s="21" t="s">
+      <c r="E1" s="20" t="s">
         <v>3</v>
       </c>
-      <c r="F1" s="21" t="s">
+      <c r="F1" s="20" t="s">
         <v>4</v>
       </c>
-      <c r="G1" s="21" t="s">
+      <c r="G1" s="20" t="s">
         <v>5</v>
       </c>
-      <c r="H1" s="21" t="s">
+      <c r="H1" s="20" t="s">
         <v>6</v>
       </c>
-      <c r="I1" s="21" t="s">
+      <c r="I1" s="20" t="s">
         <v>7</v>
       </c>
     </row>
     <row r="2" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A2" s="39">
+      <c r="A2" s="34">
         <v>0</v>
       </c>
-      <c r="B2" s="38"/>
-      <c r="C2" s="38"/>
-      <c r="D2" s="38"/>
-      <c r="E2" s="38"/>
-      <c r="F2" s="38"/>
-      <c r="G2" s="38"/>
-      <c r="H2" s="38"/>
-      <c r="I2" s="38"/>
+      <c r="B2" s="33"/>
+      <c r="C2" s="33"/>
+      <c r="D2" s="33"/>
+      <c r="E2" s="33"/>
+      <c r="F2" s="33"/>
+      <c r="G2" s="33"/>
+      <c r="H2" s="33"/>
+      <c r="I2" s="33"/>
     </row>
     <row r="3" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A3" s="19">
+      <c r="A3" s="18">
         <v>1</v>
       </c>
-      <c r="B3" s="22">
+      <c r="B3" s="21">
         <v>594</v>
       </c>
-      <c r="C3" s="22">
+      <c r="C3" s="21">
         <v>1193</v>
       </c>
-      <c r="D3" s="22">
+      <c r="D3" s="21">
         <v>8925</v>
       </c>
-      <c r="E3" s="22">
+      <c r="E3" s="21">
         <v>10736</v>
       </c>
-      <c r="F3" s="22">
+      <c r="F3" s="21">
         <v>1256</v>
       </c>
-      <c r="G3" s="22">
+      <c r="G3" s="21">
         <v>3235</v>
       </c>
-      <c r="H3" s="22">
+      <c r="H3" s="21">
         <v>321</v>
       </c>
-      <c r="I3" s="22">
+      <c r="I3" s="21">
         <v>2913</v>
       </c>
     </row>
     <row r="4" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A4" s="19">
+      <c r="A4" s="18">
         <f t="shared" ref="A4:A33" si="0">A3+1</f>
         <v>2</v>
       </c>
-      <c r="B4" s="22">
+      <c r="B4" s="21">
         <v>671</v>
       </c>
-      <c r="C4" s="22">
+      <c r="C4" s="21">
         <v>1289</v>
       </c>
-      <c r="D4" s="22">
+      <c r="D4" s="21">
         <v>8928</v>
       </c>
-      <c r="E4" s="22">
+      <c r="E4" s="21">
         <v>10736</v>
       </c>
-      <c r="F4" s="22">
+      <c r="F4" s="21">
         <v>1256</v>
       </c>
-      <c r="G4" s="22">
+      <c r="G4" s="21">
         <v>3238</v>
       </c>
-      <c r="H4" s="22">
+      <c r="H4" s="21">
         <v>321</v>
       </c>
-      <c r="I4" s="22">
+      <c r="I4" s="21">
         <v>2917</v>
       </c>
     </row>
     <row r="5" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A5" s="19">
+      <c r="A5" s="18">
         <f t="shared" si="0"/>
         <v>3</v>
       </c>
-      <c r="B5" s="22">
+      <c r="B5" s="21">
         <v>692</v>
       </c>
-      <c r="C5" s="22">
+      <c r="C5" s="21">
         <v>1453</v>
       </c>
-      <c r="D5" s="22">
+      <c r="D5" s="21">
         <v>8931</v>
       </c>
-      <c r="E5" s="22">
+      <c r="E5" s="21">
         <v>10736</v>
       </c>
-      <c r="F5" s="22">
+      <c r="F5" s="21">
         <v>1256</v>
       </c>
-      <c r="G5" s="22">
+      <c r="G5" s="21">
         <v>3243</v>
       </c>
-      <c r="H5" s="22">
+      <c r="H5" s="21">
         <v>321</v>
       </c>
-      <c r="I5" s="22">
+      <c r="I5" s="21">
         <v>2922</v>
       </c>
     </row>
     <row r="6" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A6" s="19">
+      <c r="A6" s="18">
         <f t="shared" si="0"/>
         <v>4</v>
       </c>
-      <c r="B6" s="22">
+      <c r="B6" s="21">
         <v>728</v>
       </c>
-      <c r="C6" s="22">
+      <c r="C6" s="21">
         <v>1501</v>
       </c>
-      <c r="D6" s="22">
+      <c r="D6" s="21">
         <v>8935</v>
       </c>
-      <c r="E6" s="22">
+      <c r="E6" s="21">
         <v>10738</v>
       </c>
-      <c r="F6" s="22">
+      <c r="F6" s="21">
         <v>1256</v>
       </c>
-      <c r="G6" s="22">
+      <c r="G6" s="21">
         <v>3251</v>
       </c>
-      <c r="H6" s="22">
+      <c r="H6" s="21">
         <v>322</v>
       </c>
-      <c r="I6" s="22">
+      <c r="I6" s="21">
         <v>2928</v>
       </c>
     </row>
     <row r="7" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A7" s="19">
+      <c r="A7" s="18">
         <f t="shared" si="0"/>
         <v>5</v>
       </c>
-      <c r="B7" s="23"/>
-      <c r="C7" s="23"/>
-      <c r="D7" s="23"/>
-      <c r="E7" s="23"/>
-      <c r="F7" s="23"/>
-      <c r="G7" s="23"/>
-      <c r="H7" s="23"/>
-      <c r="I7" s="23"/>
+      <c r="B7" s="22"/>
+      <c r="C7" s="22"/>
+      <c r="D7" s="22"/>
+      <c r="E7" s="22"/>
+      <c r="F7" s="22"/>
+      <c r="G7" s="22"/>
+      <c r="H7" s="22"/>
+      <c r="I7" s="22"/>
     </row>
     <row r="8" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A8" s="19">
+      <c r="A8" s="18">
         <f t="shared" si="0"/>
         <v>6</v>
       </c>
-      <c r="B8" s="22">
+      <c r="B8" s="21">
         <v>882</v>
       </c>
-      <c r="C8" s="22">
+      <c r="C8" s="21">
         <v>1705</v>
       </c>
-      <c r="D8" s="22">
+      <c r="D8" s="21">
         <v>8946</v>
       </c>
-      <c r="E8" s="22">
+      <c r="E8" s="21">
         <v>10739</v>
       </c>
-      <c r="F8" s="22">
+      <c r="F8" s="21">
         <v>1256</v>
       </c>
-      <c r="G8" s="22">
+      <c r="G8" s="21">
         <v>3263</v>
       </c>
-      <c r="H8" s="22">
+      <c r="H8" s="21">
         <v>322</v>
       </c>
-      <c r="I8" s="22">
+      <c r="I8" s="21">
         <v>2928</v>
       </c>
     </row>
     <row r="9" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A9" s="19">
+      <c r="A9" s="18">
         <f t="shared" si="0"/>
         <v>7</v>
       </c>
-      <c r="B9" s="23"/>
-      <c r="C9" s="23"/>
-      <c r="D9" s="23"/>
-      <c r="E9" s="23"/>
-      <c r="F9" s="23"/>
-      <c r="G9" s="23"/>
-      <c r="H9" s="23"/>
-      <c r="I9" s="23"/>
+      <c r="B9" s="22"/>
+      <c r="C9" s="22"/>
+      <c r="D9" s="22"/>
+      <c r="E9" s="22"/>
+      <c r="F9" s="22"/>
+      <c r="G9" s="22"/>
+      <c r="H9" s="22"/>
+      <c r="I9" s="22"/>
     </row>
     <row r="10" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A10" s="19">
+      <c r="A10" s="18">
         <f t="shared" si="0"/>
         <v>8</v>
       </c>
-      <c r="B10" s="22">
+      <c r="B10" s="21">
         <v>1058</v>
       </c>
-      <c r="C10" s="22">
+      <c r="C10" s="21">
         <v>1995</v>
       </c>
-      <c r="D10" s="22">
+      <c r="D10" s="21">
         <v>8952</v>
       </c>
-      <c r="E10" s="22">
+      <c r="E10" s="21">
         <v>10741</v>
       </c>
-      <c r="F10" s="22">
+      <c r="F10" s="21">
         <v>1257</v>
       </c>
-      <c r="G10" s="22">
+      <c r="G10" s="21">
         <v>3274</v>
       </c>
-      <c r="H10" s="22">
+      <c r="H10" s="21">
         <v>325</v>
       </c>
-      <c r="I10" s="22">
+      <c r="I10" s="21">
         <v>2948</v>
       </c>
     </row>
     <row r="11" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A11" s="19">
+      <c r="A11" s="18">
         <f t="shared" si="0"/>
         <v>9</v>
       </c>
-      <c r="B11" s="22">
+      <c r="B11" s="21">
         <v>1080</v>
       </c>
-      <c r="C11" s="22">
+      <c r="C11" s="21">
         <v>2125</v>
       </c>
-      <c r="D11" s="22">
+      <c r="D11" s="21">
         <v>8952</v>
       </c>
-      <c r="E11" s="22">
+      <c r="E11" s="21">
         <v>10741</v>
       </c>
-      <c r="F11" s="22">
+      <c r="F11" s="21">
         <v>1257</v>
       </c>
-      <c r="G11" s="22">
+      <c r="G11" s="21">
         <v>3280</v>
       </c>
-      <c r="H11" s="22">
+      <c r="H11" s="21">
         <v>325</v>
       </c>
-      <c r="I11" s="22">
+      <c r="I11" s="21">
         <v>2955</v>
       </c>
     </row>
     <row r="12" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A12" s="19">
+      <c r="A12" s="18">
         <f t="shared" si="0"/>
         <v>10</v>
       </c>
-      <c r="B12" s="22">
+      <c r="B12" s="21">
         <v>1135</v>
       </c>
-      <c r="C12" s="22">
+      <c r="C12" s="21">
         <v>2301</v>
       </c>
-      <c r="D12" s="22">
+      <c r="D12" s="21">
         <v>8960</v>
       </c>
-      <c r="E12" s="22">
+      <c r="E12" s="21">
         <v>10742</v>
       </c>
-      <c r="F12" s="22">
+      <c r="F12" s="21">
         <v>1257</v>
       </c>
-      <c r="G12" s="22">
+      <c r="G12" s="21">
         <v>3287</v>
       </c>
-      <c r="H12" s="22">
+      <c r="H12" s="21">
         <v>325</v>
       </c>
-      <c r="I12" s="22">
+      <c r="I12" s="21">
         <v>2962</v>
       </c>
     </row>
     <row r="13" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A13" s="19">
+      <c r="A13" s="18">
         <f t="shared" si="0"/>
         <v>11</v>
       </c>
-      <c r="B13" s="22">
+      <c r="B13" s="21">
         <v>1230</v>
       </c>
-      <c r="C13" s="22">
+      <c r="C13" s="21">
         <v>2418</v>
       </c>
-      <c r="D13" s="22">
+      <c r="D13" s="21">
         <v>8964</v>
       </c>
-      <c r="E13" s="22">
+      <c r="E13" s="21">
         <v>10743</v>
       </c>
-      <c r="F13" s="22">
+      <c r="F13" s="21">
         <v>1257</v>
       </c>
-      <c r="G13" s="22">
+      <c r="G13" s="21">
         <v>3287</v>
       </c>
-      <c r="H13" s="22">
+      <c r="H13" s="21">
         <v>325</v>
       </c>
-      <c r="I13" s="22">
+      <c r="I13" s="21">
         <v>2962</v>
       </c>
     </row>
     <row r="14" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A14" s="19">
+      <c r="A14" s="18">
         <f t="shared" si="0"/>
         <v>12</v>
       </c>
-      <c r="B14" s="22">
+      <c r="B14" s="21">
         <v>1347</v>
       </c>
-      <c r="C14" s="22">
+      <c r="C14" s="21">
         <v>2611</v>
       </c>
-      <c r="D14" s="22">
+      <c r="D14" s="21">
         <v>8967</v>
       </c>
-      <c r="E14" s="22">
+      <c r="E14" s="21">
         <v>10744</v>
       </c>
-      <c r="F14" s="22">
+      <c r="F14" s="21">
         <v>1257</v>
       </c>
-      <c r="G14" s="22">
+      <c r="G14" s="21">
         <v>3300</v>
       </c>
-      <c r="H14" s="22">
+      <c r="H14" s="21">
         <v>327</v>
       </c>
-      <c r="I14" s="22">
+      <c r="I14" s="21">
         <v>2973</v>
       </c>
     </row>
     <row r="15" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A15" s="19">
+      <c r="A15" s="18">
         <f t="shared" si="0"/>
         <v>13</v>
       </c>
-      <c r="B15" s="22">
+      <c r="B15" s="21">
         <v>1470</v>
       </c>
-      <c r="C15" s="22">
+      <c r="C15" s="21">
         <v>2681</v>
       </c>
-      <c r="D15" s="22">
+      <c r="D15" s="21">
         <v>8971</v>
       </c>
-      <c r="E15" s="22">
+      <c r="E15" s="21">
         <v>10744</v>
       </c>
-      <c r="F15" s="22">
+      <c r="F15" s="21">
         <v>1258</v>
       </c>
-      <c r="G15" s="22">
+      <c r="G15" s="21">
         <v>3306</v>
       </c>
-      <c r="H15" s="22">
+      <c r="H15" s="21">
         <v>328</v>
       </c>
-      <c r="I15" s="22">
+      <c r="I15" s="21">
         <v>2977</v>
       </c>
     </row>
     <row r="16" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A16" s="19">
+      <c r="A16" s="18">
         <f t="shared" si="0"/>
         <v>14</v>
       </c>
-      <c r="B16" s="23"/>
-      <c r="C16" s="23"/>
-      <c r="D16" s="23"/>
-      <c r="E16" s="23"/>
-      <c r="F16" s="23"/>
-      <c r="G16" s="23"/>
-      <c r="H16" s="23"/>
-      <c r="I16" s="23"/>
+      <c r="B16" s="22"/>
+      <c r="C16" s="22"/>
+      <c r="D16" s="22"/>
+      <c r="E16" s="22"/>
+      <c r="F16" s="22"/>
+      <c r="G16" s="22"/>
+      <c r="H16" s="22"/>
+      <c r="I16" s="22"/>
     </row>
     <row r="17" spans="1:10" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A17" s="19">
+      <c r="A17" s="18">
         <f t="shared" si="0"/>
         <v>15</v>
       </c>
-      <c r="B17" s="22">
+      <c r="B17" s="21">
         <v>1674</v>
       </c>
-      <c r="C17" s="22">
+      <c r="C17" s="21">
         <v>2914</v>
       </c>
-      <c r="D17" s="22">
+      <c r="D17" s="21">
         <v>8979</v>
       </c>
-      <c r="E17" s="22">
+      <c r="E17" s="21">
         <v>10745</v>
       </c>
-      <c r="F17" s="22">
+      <c r="F17" s="21">
         <v>1258</v>
       </c>
-      <c r="G17" s="22">
+      <c r="G17" s="21">
         <v>3317</v>
       </c>
-      <c r="H17" s="22">
+      <c r="H17" s="21">
         <v>329</v>
       </c>
-      <c r="I17" s="22">
+      <c r="I17" s="21">
         <v>2988</v>
       </c>
     </row>
     <row r="18" spans="1:10" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A18" s="19">
+      <c r="A18" s="18">
         <f t="shared" si="0"/>
         <v>16</v>
       </c>
-      <c r="B18" s="22">
+      <c r="B18" s="21">
         <v>1690</v>
       </c>
-      <c r="C18" s="22">
+      <c r="C18" s="21">
         <v>2986</v>
       </c>
-      <c r="D18" s="22">
+      <c r="D18" s="21">
         <v>8979</v>
       </c>
-      <c r="E18" s="22">
+      <c r="E18" s="21">
         <v>10747</v>
       </c>
-      <c r="F18" s="22">
+      <c r="F18" s="21">
         <v>1258</v>
       </c>
-      <c r="G18" s="22">
+      <c r="G18" s="21">
         <v>3324</v>
       </c>
-      <c r="H18" s="22">
+      <c r="H18" s="21">
         <v>329</v>
       </c>
-      <c r="I18" s="22">
+      <c r="I18" s="21">
         <v>2994</v>
       </c>
     </row>
     <row r="19" spans="1:10" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A19" s="19">
+      <c r="A19" s="18">
         <f t="shared" si="0"/>
         <v>17</v>
       </c>
-      <c r="B19" s="22">
+      <c r="B19" s="21">
         <v>1733</v>
       </c>
-      <c r="C19" s="22">
+      <c r="C19" s="21">
         <v>3061</v>
       </c>
-      <c r="D19" s="22">
+      <c r="D19" s="21">
         <v>8985</v>
       </c>
-      <c r="E19" s="22">
+      <c r="E19" s="21">
         <v>10747</v>
       </c>
-      <c r="F19" s="22">
+      <c r="F19" s="21">
         <v>1258</v>
       </c>
-      <c r="G19" s="22">
+      <c r="G19" s="21">
         <v>3330</v>
       </c>
-      <c r="H19" s="22">
+      <c r="H19" s="21">
         <v>329</v>
       </c>
-      <c r="I19" s="22">
+      <c r="I19" s="21">
         <v>3000</v>
       </c>
       <c r="J19" s="3"/>
     </row>
     <row r="20" spans="1:10" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A20" s="19">
+      <c r="A20" s="18">
         <f t="shared" si="0"/>
         <v>18</v>
       </c>
-      <c r="B20" s="22">
+      <c r="B20" s="21">
         <v>1859</v>
       </c>
-      <c r="C20" s="22">
+      <c r="C20" s="21">
         <v>3301</v>
       </c>
-      <c r="D20" s="22">
+      <c r="D20" s="21">
         <v>8988</v>
       </c>
-      <c r="E20" s="22">
+      <c r="E20" s="21">
         <v>10748</v>
       </c>
-      <c r="F20" s="22">
+      <c r="F20" s="21">
         <v>1258</v>
       </c>
-      <c r="G20" s="22">
+      <c r="G20" s="21">
         <v>3336</v>
       </c>
-      <c r="H20" s="22">
+      <c r="H20" s="21">
         <v>330</v>
       </c>
-      <c r="I20" s="22">
+      <c r="I20" s="21">
         <v>3005</v>
       </c>
     </row>
     <row r="21" spans="1:10" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A21" s="19">
+      <c r="A21" s="18">
         <f t="shared" si="0"/>
         <v>19</v>
       </c>
-      <c r="B21" s="22">
+      <c r="B21" s="21">
         <v>1951</v>
       </c>
-      <c r="C21" s="22">
+      <c r="C21" s="21">
         <v>3368</v>
       </c>
-      <c r="D21" s="22">
+      <c r="D21" s="21">
         <v>8992</v>
       </c>
-      <c r="E21" s="22">
+      <c r="E21" s="21">
         <v>10749</v>
       </c>
-      <c r="F21" s="22">
+      <c r="F21" s="21">
         <v>1258</v>
       </c>
-      <c r="G21" s="22">
+      <c r="G21" s="21">
         <v>3342</v>
       </c>
-      <c r="H21" s="22">
+      <c r="H21" s="21">
         <v>331</v>
       </c>
-      <c r="I21" s="22">
+      <c r="I21" s="21">
         <v>3010</v>
       </c>
     </row>
     <row r="22" spans="1:10" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A22" s="19">
+      <c r="A22" s="18">
         <f t="shared" si="0"/>
         <v>20</v>
       </c>
-      <c r="B22" s="22">
+      <c r="B22" s="21">
         <v>2048</v>
       </c>
-      <c r="C22" s="22">
+      <c r="C22" s="21">
         <v>3506</v>
       </c>
-      <c r="D22" s="22">
+      <c r="D22" s="21">
         <v>8995</v>
       </c>
-      <c r="E22" s="22">
+      <c r="E22" s="21">
         <v>10749</v>
       </c>
-      <c r="F22" s="22">
+      <c r="F22" s="21">
         <v>1258</v>
       </c>
-      <c r="G22" s="22">
+      <c r="G22" s="21">
         <v>3347</v>
       </c>
-      <c r="H22" s="22">
+      <c r="H22" s="21">
         <v>332</v>
       </c>
-      <c r="I22" s="22">
+      <c r="I22" s="21">
         <v>3015</v>
       </c>
     </row>
     <row r="23" spans="1:10" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A23" s="19">
+      <c r="A23" s="18">
         <f t="shared" si="0"/>
         <v>21</v>
       </c>
-      <c r="B23" s="22">
+      <c r="B23" s="21">
         <v>2170</v>
       </c>
-      <c r="C23" s="22">
+      <c r="C23" s="21">
         <v>3628</v>
       </c>
-      <c r="D23" s="22">
+      <c r="D23" s="21">
         <v>8985</v>
       </c>
-      <c r="E23" s="22">
+      <c r="E23" s="21">
         <v>10749</v>
       </c>
-      <c r="F23" s="22">
+      <c r="F23" s="21">
         <v>1258</v>
       </c>
-      <c r="G23" s="22">
+      <c r="G23" s="21">
         <v>3350</v>
       </c>
-      <c r="H23" s="22">
+      <c r="H23" s="21">
         <v>333</v>
       </c>
-      <c r="I23" s="22">
+      <c r="I23" s="21">
         <v>3017</v>
       </c>
     </row>
     <row r="24" spans="1:10" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A24" s="19">
+      <c r="A24" s="18">
         <f t="shared" si="0"/>
         <v>22</v>
       </c>
-      <c r="B24" s="22">
+      <c r="B24" s="21">
         <v>2199</v>
       </c>
-      <c r="C24" s="22">
+      <c r="C24" s="21">
         <v>3713</v>
       </c>
-      <c r="D24" s="22">
+      <c r="D24" s="21">
         <v>8999</v>
       </c>
-      <c r="E24" s="22">
+      <c r="E24" s="21">
         <v>10752</v>
       </c>
-      <c r="F24" s="22">
+      <c r="F24" s="21">
         <v>1259</v>
       </c>
-      <c r="G24" s="22">
+      <c r="G24" s="21">
         <v>3356</v>
       </c>
-      <c r="H24" s="22">
+      <c r="H24" s="21">
         <v>334</v>
       </c>
-      <c r="I24" s="22">
+      <c r="I24" s="21">
         <v>3021</v>
       </c>
     </row>
     <row r="25" spans="1:10" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A25" s="19">
+      <c r="A25" s="18">
         <f t="shared" si="0"/>
         <v>23</v>
       </c>
-      <c r="B25" s="22">
+      <c r="B25" s="21">
         <v>2248</v>
       </c>
-      <c r="C25" s="22">
+      <c r="C25" s="21">
         <v>3790</v>
       </c>
-      <c r="D25" s="22">
+      <c r="D25" s="21">
         <v>9004</v>
       </c>
-      <c r="E25" s="22">
+      <c r="E25" s="21">
         <v>10752</v>
       </c>
-      <c r="F25" s="22">
+      <c r="F25" s="21">
         <v>1259</v>
       </c>
-      <c r="G25" s="22">
+      <c r="G25" s="21">
         <v>3364</v>
       </c>
-      <c r="H25" s="22">
+      <c r="H25" s="21">
         <v>334</v>
       </c>
-      <c r="I25" s="22">
+      <c r="I25" s="21">
         <v>3023</v>
       </c>
     </row>
     <row r="26" spans="1:10" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A26" s="19">
+      <c r="A26" s="18">
         <f t="shared" si="0"/>
         <v>24</v>
       </c>
-      <c r="B26" s="22">
+      <c r="B26" s="21">
         <v>2286</v>
       </c>
-      <c r="C26" s="22">
+      <c r="C26" s="21">
         <v>3790</v>
       </c>
-      <c r="D26" s="22">
+      <c r="D26" s="21">
         <v>9009</v>
       </c>
-      <c r="E26" s="22">
+      <c r="E26" s="21">
         <v>10753</v>
       </c>
-      <c r="F26" s="22">
+      <c r="F26" s="21">
         <v>1259</v>
       </c>
-      <c r="G26" s="22">
+      <c r="G26" s="21">
         <v>3369</v>
       </c>
-      <c r="H26" s="22">
+      <c r="H26" s="21">
         <v>334</v>
       </c>
-      <c r="I26" s="22">
+      <c r="I26" s="21">
         <v>3035</v>
       </c>
     </row>
     <row r="27" spans="1:10" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A27" s="19">
+      <c r="A27" s="18">
         <f t="shared" si="0"/>
         <v>25</v>
       </c>
-      <c r="B27" s="22">
+      <c r="B27" s="21">
         <v>2384</v>
       </c>
-      <c r="C27" s="22">
+      <c r="C27" s="21">
         <v>3934</v>
       </c>
-      <c r="D27" s="22">
+      <c r="D27" s="21">
         <v>9011</v>
       </c>
-      <c r="E27" s="22">
+      <c r="E27" s="21">
         <v>10753</v>
       </c>
-      <c r="F27" s="22">
+      <c r="F27" s="21">
         <v>1259</v>
       </c>
-      <c r="G27" s="22">
+      <c r="G27" s="21">
         <v>3371</v>
       </c>
-      <c r="H27" s="22">
+      <c r="H27" s="21">
         <v>334</v>
       </c>
-      <c r="I27" s="22">
+      <c r="I27" s="21">
         <v>3036</v>
       </c>
     </row>
     <row r="28" spans="1:10" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A28" s="19">
+      <c r="A28" s="18">
         <f t="shared" si="0"/>
         <v>26</v>
       </c>
-      <c r="B28" s="22">
+      <c r="B28" s="21">
         <v>2452</v>
       </c>
-      <c r="C28" s="22">
+      <c r="C28" s="21">
         <v>4054</v>
       </c>
-      <c r="D28" s="22">
+      <c r="D28" s="21">
         <v>9015</v>
       </c>
-      <c r="E28" s="22">
+      <c r="E28" s="21">
         <v>10755</v>
       </c>
-      <c r="F28" s="22">
+      <c r="F28" s="21">
         <v>1259</v>
       </c>
-      <c r="G28" s="22">
+      <c r="G28" s="21">
         <v>3379</v>
       </c>
-      <c r="H28" s="22">
+      <c r="H28" s="21">
         <v>336</v>
       </c>
-      <c r="I28" s="22">
+      <c r="I28" s="21">
         <v>3043</v>
       </c>
     </row>
     <row r="29" spans="1:10" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A29" s="19">
+      <c r="A29" s="18">
         <f t="shared" si="0"/>
         <v>27</v>
       </c>
-      <c r="B29" s="22">
+      <c r="B29" s="21">
         <v>2601</v>
       </c>
-      <c r="C29" s="22">
+      <c r="C29" s="21">
         <v>4174</v>
       </c>
-      <c r="D29" s="22">
+      <c r="D29" s="21">
         <v>9017</v>
       </c>
-      <c r="E29" s="22">
+      <c r="E29" s="21">
         <v>10755</v>
       </c>
-      <c r="F29" s="22">
+      <c r="F29" s="21">
         <v>1259</v>
       </c>
-      <c r="G29" s="22">
+      <c r="G29" s="21">
         <v>3384</v>
       </c>
-      <c r="H29" s="22">
+      <c r="H29" s="21">
         <v>336</v>
       </c>
-      <c r="I29" s="22">
+      <c r="I29" s="21">
         <v>3048</v>
       </c>
     </row>
     <row r="30" spans="1:10" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A30" s="19">
+      <c r="A30" s="18">
         <f t="shared" si="0"/>
         <v>28</v>
       </c>
-      <c r="B30" s="22">
+      <c r="B30" s="21">
         <v>2674</v>
       </c>
-      <c r="C30" s="22">
+      <c r="C30" s="21">
         <v>4247</v>
       </c>
-      <c r="D30" s="22">
+      <c r="D30" s="21">
         <v>9020</v>
       </c>
-      <c r="E30" s="22">
+      <c r="E30" s="21">
         <v>10756</v>
       </c>
-      <c r="F30" s="22">
+      <c r="F30" s="21">
         <v>1260</v>
       </c>
-      <c r="G30" s="22">
+      <c r="G30" s="21">
         <v>3390</v>
       </c>
-      <c r="H30" s="22">
+      <c r="H30" s="21">
         <v>337</v>
       </c>
-      <c r="I30" s="22">
+      <c r="I30" s="21">
         <v>3052</v>
       </c>
     </row>
     <row r="31" spans="1:10" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A31" s="19">
+      <c r="A31" s="18">
         <f t="shared" si="0"/>
         <v>29</v>
       </c>
-      <c r="B31" s="22">
+      <c r="B31" s="21">
         <v>2742</v>
       </c>
-      <c r="C31" s="22">
+      <c r="C31" s="21">
         <v>4306</v>
       </c>
-      <c r="D31" s="22">
+      <c r="D31" s="21">
         <v>9020</v>
       </c>
-      <c r="E31" s="22">
+      <c r="E31" s="21">
         <v>10757</v>
       </c>
-      <c r="F31" s="22">
+      <c r="F31" s="21">
         <v>1260</v>
       </c>
-      <c r="G31" s="22">
+      <c r="G31" s="21">
         <v>3395</v>
       </c>
-      <c r="H31" s="22">
+      <c r="H31" s="21">
         <v>338</v>
       </c>
-      <c r="I31" s="22">
+      <c r="I31" s="21">
         <v>3057</v>
       </c>
     </row>
     <row r="32" spans="1:10" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A32" s="19">
+      <c r="A32" s="18">
         <f t="shared" si="0"/>
         <v>30</v>
       </c>
-      <c r="B32" s="22">
+      <c r="B32" s="21">
         <v>2801</v>
       </c>
-      <c r="C32" s="22">
+      <c r="C32" s="21">
         <v>4403</v>
       </c>
-      <c r="D32" s="22">
+      <c r="D32" s="21">
         <v>9034</v>
       </c>
-      <c r="E32" s="22">
+      <c r="E32" s="21">
         <v>10757</v>
       </c>
-      <c r="F32" s="22">
+      <c r="F32" s="21">
         <v>1260</v>
       </c>
-      <c r="G32" s="22">
+      <c r="G32" s="21">
         <v>3402</v>
       </c>
-      <c r="H32" s="22">
+      <c r="H32" s="21">
         <v>338</v>
       </c>
-      <c r="I32" s="22">
+      <c r="I32" s="21">
         <v>3063</v>
       </c>
     </row>
     <row r="33" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A33" s="20">
+      <c r="A33" s="19">
         <f t="shared" si="0"/>
         <v>31</v>
       </c>
-      <c r="B33" s="22">
+      <c r="B33" s="21">
         <v>2812</v>
       </c>
-      <c r="C33" s="22">
+      <c r="C33" s="21">
         <v>4489</v>
       </c>
-      <c r="D33" s="22">
+      <c r="D33" s="21">
         <v>9036</v>
       </c>
-      <c r="E33" s="22">
+      <c r="E33" s="21">
         <v>10758</v>
       </c>
-      <c r="F33" s="22">
+      <c r="F33" s="21">
         <v>1260</v>
       </c>
-      <c r="G33" s="22">
+      <c r="G33" s="21">
         <v>3408</v>
       </c>
-      <c r="H33" s="22">
+      <c r="H33" s="21">
         <v>338</v>
       </c>
-      <c r="I33" s="22">
+      <c r="I33" s="21">
         <v>3069</v>
       </c>
     </row>
     <row r="34" spans="1:9" ht="12.75" x14ac:dyDescent="0.2"/>
     <row r="36" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A36" s="4"/>
-      <c r="B36" s="33"/>
-      <c r="C36" s="32"/>
-      <c r="D36" s="32"/>
-      <c r="E36" s="32"/>
-      <c r="F36" s="32"/>
-      <c r="G36" s="32"/>
-      <c r="H36" s="32"/>
-      <c r="I36" s="32"/>
+      <c r="B36" s="37"/>
+      <c r="C36" s="36"/>
+      <c r="D36" s="36"/>
+      <c r="E36" s="36"/>
+      <c r="F36" s="36"/>
+      <c r="G36" s="36"/>
+      <c r="H36" s="36"/>
+      <c r="I36" s="36"/>
     </row>
     <row r="37" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A37" s="4"/>
@@ -3168,15 +3236,15 @@
       <c r="I70" s="4"/>
     </row>
     <row r="71" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A71" s="33"/>
-      <c r="B71" s="32"/>
-      <c r="C71" s="32"/>
-      <c r="D71" s="32"/>
-      <c r="E71" s="32"/>
-      <c r="F71" s="32"/>
-      <c r="G71" s="32"/>
-      <c r="H71" s="32"/>
-      <c r="I71" s="32"/>
+      <c r="A71" s="37"/>
+      <c r="B71" s="36"/>
+      <c r="C71" s="36"/>
+      <c r="D71" s="36"/>
+      <c r="E71" s="36"/>
+      <c r="F71" s="36"/>
+      <c r="G71" s="36"/>
+      <c r="H71" s="36"/>
+      <c r="I71" s="36"/>
     </row>
     <row r="72" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A72" s="4"/>
@@ -3201,15 +3269,15 @@
       <c r="I73" s="6"/>
     </row>
     <row r="76" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A76" s="31"/>
-      <c r="B76" s="32"/>
-      <c r="C76" s="32"/>
-      <c r="D76" s="32"/>
-      <c r="E76" s="32"/>
-      <c r="F76" s="32"/>
-      <c r="G76" s="32"/>
-      <c r="H76" s="32"/>
-      <c r="I76" s="32"/>
+      <c r="A76" s="35"/>
+      <c r="B76" s="36"/>
+      <c r="C76" s="36"/>
+      <c r="D76" s="36"/>
+      <c r="E76" s="36"/>
+      <c r="F76" s="36"/>
+      <c r="G76" s="36"/>
+      <c r="H76" s="36"/>
+      <c r="I76" s="36"/>
     </row>
     <row r="77" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A77" s="4"/>
@@ -3245,15 +3313,15 @@
       <c r="I79" s="8"/>
     </row>
     <row r="80" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A80" s="34"/>
-      <c r="B80" s="32"/>
-      <c r="C80" s="32"/>
-      <c r="D80" s="32"/>
-      <c r="E80" s="32"/>
-      <c r="F80" s="32"/>
-      <c r="G80" s="32"/>
-      <c r="H80" s="32"/>
-      <c r="I80" s="32"/>
+      <c r="A80" s="38"/>
+      <c r="B80" s="36"/>
+      <c r="C80" s="36"/>
+      <c r="D80" s="36"/>
+      <c r="E80" s="36"/>
+      <c r="F80" s="36"/>
+      <c r="G80" s="36"/>
+      <c r="H80" s="36"/>
+      <c r="I80" s="36"/>
     </row>
     <row r="81" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A81" s="4"/>
@@ -3289,15 +3357,15 @@
       <c r="B86" s="6"/>
     </row>
     <row r="88" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A88" s="31"/>
-      <c r="B88" s="32"/>
-      <c r="C88" s="32"/>
-      <c r="D88" s="32"/>
-      <c r="E88" s="32"/>
-      <c r="F88" s="32"/>
-      <c r="G88" s="32"/>
-      <c r="H88" s="32"/>
-      <c r="I88" s="32"/>
+      <c r="A88" s="35"/>
+      <c r="B88" s="36"/>
+      <c r="C88" s="36"/>
+      <c r="D88" s="36"/>
+      <c r="E88" s="36"/>
+      <c r="F88" s="36"/>
+      <c r="G88" s="36"/>
+      <c r="H88" s="36"/>
+      <c r="I88" s="36"/>
     </row>
     <row r="89" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A89" s="4"/>
@@ -3400,15 +3468,15 @@
       <c r="B99" s="9"/>
     </row>
     <row r="101" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A101" s="33"/>
-      <c r="B101" s="32"/>
-      <c r="C101" s="32"/>
-      <c r="D101" s="32"/>
-      <c r="E101" s="32"/>
-      <c r="F101" s="32"/>
-      <c r="G101" s="32"/>
-      <c r="H101" s="32"/>
-      <c r="I101" s="32"/>
+      <c r="A101" s="37"/>
+      <c r="B101" s="36"/>
+      <c r="C101" s="36"/>
+      <c r="D101" s="36"/>
+      <c r="E101" s="36"/>
+      <c r="F101" s="36"/>
+      <c r="G101" s="36"/>
+      <c r="H101" s="36"/>
+      <c r="I101" s="36"/>
     </row>
     <row r="102" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A102" s="4"/>
@@ -3492,17 +3560,17 @@
       </c>
     </row>
     <row r="2" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A2" s="39">
+      <c r="A2" s="34">
         <v>0</v>
       </c>
-      <c r="B2" s="38"/>
-      <c r="C2" s="38"/>
-      <c r="D2" s="38"/>
-      <c r="E2" s="38"/>
-      <c r="F2" s="38"/>
-      <c r="G2" s="38"/>
-      <c r="H2" s="38"/>
-      <c r="I2" s="38"/>
+      <c r="B2" s="33"/>
+      <c r="C2" s="33"/>
+      <c r="D2" s="33"/>
+      <c r="E2" s="33"/>
+      <c r="F2" s="33"/>
+      <c r="G2" s="33"/>
+      <c r="H2" s="33"/>
+      <c r="I2" s="33"/>
     </row>
     <row r="3" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A3" s="1">
@@ -3899,14 +3967,14 @@
     <row r="31" spans="1:10" ht="12.75" x14ac:dyDescent="0.2"/>
     <row r="33" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A33" s="4"/>
-      <c r="B33" s="33"/>
-      <c r="C33" s="32"/>
-      <c r="D33" s="32"/>
-      <c r="E33" s="32"/>
-      <c r="F33" s="32"/>
-      <c r="G33" s="32"/>
-      <c r="H33" s="32"/>
-      <c r="I33" s="32"/>
+      <c r="B33" s="37"/>
+      <c r="C33" s="36"/>
+      <c r="D33" s="36"/>
+      <c r="E33" s="36"/>
+      <c r="F33" s="36"/>
+      <c r="G33" s="36"/>
+      <c r="H33" s="36"/>
+      <c r="I33" s="36"/>
     </row>
     <row r="34" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A34" s="4"/>
@@ -4283,15 +4351,15 @@
       <c r="I67" s="4"/>
     </row>
     <row r="68" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A68" s="33"/>
-      <c r="B68" s="32"/>
-      <c r="C68" s="32"/>
-      <c r="D68" s="32"/>
-      <c r="E68" s="32"/>
-      <c r="F68" s="32"/>
-      <c r="G68" s="32"/>
-      <c r="H68" s="32"/>
-      <c r="I68" s="32"/>
+      <c r="A68" s="37"/>
+      <c r="B68" s="36"/>
+      <c r="C68" s="36"/>
+      <c r="D68" s="36"/>
+      <c r="E68" s="36"/>
+      <c r="F68" s="36"/>
+      <c r="G68" s="36"/>
+      <c r="H68" s="36"/>
+      <c r="I68" s="36"/>
     </row>
     <row r="69" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A69" s="4"/>
@@ -4316,15 +4384,15 @@
       <c r="I70" s="6"/>
     </row>
     <row r="73" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A73" s="31"/>
-      <c r="B73" s="32"/>
-      <c r="C73" s="32"/>
-      <c r="D73" s="32"/>
-      <c r="E73" s="32"/>
-      <c r="F73" s="32"/>
-      <c r="G73" s="32"/>
-      <c r="H73" s="32"/>
-      <c r="I73" s="32"/>
+      <c r="A73" s="35"/>
+      <c r="B73" s="36"/>
+      <c r="C73" s="36"/>
+      <c r="D73" s="36"/>
+      <c r="E73" s="36"/>
+      <c r="F73" s="36"/>
+      <c r="G73" s="36"/>
+      <c r="H73" s="36"/>
+      <c r="I73" s="36"/>
     </row>
     <row r="74" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A74" s="4"/>
@@ -4360,15 +4428,15 @@
       <c r="I76" s="8"/>
     </row>
     <row r="77" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A77" s="34"/>
-      <c r="B77" s="32"/>
-      <c r="C77" s="32"/>
-      <c r="D77" s="32"/>
-      <c r="E77" s="32"/>
-      <c r="F77" s="32"/>
-      <c r="G77" s="32"/>
-      <c r="H77" s="32"/>
-      <c r="I77" s="32"/>
+      <c r="A77" s="38"/>
+      <c r="B77" s="36"/>
+      <c r="C77" s="36"/>
+      <c r="D77" s="36"/>
+      <c r="E77" s="36"/>
+      <c r="F77" s="36"/>
+      <c r="G77" s="36"/>
+      <c r="H77" s="36"/>
+      <c r="I77" s="36"/>
     </row>
     <row r="78" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A78" s="4"/>
@@ -4404,15 +4472,15 @@
       <c r="B83" s="6"/>
     </row>
     <row r="85" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A85" s="31"/>
-      <c r="B85" s="32"/>
-      <c r="C85" s="32"/>
-      <c r="D85" s="32"/>
-      <c r="E85" s="32"/>
-      <c r="F85" s="32"/>
-      <c r="G85" s="32"/>
-      <c r="H85" s="32"/>
-      <c r="I85" s="32"/>
+      <c r="A85" s="35"/>
+      <c r="B85" s="36"/>
+      <c r="C85" s="36"/>
+      <c r="D85" s="36"/>
+      <c r="E85" s="36"/>
+      <c r="F85" s="36"/>
+      <c r="G85" s="36"/>
+      <c r="H85" s="36"/>
+      <c r="I85" s="36"/>
     </row>
     <row r="86" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A86" s="4"/>
@@ -4515,15 +4583,15 @@
       <c r="B96" s="9"/>
     </row>
     <row r="98" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A98" s="33"/>
-      <c r="B98" s="32"/>
-      <c r="C98" s="32"/>
-      <c r="D98" s="32"/>
-      <c r="E98" s="32"/>
-      <c r="F98" s="32"/>
-      <c r="G98" s="32"/>
-      <c r="H98" s="32"/>
-      <c r="I98" s="32"/>
+      <c r="A98" s="37"/>
+      <c r="B98" s="36"/>
+      <c r="C98" s="36"/>
+      <c r="D98" s="36"/>
+      <c r="E98" s="36"/>
+      <c r="F98" s="36"/>
+      <c r="G98" s="36"/>
+      <c r="H98" s="36"/>
+      <c r="I98" s="36"/>
     </row>
     <row r="99" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A99" s="4"/>
@@ -4606,17 +4674,17 @@
       </c>
     </row>
     <row r="2" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A2" s="39">
+      <c r="A2" s="34">
         <v>0</v>
       </c>
-      <c r="B2" s="38"/>
-      <c r="C2" s="38"/>
-      <c r="D2" s="38"/>
-      <c r="E2" s="38"/>
-      <c r="F2" s="38"/>
-      <c r="G2" s="38"/>
-      <c r="H2" s="38"/>
-      <c r="I2" s="38"/>
+      <c r="B2" s="33"/>
+      <c r="C2" s="33"/>
+      <c r="D2" s="33"/>
+      <c r="E2" s="33"/>
+      <c r="F2" s="33"/>
+      <c r="G2" s="33"/>
+      <c r="H2" s="33"/>
+      <c r="I2" s="33"/>
     </row>
     <row r="3" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A3" s="1">
@@ -5055,14 +5123,14 @@
     <row r="34" spans="1:9" ht="12.75" x14ac:dyDescent="0.2"/>
     <row r="36" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A36" s="4"/>
-      <c r="B36" s="33"/>
-      <c r="C36" s="32"/>
-      <c r="D36" s="32"/>
-      <c r="E36" s="32"/>
-      <c r="F36" s="32"/>
-      <c r="G36" s="32"/>
-      <c r="H36" s="32"/>
-      <c r="I36" s="32"/>
+      <c r="B36" s="37"/>
+      <c r="C36" s="36"/>
+      <c r="D36" s="36"/>
+      <c r="E36" s="36"/>
+      <c r="F36" s="36"/>
+      <c r="G36" s="36"/>
+      <c r="H36" s="36"/>
+      <c r="I36" s="36"/>
     </row>
     <row r="37" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A37" s="4"/>
@@ -5439,15 +5507,15 @@
       <c r="I70" s="4"/>
     </row>
     <row r="71" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A71" s="33"/>
-      <c r="B71" s="32"/>
-      <c r="C71" s="32"/>
-      <c r="D71" s="32"/>
-      <c r="E71" s="32"/>
-      <c r="F71" s="32"/>
-      <c r="G71" s="32"/>
-      <c r="H71" s="32"/>
-      <c r="I71" s="32"/>
+      <c r="A71" s="37"/>
+      <c r="B71" s="36"/>
+      <c r="C71" s="36"/>
+      <c r="D71" s="36"/>
+      <c r="E71" s="36"/>
+      <c r="F71" s="36"/>
+      <c r="G71" s="36"/>
+      <c r="H71" s="36"/>
+      <c r="I71" s="36"/>
     </row>
     <row r="72" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A72" s="4"/>
@@ -5472,15 +5540,15 @@
       <c r="I73" s="6"/>
     </row>
     <row r="76" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A76" s="31"/>
-      <c r="B76" s="32"/>
-      <c r="C76" s="32"/>
-      <c r="D76" s="32"/>
-      <c r="E76" s="32"/>
-      <c r="F76" s="32"/>
-      <c r="G76" s="32"/>
-      <c r="H76" s="32"/>
-      <c r="I76" s="32"/>
+      <c r="A76" s="35"/>
+      <c r="B76" s="36"/>
+      <c r="C76" s="36"/>
+      <c r="D76" s="36"/>
+      <c r="E76" s="36"/>
+      <c r="F76" s="36"/>
+      <c r="G76" s="36"/>
+      <c r="H76" s="36"/>
+      <c r="I76" s="36"/>
     </row>
     <row r="77" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A77" s="4"/>
@@ -5516,15 +5584,15 @@
       <c r="I79" s="8"/>
     </row>
     <row r="80" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A80" s="34"/>
-      <c r="B80" s="32"/>
-      <c r="C80" s="32"/>
-      <c r="D80" s="32"/>
-      <c r="E80" s="32"/>
-      <c r="F80" s="32"/>
-      <c r="G80" s="32"/>
-      <c r="H80" s="32"/>
-      <c r="I80" s="32"/>
+      <c r="A80" s="38"/>
+      <c r="B80" s="36"/>
+      <c r="C80" s="36"/>
+      <c r="D80" s="36"/>
+      <c r="E80" s="36"/>
+      <c r="F80" s="36"/>
+      <c r="G80" s="36"/>
+      <c r="H80" s="36"/>
+      <c r="I80" s="36"/>
     </row>
     <row r="81" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A81" s="4"/>
@@ -5560,15 +5628,15 @@
       <c r="B86" s="6"/>
     </row>
     <row r="88" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A88" s="31"/>
-      <c r="B88" s="32"/>
-      <c r="C88" s="32"/>
-      <c r="D88" s="32"/>
-      <c r="E88" s="32"/>
-      <c r="F88" s="32"/>
-      <c r="G88" s="32"/>
-      <c r="H88" s="32"/>
-      <c r="I88" s="32"/>
+      <c r="A88" s="35"/>
+      <c r="B88" s="36"/>
+      <c r="C88" s="36"/>
+      <c r="D88" s="36"/>
+      <c r="E88" s="36"/>
+      <c r="F88" s="36"/>
+      <c r="G88" s="36"/>
+      <c r="H88" s="36"/>
+      <c r="I88" s="36"/>
     </row>
     <row r="89" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A89" s="4"/>
@@ -5671,15 +5739,15 @@
       <c r="B99" s="9"/>
     </row>
     <row r="101" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A101" s="33"/>
-      <c r="B101" s="32"/>
-      <c r="C101" s="32"/>
-      <c r="D101" s="32"/>
-      <c r="E101" s="32"/>
-      <c r="F101" s="32"/>
-      <c r="G101" s="32"/>
-      <c r="H101" s="32"/>
-      <c r="I101" s="32"/>
+      <c r="A101" s="37"/>
+      <c r="B101" s="36"/>
+      <c r="C101" s="36"/>
+      <c r="D101" s="36"/>
+      <c r="E101" s="36"/>
+      <c r="F101" s="36"/>
+      <c r="G101" s="36"/>
+      <c r="H101" s="36"/>
+      <c r="I101" s="36"/>
     </row>
     <row r="102" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A102" s="4"/>
@@ -5717,6 +5785,60 @@
       <formula1>"Bandeira,Verde,Amarela,Vermelha p1,Vermelha p2"</formula1>
     </dataValidation>
   </dataValidations>
+  <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{95ECE5E3-60F9-4CA5-88B7-AB46BB9D8812}">
+  <dimension ref="A1:B5"/>
+  <sheetFormatPr defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="1" max="1" width="13.140625" customWidth="1"/>
+    <col min="2" max="2" width="9.5703125" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A1" s="25" t="s">
+        <v>9</v>
+      </c>
+      <c r="B1" s="25" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A2" s="39" t="s">
+        <v>12</v>
+      </c>
+      <c r="B2" s="40">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A3" s="39" t="s">
+        <v>13</v>
+      </c>
+      <c r="B3" s="40">
+        <v>1.885</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A4" s="39" t="s">
+        <v>10</v>
+      </c>
+      <c r="B4" s="40">
+        <v>4.4630000000000001</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A5" s="39" t="s">
+        <v>14</v>
+      </c>
+      <c r="B5" s="40">
+        <v>7.8769999999999998</v>
+      </c>
+    </row>
+  </sheetData>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
 </worksheet>
 </file>
@@ -5770,17 +5892,17 @@
       </c>
     </row>
     <row r="2" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A2" s="39">
+      <c r="A2" s="34">
         <v>0</v>
       </c>
-      <c r="B2" s="38"/>
-      <c r="C2" s="38"/>
-      <c r="D2" s="38"/>
-      <c r="E2" s="38"/>
-      <c r="F2" s="38"/>
-      <c r="G2" s="38"/>
-      <c r="H2" s="38"/>
-      <c r="I2" s="38"/>
+      <c r="B2" s="33"/>
+      <c r="C2" s="33"/>
+      <c r="D2" s="33"/>
+      <c r="E2" s="33"/>
+      <c r="F2" s="33"/>
+      <c r="G2" s="33"/>
+      <c r="H2" s="33"/>
+      <c r="I2" s="33"/>
     </row>
     <row r="3" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A3" s="1">
@@ -6205,14 +6327,14 @@
     <row r="33" spans="1:9" ht="12.75" x14ac:dyDescent="0.2"/>
     <row r="35" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A35" s="4"/>
-      <c r="B35" s="33"/>
-      <c r="C35" s="32"/>
-      <c r="D35" s="32"/>
-      <c r="E35" s="32"/>
-      <c r="F35" s="32"/>
-      <c r="G35" s="32"/>
-      <c r="H35" s="32"/>
-      <c r="I35" s="32"/>
+      <c r="B35" s="37"/>
+      <c r="C35" s="36"/>
+      <c r="D35" s="36"/>
+      <c r="E35" s="36"/>
+      <c r="F35" s="36"/>
+      <c r="G35" s="36"/>
+      <c r="H35" s="36"/>
+      <c r="I35" s="36"/>
     </row>
     <row r="36" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A36" s="4"/>
@@ -6590,15 +6712,15 @@
       <c r="I69" s="4"/>
     </row>
     <row r="70" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A70" s="33"/>
-      <c r="B70" s="32"/>
-      <c r="C70" s="32"/>
-      <c r="D70" s="32"/>
-      <c r="E70" s="32"/>
-      <c r="F70" s="32"/>
-      <c r="G70" s="32"/>
-      <c r="H70" s="32"/>
-      <c r="I70" s="32"/>
+      <c r="A70" s="37"/>
+      <c r="B70" s="36"/>
+      <c r="C70" s="36"/>
+      <c r="D70" s="36"/>
+      <c r="E70" s="36"/>
+      <c r="F70" s="36"/>
+      <c r="G70" s="36"/>
+      <c r="H70" s="36"/>
+      <c r="I70" s="36"/>
     </row>
     <row r="71" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A71" s="4"/>
@@ -6623,15 +6745,15 @@
       <c r="I72" s="6"/>
     </row>
     <row r="75" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A75" s="31"/>
-      <c r="B75" s="32"/>
-      <c r="C75" s="32"/>
-      <c r="D75" s="32"/>
-      <c r="E75" s="32"/>
-      <c r="F75" s="32"/>
-      <c r="G75" s="32"/>
-      <c r="H75" s="32"/>
-      <c r="I75" s="32"/>
+      <c r="A75" s="35"/>
+      <c r="B75" s="36"/>
+      <c r="C75" s="36"/>
+      <c r="D75" s="36"/>
+      <c r="E75" s="36"/>
+      <c r="F75" s="36"/>
+      <c r="G75" s="36"/>
+      <c r="H75" s="36"/>
+      <c r="I75" s="36"/>
     </row>
     <row r="76" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A76" s="4"/>
@@ -6667,15 +6789,15 @@
       <c r="I78" s="8"/>
     </row>
     <row r="79" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A79" s="34"/>
-      <c r="B79" s="32"/>
-      <c r="C79" s="32"/>
-      <c r="D79" s="32"/>
-      <c r="E79" s="32"/>
-      <c r="F79" s="32"/>
-      <c r="G79" s="32"/>
-      <c r="H79" s="32"/>
-      <c r="I79" s="32"/>
+      <c r="A79" s="38"/>
+      <c r="B79" s="36"/>
+      <c r="C79" s="36"/>
+      <c r="D79" s="36"/>
+      <c r="E79" s="36"/>
+      <c r="F79" s="36"/>
+      <c r="G79" s="36"/>
+      <c r="H79" s="36"/>
+      <c r="I79" s="36"/>
     </row>
     <row r="80" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A80" s="4"/>
@@ -6711,15 +6833,15 @@
       <c r="B85" s="6"/>
     </row>
     <row r="87" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A87" s="31"/>
-      <c r="B87" s="32"/>
-      <c r="C87" s="32"/>
-      <c r="D87" s="32"/>
-      <c r="E87" s="32"/>
-      <c r="F87" s="32"/>
-      <c r="G87" s="32"/>
-      <c r="H87" s="32"/>
-      <c r="I87" s="32"/>
+      <c r="A87" s="35"/>
+      <c r="B87" s="36"/>
+      <c r="C87" s="36"/>
+      <c r="D87" s="36"/>
+      <c r="E87" s="36"/>
+      <c r="F87" s="36"/>
+      <c r="G87" s="36"/>
+      <c r="H87" s="36"/>
+      <c r="I87" s="36"/>
     </row>
     <row r="88" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A88" s="4"/>
@@ -6822,15 +6944,15 @@
       <c r="B98" s="9"/>
     </row>
     <row r="100" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A100" s="33"/>
-      <c r="B100" s="32"/>
-      <c r="C100" s="32"/>
-      <c r="D100" s="32"/>
-      <c r="E100" s="32"/>
-      <c r="F100" s="32"/>
-      <c r="G100" s="32"/>
-      <c r="H100" s="32"/>
-      <c r="I100" s="32"/>
+      <c r="A100" s="37"/>
+      <c r="B100" s="36"/>
+      <c r="C100" s="36"/>
+      <c r="D100" s="36"/>
+      <c r="E100" s="36"/>
+      <c r="F100" s="36"/>
+      <c r="G100" s="36"/>
+      <c r="H100" s="36"/>
+      <c r="I100" s="36"/>
     </row>
     <row r="101" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A101" s="4"/>
@@ -6921,17 +7043,17 @@
       </c>
     </row>
     <row r="2" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A2" s="39">
+      <c r="A2" s="34">
         <v>0</v>
       </c>
-      <c r="B2" s="38"/>
-      <c r="C2" s="38"/>
-      <c r="D2" s="38"/>
-      <c r="E2" s="38"/>
-      <c r="F2" s="38"/>
-      <c r="G2" s="38"/>
-      <c r="H2" s="38"/>
-      <c r="I2" s="38"/>
+      <c r="B2" s="33"/>
+      <c r="C2" s="33"/>
+      <c r="D2" s="33"/>
+      <c r="E2" s="33"/>
+      <c r="F2" s="33"/>
+      <c r="G2" s="33"/>
+      <c r="H2" s="33"/>
+      <c r="I2" s="33"/>
     </row>
     <row r="3" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A3" s="1">
@@ -7370,14 +7492,14 @@
     <row r="34" spans="1:9" ht="12.75" x14ac:dyDescent="0.2"/>
     <row r="36" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A36" s="4"/>
-      <c r="B36" s="33"/>
-      <c r="C36" s="32"/>
-      <c r="D36" s="32"/>
-      <c r="E36" s="32"/>
-      <c r="F36" s="32"/>
-      <c r="G36" s="32"/>
-      <c r="H36" s="32"/>
-      <c r="I36" s="32"/>
+      <c r="B36" s="37"/>
+      <c r="C36" s="36"/>
+      <c r="D36" s="36"/>
+      <c r="E36" s="36"/>
+      <c r="F36" s="36"/>
+      <c r="G36" s="36"/>
+      <c r="H36" s="36"/>
+      <c r="I36" s="36"/>
     </row>
     <row r="37" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A37" s="4"/>
@@ -7755,15 +7877,15 @@
       <c r="I70" s="4"/>
     </row>
     <row r="71" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A71" s="33"/>
-      <c r="B71" s="32"/>
-      <c r="C71" s="32"/>
-      <c r="D71" s="32"/>
-      <c r="E71" s="32"/>
-      <c r="F71" s="32"/>
-      <c r="G71" s="32"/>
-      <c r="H71" s="32"/>
-      <c r="I71" s="32"/>
+      <c r="A71" s="37"/>
+      <c r="B71" s="36"/>
+      <c r="C71" s="36"/>
+      <c r="D71" s="36"/>
+      <c r="E71" s="36"/>
+      <c r="F71" s="36"/>
+      <c r="G71" s="36"/>
+      <c r="H71" s="36"/>
+      <c r="I71" s="36"/>
     </row>
     <row r="72" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A72" s="4"/>
@@ -7788,15 +7910,15 @@
       <c r="I73" s="6"/>
     </row>
     <row r="76" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A76" s="31"/>
-      <c r="B76" s="32"/>
-      <c r="C76" s="32"/>
-      <c r="D76" s="32"/>
-      <c r="E76" s="32"/>
-      <c r="F76" s="32"/>
-      <c r="G76" s="32"/>
-      <c r="H76" s="32"/>
-      <c r="I76" s="32"/>
+      <c r="A76" s="35"/>
+      <c r="B76" s="36"/>
+      <c r="C76" s="36"/>
+      <c r="D76" s="36"/>
+      <c r="E76" s="36"/>
+      <c r="F76" s="36"/>
+      <c r="G76" s="36"/>
+      <c r="H76" s="36"/>
+      <c r="I76" s="36"/>
     </row>
     <row r="77" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A77" s="4"/>
@@ -7832,15 +7954,15 @@
       <c r="I79" s="8"/>
     </row>
     <row r="80" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A80" s="34"/>
-      <c r="B80" s="32"/>
-      <c r="C80" s="32"/>
-      <c r="D80" s="32"/>
-      <c r="E80" s="32"/>
-      <c r="F80" s="32"/>
-      <c r="G80" s="32"/>
-      <c r="H80" s="32"/>
-      <c r="I80" s="32"/>
+      <c r="A80" s="38"/>
+      <c r="B80" s="36"/>
+      <c r="C80" s="36"/>
+      <c r="D80" s="36"/>
+      <c r="E80" s="36"/>
+      <c r="F80" s="36"/>
+      <c r="G80" s="36"/>
+      <c r="H80" s="36"/>
+      <c r="I80" s="36"/>
     </row>
     <row r="81" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A81" s="4"/>
@@ -7876,15 +7998,15 @@
       <c r="B86" s="6"/>
     </row>
     <row r="88" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A88" s="31"/>
-      <c r="B88" s="32"/>
-      <c r="C88" s="32"/>
-      <c r="D88" s="32"/>
-      <c r="E88" s="32"/>
-      <c r="F88" s="32"/>
-      <c r="G88" s="32"/>
-      <c r="H88" s="32"/>
-      <c r="I88" s="32"/>
+      <c r="A88" s="35"/>
+      <c r="B88" s="36"/>
+      <c r="C88" s="36"/>
+      <c r="D88" s="36"/>
+      <c r="E88" s="36"/>
+      <c r="F88" s="36"/>
+      <c r="G88" s="36"/>
+      <c r="H88" s="36"/>
+      <c r="I88" s="36"/>
     </row>
     <row r="89" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A89" s="4"/>
@@ -7987,15 +8109,15 @@
       <c r="B99" s="9"/>
     </row>
     <row r="101" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A101" s="33"/>
-      <c r="B101" s="32"/>
-      <c r="C101" s="32"/>
-      <c r="D101" s="32"/>
-      <c r="E101" s="32"/>
-      <c r="F101" s="32"/>
-      <c r="G101" s="32"/>
-      <c r="H101" s="32"/>
-      <c r="I101" s="32"/>
+      <c r="A101" s="37"/>
+      <c r="B101" s="36"/>
+      <c r="C101" s="36"/>
+      <c r="D101" s="36"/>
+      <c r="E101" s="36"/>
+      <c r="F101" s="36"/>
+      <c r="G101" s="36"/>
+      <c r="H101" s="36"/>
+      <c r="I101" s="36"/>
     </row>
     <row r="102" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A102" s="4"/>
@@ -8086,17 +8208,17 @@
       </c>
     </row>
     <row r="2" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A2" s="39">
+      <c r="A2" s="34">
         <v>0</v>
       </c>
-      <c r="B2" s="38"/>
-      <c r="C2" s="38"/>
-      <c r="D2" s="38"/>
-      <c r="E2" s="38"/>
-      <c r="F2" s="38"/>
-      <c r="G2" s="38"/>
-      <c r="H2" s="38"/>
-      <c r="I2" s="38"/>
+      <c r="B2" s="33"/>
+      <c r="C2" s="33"/>
+      <c r="D2" s="33"/>
+      <c r="E2" s="33"/>
+      <c r="F2" s="33"/>
+      <c r="G2" s="33"/>
+      <c r="H2" s="33"/>
+      <c r="I2" s="33"/>
     </row>
     <row r="3" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A3" s="1">
@@ -8521,14 +8643,14 @@
     <row r="33" spans="1:9" ht="12.75" x14ac:dyDescent="0.2"/>
     <row r="35" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A35" s="4"/>
-      <c r="B35" s="33"/>
-      <c r="C35" s="32"/>
-      <c r="D35" s="32"/>
-      <c r="E35" s="32"/>
-      <c r="F35" s="32"/>
-      <c r="G35" s="32"/>
-      <c r="H35" s="32"/>
-      <c r="I35" s="32"/>
+      <c r="B35" s="37"/>
+      <c r="C35" s="36"/>
+      <c r="D35" s="36"/>
+      <c r="E35" s="36"/>
+      <c r="F35" s="36"/>
+      <c r="G35" s="36"/>
+      <c r="H35" s="36"/>
+      <c r="I35" s="36"/>
     </row>
     <row r="36" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A36" s="4"/>
@@ -8906,15 +9028,15 @@
       <c r="I69" s="4"/>
     </row>
     <row r="70" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A70" s="33"/>
-      <c r="B70" s="32"/>
-      <c r="C70" s="32"/>
-      <c r="D70" s="32"/>
-      <c r="E70" s="32"/>
-      <c r="F70" s="32"/>
-      <c r="G70" s="32"/>
-      <c r="H70" s="32"/>
-      <c r="I70" s="32"/>
+      <c r="A70" s="37"/>
+      <c r="B70" s="36"/>
+      <c r="C70" s="36"/>
+      <c r="D70" s="36"/>
+      <c r="E70" s="36"/>
+      <c r="F70" s="36"/>
+      <c r="G70" s="36"/>
+      <c r="H70" s="36"/>
+      <c r="I70" s="36"/>
     </row>
     <row r="71" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A71" s="4"/>
@@ -8939,15 +9061,15 @@
       <c r="I72" s="6"/>
     </row>
     <row r="75" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A75" s="31"/>
-      <c r="B75" s="32"/>
-      <c r="C75" s="32"/>
-      <c r="D75" s="32"/>
-      <c r="E75" s="32"/>
-      <c r="F75" s="32"/>
-      <c r="G75" s="32"/>
-      <c r="H75" s="32"/>
-      <c r="I75" s="32"/>
+      <c r="A75" s="35"/>
+      <c r="B75" s="36"/>
+      <c r="C75" s="36"/>
+      <c r="D75" s="36"/>
+      <c r="E75" s="36"/>
+      <c r="F75" s="36"/>
+      <c r="G75" s="36"/>
+      <c r="H75" s="36"/>
+      <c r="I75" s="36"/>
     </row>
     <row r="76" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A76" s="4"/>
@@ -8983,15 +9105,15 @@
       <c r="I78" s="8"/>
     </row>
     <row r="79" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A79" s="34"/>
-      <c r="B79" s="32"/>
-      <c r="C79" s="32"/>
-      <c r="D79" s="32"/>
-      <c r="E79" s="32"/>
-      <c r="F79" s="32"/>
-      <c r="G79" s="32"/>
-      <c r="H79" s="32"/>
-      <c r="I79" s="32"/>
+      <c r="A79" s="38"/>
+      <c r="B79" s="36"/>
+      <c r="C79" s="36"/>
+      <c r="D79" s="36"/>
+      <c r="E79" s="36"/>
+      <c r="F79" s="36"/>
+      <c r="G79" s="36"/>
+      <c r="H79" s="36"/>
+      <c r="I79" s="36"/>
     </row>
     <row r="80" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A80" s="4"/>
@@ -9027,15 +9149,15 @@
       <c r="B85" s="6"/>
     </row>
     <row r="87" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A87" s="31"/>
-      <c r="B87" s="32"/>
-      <c r="C87" s="32"/>
-      <c r="D87" s="32"/>
-      <c r="E87" s="32"/>
-      <c r="F87" s="32"/>
-      <c r="G87" s="32"/>
-      <c r="H87" s="32"/>
-      <c r="I87" s="32"/>
+      <c r="A87" s="35"/>
+      <c r="B87" s="36"/>
+      <c r="C87" s="36"/>
+      <c r="D87" s="36"/>
+      <c r="E87" s="36"/>
+      <c r="F87" s="36"/>
+      <c r="G87" s="36"/>
+      <c r="H87" s="36"/>
+      <c r="I87" s="36"/>
     </row>
     <row r="88" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A88" s="4"/>
@@ -9138,15 +9260,15 @@
       <c r="B98" s="9"/>
     </row>
     <row r="100" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A100" s="33"/>
-      <c r="B100" s="32"/>
-      <c r="C100" s="32"/>
-      <c r="D100" s="32"/>
-      <c r="E100" s="32"/>
-      <c r="F100" s="32"/>
-      <c r="G100" s="32"/>
-      <c r="H100" s="32"/>
-      <c r="I100" s="32"/>
+      <c r="A100" s="37"/>
+      <c r="B100" s="36"/>
+      <c r="C100" s="36"/>
+      <c r="D100" s="36"/>
+      <c r="E100" s="36"/>
+      <c r="F100" s="36"/>
+      <c r="G100" s="36"/>
+      <c r="H100" s="36"/>
+      <c r="I100" s="36"/>
     </row>
     <row r="101" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A101" s="4"/>
@@ -9237,17 +9359,17 @@
       </c>
     </row>
     <row r="2" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A2" s="39">
+      <c r="A2" s="34">
         <v>0</v>
       </c>
-      <c r="B2" s="38"/>
-      <c r="C2" s="38"/>
-      <c r="D2" s="38"/>
-      <c r="E2" s="38"/>
-      <c r="F2" s="38"/>
-      <c r="G2" s="38"/>
-      <c r="H2" s="38"/>
-      <c r="I2" s="38"/>
+      <c r="B2" s="33"/>
+      <c r="C2" s="33"/>
+      <c r="D2" s="33"/>
+      <c r="E2" s="33"/>
+      <c r="F2" s="33"/>
+      <c r="G2" s="33"/>
+      <c r="H2" s="33"/>
+      <c r="I2" s="33"/>
     </row>
     <row r="3" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A3" s="1">
@@ -9685,14 +9807,14 @@
     </row>
     <row r="35" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A35" s="4"/>
-      <c r="B35" s="33"/>
-      <c r="C35" s="32"/>
-      <c r="D35" s="32"/>
-      <c r="E35" s="32"/>
-      <c r="F35" s="32"/>
-      <c r="G35" s="32"/>
-      <c r="H35" s="32"/>
-      <c r="I35" s="32"/>
+      <c r="B35" s="37"/>
+      <c r="C35" s="36"/>
+      <c r="D35" s="36"/>
+      <c r="E35" s="36"/>
+      <c r="F35" s="36"/>
+      <c r="G35" s="36"/>
+      <c r="H35" s="36"/>
+      <c r="I35" s="36"/>
     </row>
     <row r="36" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A36" s="4"/>
@@ -10070,15 +10192,15 @@
       <c r="I69" s="4"/>
     </row>
     <row r="70" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A70" s="33"/>
-      <c r="B70" s="32"/>
-      <c r="C70" s="32"/>
-      <c r="D70" s="32"/>
-      <c r="E70" s="32"/>
-      <c r="F70" s="32"/>
-      <c r="G70" s="32"/>
-      <c r="H70" s="32"/>
-      <c r="I70" s="32"/>
+      <c r="A70" s="37"/>
+      <c r="B70" s="36"/>
+      <c r="C70" s="36"/>
+      <c r="D70" s="36"/>
+      <c r="E70" s="36"/>
+      <c r="F70" s="36"/>
+      <c r="G70" s="36"/>
+      <c r="H70" s="36"/>
+      <c r="I70" s="36"/>
     </row>
     <row r="71" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A71" s="4"/>
@@ -10103,15 +10225,15 @@
       <c r="I72" s="6"/>
     </row>
     <row r="75" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A75" s="31"/>
-      <c r="B75" s="32"/>
-      <c r="C75" s="32"/>
-      <c r="D75" s="32"/>
-      <c r="E75" s="32"/>
-      <c r="F75" s="32"/>
-      <c r="G75" s="32"/>
-      <c r="H75" s="32"/>
-      <c r="I75" s="32"/>
+      <c r="A75" s="35"/>
+      <c r="B75" s="36"/>
+      <c r="C75" s="36"/>
+      <c r="D75" s="36"/>
+      <c r="E75" s="36"/>
+      <c r="F75" s="36"/>
+      <c r="G75" s="36"/>
+      <c r="H75" s="36"/>
+      <c r="I75" s="36"/>
     </row>
     <row r="76" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A76" s="4"/>
@@ -10147,15 +10269,15 @@
       <c r="I78" s="8"/>
     </row>
     <row r="79" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A79" s="34"/>
-      <c r="B79" s="32"/>
-      <c r="C79" s="32"/>
-      <c r="D79" s="32"/>
-      <c r="E79" s="32"/>
-      <c r="F79" s="32"/>
-      <c r="G79" s="32"/>
-      <c r="H79" s="32"/>
-      <c r="I79" s="32"/>
+      <c r="A79" s="38"/>
+      <c r="B79" s="36"/>
+      <c r="C79" s="36"/>
+      <c r="D79" s="36"/>
+      <c r="E79" s="36"/>
+      <c r="F79" s="36"/>
+      <c r="G79" s="36"/>
+      <c r="H79" s="36"/>
+      <c r="I79" s="36"/>
     </row>
     <row r="80" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A80" s="4"/>
@@ -10191,15 +10313,15 @@
       <c r="B85" s="6"/>
     </row>
     <row r="87" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A87" s="31"/>
-      <c r="B87" s="32"/>
-      <c r="C87" s="32"/>
-      <c r="D87" s="32"/>
-      <c r="E87" s="32"/>
-      <c r="F87" s="32"/>
-      <c r="G87" s="32"/>
-      <c r="H87" s="32"/>
-      <c r="I87" s="32"/>
+      <c r="A87" s="35"/>
+      <c r="B87" s="36"/>
+      <c r="C87" s="36"/>
+      <c r="D87" s="36"/>
+      <c r="E87" s="36"/>
+      <c r="F87" s="36"/>
+      <c r="G87" s="36"/>
+      <c r="H87" s="36"/>
+      <c r="I87" s="36"/>
     </row>
     <row r="88" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A88" s="4"/>
@@ -10302,15 +10424,15 @@
       <c r="B98" s="9"/>
     </row>
     <row r="100" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A100" s="33"/>
-      <c r="B100" s="32"/>
-      <c r="C100" s="32"/>
-      <c r="D100" s="32"/>
-      <c r="E100" s="32"/>
-      <c r="F100" s="32"/>
-      <c r="G100" s="32"/>
-      <c r="H100" s="32"/>
-      <c r="I100" s="32"/>
+      <c r="A100" s="37"/>
+      <c r="B100" s="36"/>
+      <c r="C100" s="36"/>
+      <c r="D100" s="36"/>
+      <c r="E100" s="36"/>
+      <c r="F100" s="36"/>
+      <c r="G100" s="36"/>
+      <c r="H100" s="36"/>
+      <c r="I100" s="36"/>
     </row>
     <row r="101" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A101" s="4"/>
@@ -10401,17 +10523,17 @@
       </c>
     </row>
     <row r="2" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A2" s="39">
+      <c r="A2" s="34">
         <v>0</v>
       </c>
-      <c r="B2" s="38"/>
-      <c r="C2" s="38"/>
-      <c r="D2" s="38"/>
-      <c r="E2" s="38"/>
-      <c r="F2" s="38"/>
-      <c r="G2" s="38"/>
-      <c r="H2" s="38"/>
-      <c r="I2" s="38"/>
+      <c r="B2" s="33"/>
+      <c r="C2" s="33"/>
+      <c r="D2" s="33"/>
+      <c r="E2" s="33"/>
+      <c r="F2" s="33"/>
+      <c r="G2" s="33"/>
+      <c r="H2" s="33"/>
+      <c r="I2" s="33"/>
     </row>
     <row r="3" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A3" s="1">
@@ -10849,14 +10971,14 @@
     </row>
     <row r="36" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A36" s="4"/>
-      <c r="B36" s="33"/>
-      <c r="C36" s="32"/>
-      <c r="D36" s="32"/>
-      <c r="E36" s="32"/>
-      <c r="F36" s="32"/>
-      <c r="G36" s="32"/>
-      <c r="H36" s="32"/>
-      <c r="I36" s="32"/>
+      <c r="B36" s="37"/>
+      <c r="C36" s="36"/>
+      <c r="D36" s="36"/>
+      <c r="E36" s="36"/>
+      <c r="F36" s="36"/>
+      <c r="G36" s="36"/>
+      <c r="H36" s="36"/>
+      <c r="I36" s="36"/>
     </row>
     <row r="37" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A37" s="4"/>
@@ -11234,15 +11356,15 @@
       <c r="I70" s="4"/>
     </row>
     <row r="71" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A71" s="33"/>
-      <c r="B71" s="32"/>
-      <c r="C71" s="32"/>
-      <c r="D71" s="32"/>
-      <c r="E71" s="32"/>
-      <c r="F71" s="32"/>
-      <c r="G71" s="32"/>
-      <c r="H71" s="32"/>
-      <c r="I71" s="32"/>
+      <c r="A71" s="37"/>
+      <c r="B71" s="36"/>
+      <c r="C71" s="36"/>
+      <c r="D71" s="36"/>
+      <c r="E71" s="36"/>
+      <c r="F71" s="36"/>
+      <c r="G71" s="36"/>
+      <c r="H71" s="36"/>
+      <c r="I71" s="36"/>
     </row>
     <row r="72" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A72" s="4"/>
@@ -11267,15 +11389,15 @@
       <c r="I73" s="6"/>
     </row>
     <row r="76" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A76" s="31"/>
-      <c r="B76" s="32"/>
-      <c r="C76" s="32"/>
-      <c r="D76" s="32"/>
-      <c r="E76" s="32"/>
-      <c r="F76" s="32"/>
-      <c r="G76" s="32"/>
-      <c r="H76" s="32"/>
-      <c r="I76" s="32"/>
+      <c r="A76" s="35"/>
+      <c r="B76" s="36"/>
+      <c r="C76" s="36"/>
+      <c r="D76" s="36"/>
+      <c r="E76" s="36"/>
+      <c r="F76" s="36"/>
+      <c r="G76" s="36"/>
+      <c r="H76" s="36"/>
+      <c r="I76" s="36"/>
     </row>
     <row r="77" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A77" s="4"/>
@@ -11311,15 +11433,15 @@
       <c r="I79" s="8"/>
     </row>
     <row r="80" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A80" s="34"/>
-      <c r="B80" s="32"/>
-      <c r="C80" s="32"/>
-      <c r="D80" s="32"/>
-      <c r="E80" s="32"/>
-      <c r="F80" s="32"/>
-      <c r="G80" s="32"/>
-      <c r="H80" s="32"/>
-      <c r="I80" s="32"/>
+      <c r="A80" s="38"/>
+      <c r="B80" s="36"/>
+      <c r="C80" s="36"/>
+      <c r="D80" s="36"/>
+      <c r="E80" s="36"/>
+      <c r="F80" s="36"/>
+      <c r="G80" s="36"/>
+      <c r="H80" s="36"/>
+      <c r="I80" s="36"/>
     </row>
     <row r="81" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A81" s="4"/>
@@ -11355,15 +11477,15 @@
       <c r="B86" s="6"/>
     </row>
     <row r="88" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A88" s="31"/>
-      <c r="B88" s="32"/>
-      <c r="C88" s="32"/>
-      <c r="D88" s="32"/>
-      <c r="E88" s="32"/>
-      <c r="F88" s="32"/>
-      <c r="G88" s="32"/>
-      <c r="H88" s="32"/>
-      <c r="I88" s="32"/>
+      <c r="A88" s="35"/>
+      <c r="B88" s="36"/>
+      <c r="C88" s="36"/>
+      <c r="D88" s="36"/>
+      <c r="E88" s="36"/>
+      <c r="F88" s="36"/>
+      <c r="G88" s="36"/>
+      <c r="H88" s="36"/>
+      <c r="I88" s="36"/>
     </row>
     <row r="89" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A89" s="4"/>
@@ -11466,15 +11588,15 @@
       <c r="B99" s="9"/>
     </row>
     <row r="101" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A101" s="33"/>
-      <c r="B101" s="32"/>
-      <c r="C101" s="32"/>
-      <c r="D101" s="32"/>
-      <c r="E101" s="32"/>
-      <c r="F101" s="32"/>
-      <c r="G101" s="32"/>
-      <c r="H101" s="32"/>
-      <c r="I101" s="32"/>
+      <c r="A101" s="37"/>
+      <c r="B101" s="36"/>
+      <c r="C101" s="36"/>
+      <c r="D101" s="36"/>
+      <c r="E101" s="36"/>
+      <c r="F101" s="36"/>
+      <c r="G101" s="36"/>
+      <c r="H101" s="36"/>
+      <c r="I101" s="36"/>
     </row>
     <row r="102" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A102" s="4"/>
@@ -11521,7 +11643,7 @@
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
-  <dimension ref="A1:K102"/>
+  <dimension ref="A1:L102"/>
   <sheetFormatPr defaultColWidth="12.5703125" defaultRowHeight="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="19.42578125" customWidth="1"/>
@@ -11532,496 +11654,520 @@
     <col min="7" max="7" width="13.42578125" customWidth="1"/>
     <col min="8" max="8" width="14.140625" customWidth="1"/>
     <col min="9" max="9" width="14.28515625" customWidth="1"/>
-    <col min="12" max="12" width="3.42578125" customWidth="1"/>
+    <col min="10" max="10" width="12.5703125" style="17"/>
+    <col min="11" max="11" width="13" customWidth="1"/>
+    <col min="12" max="12" width="11.5703125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A1" s="25" t="s">
+    <row r="1" spans="1:12" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="A1" s="24" t="s">
         <v>8</v>
       </c>
-      <c r="B1" s="26" t="s">
+      <c r="B1" s="25" t="s">
         <v>0</v>
       </c>
-      <c r="C1" s="26" t="s">
+      <c r="C1" s="25" t="s">
         <v>1</v>
       </c>
-      <c r="D1" s="26" t="s">
+      <c r="D1" s="25" t="s">
         <v>2</v>
       </c>
-      <c r="E1" s="26" t="s">
+      <c r="E1" s="25" t="s">
         <v>3</v>
       </c>
-      <c r="F1" s="26" t="s">
+      <c r="F1" s="25" t="s">
         <v>4</v>
       </c>
-      <c r="G1" s="26" t="s">
+      <c r="G1" s="25" t="s">
         <v>5</v>
       </c>
-      <c r="H1" s="26" t="s">
+      <c r="H1" s="25" t="s">
         <v>6</v>
       </c>
-      <c r="I1" s="26" t="s">
+      <c r="I1" s="25" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="2" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A2" s="37">
+      <c r="K1" s="25" t="s">
+        <v>9</v>
+      </c>
+      <c r="L1" s="25" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="2" spans="1:12" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="A2" s="32">
         <v>0</v>
       </c>
-      <c r="B2" s="28">
+      <c r="B2" s="27">
         <v>6407</v>
       </c>
-      <c r="C2" s="28">
+      <c r="C2" s="27">
         <v>8185</v>
       </c>
-      <c r="D2" s="28">
+      <c r="D2" s="27">
         <v>9265</v>
       </c>
-      <c r="E2" s="28">
+      <c r="E2" s="27">
         <v>10802</v>
       </c>
-      <c r="F2" s="28">
+      <c r="F2" s="27">
         <v>1271</v>
       </c>
-      <c r="G2" s="28">
+      <c r="G2" s="27">
         <v>3691</v>
       </c>
-      <c r="H2" s="28">
+      <c r="H2" s="27">
         <v>369</v>
       </c>
-      <c r="I2" s="28">
+      <c r="I2" s="27">
         <v>3321</v>
       </c>
-    </row>
-    <row r="3" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A3" s="35">
+      <c r="K2" s="39" t="s">
+        <v>10</v>
+      </c>
+      <c r="L2" s="40" cm="1">
+        <f t="array" ref="L2">_xlfn.IFS(K2="Verde",0,K2="Amarela",1.885,K2="Vermelha P1",4.463,K2="Vermelha P2",7.877)</f>
+        <v>4.4630000000000001</v>
+      </c>
+    </row>
+    <row r="3" spans="1:12" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="A3" s="30">
         <v>1</v>
       </c>
-      <c r="B3" s="36">
+      <c r="B3" s="31">
         <v>6429</v>
       </c>
-      <c r="C3" s="36">
+      <c r="C3" s="31">
         <v>8198</v>
       </c>
-      <c r="D3" s="36">
+      <c r="D3" s="31">
         <v>9269</v>
       </c>
-      <c r="E3" s="36">
+      <c r="E3" s="31">
         <v>10803</v>
       </c>
-      <c r="F3" s="36">
+      <c r="F3" s="31">
         <v>1271</v>
       </c>
-      <c r="G3" s="36">
+      <c r="G3" s="31">
         <v>3694</v>
       </c>
-      <c r="H3" s="36">
+      <c r="H3" s="31">
         <v>369</v>
       </c>
-      <c r="I3" s="36">
+      <c r="I3" s="31">
         <v>3325</v>
       </c>
-    </row>
-    <row r="4" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A4" s="19">
+      <c r="L3" s="17"/>
+    </row>
+    <row r="4" spans="1:12" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="A4" s="18">
         <f t="shared" ref="A4:A32" si="0">A3+1</f>
         <v>2</v>
       </c>
-      <c r="B4" s="22">
+      <c r="B4" s="21">
         <v>6461</v>
       </c>
-      <c r="C4" s="22">
+      <c r="C4" s="21">
         <v>8283</v>
       </c>
-      <c r="D4" s="22">
+      <c r="D4" s="21">
         <v>9272</v>
       </c>
-      <c r="E4" s="22">
+      <c r="E4" s="21">
         <v>10804</v>
       </c>
-      <c r="F4" s="22">
+      <c r="F4" s="21">
         <v>1271</v>
       </c>
-      <c r="G4" s="22">
+      <c r="G4" s="21">
         <v>3697</v>
       </c>
-      <c r="H4" s="22">
+      <c r="H4" s="21">
         <v>369</v>
       </c>
-      <c r="I4" s="22">
+      <c r="I4" s="21">
         <v>3328</v>
       </c>
     </row>
-    <row r="5" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A5" s="19">
+    <row r="5" spans="1:12" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="A5" s="18">
         <f t="shared" si="0"/>
         <v>3</v>
       </c>
-      <c r="B5" s="22">
+      <c r="B5" s="21">
         <v>6524</v>
       </c>
-      <c r="C5" s="22">
+      <c r="C5" s="21">
         <v>8298</v>
       </c>
-      <c r="D5" s="22">
+      <c r="D5" s="21">
         <v>9275</v>
       </c>
-      <c r="E5" s="22">
+      <c r="E5" s="21">
         <v>10804</v>
       </c>
-      <c r="F5" s="22">
+      <c r="F5" s="21">
         <v>1271</v>
       </c>
-      <c r="G5" s="22">
+      <c r="G5" s="21">
         <v>3702</v>
       </c>
-      <c r="H5" s="22">
+      <c r="H5" s="21">
         <v>369</v>
       </c>
-      <c r="I5" s="22">
+      <c r="I5" s="21">
         <v>3333</v>
       </c>
-    </row>
-    <row r="6" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A6" s="19">
+      <c r="K5" s="41"/>
+      <c r="L5" s="42"/>
+    </row>
+    <row r="6" spans="1:12" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="A6" s="18">
         <f t="shared" si="0"/>
         <v>4</v>
       </c>
-      <c r="B6" s="22">
+      <c r="B6" s="21">
         <v>6619</v>
       </c>
-      <c r="C6" s="22">
+      <c r="C6" s="21">
         <v>8371</v>
       </c>
-      <c r="D6" s="22">
+      <c r="D6" s="21">
         <v>9279</v>
       </c>
-      <c r="E6" s="22">
+      <c r="E6" s="21">
         <v>10805</v>
       </c>
-      <c r="F6" s="22">
+      <c r="F6" s="21">
         <v>1271</v>
       </c>
-      <c r="G6" s="22">
+      <c r="G6" s="21">
         <v>3707</v>
       </c>
-      <c r="H6" s="22">
+      <c r="H6" s="21">
         <v>370</v>
       </c>
-      <c r="I6" s="22">
+      <c r="I6" s="21">
         <v>3336</v>
       </c>
-    </row>
-    <row r="7" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A7" s="19">
+      <c r="K6" s="41"/>
+      <c r="L6" s="42"/>
+    </row>
+    <row r="7" spans="1:12" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="A7" s="18">
         <f t="shared" si="0"/>
         <v>5</v>
       </c>
-      <c r="B7" s="22">
+      <c r="B7" s="21">
         <v>6676</v>
       </c>
-      <c r="C7" s="22">
+      <c r="C7" s="21">
         <v>8399</v>
       </c>
-      <c r="D7" s="22">
+      <c r="D7" s="21">
         <v>9281</v>
       </c>
-      <c r="E7" s="22">
+      <c r="E7" s="21">
         <v>10806</v>
       </c>
-      <c r="F7" s="22">
+      <c r="F7" s="21">
         <v>1271</v>
       </c>
-      <c r="G7" s="22">
+      <c r="G7" s="21">
         <v>3711</v>
       </c>
-      <c r="H7" s="22">
+      <c r="H7" s="21">
         <v>371</v>
       </c>
-      <c r="I7" s="22">
+      <c r="I7" s="21">
         <v>3340</v>
       </c>
-    </row>
-    <row r="8" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A8" s="19">
+      <c r="K7" s="41"/>
+      <c r="L7" s="42"/>
+    </row>
+    <row r="8" spans="1:12" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="A8" s="18">
         <f t="shared" si="0"/>
         <v>6</v>
       </c>
-      <c r="B8" s="22">
+      <c r="B8" s="21">
         <v>6759</v>
       </c>
-      <c r="C8" s="22">
+      <c r="C8" s="21">
         <v>8479</v>
       </c>
-      <c r="D8" s="22">
+      <c r="D8" s="21">
         <v>9287</v>
       </c>
-      <c r="E8" s="22">
+      <c r="E8" s="21">
         <v>10807</v>
       </c>
-      <c r="F8" s="22">
+      <c r="F8" s="21">
         <v>1272</v>
       </c>
-      <c r="G8" s="22">
+      <c r="G8" s="21">
         <v>3712</v>
       </c>
-      <c r="H8" s="22">
+      <c r="H8" s="21">
         <v>371</v>
       </c>
-      <c r="I8" s="22">
+      <c r="I8" s="21">
         <v>3343</v>
       </c>
-    </row>
-    <row r="9" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A9" s="19">
+      <c r="K8" s="41"/>
+      <c r="L8" s="42"/>
+    </row>
+    <row r="9" spans="1:12" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="A9" s="18">
         <f t="shared" si="0"/>
         <v>7</v>
       </c>
-      <c r="B9" s="22">
+      <c r="B9" s="21">
         <v>6793</v>
       </c>
-      <c r="C9" s="22">
+      <c r="C9" s="21">
         <v>8509</v>
       </c>
-      <c r="D9" s="22">
+      <c r="D9" s="21">
         <v>9291</v>
       </c>
-      <c r="E9" s="22">
+      <c r="E9" s="21">
         <v>10808</v>
       </c>
-      <c r="F9" s="22">
+      <c r="F9" s="21">
         <v>1273</v>
       </c>
-      <c r="G9" s="22">
+      <c r="G9" s="21">
         <v>3719</v>
       </c>
-      <c r="H9" s="22">
+      <c r="H9" s="21">
         <v>372</v>
       </c>
-      <c r="I9" s="22">
+      <c r="I9" s="21">
         <v>3347</v>
       </c>
     </row>
-    <row r="10" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A10" s="19">
+    <row r="10" spans="1:12" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="A10" s="18">
         <f t="shared" si="0"/>
         <v>8</v>
       </c>
-      <c r="B10" s="22">
+      <c r="B10" s="21">
         <v>6840</v>
       </c>
-      <c r="C10" s="22">
+      <c r="C10" s="21">
         <v>8572</v>
       </c>
-      <c r="D10" s="22">
+      <c r="D10" s="21">
         <v>9291</v>
       </c>
-      <c r="E10" s="22">
+      <c r="E10" s="21">
         <v>10808</v>
       </c>
-      <c r="F10" s="22">
+      <c r="F10" s="21">
         <v>1273</v>
       </c>
-      <c r="G10" s="22">
+      <c r="G10" s="21">
         <v>3723</v>
       </c>
-      <c r="H10" s="22">
+      <c r="H10" s="21">
         <v>372</v>
       </c>
-      <c r="I10" s="22">
+      <c r="I10" s="21">
         <v>3351</v>
       </c>
     </row>
-    <row r="11" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A11" s="19">
+    <row r="11" spans="1:12" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="A11" s="18">
         <f t="shared" si="0"/>
         <v>9</v>
       </c>
-      <c r="B11" s="22">
+      <c r="B11" s="21">
         <v>6845</v>
       </c>
-      <c r="C11" s="22">
+      <c r="C11" s="21">
         <v>8607</v>
       </c>
-      <c r="D11" s="22">
+      <c r="D11" s="21">
         <v>9299</v>
       </c>
-      <c r="E11" s="22">
+      <c r="E11" s="21">
         <v>10809</v>
       </c>
-      <c r="F11" s="22">
+      <c r="F11" s="21">
         <v>1273</v>
       </c>
-      <c r="G11" s="22">
+      <c r="G11" s="21">
         <v>3726</v>
       </c>
-      <c r="H11" s="22">
+      <c r="H11" s="21">
         <v>373</v>
       </c>
-      <c r="I11" s="22">
+      <c r="I11" s="21">
         <v>3349</v>
       </c>
     </row>
-    <row r="12" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A12" s="19">
+    <row r="12" spans="1:12" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="A12" s="18">
         <f t="shared" si="0"/>
         <v>10</v>
       </c>
-      <c r="B12" s="22">
+      <c r="B12" s="21">
         <v>6902</v>
       </c>
-      <c r="C12" s="22">
+      <c r="C12" s="21">
         <v>8690</v>
       </c>
-      <c r="D12" s="22">
+      <c r="D12" s="21">
         <v>9302</v>
       </c>
-      <c r="E12" s="22">
+      <c r="E12" s="21">
         <v>10810</v>
       </c>
-      <c r="F12" s="22">
+      <c r="F12" s="21">
         <v>1273</v>
       </c>
-      <c r="G12" s="22">
+      <c r="G12" s="21">
         <v>3733</v>
       </c>
-      <c r="H12" s="22">
+      <c r="H12" s="21">
         <v>373</v>
       </c>
-      <c r="I12" s="22">
+      <c r="I12" s="21">
         <v>3359</v>
       </c>
     </row>
-    <row r="13" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A13" s="19">
+    <row r="13" spans="1:12" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="A13" s="18">
         <f t="shared" si="0"/>
         <v>11</v>
       </c>
-      <c r="B13" s="29">
+      <c r="B13" s="28">
         <v>6917</v>
       </c>
-      <c r="C13" s="30">
+      <c r="C13" s="29">
         <v>8710</v>
       </c>
-      <c r="D13" s="29">
+      <c r="D13" s="28">
         <v>9309</v>
       </c>
-      <c r="E13" s="29">
+      <c r="E13" s="28">
         <v>10811</v>
       </c>
-      <c r="F13" s="29">
+      <c r="F13" s="28">
         <v>1274</v>
       </c>
-      <c r="G13" s="29">
+      <c r="G13" s="28">
         <v>3734</v>
       </c>
-      <c r="H13" s="29">
+      <c r="H13" s="28">
         <v>373</v>
       </c>
-      <c r="I13" s="29">
+      <c r="I13" s="28">
         <v>3360</v>
       </c>
     </row>
-    <row r="14" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A14" s="19">
+    <row r="14" spans="1:12" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="A14" s="18">
         <f t="shared" si="0"/>
         <v>12</v>
       </c>
-      <c r="B14" s="22">
+      <c r="B14" s="21">
         <v>7029</v>
       </c>
-      <c r="C14" s="22">
+      <c r="C14" s="21">
         <v>8819</v>
       </c>
-      <c r="D14" s="22">
+      <c r="D14" s="21">
         <v>9312</v>
       </c>
-      <c r="E14" s="22">
+      <c r="E14" s="21">
         <v>10811</v>
       </c>
-      <c r="F14" s="22">
+      <c r="F14" s="21">
         <v>1274</v>
       </c>
-      <c r="G14" s="22">
+      <c r="G14" s="21">
         <v>3738</v>
       </c>
-      <c r="H14" s="22">
+      <c r="H14" s="21">
         <v>374</v>
       </c>
-      <c r="I14" s="22">
+      <c r="I14" s="21">
         <v>3364</v>
       </c>
     </row>
-    <row r="15" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A15" s="19">
+    <row r="15" spans="1:12" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="A15" s="18">
         <f t="shared" si="0"/>
         <v>13</v>
       </c>
-      <c r="B15" s="29"/>
-      <c r="C15" s="29"/>
-      <c r="D15" s="29"/>
-      <c r="E15" s="29"/>
-      <c r="F15" s="29"/>
-      <c r="G15" s="29"/>
-      <c r="H15" s="29"/>
-      <c r="I15" s="29"/>
-    </row>
-    <row r="16" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A16" s="19">
+      <c r="B15" s="28"/>
+      <c r="C15" s="28"/>
+      <c r="D15" s="28"/>
+      <c r="E15" s="28"/>
+      <c r="F15" s="28"/>
+      <c r="G15" s="28"/>
+      <c r="H15" s="28"/>
+      <c r="I15" s="28"/>
+    </row>
+    <row r="16" spans="1:12" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="A16" s="18">
         <f t="shared" si="0"/>
         <v>14</v>
       </c>
-      <c r="B16" s="29"/>
-      <c r="C16" s="29"/>
-      <c r="D16" s="29"/>
-      <c r="E16" s="29"/>
-      <c r="F16" s="29"/>
-      <c r="G16" s="29"/>
-      <c r="H16" s="29"/>
-      <c r="I16" s="29"/>
+      <c r="B16" s="28"/>
+      <c r="C16" s="28"/>
+      <c r="D16" s="28"/>
+      <c r="E16" s="28"/>
+      <c r="F16" s="28"/>
+      <c r="G16" s="28"/>
+      <c r="H16" s="28"/>
+      <c r="I16" s="28"/>
     </row>
     <row r="17" spans="1:10" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A17" s="19">
+      <c r="A17" s="18">
         <f t="shared" si="0"/>
         <v>15</v>
       </c>
-      <c r="B17" s="29"/>
-      <c r="C17" s="29"/>
-      <c r="D17" s="29"/>
-      <c r="E17" s="29"/>
-      <c r="F17" s="29"/>
-      <c r="G17" s="29"/>
-      <c r="H17" s="29"/>
-      <c r="I17" s="29"/>
+      <c r="B17" s="28"/>
+      <c r="C17" s="28"/>
+      <c r="D17" s="28"/>
+      <c r="E17" s="28"/>
+      <c r="F17" s="28"/>
+      <c r="G17" s="28"/>
+      <c r="H17" s="28"/>
+      <c r="I17" s="28"/>
     </row>
     <row r="18" spans="1:10" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A18" s="19">
+      <c r="A18" s="18">
         <f t="shared" si="0"/>
         <v>16</v>
       </c>
-      <c r="B18" s="29"/>
-      <c r="C18" s="29"/>
-      <c r="D18" s="29"/>
-      <c r="E18" s="29"/>
-      <c r="F18" s="29"/>
-      <c r="G18" s="29"/>
-      <c r="H18" s="29"/>
-      <c r="I18" s="29"/>
+      <c r="B18" s="28"/>
+      <c r="C18" s="28"/>
+      <c r="D18" s="28"/>
+      <c r="E18" s="28"/>
+      <c r="F18" s="28"/>
+      <c r="G18" s="28"/>
+      <c r="H18" s="28"/>
+      <c r="I18" s="28"/>
     </row>
     <row r="19" spans="1:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A19" s="1">
         <f t="shared" si="0"/>
         <v>17</v>
       </c>
-      <c r="B19" s="24"/>
-      <c r="C19" s="24"/>
-      <c r="D19" s="24"/>
-      <c r="E19" s="24"/>
-      <c r="F19" s="24"/>
-      <c r="G19" s="24"/>
-      <c r="H19" s="24"/>
-      <c r="I19" s="24"/>
-      <c r="J19" s="3"/>
+      <c r="B19" s="23"/>
+      <c r="C19" s="23"/>
+      <c r="D19" s="23"/>
+      <c r="E19" s="23"/>
+      <c r="F19" s="23"/>
+      <c r="G19" s="23"/>
+      <c r="H19" s="23"/>
+      <c r="I19" s="23"/>
+      <c r="J19" s="43"/>
     </row>
     <row r="20" spans="1:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A20" s="1">
@@ -12122,100 +12268,100 @@
       <c r="I26" s="11"/>
     </row>
     <row r="27" spans="1:10" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A27" s="27">
+      <c r="A27" s="26">
         <f t="shared" si="0"/>
         <v>25</v>
       </c>
-      <c r="B27" s="29"/>
-      <c r="C27" s="29"/>
-      <c r="D27" s="29"/>
-      <c r="E27" s="29"/>
-      <c r="F27" s="29"/>
-      <c r="G27" s="29"/>
-      <c r="H27" s="29"/>
-      <c r="I27" s="29"/>
+      <c r="B27" s="28"/>
+      <c r="C27" s="28"/>
+      <c r="D27" s="28"/>
+      <c r="E27" s="28"/>
+      <c r="F27" s="28"/>
+      <c r="G27" s="28"/>
+      <c r="H27" s="28"/>
+      <c r="I27" s="28"/>
     </row>
     <row r="28" spans="1:10" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A28" s="27">
+      <c r="A28" s="26">
         <f t="shared" si="0"/>
         <v>26</v>
       </c>
-      <c r="B28" s="29"/>
-      <c r="C28" s="29"/>
-      <c r="D28" s="29"/>
-      <c r="E28" s="29"/>
-      <c r="F28" s="29"/>
-      <c r="G28" s="29"/>
-      <c r="H28" s="29"/>
-      <c r="I28" s="29"/>
+      <c r="B28" s="28"/>
+      <c r="C28" s="28"/>
+      <c r="D28" s="28"/>
+      <c r="E28" s="28"/>
+      <c r="F28" s="28"/>
+      <c r="G28" s="28"/>
+      <c r="H28" s="28"/>
+      <c r="I28" s="28"/>
     </row>
     <row r="29" spans="1:10" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A29" s="27">
+      <c r="A29" s="26">
         <f t="shared" si="0"/>
         <v>27</v>
       </c>
-      <c r="B29" s="29"/>
-      <c r="C29" s="29"/>
-      <c r="D29" s="29"/>
-      <c r="E29" s="29"/>
-      <c r="F29" s="29"/>
-      <c r="G29" s="29"/>
-      <c r="H29" s="29"/>
-      <c r="I29" s="29"/>
+      <c r="B29" s="28"/>
+      <c r="C29" s="28"/>
+      <c r="D29" s="28"/>
+      <c r="E29" s="28"/>
+      <c r="F29" s="28"/>
+      <c r="G29" s="28"/>
+      <c r="H29" s="28"/>
+      <c r="I29" s="28"/>
     </row>
     <row r="30" spans="1:10" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A30" s="27">
+      <c r="A30" s="26">
         <f t="shared" si="0"/>
         <v>28</v>
       </c>
-      <c r="B30" s="29"/>
-      <c r="C30" s="29"/>
-      <c r="D30" s="29"/>
-      <c r="E30" s="29"/>
-      <c r="F30" s="29"/>
-      <c r="G30" s="29"/>
-      <c r="H30" s="29"/>
-      <c r="I30" s="29"/>
+      <c r="B30" s="28"/>
+      <c r="C30" s="28"/>
+      <c r="D30" s="28"/>
+      <c r="E30" s="28"/>
+      <c r="F30" s="28"/>
+      <c r="G30" s="28"/>
+      <c r="H30" s="28"/>
+      <c r="I30" s="28"/>
     </row>
     <row r="31" spans="1:10" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A31" s="27">
+      <c r="A31" s="26">
         <f t="shared" si="0"/>
         <v>29</v>
       </c>
-      <c r="B31" s="29"/>
-      <c r="C31" s="29"/>
-      <c r="D31" s="29"/>
-      <c r="E31" s="29"/>
-      <c r="F31" s="29"/>
-      <c r="G31" s="29"/>
-      <c r="H31" s="29"/>
-      <c r="I31" s="29"/>
+      <c r="B31" s="28"/>
+      <c r="C31" s="28"/>
+      <c r="D31" s="28"/>
+      <c r="E31" s="28"/>
+      <c r="F31" s="28"/>
+      <c r="G31" s="28"/>
+      <c r="H31" s="28"/>
+      <c r="I31" s="28"/>
     </row>
     <row r="32" spans="1:10" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A32" s="27">
+      <c r="A32" s="26">
         <f t="shared" si="0"/>
         <v>30</v>
       </c>
-      <c r="B32" s="29"/>
-      <c r="C32" s="29"/>
-      <c r="D32" s="29"/>
-      <c r="E32" s="29"/>
-      <c r="F32" s="29"/>
-      <c r="G32" s="29"/>
-      <c r="H32" s="29"/>
-      <c r="I32" s="29"/>
+      <c r="B32" s="28"/>
+      <c r="C32" s="28"/>
+      <c r="D32" s="28"/>
+      <c r="E32" s="28"/>
+      <c r="F32" s="28"/>
+      <c r="G32" s="28"/>
+      <c r="H32" s="28"/>
+      <c r="I32" s="28"/>
     </row>
     <row r="33" spans="1:9" ht="12.75" x14ac:dyDescent="0.2"/>
     <row r="35" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A35" s="4"/>
-      <c r="B35" s="33"/>
-      <c r="C35" s="32"/>
-      <c r="D35" s="32"/>
-      <c r="E35" s="32"/>
-      <c r="F35" s="32"/>
-      <c r="G35" s="32"/>
-      <c r="H35" s="32"/>
-      <c r="I35" s="32"/>
+      <c r="B35" s="37"/>
+      <c r="C35" s="36"/>
+      <c r="D35" s="36"/>
+      <c r="E35" s="36"/>
+      <c r="F35" s="36"/>
+      <c r="G35" s="36"/>
+      <c r="H35" s="36"/>
+      <c r="I35" s="36"/>
     </row>
     <row r="36" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A36" s="4"/>
@@ -12593,15 +12739,15 @@
       <c r="I69" s="4"/>
     </row>
     <row r="70" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A70" s="33"/>
-      <c r="B70" s="32"/>
-      <c r="C70" s="32"/>
-      <c r="D70" s="32"/>
-      <c r="E70" s="32"/>
-      <c r="F70" s="32"/>
-      <c r="G70" s="32"/>
-      <c r="H70" s="32"/>
-      <c r="I70" s="32"/>
+      <c r="A70" s="37"/>
+      <c r="B70" s="36"/>
+      <c r="C70" s="36"/>
+      <c r="D70" s="36"/>
+      <c r="E70" s="36"/>
+      <c r="F70" s="36"/>
+      <c r="G70" s="36"/>
+      <c r="H70" s="36"/>
+      <c r="I70" s="36"/>
     </row>
     <row r="71" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A71" s="4"/>
@@ -12626,15 +12772,15 @@
       <c r="I72" s="6"/>
     </row>
     <row r="75" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A75" s="31"/>
-      <c r="B75" s="32"/>
-      <c r="C75" s="32"/>
-      <c r="D75" s="32"/>
-      <c r="E75" s="32"/>
-      <c r="F75" s="32"/>
-      <c r="G75" s="32"/>
-      <c r="H75" s="32"/>
-      <c r="I75" s="32"/>
+      <c r="A75" s="35"/>
+      <c r="B75" s="36"/>
+      <c r="C75" s="36"/>
+      <c r="D75" s="36"/>
+      <c r="E75" s="36"/>
+      <c r="F75" s="36"/>
+      <c r="G75" s="36"/>
+      <c r="H75" s="36"/>
+      <c r="I75" s="36"/>
     </row>
     <row r="76" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A76" s="4"/>
@@ -12670,15 +12816,15 @@
       <c r="I78" s="8"/>
     </row>
     <row r="79" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A79" s="34"/>
-      <c r="B79" s="32"/>
-      <c r="C79" s="32"/>
-      <c r="D79" s="32"/>
-      <c r="E79" s="32"/>
-      <c r="F79" s="32"/>
-      <c r="G79" s="32"/>
-      <c r="H79" s="32"/>
-      <c r="I79" s="32"/>
+      <c r="A79" s="38"/>
+      <c r="B79" s="36"/>
+      <c r="C79" s="36"/>
+      <c r="D79" s="36"/>
+      <c r="E79" s="36"/>
+      <c r="F79" s="36"/>
+      <c r="G79" s="36"/>
+      <c r="H79" s="36"/>
+      <c r="I79" s="36"/>
     </row>
     <row r="80" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A80" s="4"/>
@@ -12714,15 +12860,15 @@
       <c r="B85" s="6"/>
     </row>
     <row r="87" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A87" s="31"/>
-      <c r="B87" s="32"/>
-      <c r="C87" s="32"/>
-      <c r="D87" s="32"/>
-      <c r="E87" s="32"/>
-      <c r="F87" s="32"/>
-      <c r="G87" s="32"/>
-      <c r="H87" s="32"/>
-      <c r="I87" s="32"/>
+      <c r="A87" s="35"/>
+      <c r="B87" s="36"/>
+      <c r="C87" s="36"/>
+      <c r="D87" s="36"/>
+      <c r="E87" s="36"/>
+      <c r="F87" s="36"/>
+      <c r="G87" s="36"/>
+      <c r="H87" s="36"/>
+      <c r="I87" s="36"/>
     </row>
     <row r="88" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A88" s="4"/>
@@ -12825,15 +12971,15 @@
       <c r="B98" s="9"/>
     </row>
     <row r="100" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A100" s="33"/>
-      <c r="B100" s="32"/>
-      <c r="C100" s="32"/>
-      <c r="D100" s="32"/>
-      <c r="E100" s="32"/>
-      <c r="F100" s="32"/>
-      <c r="G100" s="32"/>
-      <c r="H100" s="32"/>
-      <c r="I100" s="32"/>
+      <c r="A100" s="37"/>
+      <c r="B100" s="36"/>
+      <c r="C100" s="36"/>
+      <c r="D100" s="36"/>
+      <c r="E100" s="36"/>
+      <c r="F100" s="36"/>
+      <c r="G100" s="36"/>
+      <c r="H100" s="36"/>
+      <c r="I100" s="36"/>
     </row>
     <row r="101" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A101" s="4"/>
@@ -12873,6 +13019,18 @@
   </dataValidations>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{CCE6A557-97BC-4b89-ADB6-D9C93CAAB3DF}">
+      <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="1">
+        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{60AE3C60-7765-41C0-BC47-1028C708BE5C}">
+          <x14:formula1>
+            <xm:f>Planilha1!$A$2:$A$5</xm:f>
+          </x14:formula1>
+          <xm:sqref>K2</xm:sqref>
+        </x14:dataValidation>
+      </x14:dataValidations>
+    </ext>
+  </extLst>
 </worksheet>
 </file>
 
@@ -12881,7 +13039,7 @@
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
-  <dimension ref="A1:K103"/>
+  <dimension ref="A1:L103"/>
   <sheetFormatPr defaultColWidth="12.5703125" defaultRowHeight="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="19.42578125" customWidth="1"/>
@@ -12892,714 +13050,728 @@
     <col min="7" max="7" width="13.42578125" customWidth="1"/>
     <col min="8" max="8" width="14.140625" customWidth="1"/>
     <col min="9" max="9" width="14.28515625" customWidth="1"/>
-    <col min="12" max="12" width="3.42578125" customWidth="1"/>
+    <col min="11" max="11" width="11.7109375" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="9.5703125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A1" s="25" t="s">
+    <row r="1" spans="1:12" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="A1" s="24" t="s">
         <v>8</v>
       </c>
-      <c r="B1" s="26" t="s">
+      <c r="B1" s="25" t="s">
         <v>0</v>
       </c>
-      <c r="C1" s="26" t="s">
+      <c r="C1" s="25" t="s">
         <v>1</v>
       </c>
-      <c r="D1" s="26" t="s">
+      <c r="D1" s="25" t="s">
         <v>2</v>
       </c>
-      <c r="E1" s="26" t="s">
+      <c r="E1" s="25" t="s">
         <v>3</v>
       </c>
-      <c r="F1" s="26" t="s">
+      <c r="F1" s="25" t="s">
         <v>4</v>
       </c>
-      <c r="G1" s="26" t="s">
+      <c r="G1" s="25" t="s">
         <v>5</v>
       </c>
-      <c r="H1" s="26" t="s">
+      <c r="H1" s="25" t="s">
         <v>6</v>
       </c>
-      <c r="I1" s="26" t="s">
+      <c r="I1" s="25" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="2" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A2" s="39">
+      <c r="K1" s="25" t="s">
+        <v>9</v>
+      </c>
+      <c r="L1" s="25" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="2" spans="1:12" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="A2" s="34">
         <v>0</v>
       </c>
-      <c r="B2" s="38"/>
-      <c r="C2" s="38"/>
-      <c r="D2" s="38"/>
-      <c r="E2" s="38"/>
-      <c r="F2" s="38"/>
-      <c r="G2" s="38"/>
-      <c r="H2" s="38"/>
-      <c r="I2" s="38"/>
-    </row>
-    <row r="3" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A3" s="27">
+      <c r="B2" s="33"/>
+      <c r="C2" s="33"/>
+      <c r="D2" s="33"/>
+      <c r="E2" s="33"/>
+      <c r="F2" s="33"/>
+      <c r="G2" s="33"/>
+      <c r="H2" s="33"/>
+      <c r="I2" s="33"/>
+      <c r="K2" s="39" t="s">
+        <v>12</v>
+      </c>
+      <c r="L2" s="40" cm="1">
+        <f t="array" ref="L2">_xlfn.IFS(K2="Verde",0,K2="Amarela",1.885,K2="Vermelha P1",4.463,K2="Vermelha P2",7.877)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3" spans="1:12" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="A3" s="26">
         <v>1</v>
       </c>
-      <c r="B3" s="22">
+      <c r="B3" s="21">
         <v>4909</v>
       </c>
-      <c r="C3" s="22">
+      <c r="C3" s="21">
         <v>6810</v>
       </c>
-      <c r="D3" s="22">
+      <c r="D3" s="21">
         <v>9145</v>
       </c>
-      <c r="E3" s="22">
+      <c r="E3" s="21">
         <v>10783</v>
       </c>
-      <c r="F3" s="22">
+      <c r="F3" s="21">
         <v>1266</v>
       </c>
-      <c r="G3" s="22">
+      <c r="G3" s="21">
         <v>3565</v>
       </c>
-      <c r="H3" s="22">
+      <c r="H3" s="21">
         <v>354</v>
       </c>
-      <c r="I3" s="22">
+      <c r="I3" s="21">
         <v>3210</v>
       </c>
     </row>
-    <row r="4" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A4" s="27">
+    <row r="4" spans="1:12" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="A4" s="26">
         <f t="shared" ref="A4:A33" si="0">A3+1</f>
         <v>2</v>
       </c>
-      <c r="B4" s="23"/>
-      <c r="C4" s="23"/>
-      <c r="D4" s="23"/>
-      <c r="E4" s="23"/>
-      <c r="F4" s="23"/>
-      <c r="G4" s="23"/>
-      <c r="H4" s="23"/>
-      <c r="I4" s="23"/>
-    </row>
-    <row r="5" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A5" s="27">
+      <c r="B4" s="22"/>
+      <c r="C4" s="22"/>
+      <c r="D4" s="22"/>
+      <c r="E4" s="22"/>
+      <c r="F4" s="22"/>
+      <c r="G4" s="22"/>
+      <c r="H4" s="22"/>
+      <c r="I4" s="22"/>
+    </row>
+    <row r="5" spans="1:12" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="A5" s="26">
         <f t="shared" si="0"/>
         <v>3</v>
       </c>
-      <c r="B5" s="22">
+      <c r="B5" s="21">
         <v>5009</v>
       </c>
-      <c r="C5" s="22">
+      <c r="C5" s="21">
         <v>6932</v>
       </c>
-      <c r="D5" s="22">
+      <c r="D5" s="21">
         <v>9157</v>
       </c>
-      <c r="E5" s="22">
+      <c r="E5" s="21">
         <v>10784</v>
       </c>
-      <c r="F5" s="22">
+      <c r="F5" s="21">
         <v>1267</v>
       </c>
-      <c r="G5" s="22">
+      <c r="G5" s="21">
         <v>3574</v>
       </c>
-      <c r="H5" s="22">
+      <c r="H5" s="21">
         <v>355</v>
       </c>
-      <c r="I5" s="22">
+      <c r="I5" s="21">
         <v>3218</v>
       </c>
     </row>
-    <row r="6" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A6" s="27">
+    <row r="6" spans="1:12" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="A6" s="26">
         <f t="shared" si="0"/>
         <v>4</v>
       </c>
-      <c r="B6" s="22">
+      <c r="B6" s="21">
         <v>5025</v>
       </c>
-      <c r="C6" s="22">
+      <c r="C6" s="21">
         <v>6932</v>
       </c>
-      <c r="D6" s="22">
+      <c r="D6" s="21">
         <v>9158</v>
       </c>
-      <c r="E6" s="22">
+      <c r="E6" s="21">
         <v>10784</v>
       </c>
-      <c r="F6" s="22">
+      <c r="F6" s="21">
         <v>1267</v>
       </c>
-      <c r="G6" s="22">
+      <c r="G6" s="21">
         <v>3578</v>
       </c>
-      <c r="H6" s="22">
+      <c r="H6" s="21">
         <v>355</v>
       </c>
-      <c r="I6" s="22">
+      <c r="I6" s="21">
         <v>3223</v>
       </c>
     </row>
-    <row r="7" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A7" s="27">
+    <row r="7" spans="1:12" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="A7" s="26">
         <f t="shared" si="0"/>
         <v>5</v>
       </c>
-      <c r="B7" s="22">
+      <c r="B7" s="21">
         <v>5069</v>
       </c>
-      <c r="C7" s="22">
+      <c r="C7" s="21">
         <v>6997</v>
       </c>
-      <c r="D7" s="22">
+      <c r="D7" s="21">
         <v>9168</v>
       </c>
-      <c r="E7" s="22">
+      <c r="E7" s="21">
         <v>10784</v>
       </c>
-      <c r="F7" s="22">
+      <c r="F7" s="21">
         <v>1267</v>
       </c>
-      <c r="G7" s="22">
+      <c r="G7" s="21">
         <v>3583</v>
       </c>
-      <c r="H7" s="22">
+      <c r="H7" s="21">
         <v>355</v>
       </c>
-      <c r="I7" s="22">
+      <c r="I7" s="21">
         <v>3227</v>
       </c>
     </row>
-    <row r="8" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A8" s="27">
+    <row r="8" spans="1:12" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="A8" s="26">
         <f t="shared" si="0"/>
         <v>6</v>
       </c>
-      <c r="B8" s="22">
+      <c r="B8" s="21">
         <v>5127</v>
       </c>
-      <c r="C8" s="22">
+      <c r="C8" s="21">
         <v>7107</v>
       </c>
-      <c r="D8" s="22">
+      <c r="D8" s="21">
         <v>9172</v>
       </c>
-      <c r="E8" s="22">
+      <c r="E8" s="21">
         <v>10785</v>
       </c>
-      <c r="F8" s="22">
+      <c r="F8" s="21">
         <v>1267</v>
       </c>
-      <c r="G8" s="22">
+      <c r="G8" s="21">
         <v>3584</v>
       </c>
-      <c r="H8" s="22">
+      <c r="H8" s="21">
         <v>355</v>
       </c>
-      <c r="I8" s="22">
+      <c r="I8" s="21">
         <v>3228</v>
       </c>
     </row>
-    <row r="9" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A9" s="27">
+    <row r="9" spans="1:12" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="A9" s="26">
         <f t="shared" si="0"/>
         <v>7</v>
       </c>
-      <c r="B9" s="22">
+      <c r="B9" s="21">
         <v>5130</v>
       </c>
-      <c r="C9" s="22">
+      <c r="C9" s="21">
         <v>7110</v>
       </c>
-      <c r="D9" s="22">
+      <c r="D9" s="21">
         <v>9176</v>
       </c>
-      <c r="E9" s="22">
+      <c r="E9" s="21">
         <v>10787</v>
       </c>
-      <c r="F9" s="22">
+      <c r="F9" s="21">
         <v>1268</v>
       </c>
-      <c r="G9" s="22">
+      <c r="G9" s="21">
         <v>3590</v>
       </c>
-      <c r="H9" s="22">
+      <c r="H9" s="21">
         <v>356</v>
       </c>
-      <c r="I9" s="22">
+      <c r="I9" s="21">
         <v>3233</v>
       </c>
     </row>
-    <row r="10" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A10" s="27">
+    <row r="10" spans="1:12" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="A10" s="26">
         <f t="shared" si="0"/>
         <v>8</v>
       </c>
-      <c r="B10" s="23"/>
-      <c r="C10" s="23"/>
-      <c r="D10" s="23"/>
-      <c r="E10" s="23"/>
-      <c r="F10" s="23"/>
-      <c r="G10" s="23"/>
-      <c r="H10" s="23"/>
-      <c r="I10" s="23"/>
-    </row>
-    <row r="11" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A11" s="27">
+      <c r="B10" s="22"/>
+      <c r="C10" s="22"/>
+      <c r="D10" s="22"/>
+      <c r="E10" s="22"/>
+      <c r="F10" s="22"/>
+      <c r="G10" s="22"/>
+      <c r="H10" s="22"/>
+      <c r="I10" s="22"/>
+    </row>
+    <row r="11" spans="1:12" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="A11" s="26">
         <f t="shared" si="0"/>
         <v>9</v>
       </c>
-      <c r="B11" s="23"/>
-      <c r="C11" s="23"/>
-      <c r="D11" s="23"/>
-      <c r="E11" s="23"/>
-      <c r="F11" s="23"/>
-      <c r="G11" s="23"/>
-      <c r="H11" s="23"/>
-      <c r="I11" s="23"/>
-    </row>
-    <row r="12" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A12" s="27">
+      <c r="B11" s="22"/>
+      <c r="C11" s="22"/>
+      <c r="D11" s="22"/>
+      <c r="E11" s="22"/>
+      <c r="F11" s="22"/>
+      <c r="G11" s="22"/>
+      <c r="H11" s="22"/>
+      <c r="I11" s="22"/>
+    </row>
+    <row r="12" spans="1:12" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="A12" s="26">
         <f t="shared" si="0"/>
         <v>10</v>
       </c>
-      <c r="B12" s="22">
+      <c r="B12" s="21">
         <v>5416</v>
       </c>
-      <c r="C12" s="22">
+      <c r="C12" s="21">
         <v>7409</v>
       </c>
-      <c r="D12" s="22">
+      <c r="D12" s="21">
         <v>9192</v>
       </c>
-      <c r="E12" s="22">
+      <c r="E12" s="21">
         <v>10787</v>
       </c>
-      <c r="F12" s="22">
+      <c r="F12" s="21">
         <v>1269</v>
       </c>
-      <c r="G12" s="22">
+      <c r="G12" s="21">
         <v>3604</v>
       </c>
-      <c r="H12" s="22">
+      <c r="H12" s="21">
         <v>358</v>
       </c>
-      <c r="I12" s="22">
+      <c r="I12" s="21">
         <v>3245</v>
       </c>
     </row>
-    <row r="13" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A13" s="27">
+    <row r="13" spans="1:12" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="A13" s="26">
         <f t="shared" si="0"/>
         <v>11</v>
       </c>
-      <c r="B13" s="22">
+      <c r="B13" s="21">
         <v>5429</v>
       </c>
-      <c r="C13" s="22">
+      <c r="C13" s="21">
         <v>7435</v>
       </c>
-      <c r="D13" s="22">
+      <c r="D13" s="21">
         <v>9195</v>
       </c>
-      <c r="E13" s="22">
+      <c r="E13" s="21">
         <v>10788</v>
       </c>
-      <c r="F13" s="22">
+      <c r="F13" s="21">
         <v>1269</v>
       </c>
-      <c r="G13" s="22">
+      <c r="G13" s="21">
         <v>3609</v>
       </c>
-      <c r="H13" s="22">
+      <c r="H13" s="21">
         <v>358</v>
       </c>
-      <c r="I13" s="22">
+      <c r="I13" s="21">
         <v>3250</v>
       </c>
     </row>
-    <row r="14" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A14" s="27">
+    <row r="14" spans="1:12" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="A14" s="26">
         <f t="shared" si="0"/>
         <v>12</v>
       </c>
-      <c r="B14" s="22">
+      <c r="B14" s="21">
         <v>5458</v>
       </c>
-      <c r="C14" s="22">
+      <c r="C14" s="21">
         <v>7553</v>
       </c>
-      <c r="D14" s="22">
+      <c r="D14" s="21">
         <v>9200</v>
       </c>
-      <c r="E14" s="22">
+      <c r="E14" s="21">
         <v>10789</v>
       </c>
-      <c r="F14" s="22">
+      <c r="F14" s="21">
         <v>1269</v>
       </c>
-      <c r="G14" s="22">
+      <c r="G14" s="21">
         <v>3614</v>
       </c>
-      <c r="H14" s="22">
+      <c r="H14" s="21">
         <v>358</v>
       </c>
-      <c r="I14" s="22">
+      <c r="I14" s="21">
         <v>3255</v>
       </c>
     </row>
-    <row r="15" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A15" s="27">
+    <row r="15" spans="1:12" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="A15" s="26">
         <f t="shared" si="0"/>
         <v>13</v>
       </c>
-      <c r="B15" s="22">
+      <c r="B15" s="21">
         <v>5553</v>
       </c>
-      <c r="C15" s="22">
+      <c r="C15" s="21">
         <v>7571</v>
       </c>
-      <c r="D15" s="22">
+      <c r="D15" s="21">
         <v>9201</v>
       </c>
-      <c r="E15" s="22">
+      <c r="E15" s="21">
         <v>10789</v>
       </c>
-      <c r="F15" s="22">
+      <c r="F15" s="21">
         <v>1269</v>
       </c>
-      <c r="G15" s="23"/>
-      <c r="H15" s="23"/>
-      <c r="I15" s="23"/>
-    </row>
-    <row r="16" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A16" s="27">
+      <c r="G15" s="22"/>
+      <c r="H15" s="22"/>
+      <c r="I15" s="22"/>
+    </row>
+    <row r="16" spans="1:12" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="A16" s="26">
         <f t="shared" si="0"/>
         <v>14</v>
       </c>
-      <c r="B16" s="23"/>
-      <c r="C16" s="23"/>
-      <c r="D16" s="23"/>
-      <c r="E16" s="23"/>
-      <c r="F16" s="23"/>
-      <c r="G16" s="23"/>
-      <c r="H16" s="23"/>
-      <c r="I16" s="23"/>
+      <c r="B16" s="22"/>
+      <c r="C16" s="22"/>
+      <c r="D16" s="22"/>
+      <c r="E16" s="22"/>
+      <c r="F16" s="22"/>
+      <c r="G16" s="22"/>
+      <c r="H16" s="22"/>
+      <c r="I16" s="22"/>
     </row>
     <row r="17" spans="1:10" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A17" s="27">
+      <c r="A17" s="26">
         <f t="shared" si="0"/>
         <v>15</v>
       </c>
-      <c r="B17" s="22">
+      <c r="B17" s="21">
         <v>5695</v>
       </c>
-      <c r="C17" s="22">
+      <c r="C17" s="21">
         <v>7647</v>
       </c>
-      <c r="D17" s="22">
+      <c r="D17" s="21">
         <v>9209</v>
       </c>
-      <c r="E17" s="22">
+      <c r="E17" s="21">
         <v>10791</v>
       </c>
-      <c r="F17" s="22">
+      <c r="F17" s="21">
         <v>1269</v>
       </c>
-      <c r="G17" s="22">
+      <c r="G17" s="21">
         <v>3627</v>
       </c>
-      <c r="H17" s="22">
+      <c r="H17" s="21">
         <v>360</v>
       </c>
-      <c r="I17" s="22">
+      <c r="I17" s="21">
         <v>3266</v>
       </c>
     </row>
     <row r="18" spans="1:10" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A18" s="27">
+      <c r="A18" s="26">
         <f t="shared" si="0"/>
         <v>16</v>
       </c>
-      <c r="B18" s="23"/>
-      <c r="C18" s="23"/>
-      <c r="D18" s="23"/>
-      <c r="E18" s="23"/>
-      <c r="F18" s="23"/>
-      <c r="G18" s="23"/>
-      <c r="H18" s="23"/>
-      <c r="I18" s="23"/>
+      <c r="B18" s="22"/>
+      <c r="C18" s="22"/>
+      <c r="D18" s="22"/>
+      <c r="E18" s="22"/>
+      <c r="F18" s="22"/>
+      <c r="G18" s="22"/>
+      <c r="H18" s="22"/>
+      <c r="I18" s="22"/>
     </row>
     <row r="19" spans="1:10" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A19" s="27">
+      <c r="A19" s="26">
         <f t="shared" si="0"/>
         <v>17</v>
       </c>
-      <c r="B19" s="23"/>
-      <c r="C19" s="23"/>
-      <c r="D19" s="23"/>
-      <c r="E19" s="23"/>
-      <c r="F19" s="23"/>
-      <c r="G19" s="23"/>
-      <c r="H19" s="23"/>
-      <c r="I19" s="23"/>
+      <c r="B19" s="22"/>
+      <c r="C19" s="22"/>
+      <c r="D19" s="22"/>
+      <c r="E19" s="22"/>
+      <c r="F19" s="22"/>
+      <c r="G19" s="22"/>
+      <c r="H19" s="22"/>
+      <c r="I19" s="22"/>
       <c r="J19" s="3"/>
     </row>
     <row r="20" spans="1:10" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A20" s="27">
+      <c r="A20" s="26">
         <f t="shared" si="0"/>
         <v>18</v>
       </c>
-      <c r="B20" s="23"/>
-      <c r="C20" s="23"/>
-      <c r="D20" s="23"/>
-      <c r="E20" s="23"/>
-      <c r="F20" s="23"/>
-      <c r="G20" s="23"/>
-      <c r="H20" s="23"/>
-      <c r="I20" s="23"/>
+      <c r="B20" s="22"/>
+      <c r="C20" s="22"/>
+      <c r="D20" s="22"/>
+      <c r="E20" s="22"/>
+      <c r="F20" s="22"/>
+      <c r="G20" s="22"/>
+      <c r="H20" s="22"/>
+      <c r="I20" s="22"/>
     </row>
     <row r="21" spans="1:10" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A21" s="27">
+      <c r="A21" s="26">
         <f t="shared" si="0"/>
         <v>19</v>
       </c>
-      <c r="B21" s="23"/>
-      <c r="C21" s="23"/>
-      <c r="D21" s="23"/>
-      <c r="E21" s="23"/>
-      <c r="F21" s="23"/>
-      <c r="G21" s="23"/>
-      <c r="H21" s="23"/>
-      <c r="I21" s="23"/>
+      <c r="B21" s="22"/>
+      <c r="C21" s="22"/>
+      <c r="D21" s="22"/>
+      <c r="E21" s="22"/>
+      <c r="F21" s="22"/>
+      <c r="G21" s="22"/>
+      <c r="H21" s="22"/>
+      <c r="I21" s="22"/>
     </row>
     <row r="22" spans="1:10" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A22" s="27">
+      <c r="A22" s="26">
         <f t="shared" si="0"/>
         <v>20</v>
       </c>
-      <c r="B22" s="23"/>
-      <c r="C22" s="23"/>
-      <c r="D22" s="23"/>
-      <c r="E22" s="23"/>
-      <c r="F22" s="23"/>
-      <c r="G22" s="23"/>
-      <c r="H22" s="23"/>
-      <c r="I22" s="23"/>
+      <c r="B22" s="22"/>
+      <c r="C22" s="22"/>
+      <c r="D22" s="22"/>
+      <c r="E22" s="22"/>
+      <c r="F22" s="22"/>
+      <c r="G22" s="22"/>
+      <c r="H22" s="22"/>
+      <c r="I22" s="22"/>
     </row>
     <row r="23" spans="1:10" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A23" s="27">
+      <c r="A23" s="26">
         <f t="shared" si="0"/>
         <v>21</v>
       </c>
-      <c r="B23" s="23"/>
-      <c r="C23" s="23"/>
-      <c r="D23" s="23"/>
-      <c r="E23" s="23"/>
-      <c r="F23" s="23"/>
-      <c r="G23" s="23"/>
-      <c r="H23" s="23"/>
-      <c r="I23" s="23"/>
+      <c r="B23" s="22"/>
+      <c r="C23" s="22"/>
+      <c r="D23" s="22"/>
+      <c r="E23" s="22"/>
+      <c r="F23" s="22"/>
+      <c r="G23" s="22"/>
+      <c r="H23" s="22"/>
+      <c r="I23" s="22"/>
     </row>
     <row r="24" spans="1:10" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A24" s="27">
+      <c r="A24" s="26">
         <f t="shared" si="0"/>
         <v>22</v>
       </c>
-      <c r="B24" s="23"/>
-      <c r="C24" s="23"/>
-      <c r="D24" s="23"/>
-      <c r="E24" s="23"/>
-      <c r="F24" s="23"/>
-      <c r="G24" s="23"/>
-      <c r="H24" s="23"/>
-      <c r="I24" s="23"/>
+      <c r="B24" s="22"/>
+      <c r="C24" s="22"/>
+      <c r="D24" s="22"/>
+      <c r="E24" s="22"/>
+      <c r="F24" s="22"/>
+      <c r="G24" s="22"/>
+      <c r="H24" s="22"/>
+      <c r="I24" s="22"/>
     </row>
     <row r="25" spans="1:10" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A25" s="27">
+      <c r="A25" s="26">
         <f t="shared" si="0"/>
         <v>23</v>
       </c>
-      <c r="B25" s="23"/>
-      <c r="C25" s="23"/>
-      <c r="D25" s="23"/>
-      <c r="E25" s="23"/>
-      <c r="F25" s="23"/>
-      <c r="G25" s="23"/>
-      <c r="H25" s="23"/>
-      <c r="I25" s="23"/>
+      <c r="B25" s="22"/>
+      <c r="C25" s="22"/>
+      <c r="D25" s="22"/>
+      <c r="E25" s="22"/>
+      <c r="F25" s="22"/>
+      <c r="G25" s="22"/>
+      <c r="H25" s="22"/>
+      <c r="I25" s="22"/>
     </row>
     <row r="26" spans="1:10" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A26" s="27">
+      <c r="A26" s="26">
         <f t="shared" si="0"/>
         <v>24</v>
       </c>
-      <c r="B26" s="23"/>
-      <c r="C26" s="23"/>
-      <c r="D26" s="23"/>
-      <c r="E26" s="23"/>
-      <c r="F26" s="23"/>
-      <c r="G26" s="23"/>
-      <c r="H26" s="23"/>
-      <c r="I26" s="23"/>
+      <c r="B26" s="22"/>
+      <c r="C26" s="22"/>
+      <c r="D26" s="22"/>
+      <c r="E26" s="22"/>
+      <c r="F26" s="22"/>
+      <c r="G26" s="22"/>
+      <c r="H26" s="22"/>
+      <c r="I26" s="22"/>
     </row>
     <row r="27" spans="1:10" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A27" s="27">
+      <c r="A27" s="26">
         <f t="shared" si="0"/>
         <v>25</v>
       </c>
-      <c r="B27" s="23"/>
-      <c r="C27" s="23"/>
-      <c r="D27" s="23"/>
-      <c r="E27" s="23"/>
-      <c r="F27" s="23"/>
-      <c r="G27" s="23"/>
-      <c r="H27" s="23"/>
-      <c r="I27" s="23"/>
+      <c r="B27" s="22"/>
+      <c r="C27" s="22"/>
+      <c r="D27" s="22"/>
+      <c r="E27" s="22"/>
+      <c r="F27" s="22"/>
+      <c r="G27" s="22"/>
+      <c r="H27" s="22"/>
+      <c r="I27" s="22"/>
     </row>
     <row r="28" spans="1:10" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A28" s="27">
+      <c r="A28" s="26">
         <f t="shared" si="0"/>
         <v>26</v>
       </c>
-      <c r="B28" s="23"/>
-      <c r="C28" s="23"/>
-      <c r="D28" s="23"/>
-      <c r="E28" s="23"/>
-      <c r="F28" s="23"/>
-      <c r="G28" s="23"/>
-      <c r="H28" s="23"/>
-      <c r="I28" s="23"/>
+      <c r="B28" s="22"/>
+      <c r="C28" s="22"/>
+      <c r="D28" s="22"/>
+      <c r="E28" s="22"/>
+      <c r="F28" s="22"/>
+      <c r="G28" s="22"/>
+      <c r="H28" s="22"/>
+      <c r="I28" s="22"/>
     </row>
     <row r="29" spans="1:10" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A29" s="27">
+      <c r="A29" s="26">
         <f t="shared" si="0"/>
         <v>27</v>
       </c>
-      <c r="B29" s="23"/>
-      <c r="C29" s="23"/>
-      <c r="D29" s="23"/>
-      <c r="E29" s="23"/>
-      <c r="F29" s="23"/>
-      <c r="G29" s="23"/>
-      <c r="H29" s="23"/>
-      <c r="I29" s="23"/>
+      <c r="B29" s="22"/>
+      <c r="C29" s="22"/>
+      <c r="D29" s="22"/>
+      <c r="E29" s="22"/>
+      <c r="F29" s="22"/>
+      <c r="G29" s="22"/>
+      <c r="H29" s="22"/>
+      <c r="I29" s="22"/>
     </row>
     <row r="30" spans="1:10" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A30" s="27">
+      <c r="A30" s="26">
         <f t="shared" si="0"/>
         <v>28</v>
       </c>
-      <c r="B30" s="23"/>
-      <c r="C30" s="23"/>
-      <c r="D30" s="23"/>
-      <c r="E30" s="23"/>
-      <c r="F30" s="23"/>
-      <c r="G30" s="23"/>
-      <c r="H30" s="23"/>
-      <c r="I30" s="23"/>
+      <c r="B30" s="22"/>
+      <c r="C30" s="22"/>
+      <c r="D30" s="22"/>
+      <c r="E30" s="22"/>
+      <c r="F30" s="22"/>
+      <c r="G30" s="22"/>
+      <c r="H30" s="22"/>
+      <c r="I30" s="22"/>
     </row>
     <row r="31" spans="1:10" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A31" s="27">
+      <c r="A31" s="26">
         <f t="shared" si="0"/>
         <v>29</v>
       </c>
-      <c r="B31" s="22">
+      <c r="B31" s="21">
         <v>6351</v>
       </c>
-      <c r="C31" s="22">
+      <c r="C31" s="21">
         <v>8113</v>
       </c>
-      <c r="D31" s="22">
+      <c r="D31" s="21">
         <v>9260</v>
       </c>
-      <c r="E31" s="22">
+      <c r="E31" s="21">
         <v>10801</v>
       </c>
-      <c r="F31" s="22">
+      <c r="F31" s="21">
         <v>1270</v>
       </c>
-      <c r="G31" s="22">
+      <c r="G31" s="21">
         <v>3684</v>
       </c>
-      <c r="H31" s="22">
+      <c r="H31" s="21">
         <v>367</v>
       </c>
-      <c r="I31" s="22">
+      <c r="I31" s="21">
         <v>3316</v>
       </c>
     </row>
     <row r="32" spans="1:10" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A32" s="27">
+      <c r="A32" s="26">
         <f t="shared" si="0"/>
         <v>30</v>
       </c>
-      <c r="B32" s="22">
+      <c r="B32" s="21">
         <v>6375</v>
       </c>
-      <c r="C32" s="22">
+      <c r="C32" s="21">
         <v>8136</v>
       </c>
-      <c r="D32" s="22">
+      <c r="D32" s="21">
         <v>9263</v>
       </c>
-      <c r="E32" s="22">
+      <c r="E32" s="21">
         <v>10802</v>
       </c>
-      <c r="F32" s="22">
+      <c r="F32" s="21">
         <v>1270</v>
       </c>
-      <c r="G32" s="22">
+      <c r="G32" s="21">
         <v>3687</v>
       </c>
-      <c r="H32" s="22">
+      <c r="H32" s="21">
         <v>368</v>
       </c>
-      <c r="I32" s="22">
+      <c r="I32" s="21">
         <v>3318</v>
       </c>
     </row>
     <row r="33" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A33" s="27">
+      <c r="A33" s="26">
         <f t="shared" si="0"/>
         <v>31</v>
       </c>
-      <c r="B33" s="28">
+      <c r="B33" s="27">
         <v>6407</v>
       </c>
-      <c r="C33" s="28">
+      <c r="C33" s="27">
         <v>8185</v>
       </c>
-      <c r="D33" s="28">
+      <c r="D33" s="27">
         <v>9265</v>
       </c>
-      <c r="E33" s="28">
+      <c r="E33" s="27">
         <v>10802</v>
       </c>
-      <c r="F33" s="28">
+      <c r="F33" s="27">
         <v>1271</v>
       </c>
-      <c r="G33" s="28">
+      <c r="G33" s="27">
         <v>3691</v>
       </c>
-      <c r="H33" s="28">
+      <c r="H33" s="27">
         <v>369</v>
       </c>
-      <c r="I33" s="28">
+      <c r="I33" s="27">
         <v>3321</v>
       </c>
     </row>
     <row r="34" spans="1:9" ht="12.75" x14ac:dyDescent="0.2"/>
     <row r="36" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A36" s="4"/>
-      <c r="B36" s="33"/>
-      <c r="C36" s="32"/>
-      <c r="D36" s="32"/>
-      <c r="E36" s="32"/>
-      <c r="F36" s="32"/>
-      <c r="G36" s="32"/>
-      <c r="H36" s="32"/>
-      <c r="I36" s="32"/>
+      <c r="B36" s="37"/>
+      <c r="C36" s="36"/>
+      <c r="D36" s="36"/>
+      <c r="E36" s="36"/>
+      <c r="F36" s="36"/>
+      <c r="G36" s="36"/>
+      <c r="H36" s="36"/>
+      <c r="I36" s="36"/>
     </row>
     <row r="37" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A37" s="4"/>
@@ -13977,15 +14149,15 @@
       <c r="I70" s="4"/>
     </row>
     <row r="71" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A71" s="33"/>
-      <c r="B71" s="32"/>
-      <c r="C71" s="32"/>
-      <c r="D71" s="32"/>
-      <c r="E71" s="32"/>
-      <c r="F71" s="32"/>
-      <c r="G71" s="32"/>
-      <c r="H71" s="32"/>
-      <c r="I71" s="32"/>
+      <c r="A71" s="37"/>
+      <c r="B71" s="36"/>
+      <c r="C71" s="36"/>
+      <c r="D71" s="36"/>
+      <c r="E71" s="36"/>
+      <c r="F71" s="36"/>
+      <c r="G71" s="36"/>
+      <c r="H71" s="36"/>
+      <c r="I71" s="36"/>
     </row>
     <row r="72" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A72" s="4"/>
@@ -14010,15 +14182,15 @@
       <c r="I73" s="6"/>
     </row>
     <row r="76" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A76" s="31"/>
-      <c r="B76" s="32"/>
-      <c r="C76" s="32"/>
-      <c r="D76" s="32"/>
-      <c r="E76" s="32"/>
-      <c r="F76" s="32"/>
-      <c r="G76" s="32"/>
-      <c r="H76" s="32"/>
-      <c r="I76" s="32"/>
+      <c r="A76" s="35"/>
+      <c r="B76" s="36"/>
+      <c r="C76" s="36"/>
+      <c r="D76" s="36"/>
+      <c r="E76" s="36"/>
+      <c r="F76" s="36"/>
+      <c r="G76" s="36"/>
+      <c r="H76" s="36"/>
+      <c r="I76" s="36"/>
     </row>
     <row r="77" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A77" s="4"/>
@@ -14054,15 +14226,15 @@
       <c r="I79" s="8"/>
     </row>
     <row r="80" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A80" s="34"/>
-      <c r="B80" s="32"/>
-      <c r="C80" s="32"/>
-      <c r="D80" s="32"/>
-      <c r="E80" s="32"/>
-      <c r="F80" s="32"/>
-      <c r="G80" s="32"/>
-      <c r="H80" s="32"/>
-      <c r="I80" s="32"/>
+      <c r="A80" s="38"/>
+      <c r="B80" s="36"/>
+      <c r="C80" s="36"/>
+      <c r="D80" s="36"/>
+      <c r="E80" s="36"/>
+      <c r="F80" s="36"/>
+      <c r="G80" s="36"/>
+      <c r="H80" s="36"/>
+      <c r="I80" s="36"/>
     </row>
     <row r="81" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A81" s="4"/>
@@ -14098,15 +14270,15 @@
       <c r="B86" s="6"/>
     </row>
     <row r="88" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A88" s="31"/>
-      <c r="B88" s="32"/>
-      <c r="C88" s="32"/>
-      <c r="D88" s="32"/>
-      <c r="E88" s="32"/>
-      <c r="F88" s="32"/>
-      <c r="G88" s="32"/>
-      <c r="H88" s="32"/>
-      <c r="I88" s="32"/>
+      <c r="A88" s="35"/>
+      <c r="B88" s="36"/>
+      <c r="C88" s="36"/>
+      <c r="D88" s="36"/>
+      <c r="E88" s="36"/>
+      <c r="F88" s="36"/>
+      <c r="G88" s="36"/>
+      <c r="H88" s="36"/>
+      <c r="I88" s="36"/>
     </row>
     <row r="89" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A89" s="4"/>
@@ -14209,15 +14381,15 @@
       <c r="B99" s="9"/>
     </row>
     <row r="101" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A101" s="33"/>
-      <c r="B101" s="32"/>
-      <c r="C101" s="32"/>
-      <c r="D101" s="32"/>
-      <c r="E101" s="32"/>
-      <c r="F101" s="32"/>
-      <c r="G101" s="32"/>
-      <c r="H101" s="32"/>
-      <c r="I101" s="32"/>
+      <c r="A101" s="37"/>
+      <c r="B101" s="36"/>
+      <c r="C101" s="36"/>
+      <c r="D101" s="36"/>
+      <c r="E101" s="36"/>
+      <c r="F101" s="36"/>
+      <c r="G101" s="36"/>
+      <c r="H101" s="36"/>
+      <c r="I101" s="36"/>
     </row>
     <row r="102" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A102" s="4"/>
@@ -14256,6 +14428,18 @@
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{CCE6A557-97BC-4b89-ADB6-D9C93CAAB3DF}">
+      <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="1">
+        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{0DDB1F87-E0DC-4AE6-9AA5-E5454A5FF19D}">
+          <x14:formula1>
+            <xm:f>Planilha1!$A$2:$A$5</xm:f>
+          </x14:formula1>
+          <xm:sqref>K2</xm:sqref>
+        </x14:dataValidation>
+      </x14:dataValidations>
+    </ext>
+  </extLst>
 </worksheet>
 </file>
 
@@ -14275,8 +14459,9 @@
     <col min="7" max="7" width="13.42578125" customWidth="1"/>
     <col min="8" max="8" width="14.140625" customWidth="1"/>
     <col min="9" max="9" width="14.28515625" customWidth="1"/>
-    <col min="11" max="11" width="8.85546875" bestFit="1" customWidth="1"/>
-    <col min="12" max="13" width="5.5703125" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="11.7109375" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="9.5703125" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="5.5703125" bestFit="1" customWidth="1"/>
     <col min="14" max="14" width="6.28515625" bestFit="1" customWidth="1"/>
     <col min="15" max="15" width="13.7109375" bestFit="1" customWidth="1"/>
     <col min="16" max="16" width="7.42578125" bestFit="1" customWidth="1"/>
@@ -14311,8 +14496,12 @@
       <c r="I1" s="13" t="s">
         <v>7</v>
       </c>
-      <c r="K1" s="15"/>
-      <c r="L1" s="5"/>
+      <c r="K1" s="25" t="s">
+        <v>9</v>
+      </c>
+      <c r="L1" s="25" t="s">
+        <v>11</v>
+      </c>
       <c r="M1" s="5"/>
       <c r="N1" s="5"/>
       <c r="O1" s="5"/>
@@ -14322,17 +14511,24 @@
       <c r="S1" s="5"/>
     </row>
     <row r="2" spans="1:19" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A2" s="39">
+      <c r="A2" s="34">
         <v>0</v>
       </c>
-      <c r="B2" s="38"/>
-      <c r="C2" s="38"/>
-      <c r="D2" s="38"/>
-      <c r="E2" s="38"/>
-      <c r="F2" s="38"/>
-      <c r="G2" s="38"/>
-      <c r="H2" s="38"/>
-      <c r="I2" s="38"/>
+      <c r="B2" s="33"/>
+      <c r="C2" s="33"/>
+      <c r="D2" s="33"/>
+      <c r="E2" s="33"/>
+      <c r="F2" s="33"/>
+      <c r="G2" s="33"/>
+      <c r="H2" s="33"/>
+      <c r="I2" s="33"/>
+      <c r="K2" s="39" t="s">
+        <v>13</v>
+      </c>
+      <c r="L2" s="40" cm="1">
+        <f t="array" ref="L2">_xlfn.IFS(K2="Verde",0,K2="Amarela",1.885,K2="Vermelha P1",4.463,K2="Vermelha P2",7.877)</f>
+        <v>1.885</v>
+      </c>
     </row>
     <row r="3" spans="1:19" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A3" s="1">
@@ -14364,13 +14560,13 @@
         <v>3079</v>
       </c>
       <c r="K3" s="4"/>
-      <c r="L3" s="4"/>
+      <c r="L3" s="16"/>
       <c r="M3" s="4"/>
       <c r="N3" s="4"/>
       <c r="O3" s="4"/>
       <c r="P3" s="4"/>
       <c r="Q3" s="4"/>
-      <c r="R3" s="17"/>
+      <c r="R3" s="16"/>
       <c r="S3" s="4"/>
     </row>
     <row r="4" spans="1:19" ht="12.75" x14ac:dyDescent="0.2">
@@ -14952,7 +15148,7 @@
       <c r="K18" s="4"/>
       <c r="L18" s="4"/>
       <c r="M18" s="4"/>
-      <c r="N18" s="17"/>
+      <c r="N18" s="16"/>
       <c r="O18" s="4"/>
       <c r="P18" s="4"/>
       <c r="Q18" s="4"/>
@@ -15300,7 +15496,7 @@
       <c r="I27" s="2">
         <v>3188</v>
       </c>
-      <c r="J27" s="16"/>
+      <c r="J27" s="15"/>
       <c r="K27" s="4"/>
       <c r="L27" s="4"/>
       <c r="M27" s="4"/>
@@ -15475,10 +15671,10 @@
       <c r="S32" s="4"/>
     </row>
     <row r="34" spans="4:6" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="F34" s="18"/>
+      <c r="F34" s="17"/>
     </row>
     <row r="35" spans="4:6" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="D35" s="18"/>
+      <c r="D35" s="17"/>
     </row>
     <row r="36" spans="4:6" ht="12.75" x14ac:dyDescent="0.2"/>
     <row r="37" spans="4:6" ht="12.75" x14ac:dyDescent="0.2"/>
@@ -15546,15 +15742,15 @@
       <c r="I68" s="4"/>
     </row>
     <row r="69" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A69" s="33"/>
-      <c r="B69" s="32"/>
-      <c r="C69" s="32"/>
-      <c r="D69" s="32"/>
-      <c r="E69" s="32"/>
-      <c r="F69" s="32"/>
-      <c r="G69" s="32"/>
-      <c r="H69" s="32"/>
-      <c r="I69" s="32"/>
+      <c r="A69" s="37"/>
+      <c r="B69" s="36"/>
+      <c r="C69" s="36"/>
+      <c r="D69" s="36"/>
+      <c r="E69" s="36"/>
+      <c r="F69" s="36"/>
+      <c r="G69" s="36"/>
+      <c r="H69" s="36"/>
+      <c r="I69" s="36"/>
     </row>
     <row r="70" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A70" s="4"/>
@@ -15579,15 +15775,15 @@
       <c r="I71" s="6"/>
     </row>
     <row r="74" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A74" s="31"/>
-      <c r="B74" s="32"/>
-      <c r="C74" s="32"/>
-      <c r="D74" s="32"/>
-      <c r="E74" s="32"/>
-      <c r="F74" s="32"/>
-      <c r="G74" s="32"/>
-      <c r="H74" s="32"/>
-      <c r="I74" s="32"/>
+      <c r="A74" s="35"/>
+      <c r="B74" s="36"/>
+      <c r="C74" s="36"/>
+      <c r="D74" s="36"/>
+      <c r="E74" s="36"/>
+      <c r="F74" s="36"/>
+      <c r="G74" s="36"/>
+      <c r="H74" s="36"/>
+      <c r="I74" s="36"/>
     </row>
     <row r="75" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A75" s="4"/>
@@ -15623,15 +15819,15 @@
       <c r="I77" s="8"/>
     </row>
     <row r="78" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A78" s="34"/>
-      <c r="B78" s="32"/>
-      <c r="C78" s="32"/>
-      <c r="D78" s="32"/>
-      <c r="E78" s="32"/>
-      <c r="F78" s="32"/>
-      <c r="G78" s="32"/>
-      <c r="H78" s="32"/>
-      <c r="I78" s="32"/>
+      <c r="A78" s="38"/>
+      <c r="B78" s="36"/>
+      <c r="C78" s="36"/>
+      <c r="D78" s="36"/>
+      <c r="E78" s="36"/>
+      <c r="F78" s="36"/>
+      <c r="G78" s="36"/>
+      <c r="H78" s="36"/>
+      <c r="I78" s="36"/>
     </row>
     <row r="79" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A79" s="4"/>
@@ -15667,15 +15863,15 @@
       <c r="B84" s="6"/>
     </row>
     <row r="86" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A86" s="31"/>
-      <c r="B86" s="32"/>
-      <c r="C86" s="32"/>
-      <c r="D86" s="32"/>
-      <c r="E86" s="32"/>
-      <c r="F86" s="32"/>
-      <c r="G86" s="32"/>
-      <c r="H86" s="32"/>
-      <c r="I86" s="32"/>
+      <c r="A86" s="35"/>
+      <c r="B86" s="36"/>
+      <c r="C86" s="36"/>
+      <c r="D86" s="36"/>
+      <c r="E86" s="36"/>
+      <c r="F86" s="36"/>
+      <c r="G86" s="36"/>
+      <c r="H86" s="36"/>
+      <c r="I86" s="36"/>
     </row>
     <row r="87" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A87" s="4"/>
@@ -15778,15 +15974,15 @@
       <c r="B97" s="9"/>
     </row>
     <row r="99" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A99" s="33"/>
-      <c r="B99" s="32"/>
-      <c r="C99" s="32"/>
-      <c r="D99" s="32"/>
-      <c r="E99" s="32"/>
-      <c r="F99" s="32"/>
-      <c r="G99" s="32"/>
-      <c r="H99" s="32"/>
-      <c r="I99" s="32"/>
+      <c r="A99" s="37"/>
+      <c r="B99" s="36"/>
+      <c r="C99" s="36"/>
+      <c r="D99" s="36"/>
+      <c r="E99" s="36"/>
+      <c r="F99" s="36"/>
+      <c r="G99" s="36"/>
+      <c r="H99" s="36"/>
+      <c r="I99" s="36"/>
     </row>
     <row r="100" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A100" s="4"/>
@@ -15825,5 +16021,17 @@
   </dataValidations>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{CCE6A557-97BC-4b89-ADB6-D9C93CAAB3DF}">
+      <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="1">
+        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{282BB2DC-05F6-4C41-93EF-5DB1EAF56F09}">
+          <x14:formula1>
+            <xm:f>Planilha1!$A$2:$A$5</xm:f>
+          </x14:formula1>
+          <xm:sqref>K2</xm:sqref>
+        </x14:dataValidation>
+      </x14:dataValidations>
+    </ext>
+  </extLst>
 </worksheet>
 </file>